--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -624,10 +624,10 @@
         <v>0.95299771075168</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2.9548151614259</v>
+        <v>2.954814755424023</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.5814011980408651</v>
+        <v>0.5814011439252407</v>
       </c>
     </row>
     <row r="3">
@@ -677,10 +677,10 @@
         <v>0.9144533099530932</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1.586255716658352</v>
+        <v>1.586255904171916</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.3726415931564593</v>
+        <v>0.372641626330404</v>
       </c>
     </row>
     <row r="4">
@@ -833,7 +833,7 @@
         <v>0.3397632492645797</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3960021134484679</v>
+        <v>0.3960019641680483</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1.221987887698371</v>
@@ -889,10 +889,10 @@
         <v>0.7654398431849179</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.979314708832606</v>
+        <v>0.979314329065486</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.2555623493855865</v>
+        <v>0.2555622690848429</v>
       </c>
     </row>
     <row r="8">
@@ -933,7 +933,7 @@
         <v>0.2070791853664002</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2514247774409466</v>
+        <v>0.2514246932755579</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>0.4041424165671308</v>
@@ -942,10 +942,10 @@
         <v>0.5572769562876529</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6907124487604233</v>
+        <v>0.6907126023860271</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.1913057833565071</v>
+        <v>0.1913058194389419</v>
       </c>
     </row>
     <row r="9">
@@ -1092,19 +1092,19 @@
         <v>0.06431423521401536</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.3208051719641856</v>
+        <v>0.3208050864978083</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.4800649400558907</v>
+        <v>0.4800650473755725</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>0.5794660091439812</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>1.356429180974054</v>
+        <v>1.356429725046437</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3307142188698127</v>
+        <v>0.3307143212853385</v>
       </c>
     </row>
     <row r="12">
@@ -1254,16 +1254,16 @@
         <v>0.231344858273878</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.3688012283877549</v>
+        <v>0.3688010699905064</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>0.4756982657734323</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.3110364493752273</v>
+        <v>0.3110368853063166</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.0944726718362876</v>
+        <v>0.09447279314352053</v>
       </c>
     </row>
     <row r="15">
@@ -1304,13 +1304,13 @@
         <v>0.1573447558606693</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1503345692653111</v>
+        <v>0.1503346711088214</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>0.2098624919979049</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.4479823511797401</v>
+        <v>0.4479826739114277</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>0.5568193725126842</v>
@@ -1366,10 +1366,10 @@
         <v>0.5655113038381461</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7595235911829428</v>
+        <v>0.7595234817904883</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2072531985186861</v>
+        <v>0.2072531734997181</v>
       </c>
     </row>
     <row r="17">
@@ -1463,7 +1463,7 @@
         <v>0.1571561877031578</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1060746257359479</v>
+        <v>0.1060745059642498</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>0.3022682955919407</v>
@@ -1472,10 +1472,10 @@
         <v>0.2751251476180132</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.8088847221363824</v>
+        <v>0.808884401799385</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.2184385475171322</v>
+        <v>0.2184384755923408</v>
       </c>
     </row>
     <row r="19">
@@ -1519,16 +1519,16 @@
         <v>0.2396643814929893</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2077640170159634</v>
+        <v>0.2077639196498198</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.3098621497766205</v>
+        <v>0.3098622643002373</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1315511385089385</v>
+        <v>0.1315509675774269</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.0420568080542576</v>
+        <v>0.04205675558340638</v>
       </c>
     </row>
     <row r="20">
@@ -1572,7 +1572,7 @@
         <v>0.1019114933429084</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.3471703568961428</v>
+        <v>0.347170232680279</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>0.3210496102158449</v>
@@ -1628,13 +1628,13 @@
         <v>0.3026925508607157</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.3748939037679513</v>
+        <v>0.3748940009748305</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.472020523117808</v>
+        <v>1.472020837358771</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3521266022186644</v>
+        <v>0.3521266595123564</v>
       </c>
     </row>
     <row r="22">
@@ -1681,7 +1681,7 @@
         <v>0.274053897058689</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2471737079378604</v>
+        <v>0.2471736251481147</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>0.9106330041022781</v>
@@ -1790,10 +1790,10 @@
         <v>0.1887834338245813</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.6631831963805108</v>
+        <v>0.6631833494208939</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.184804503200328</v>
+        <v>0.1848045395408686</v>
       </c>
     </row>
     <row r="25">
@@ -1837,16 +1837,16 @@
         <v>0.1001464246337416</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2336980016155172</v>
+        <v>0.233698134415397</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>0.2569592952828943</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.4165680804678447</v>
+        <v>0.4165681680115343</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.1230846303424595</v>
+        <v>0.1230846534779448</v>
       </c>
     </row>
     <row r="26">
@@ -1887,19 +1887,19 @@
         <v>0.002045241333242798</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.1376339895011602</v>
+        <v>0.1376340719497873</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.2621967982854201</v>
+        <v>0.2621968997775723</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.3290652522197257</v>
+        <v>0.32906513968907</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.2365885238801311</v>
+        <v>0.2365884264644957</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.07335093079657229</v>
+        <v>0.07335090261118871</v>
       </c>
     </row>
     <row r="27">
@@ -1949,10 +1949,10 @@
         <v>0.6847379935933298</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2.61042999959474</v>
+        <v>2.610430554875208</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.5340975500988288</v>
+        <v>0.5340976287463735</v>
       </c>
     </row>
     <row r="28">
@@ -1993,7 +1993,7 @@
         <v>-0.0309982871503458</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.004559294459831276</v>
+        <v>-0.00455935899784865</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>0.2787111694241451</v>
@@ -2002,10 +2002,10 @@
         <v>0.4584814452192709</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1.28961643513672</v>
+        <v>1.289616264418334</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.3180166946506007</v>
+        <v>0.3180166618926119</v>
       </c>
     </row>
     <row r="29">
@@ -2052,13 +2052,13 @@
         <v>0.2404318849321641</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.2378593642696347</v>
+        <v>0.2378592579151184</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.7186350938961186</v>
+        <v>0.7186349913897871</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.1978282696883629</v>
+        <v>0.1978282458739253</v>
       </c>
     </row>
     <row r="30">
@@ -2108,10 +2108,10 @@
         <v>0.2723625822594464</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.8491257596152417</v>
+        <v>0.8491256483038905</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2274076230404236</v>
+        <v>0.2274075984117752</v>
       </c>
     </row>
     <row r="31">
@@ -2161,10 +2161,10 @@
         <v>0.6708988106605565</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2950530666495053</v>
+        <v>0.2950531516935986</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.09000675209730469</v>
+        <v>0.09000677595697915</v>
       </c>
     </row>
     <row r="32">
@@ -2214,10 +2214,10 @@
         <v>0.124953949922479</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.6936872604525228</v>
+        <v>0.6936870963932948</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1920040755467858</v>
+        <v>0.19200403705891</v>
       </c>
     </row>
     <row r="33">
@@ -2264,7 +2264,7 @@
         <v>0.1160803368943923</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1328895332508482</v>
+        <v>0.1328896676160121</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>0.6989227383543883</v>
@@ -2364,19 +2364,19 @@
         <v>-0.04409912349568212</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.07605563983556052</v>
+        <v>0.07605573387978715</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>0.2386292015036688</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.3167192491771473</v>
+        <v>0.3167193899921932</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.9405797680508543</v>
+        <v>0.9405794621888182</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.2473179331808364</v>
+        <v>0.2473178676493513</v>
       </c>
     </row>
     <row r="36">
@@ -2638,10 +2638,10 @@
         <v>0.09658321815512561</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.089480023965987</v>
+        <v>1.089480372445181</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.2784372252370713</v>
+        <v>0.2784372963087802</v>
       </c>
     </row>
     <row r="41">
@@ -2685,7 +2685,7 @@
         <v>0.03125610303028381</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.2035776529182052</v>
+        <v>0.2035777422773202</v>
       </c>
       <c r="M41" s="6" t="n">
         <v>0.2167677826073577</v>
@@ -2744,10 +2744,10 @@
         <v>0.3380234749134581</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.5619850625887528</v>
+        <v>0.5619853496083884</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.1602697209178832</v>
+        <v>0.1602697919856075</v>
       </c>
     </row>
     <row r="43">
@@ -2797,10 +2797,10 @@
         <v>0.151385429832561</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.3445071083588671</v>
+        <v>0.3445072479081215</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.1037084500748127</v>
+        <v>0.1037084882602277</v>
       </c>
     </row>
     <row r="44">
@@ -2847,7 +2847,7 @@
         <v>0.1190791319507669</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.07062297373180471</v>
+        <v>0.07062307204624085</v>
       </c>
       <c r="N44" s="6" t="n">
         <v>0.3948477800508428</v>
@@ -2900,13 +2900,13 @@
         <v>0.2161038148867669</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.1726305308357707</v>
+        <v>0.1726306199379812</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.356013761164383</v>
+        <v>0.3560138803144475</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.1068481213993173</v>
+        <v>0.1068481538181185</v>
       </c>
     </row>
     <row r="46">
@@ -3059,13 +3059,13 @@
         <v>0.03069357316529486</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>-0.0698954653670355</v>
+        <v>-0.06989552707371516</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>0.1818285276219205</v>
+        <v>0.1818284279947984</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.05726735548448136</v>
+        <v>0.0572673257755727</v>
       </c>
     </row>
     <row r="49">
@@ -3218,7 +3218,7 @@
         <v>0.06170921921053307</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>-0.03352664420541507</v>
+        <v>-0.03352670957318238</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0.3320393086449767</v>
@@ -3268,16 +3268,16 @@
         <v>-0.008747308580336233</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0.08113601174255214</v>
+        <v>0.08113588931454596</v>
       </c>
       <c r="M52" s="6" t="n">
         <v>0.3470668833309982</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.1306766046082197</v>
+        <v>0.1306764707031811</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.04178828318058359</v>
+        <v>0.04178824205455767</v>
       </c>
     </row>
     <row r="53">
@@ -3324,13 +3324,13 @@
         <v>0.09701398276227624</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.02565681742549941</v>
+        <v>0.02565690095910922</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.1189502582664914</v>
+        <v>0.1189501588453845</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.03817426789426404</v>
+        <v>0.03817423714626678</v>
       </c>
     </row>
     <row r="54">
@@ -3374,16 +3374,16 @@
         <v>-0.03625527575134335</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.1021700090740284</v>
+        <v>-0.1021699539265614</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.0907549437557702</v>
+        <v>-0.09075488719709224</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>0.0591435465795962</v>
+        <v>0.05914377681299454</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.01933814123254596</v>
+        <v>0.01933821509274747</v>
       </c>
     </row>
     <row r="55">
@@ -3430,7 +3430,7 @@
         <v>0.01940347051404068</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.06080485488319431</v>
+        <v>0.06080475800427787</v>
       </c>
       <c r="N55" s="6" t="n">
         <v>0.5139823339199088</v>
@@ -3539,10 +3539,10 @@
         <v>-0.09193159405018547</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.1561786474059703</v>
+        <v>0.1561783376696857</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.04956252293975383</v>
+        <v>0.04956242921501497</v>
       </c>
     </row>
     <row r="58">
@@ -3586,16 +3586,16 @@
         <v>-0.008507453850260749</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.02374017107350679</v>
+        <v>0.02374024186537449</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.02851159089912803</v>
+        <v>0.02851151944584274</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.7280283252907616</v>
+        <v>0.7280281235909403</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.2000065567444431</v>
+        <v>0.200006510055178</v>
       </c>
     </row>
     <row r="59">
@@ -3695,7 +3695,7 @@
         <v>-0.1064804232815015</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.1887068609290272</v>
+        <v>-0.1887067671016402</v>
       </c>
       <c r="N60" s="6" t="n">
         <v>0.2084527758041173</v>
@@ -3804,10 +3804,10 @@
         <v>0.2061187990351565</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>1.265852253943098</v>
+        <v>1.265852035993138</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>0.3134408801652884</v>
+        <v>0.3134408380524516</v>
       </c>
     </row>
   </sheetData>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.3208051719641856</v>
+        <v>0.3208050864978083</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.2514247774409466</v>
+        <v>0.2514246932755579</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1887068609290272</v>
+        <v>-0.1887067671016402</v>
       </c>
     </row>
     <row r="46">
@@ -5606,7 +5606,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.0907549437557702</v>
+        <v>-0.09075488719709224</v>
       </c>
     </row>
     <row r="49">
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.0698954653670355</v>
+        <v>-0.06989552707371516</v>
       </c>
     </row>
     <row r="50">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.03352664420541507</v>
+        <v>-0.03352670957318238</v>
       </c>
     </row>
     <row r="54">
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>2.9548151614259</v>
+        <v>2.954814755424023</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>2.61042999959474</v>
+        <v>2.610430554875208</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.0591435465795962</v>
+        <v>0.05914377681299454</v>
       </c>
     </row>
     <row r="62">
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>1.586255716658352</v>
+        <v>1.586255904171916</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.1189502582664914</v>
+        <v>0.1189501588453845</v>
       </c>
     </row>
     <row r="64">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>1.472020523117808</v>
+        <v>1.472020837358771</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.1306766046082197</v>
+        <v>0.1306764707031811</v>
       </c>
     </row>
     <row r="65">
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.1315511385089385</v>
+        <v>0.1315509675774269</v>
       </c>
     </row>
     <row r="66">
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>1.356429180974054</v>
+        <v>1.356429725046437</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.1561786474059703</v>
+        <v>0.1561783376696857</v>
       </c>
     </row>
     <row r="67">
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>1.28961643513672</v>
+        <v>1.289616264418334</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6387,7 +6387,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.1818285276219205</v>
+        <v>0.1818284279947984</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -491,13 +491,14 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -543,35 +544,40 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>3Y (Ann.)</t>
         </is>
@@ -609,25 +615,28 @@
         <v>0.008786674120350613</v>
       </c>
       <c r="I2" s="6" t="n">
+        <v>0.0874881606279283</v>
+      </c>
+      <c r="J2" s="6" t="n">
         <v>-0.02080590075989186</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="6" t="n">
         <v>0.01639170734955742</v>
       </c>
-      <c r="K2" s="6" t="n">
+      <c r="L2" s="6" t="n">
         <v>0.4417247266857178</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="6" t="n">
         <v>0.7092267091658355</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="N2" s="6" t="n">
         <v>0.95299771075168</v>
       </c>
-      <c r="N2" s="6" t="n">
-        <v>2.954814755424023</v>
-      </c>
       <c r="O2" s="6" t="n">
-        <v>0.5814011439252407</v>
+        <v>2.9548151614259</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>0.5814011980408651</v>
       </c>
     </row>
     <row r="3">
@@ -662,25 +671,28 @@
         <v>-0.0006976791355054468</v>
       </c>
       <c r="I3" s="6" t="n">
+        <v>0.1165609712687024</v>
+      </c>
+      <c r="J3" s="6" t="n">
         <v>-0.005190771535326544</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="6" t="n">
         <v>-0.03662597462027972</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="L3" s="6" t="n">
         <v>0.5027122941071647</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="6" t="n">
         <v>0.7585618661923608</v>
       </c>
-      <c r="M3" s="6" t="n">
-        <v>0.9144533099530932</v>
-      </c>
       <c r="N3" s="6" t="n">
-        <v>1.586255904171916</v>
+        <v>0.9144535154519131</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.372641626330404</v>
+        <v>1.586255716658352</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v>0.3726415931564593</v>
       </c>
     </row>
     <row r="4">
@@ -715,25 +727,28 @@
         <v>0.02391268566986571</v>
       </c>
       <c r="I4" s="6" t="n">
+        <v>0.1066579201423372</v>
+      </c>
+      <c r="J4" s="6" t="n">
         <v>0.03403621802858825</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="6" t="n">
         <v>0.3490867849739594</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="L4" s="6" t="n">
         <v>0.5172679577768988</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="6" t="n">
         <v>0.400937637017968</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="6" t="n">
         <v>0.4347586391378604</v>
       </c>
-      <c r="N4" s="6" t="n">
-        <v>1.317869164743662</v>
-      </c>
       <c r="O4" s="6" t="n">
-        <v>0.3234157716570911</v>
+        <v>1.317869338161576</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>0.3234158046621174</v>
       </c>
     </row>
     <row r="5">
@@ -768,24 +783,27 @@
         <v>0.03829937970971975</v>
       </c>
       <c r="I5" s="6" t="n">
+        <v>0.06460503883984314</v>
+      </c>
+      <c r="J5" s="6" t="n">
         <v>0.09061063255104385</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>0.1032432365158735</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="L5" s="6" t="n">
         <v>0.2434290676285413</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="6" t="n">
         <v>0.6612789614797654</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="N5" s="6" t="n">
         <v>0.7573185118504884</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="6" t="n">
         <v>1.675468032623519</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="P5" s="6" t="n">
         <v>0.3882465048958965</v>
       </c>
     </row>
@@ -821,25 +839,28 @@
         <v>0.01788451739692998</v>
       </c>
       <c r="I6" s="6" t="n">
+        <v>0.08461283336747982</v>
+      </c>
+      <c r="J6" s="6" t="n">
         <v>0.05140921508086338</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="6" t="n">
         <v>0.27214970370719</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="L6" s="6" t="n">
         <v>0.4942238735723645</v>
       </c>
-      <c r="L6" s="6" t="n">
-        <v>0.3397632492645797</v>
-      </c>
       <c r="M6" s="6" t="n">
-        <v>0.3960019641680483</v>
+        <v>0.3397633867595804</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>1.221987887698371</v>
+        <v>0.3960021134484679</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.3049100093449761</v>
+        <v>1.221988076795161</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>0.3049100463620229</v>
       </c>
     </row>
     <row r="7">
@@ -874,25 +895,28 @@
         <v>0.000254232357903339</v>
       </c>
       <c r="I7" s="6" t="n">
+        <v>0.07074355175756319</v>
+      </c>
+      <c r="J7" s="6" t="n">
         <v>0.01260859924313662</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>0.1684428674451059</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="L7" s="6" t="n">
         <v>0.2824720777607062</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="6" t="n">
         <v>0.3865958298179029</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>0.7654398431849179</v>
       </c>
-      <c r="N7" s="6" t="n">
-        <v>0.979314329065486</v>
-      </c>
       <c r="O7" s="6" t="n">
-        <v>0.2555622690848429</v>
+        <v>0.979314708832606</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>0.2555623493855865</v>
       </c>
     </row>
     <row r="8">
@@ -927,25 +951,28 @@
         <v>0.006523067722131293</v>
       </c>
       <c r="I8" s="6" t="n">
+        <v>0.04290340733300746</v>
+      </c>
+      <c r="J8" s="6" t="n">
         <v>0.05687908705370437</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="6" t="n">
         <v>0.2070791853664002</v>
       </c>
-      <c r="K8" s="6" t="n">
-        <v>0.2514246932755579</v>
-      </c>
       <c r="L8" s="6" t="n">
+        <v>0.2514247774409466</v>
+      </c>
+      <c r="M8" s="6" t="n">
         <v>0.4041424165671308</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="N8" s="6" t="n">
         <v>0.5572769562876529</v>
       </c>
-      <c r="N8" s="6" t="n">
-        <v>0.6907126023860271</v>
-      </c>
       <c r="O8" s="6" t="n">
-        <v>0.1913058194389419</v>
+        <v>0.6907129096373184</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>0.1913058916038244</v>
       </c>
     </row>
     <row r="9">
@@ -980,24 +1007,27 @@
         <v>0.04178883287955726</v>
       </c>
       <c r="I9" s="6" t="n">
+        <v>0.1295707571006663</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>0.1714756722244206</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>0.3018781573806397</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="L9" s="6" t="n">
         <v>0.448521858340776</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="6" t="n">
         <v>0.2228915815917218</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="N9" s="6" t="n">
         <v>0.3163501563425128</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="6" t="n">
         <v>0.4231347548063611</v>
       </c>
-      <c r="O9" s="6" t="n">
+      <c r="P9" s="6" t="n">
         <v>0.124817354330691</v>
       </c>
     </row>
@@ -1033,24 +1063,27 @@
         <v>0.01293849277554671</v>
       </c>
       <c r="I10" s="6" t="n">
+        <v>0.08969989319320226</v>
+      </c>
+      <c r="J10" s="6" t="n">
         <v>0.07343083089035396</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="6" t="n">
         <v>0.1976489060938356</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="L10" s="6" t="n">
         <v>0.2174311665377875</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="6" t="n">
         <v>0.3629528389571743</v>
       </c>
-      <c r="M10" s="6" t="n">
-        <v>0.5886917779864802</v>
-      </c>
       <c r="N10" s="6" t="n">
+        <v>0.5886919146324345</v>
+      </c>
+      <c r="O10" s="6" t="n">
         <v>0.6435209658821086</v>
       </c>
-      <c r="O10" s="6" t="n">
+      <c r="P10" s="6" t="n">
         <v>0.1801170442843902</v>
       </c>
     </row>
@@ -1086,25 +1119,28 @@
         <v>0.02111337837966287</v>
       </c>
       <c r="I11" s="6" t="n">
+        <v>0.07451875800420549</v>
+      </c>
+      <c r="J11" s="6" t="n">
         <v>0.04278826534313485</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>0.06431423521401536</v>
       </c>
-      <c r="K11" s="6" t="n">
-        <v>0.3208050864978083</v>
-      </c>
       <c r="L11" s="6" t="n">
-        <v>0.4800650473755725</v>
+        <v>0.3208051719641856</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.5794660091439812</v>
+        <v>0.4800649400558907</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>1.356429725046437</v>
+        <v>0.5794661313628906</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3307143212853385</v>
+        <v>1.356428908937956</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>0.3307141676620615</v>
       </c>
     </row>
     <row r="12">
@@ -1139,24 +1175,27 @@
         <v>0.08511895512741763</v>
       </c>
       <c r="I12" s="6" t="n">
+        <v>0.0949039506389413</v>
+      </c>
+      <c r="J12" s="6" t="n">
         <v>0.09319940470888111</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="6" t="n">
         <v>-0.0455338478060292</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="L12" s="6" t="n">
         <v>0.1049249409408204</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="6" t="n">
         <v>0.4919701250244364</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="N12" s="6" t="n">
         <v>0.7887702369085763</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="6" t="n">
         <v>0.2896308980675164</v>
       </c>
-      <c r="O12" s="6" t="n">
+      <c r="P12" s="6" t="n">
         <v>0.08848339934974181</v>
       </c>
     </row>
@@ -1192,24 +1231,27 @@
         <v>-0.02646827062779267</v>
       </c>
       <c r="I13" s="6" t="n">
+        <v>0.08673594071710888</v>
+      </c>
+      <c r="J13" s="6" t="n">
         <v>0.08866864353786807</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="6" t="n">
         <v>-0.0379142239171999</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="L13" s="6" t="n">
         <v>-0.02216029949244547</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="6" t="n">
         <v>0.4392069599844457</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="N13" s="6" t="n">
         <v>0.8926345034144225</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="6" t="n">
         <v>1.401177922545565</v>
       </c>
-      <c r="O13" s="6" t="n">
+      <c r="P13" s="6" t="n">
         <v>0.3390849032738834</v>
       </c>
     </row>
@@ -1245,25 +1287,28 @@
         <v>0.08467555356669632</v>
       </c>
       <c r="I14" s="6" t="n">
+        <v>0.01741832978011693</v>
+      </c>
+      <c r="J14" s="6" t="n">
         <v>0.0882725284948791</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="6" t="n">
         <v>0.07182741217943756</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="L14" s="6" t="n">
         <v>0.231344858273878</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="6" t="n">
         <v>0.3688010699905064</v>
       </c>
-      <c r="M14" s="6" t="n">
-        <v>0.4756982657734323</v>
-      </c>
       <c r="N14" s="6" t="n">
-        <v>0.3110368853063166</v>
+        <v>0.4756981737216881</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.09447279314352053</v>
+        <v>0.3110367399959213</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>0.09447275270777022</v>
       </c>
     </row>
     <row r="15">
@@ -1298,25 +1343,28 @@
         <v>0.00278179037121129</v>
       </c>
       <c r="I15" s="6" t="n">
+        <v>0.06356950062726296</v>
+      </c>
+      <c r="J15" s="6" t="n">
         <v>0.05082947172821406</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>0.1573447558606693</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="L15" s="6" t="n">
         <v>0.1503346711088214</v>
       </c>
-      <c r="L15" s="6" t="n">
-        <v>0.2098624919979049</v>
-      </c>
       <c r="M15" s="6" t="n">
-        <v>0.4479826739114277</v>
+        <v>0.2098626046546102</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.5568193725126842</v>
+        <v>0.4479825125455659</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.1589892534550683</v>
+        <v>0.5568191859772329</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>0.1589892071656922</v>
       </c>
     </row>
     <row r="16">
@@ -1351,25 +1399,28 @@
         <v>-0.01872384676830086</v>
       </c>
       <c r="I16" s="6" t="n">
+        <v>0.02351152492048203</v>
+      </c>
+      <c r="J16" s="6" t="n">
         <v>0.06627159589602627</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="6" t="n">
         <v>-0.01244054714734832</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="L16" s="6" t="n">
         <v>0.09381968006631625</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="6" t="n">
         <v>0.3907936857396435</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="N16" s="6" t="n">
         <v>0.5655113038381461</v>
       </c>
-      <c r="N16" s="6" t="n">
-        <v>0.7595234817904883</v>
-      </c>
       <c r="O16" s="6" t="n">
-        <v>0.2072531734997181</v>
+        <v>0.7595235911829428</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>0.2072531985186861</v>
       </c>
     </row>
     <row r="17">
@@ -1404,24 +1455,27 @@
         <v>-0.03011682304893015</v>
       </c>
       <c r="I17" s="6" t="n">
+        <v>0.008951367428083667</v>
+      </c>
+      <c r="J17" s="6" t="n">
         <v>0.02301455674856734</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="6" t="n">
         <v>0.2036613383840975</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="L17" s="6" t="n">
         <v>0.07493183957275384</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="6" t="n">
         <v>0.279392693730635</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="N17" s="6" t="n">
         <v>0.2526967208876374</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="6" t="n">
         <v>0.5712837279618026</v>
       </c>
-      <c r="O17" s="6" t="n">
+      <c r="P17" s="6" t="n">
         <v>0.1625675707035459</v>
       </c>
     </row>
@@ -1457,25 +1511,28 @@
         <v>0.02256923292698954</v>
       </c>
       <c r="I18" s="6" t="n">
+        <v>0.02458589017362844</v>
+      </c>
+      <c r="J18" s="6" t="n">
         <v>0.03906667073567704</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="6" t="n">
         <v>0.1571561877031578</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="L18" s="6" t="n">
         <v>0.1060745059642498</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="6" t="n">
         <v>0.3022682955919407</v>
       </c>
-      <c r="M18" s="6" t="n">
+      <c r="N18" s="6" t="n">
         <v>0.2751251476180132</v>
       </c>
-      <c r="N18" s="6" t="n">
-        <v>0.808884401799385</v>
-      </c>
       <c r="O18" s="6" t="n">
-        <v>0.2184384755923408</v>
+        <v>0.8088847221363824</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>0.2184385475171322</v>
       </c>
     </row>
     <row r="19">
@@ -1510,25 +1567,28 @@
         <v>0.0014018193706411</v>
       </c>
       <c r="I19" s="6" t="n">
+        <v>0.01365733315317597</v>
+      </c>
+      <c r="J19" s="6" t="n">
         <v>0.002279920502833654</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="6" t="n">
         <v>0.1113738011111118</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="L19" s="6" t="n">
         <v>0.2396643814929893</v>
       </c>
-      <c r="L19" s="6" t="n">
-        <v>0.2077639196498198</v>
-      </c>
       <c r="M19" s="6" t="n">
-        <v>0.3098622643002373</v>
+        <v>0.2077640170159634</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1315509675774269</v>
+        <v>0.3098621497766205</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.04205675558340638</v>
+        <v>0.1315510530431763</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>0.04205678181883066</v>
       </c>
     </row>
     <row r="20">
@@ -1563,25 +1623,28 @@
         <v>-0.008450426647530485</v>
       </c>
       <c r="I20" s="6" t="n">
+        <v>0.02294209389735258</v>
+      </c>
+      <c r="J20" s="6" t="n">
         <v>-0.02756692060045063</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="6" t="n">
         <v>0.09790039060665423</v>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="L20" s="6" t="n">
         <v>0.1019114933429084</v>
       </c>
-      <c r="L20" s="6" t="n">
-        <v>0.347170232680279</v>
-      </c>
       <c r="M20" s="6" t="n">
-        <v>0.3210496102158449</v>
+        <v>0.3471703568961428</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3731333408456297</v>
+        <v>0.3210497296615014</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1114866158513359</v>
+        <v>0.3731334698954882</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>0.1114866506712575</v>
       </c>
     </row>
     <row r="21">
@@ -1616,25 +1679,28 @@
         <v>0.03451530480606935</v>
       </c>
       <c r="I21" s="6" t="n">
+        <v>0.1203278237460554</v>
+      </c>
+      <c r="J21" s="6" t="n">
         <v>0.1131828245200317</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="6" t="n">
         <v>0.09377087397512929</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="L21" s="6" t="n">
         <v>0.09679080438402776</v>
       </c>
-      <c r="L21" s="6" t="n">
-        <v>0.3026925508607157</v>
-      </c>
       <c r="M21" s="6" t="n">
-        <v>0.3748940009748305</v>
+        <v>0.3026926381261963</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.472020837358771</v>
+        <v>0.3748939037679513</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.3521266595123564</v>
+        <v>1.472020523117808</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>0.3521266022186644</v>
       </c>
     </row>
     <row r="22">
@@ -1669,25 +1735,28 @@
         <v>0.02429608287242946</v>
       </c>
       <c r="I22" s="6" t="n">
+        <v>0.02900210479271648</v>
+      </c>
+      <c r="J22" s="6" t="n">
         <v>0.04201802036842062</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="6" t="n">
         <v>0.1550960385161122</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="L22" s="6" t="n">
         <v>0.1134711934890489</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="6" t="n">
         <v>0.274053897058689</v>
       </c>
-      <c r="M22" s="6" t="n">
-        <v>0.2471736251481147</v>
-      </c>
       <c r="N22" s="6" t="n">
-        <v>0.9106330041022781</v>
+        <v>0.2471737907276172</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2408684958175165</v>
+        <v>0.9106328098003136</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>0.2408684537541106</v>
       </c>
     </row>
     <row r="23">
@@ -1722,24 +1791,27 @@
         <v>0.009850453522245672</v>
       </c>
       <c r="I23" s="6" t="n">
+        <v>0.05658014416836799</v>
+      </c>
+      <c r="J23" s="6" t="n">
         <v>0.0762953059135183</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>0.1289216274514127</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="L23" s="6" t="n">
         <v>0.07958545804894923</v>
       </c>
-      <c r="L23" s="6" t="n">
-        <v>0.2312432131487518</v>
-      </c>
       <c r="M23" s="6" t="n">
+        <v>0.231243121798504</v>
+      </c>
+      <c r="N23" s="6" t="n">
         <v>0.2985765057164664</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="6" t="n">
         <v>1.214322608485292</v>
       </c>
-      <c r="O23" s="6" t="n">
+      <c r="P23" s="6" t="n">
         <v>0.3034077473801564</v>
       </c>
     </row>
@@ -1775,25 +1847,28 @@
         <v>0.02178413630973175</v>
       </c>
       <c r="I24" s="6" t="n">
+        <v>0.03110504136724401</v>
+      </c>
+      <c r="J24" s="6" t="n">
         <v>0.05331496963918192</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>0.1594266226386121</v>
       </c>
-      <c r="K24" s="6" t="n">
+      <c r="L24" s="6" t="n">
         <v>0.1531784548359023</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="6" t="n">
         <v>0.1963610949333312</v>
       </c>
-      <c r="M24" s="6" t="n">
+      <c r="N24" s="6" t="n">
         <v>0.1887834338245813</v>
       </c>
-      <c r="N24" s="6" t="n">
-        <v>0.6631833494208939</v>
-      </c>
       <c r="O24" s="6" t="n">
-        <v>0.1848045395408686</v>
+        <v>0.6631828902998294</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0.1848044305192602</v>
       </c>
     </row>
     <row r="25">
@@ -1828,25 +1903,28 @@
         <v>0.002407418048734566</v>
       </c>
       <c r="I25" s="6" t="n">
+        <v>0.03003891000226311</v>
+      </c>
+      <c r="J25" s="6" t="n">
         <v>-0.00205432891501256</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="6" t="n">
         <v>0.09235487425458344</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="L25" s="6" t="n">
         <v>0.1001464246337416</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="6" t="n">
         <v>0.233698134415397</v>
       </c>
-      <c r="M25" s="6" t="n">
-        <v>0.2569592952828943</v>
-      </c>
       <c r="N25" s="6" t="n">
-        <v>0.4165681680115343</v>
+        <v>0.2569594331378515</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.1230846534779448</v>
+        <v>0.4165680804678447</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>0.1230846303424595</v>
       </c>
     </row>
     <row r="26">
@@ -1881,25 +1959,28 @@
         <v>0.05534013564966256</v>
       </c>
       <c r="I26" s="6" t="n">
+        <v>0.02010221958839864</v>
+      </c>
+      <c r="J26" s="6" t="n">
         <v>0.08714595275039105</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="6" t="n">
         <v>0.002045241333242798</v>
       </c>
-      <c r="K26" s="6" t="n">
-        <v>0.1376340719497873</v>
-      </c>
       <c r="L26" s="6" t="n">
-        <v>0.2621968997775723</v>
+        <v>0.1376339895011602</v>
       </c>
       <c r="M26" s="6" t="n">
+        <v>0.2621967982854201</v>
+      </c>
+      <c r="N26" s="6" t="n">
         <v>0.32906513968907</v>
       </c>
-      <c r="N26" s="6" t="n">
-        <v>0.2365884264644957</v>
-      </c>
       <c r="O26" s="6" t="n">
-        <v>0.07335090261118871</v>
+        <v>0.236588621295782</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>0.07335095898195876</v>
       </c>
     </row>
     <row r="27">
@@ -1934,24 +2015,27 @@
         <v>0.01186444126280017</v>
       </c>
       <c r="I27" s="6" t="n">
+        <v>0.2142373295153601</v>
+      </c>
+      <c r="J27" s="6" t="n">
         <v>0.1856216668747503</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="6" t="n">
         <v>-0.09493844770755866</v>
       </c>
-      <c r="K27" s="6" t="n">
+      <c r="L27" s="6" t="n">
         <v>-0.1177340927147937</v>
       </c>
-      <c r="L27" s="6" t="n">
-        <v>0.3270702016016425</v>
-      </c>
       <c r="M27" s="6" t="n">
+        <v>0.327070351643459</v>
+      </c>
+      <c r="N27" s="6" t="n">
         <v>0.6847379935933298</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="6" t="n">
         <v>2.610430554875208</v>
       </c>
-      <c r="O27" s="6" t="n">
+      <c r="P27" s="6" t="n">
         <v>0.5340976287463735</v>
       </c>
     </row>
@@ -1987,24 +2071,27 @@
         <v>0.01209609082183283</v>
       </c>
       <c r="I28" s="6" t="n">
+        <v>0.163835048323667</v>
+      </c>
+      <c r="J28" s="6" t="n">
         <v>0.1218157579367405</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="6" t="n">
         <v>-0.0309982871503458</v>
       </c>
-      <c r="K28" s="6" t="n">
-        <v>-0.00455935899784865</v>
-      </c>
       <c r="L28" s="6" t="n">
+        <v>-0.004559294459831276</v>
+      </c>
+      <c r="M28" s="6" t="n">
         <v>0.2787111694241451</v>
       </c>
-      <c r="M28" s="6" t="n">
+      <c r="N28" s="6" t="n">
         <v>0.4584814452192709</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="6" t="n">
         <v>1.289616264418334</v>
       </c>
-      <c r="O28" s="6" t="n">
+      <c r="P28" s="6" t="n">
         <v>0.3180166618926119</v>
       </c>
     </row>
@@ -2040,25 +2127,28 @@
         <v>0.03020850457373192</v>
       </c>
       <c r="I29" s="6" t="n">
+        <v>0.01233071181280643</v>
+      </c>
+      <c r="J29" s="6" t="n">
         <v>0.04054507984048872</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="6" t="n">
         <v>0.03957930884597838</v>
       </c>
-      <c r="K29" s="6" t="n">
+      <c r="L29" s="6" t="n">
         <v>0.1126419720670175</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="6" t="n">
         <v>0.2404318849321641</v>
       </c>
-      <c r="M29" s="6" t="n">
-        <v>0.2378592579151184</v>
-      </c>
       <c r="N29" s="6" t="n">
-        <v>0.7186349913897871</v>
+        <v>0.2378593642696347</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.1978282458739253</v>
+        <v>0.7186350938961186</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>0.1978282696883629</v>
       </c>
     </row>
     <row r="30">
@@ -2093,25 +2183,28 @@
         <v>-0.001703841820769547</v>
       </c>
       <c r="I30" s="6" t="n">
+        <v>0.03956706029252155</v>
+      </c>
+      <c r="J30" s="6" t="n">
         <v>0.03315113910185175</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="6" t="n">
         <v>0.03277745146526279</v>
       </c>
-      <c r="K30" s="6" t="n">
+      <c r="L30" s="6" t="n">
         <v>0.0648175693387234</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="6" t="n">
         <v>0.2574699395507958</v>
       </c>
-      <c r="M30" s="6" t="n">
+      <c r="N30" s="6" t="n">
         <v>0.2723625822594464</v>
       </c>
-      <c r="N30" s="6" t="n">
-        <v>0.8491256483038905</v>
-      </c>
       <c r="O30" s="6" t="n">
-        <v>0.2274075984117752</v>
+        <v>0.8491257596152417</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v>0.2274076230404236</v>
       </c>
     </row>
     <row r="31">
@@ -2146,25 +2239,28 @@
         <v>0.01648427490189053</v>
       </c>
       <c r="I31" s="6" t="n">
+        <v>0.08682464649296961</v>
+      </c>
+      <c r="J31" s="6" t="n">
         <v>0.05099191719069451</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="6" t="n">
         <v>-0.1310707883350345</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="L31" s="6" t="n">
         <v>0.03924886078927092</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="6" t="n">
         <v>0.1879967419852169</v>
       </c>
-      <c r="M31" s="6" t="n">
+      <c r="N31" s="6" t="n">
         <v>0.6708988106605565</v>
       </c>
-      <c r="N31" s="6" t="n">
-        <v>0.2950531516935986</v>
-      </c>
       <c r="O31" s="6" t="n">
-        <v>0.09000677595697915</v>
+        <v>0.2950529816054233</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v>0.09000672823763223</v>
       </c>
     </row>
     <row r="32">
@@ -2199,25 +2295,28 @@
         <v>-0.0180346860283862</v>
       </c>
       <c r="I32" s="6" t="n">
+        <v>-0.01207142781269444</v>
+      </c>
+      <c r="J32" s="6" t="n">
         <v>0.009535299777931217</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="6" t="n">
         <v>0.1376207888196332</v>
       </c>
-      <c r="K32" s="6" t="n">
+      <c r="L32" s="6" t="n">
         <v>0.1071854004799808</v>
       </c>
-      <c r="L32" s="6" t="n">
-        <v>0.09717064322171143</v>
-      </c>
       <c r="M32" s="6" t="n">
+        <v>0.09717071206833539</v>
+      </c>
+      <c r="N32" s="6" t="n">
         <v>0.124953949922479</v>
       </c>
-      <c r="N32" s="6" t="n">
-        <v>0.6936870963932948</v>
-      </c>
       <c r="O32" s="6" t="n">
-        <v>0.19200403705891</v>
+        <v>0.6936872604525228</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>0.1920040755467858</v>
       </c>
     </row>
     <row r="33">
@@ -2252,25 +2351,28 @@
         <v>-0.01573475015021275</v>
       </c>
       <c r="I33" s="6" t="n">
+        <v>-0.009581432638088638</v>
+      </c>
+      <c r="J33" s="6" t="n">
         <v>0.002682989735903085</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="6" t="n">
         <v>0.1141373939239974</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="L33" s="6" t="n">
         <v>0.1033622388388482</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="6" t="n">
         <v>0.1160803368943923</v>
       </c>
-      <c r="M33" s="6" t="n">
+      <c r="N33" s="6" t="n">
         <v>0.1328896676160121</v>
       </c>
-      <c r="N33" s="6" t="n">
-        <v>0.6989227383543883</v>
-      </c>
       <c r="O33" s="6" t="n">
-        <v>0.1932310418612186</v>
+        <v>0.6989225872668208</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v>0.1932310064893175</v>
       </c>
     </row>
     <row r="34">
@@ -2305,24 +2407,27 @@
         <v>0.006911327549427249</v>
       </c>
       <c r="I34" s="6" t="n">
+        <v>0.06037336082828704</v>
+      </c>
+      <c r="J34" s="6" t="n">
         <v>0.05794782759774186</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="6" t="n">
         <v>0.08610409351656156</v>
       </c>
-      <c r="K34" s="6" t="n">
+      <c r="L34" s="6" t="n">
         <v>0.231061734240106</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="6" t="n">
         <v>0.08186989718885429</v>
       </c>
-      <c r="M34" s="6" t="n">
+      <c r="N34" s="6" t="n">
         <v>0.0745685239254501</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="6" t="n">
         <v>0.7573126420187357</v>
       </c>
-      <c r="O34" s="6" t="n">
+      <c r="P34" s="6" t="n">
         <v>0.206747324042418</v>
       </c>
     </row>
@@ -2358,24 +2463,27 @@
         <v>0.007724092141710992</v>
       </c>
       <c r="I35" s="6" t="n">
+        <v>0.04750481585573185</v>
+      </c>
+      <c r="J35" s="6" t="n">
         <v>0.02264432121979931</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="6" t="n">
         <v>-0.04409912349568212</v>
       </c>
-      <c r="K35" s="6" t="n">
+      <c r="L35" s="6" t="n">
         <v>0.07605573387978715</v>
       </c>
-      <c r="L35" s="6" t="n">
-        <v>0.2386292015036688</v>
-      </c>
       <c r="M35" s="6" t="n">
-        <v>0.3167193899921932</v>
+        <v>0.2386290768958681</v>
       </c>
       <c r="N35" s="6" t="n">
+        <v>0.3167192491771473</v>
+      </c>
+      <c r="O35" s="6" t="n">
         <v>0.9405794621888182</v>
       </c>
-      <c r="O35" s="6" t="n">
+      <c r="P35" s="6" t="n">
         <v>0.2473178676493513</v>
       </c>
     </row>
@@ -2411,24 +2519,27 @@
         <v>0.0008899970141049707</v>
       </c>
       <c r="I36" s="6" t="n">
+        <v>0.2141700819619385</v>
+      </c>
+      <c r="J36" s="6" t="n">
         <v>0.2015224962711435</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="6" t="n">
         <v>-0.04236291492091981</v>
       </c>
-      <c r="K36" s="6" t="n">
+      <c r="L36" s="6" t="n">
         <v>-0.1344044727012431</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="6" t="n">
         <v>0.1899084069398547</v>
       </c>
-      <c r="M36" s="6" t="n">
+      <c r="N36" s="6" t="n">
         <v>0.5705966851321735</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="6" t="n">
         <v>2.219097928764253</v>
       </c>
-      <c r="O36" s="6" t="n">
+      <c r="P36" s="6" t="n">
         <v>0.4765383439015742</v>
       </c>
     </row>
@@ -2464,25 +2575,28 @@
         <v>-0.01231878706841305</v>
       </c>
       <c r="I37" s="6" t="n">
+        <v>-0.007283289395451309</v>
+      </c>
+      <c r="J37" s="6" t="n">
         <v>-0.005316873608959827</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="6" t="n">
         <v>0.05167862998994366</v>
       </c>
-      <c r="K37" s="6" t="n">
+      <c r="L37" s="6" t="n">
         <v>0.07742728672366161</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="6" t="n">
         <v>0.1497681722522</v>
       </c>
-      <c r="M37" s="6" t="n">
+      <c r="N37" s="6" t="n">
         <v>0.1971306573287468</v>
       </c>
-      <c r="N37" s="6" t="n">
-        <v>0.443517786073083</v>
-      </c>
       <c r="O37" s="6" t="n">
-        <v>0.1301620322829267</v>
+        <v>0.4435174528229471</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>0.1301619453132836</v>
       </c>
     </row>
     <row r="38">
@@ -2517,25 +2631,28 @@
         <v>0.02076552391816078</v>
       </c>
       <c r="I38" s="6" t="n">
+        <v>0.05480865861319772</v>
+      </c>
+      <c r="J38" s="6" t="n">
         <v>0.1162790721946345</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="6" t="n">
         <v>0.2168207790765724</v>
       </c>
-      <c r="K38" s="6" t="n">
+      <c r="L38" s="6" t="n">
         <v>0.1846001290985122</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="6" t="n">
         <v>-0.04342120349887479</v>
       </c>
-      <c r="M38" s="6" t="n">
+      <c r="N38" s="6" t="n">
         <v>-0.05520560798683727</v>
       </c>
-      <c r="N38" s="6" t="n">
-        <v>0.11391507147122</v>
-      </c>
       <c r="O38" s="6" t="n">
-        <v>0.03661469246477655</v>
+        <v>0.1139149554589198</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v>0.03661465647757489</v>
       </c>
     </row>
     <row r="39">
@@ -2570,24 +2687,27 @@
         <v>0.01353587843608772</v>
       </c>
       <c r="I39" s="6" t="n">
+        <v>0.1004440665688457</v>
+      </c>
+      <c r="J39" s="6" t="n">
         <v>0.1116095790257565</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="6" t="n">
         <v>0.1484942211907101</v>
       </c>
-      <c r="K39" s="6" t="n">
+      <c r="L39" s="6" t="n">
         <v>0.2576963056829229</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="6" t="n">
         <v>-0.03109163410450311</v>
       </c>
-      <c r="M39" s="6" t="n">
+      <c r="N39" s="6" t="n">
         <v>-0.03914048480321919</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="6" t="n">
         <v>0.5068541449227082</v>
       </c>
-      <c r="O39" s="6" t="n">
+      <c r="P39" s="6" t="n">
         <v>0.1464551574243782</v>
       </c>
     </row>
@@ -2623,25 +2743,28 @@
         <v>0.01551127845389266</v>
       </c>
       <c r="I40" s="6" t="n">
+        <v>0.02636102119035111</v>
+      </c>
+      <c r="J40" s="6" t="n">
         <v>-0.0118881637320819</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="6" t="n">
         <v>0.066809600311174</v>
       </c>
-      <c r="K40" s="6" t="n">
+      <c r="L40" s="6" t="n">
         <v>0.1369081059890751</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="6" t="n">
         <v>0.1138930913027458</v>
       </c>
-      <c r="M40" s="6" t="n">
+      <c r="N40" s="6" t="n">
         <v>0.09658321815512561</v>
       </c>
-      <c r="N40" s="6" t="n">
-        <v>1.089480372445181</v>
-      </c>
       <c r="O40" s="6" t="n">
-        <v>0.2784372963087802</v>
+        <v>1.089480198205569</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v>0.2784372607729235</v>
       </c>
     </row>
     <row r="41">
@@ -2676,25 +2799,28 @@
         <v>0.01161457667376009</v>
       </c>
       <c r="I41" s="6" t="n">
+        <v>0.02096748331125053</v>
+      </c>
+      <c r="J41" s="6" t="n">
         <v>-0.002902294483186352</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="6" t="n">
         <v>0.00279584267714017</v>
       </c>
-      <c r="K41" s="6" t="n">
+      <c r="L41" s="6" t="n">
         <v>0.03125610303028381</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="6" t="n">
         <v>0.2035777422773202</v>
       </c>
-      <c r="M41" s="6" t="n">
+      <c r="N41" s="6" t="n">
         <v>0.2167677826073577</v>
       </c>
-      <c r="N41" s="6" t="n">
-        <v>0.66234357128457</v>
-      </c>
       <c r="O41" s="6" t="n">
-        <v>0.1846050946116091</v>
+        <v>0.6623434008207847</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>0.184605054120125</v>
       </c>
     </row>
     <row r="42">
@@ -2729,25 +2855,28 @@
         <v>0.01333332061767578</v>
       </c>
       <c r="I42" s="6" t="n">
+        <v>0.02486304947194662</v>
+      </c>
+      <c r="J42" s="6" t="n">
         <v>0.0004113627766979544</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="6" t="n">
         <v>-0.0800324503850236</v>
       </c>
-      <c r="K42" s="6" t="n">
+      <c r="L42" s="6" t="n">
         <v>0.05748442346802785</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="6" t="n">
         <v>0.2211822670477956</v>
       </c>
-      <c r="M42" s="6" t="n">
+      <c r="N42" s="6" t="n">
         <v>0.3380234749134581</v>
       </c>
-      <c r="N42" s="6" t="n">
-        <v>0.5619853496083884</v>
-      </c>
       <c r="O42" s="6" t="n">
-        <v>0.1602697919856075</v>
+        <v>0.5619848712423876</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v>0.1602696735394098</v>
       </c>
     </row>
     <row r="43">
@@ -2782,24 +2911,27 @@
         <v>0.004063817176051199</v>
       </c>
       <c r="I43" s="6" t="n">
+        <v>-0.001212684395030972</v>
+      </c>
+      <c r="J43" s="6" t="n">
         <v>0.01291382740772229</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="6" t="n">
         <v>0.04596190841466741</v>
       </c>
-      <c r="K43" s="6" t="n">
+      <c r="L43" s="6" t="n">
         <v>0.06530178563939026</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="6" t="n">
         <v>0.1350185150234462</v>
       </c>
-      <c r="M43" s="6" t="n">
+      <c r="N43" s="6" t="n">
         <v>0.151385429832561</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="6" t="n">
         <v>0.3445072479081215</v>
       </c>
-      <c r="O43" s="6" t="n">
+      <c r="P43" s="6" t="n">
         <v>0.1037084882602277</v>
       </c>
     </row>
@@ -2835,24 +2967,27 @@
         <v>-0.02059020868603467</v>
       </c>
       <c r="I44" s="6" t="n">
+        <v>-0.009244841193360331</v>
+      </c>
+      <c r="J44" s="6" t="n">
         <v>0.01332875581243753</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="6" t="n">
         <v>0.1090062441476574</v>
       </c>
-      <c r="K44" s="6" t="n">
+      <c r="L44" s="6" t="n">
         <v>0.01756439913112762</v>
       </c>
-      <c r="L44" s="6" t="n">
-        <v>0.1190791319507669</v>
-      </c>
       <c r="M44" s="6" t="n">
+        <v>0.1190792393659745</v>
+      </c>
+      <c r="N44" s="6" t="n">
         <v>0.07062307204624085</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="6" t="n">
         <v>0.3948477800508428</v>
       </c>
-      <c r="O44" s="6" t="n">
+      <c r="P44" s="6" t="n">
         <v>0.1173149381635867</v>
       </c>
     </row>
@@ -2888,24 +3023,27 @@
         <v>-0.003933877247849216</v>
       </c>
       <c r="I45" s="6" t="n">
+        <v>0.05658007307677781</v>
+      </c>
+      <c r="J45" s="6" t="n">
         <v>0.04319319622797702</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="6" t="n">
         <v>0.01058525397406229</v>
       </c>
-      <c r="K45" s="6" t="n">
+      <c r="L45" s="6" t="n">
         <v>-0.01769376488544872</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="6" t="n">
         <v>0.2161038148867669</v>
       </c>
-      <c r="M45" s="6" t="n">
+      <c r="N45" s="6" t="n">
         <v>0.1726306199379812</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="6" t="n">
         <v>0.3560138803144475</v>
       </c>
-      <c r="O45" s="6" t="n">
+      <c r="P45" s="6" t="n">
         <v>0.1068481538181185</v>
       </c>
     </row>
@@ -2941,25 +3079,28 @@
         <v>0.005238407060238925</v>
       </c>
       <c r="I46" s="6" t="n">
+        <v>0.001605930342975626</v>
+      </c>
+      <c r="J46" s="6" t="n">
         <v>0.02394308506884935</v>
       </c>
-      <c r="J46" s="6" t="n">
+      <c r="K46" s="6" t="n">
         <v>0.03827851217127076</v>
       </c>
-      <c r="K46" s="6" t="n">
+      <c r="L46" s="6" t="n">
         <v>-0.002591785716972939</v>
       </c>
-      <c r="L46" s="6" t="n">
+      <c r="M46" s="6" t="n">
         <v>0.124195941014893</v>
       </c>
-      <c r="M46" s="6" t="n">
+      <c r="N46" s="6" t="n">
         <v>0.09953649760503391</v>
       </c>
-      <c r="N46" s="6" t="n">
-        <v>0.2076746598215466</v>
-      </c>
       <c r="O46" s="6" t="n">
-        <v>0.06491918533374386</v>
+        <v>0.2076745111403082</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v>0.06491914163171186</v>
       </c>
     </row>
     <row r="47">
@@ -2994,24 +3135,27 @@
         <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="6" t="n">
         <v>-0.01831484378483172</v>
       </c>
-      <c r="J47" s="6" t="n">
+      <c r="K47" s="6" t="n">
         <v>0.02082380059436528</v>
       </c>
-      <c r="K47" s="6" t="n">
+      <c r="L47" s="6" t="n">
         <v>0.1822744791212605</v>
       </c>
-      <c r="L47" s="6" t="n">
+      <c r="M47" s="6" t="n">
         <v>-0.01137043191827602</v>
       </c>
-      <c r="M47" s="6" t="n">
+      <c r="N47" s="6" t="n">
         <v>-0.03605019350016947</v>
       </c>
-      <c r="N47" s="6" t="n">
+      <c r="O47" s="6" t="n">
         <v>0.7809939976331854</v>
       </c>
-      <c r="O47" s="6" t="n">
+      <c r="P47" s="6" t="n">
         <v>0.2121438208721309</v>
       </c>
     </row>
@@ -3047,24 +3191,27 @@
         <v>-0.002982845809707202</v>
       </c>
       <c r="I48" s="6" t="n">
+        <v>0.07822583039270925</v>
+      </c>
+      <c r="J48" s="6" t="n">
         <v>0.06449040118480354</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="K48" s="6" t="n">
         <v>0.07895963973984221</v>
       </c>
-      <c r="K48" s="6" t="n">
+      <c r="L48" s="6" t="n">
         <v>0.05517815471448317</v>
       </c>
-      <c r="L48" s="6" t="n">
+      <c r="M48" s="6" t="n">
         <v>0.03069357316529486</v>
       </c>
-      <c r="M48" s="6" t="n">
+      <c r="N48" s="6" t="n">
         <v>-0.06989552707371516</v>
       </c>
-      <c r="N48" s="6" t="n">
+      <c r="O48" s="6" t="n">
         <v>0.1818284279947984</v>
       </c>
-      <c r="O48" s="6" t="n">
+      <c r="P48" s="6" t="n">
         <v>0.0572673257755727</v>
       </c>
     </row>
@@ -3100,25 +3247,28 @@
         <v>-0.01617950227097653</v>
       </c>
       <c r="I49" s="6" t="n">
+        <v>0.005698452807500587</v>
+      </c>
+      <c r="J49" s="6" t="n">
         <v>0.06788663413665286</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="K49" s="6" t="n">
         <v>0.08779832427787637</v>
       </c>
-      <c r="K49" s="6" t="n">
+      <c r="L49" s="6" t="n">
         <v>-0.1127942168862237</v>
       </c>
-      <c r="L49" s="6" t="n">
+      <c r="M49" s="6" t="n">
         <v>0.06441155790935005</v>
       </c>
-      <c r="M49" s="6" t="n">
+      <c r="N49" s="6" t="n">
         <v>-0.007290436709227133</v>
       </c>
-      <c r="N49" s="6" t="n">
-        <v>0.03602311976075834</v>
-      </c>
       <c r="O49" s="6" t="n">
-        <v>0.0118663396048142</v>
+        <v>0.03602300659100766</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v>0.01186630276114964</v>
       </c>
     </row>
     <row r="50">
@@ -3153,24 +3303,27 @@
         <v>0.02670518323506554</v>
       </c>
       <c r="I50" s="6" t="n">
+        <v>0.02353683640098003</v>
+      </c>
+      <c r="J50" s="6" t="n">
         <v>0.008711372625436864</v>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="K50" s="6" t="n">
         <v>0.06295493787803785</v>
       </c>
-      <c r="K50" s="6" t="n">
+      <c r="L50" s="6" t="n">
         <v>0.1350928366556123</v>
       </c>
-      <c r="L50" s="6" t="n">
+      <c r="M50" s="6" t="n">
         <v>0.007099014073266963</v>
       </c>
-      <c r="M50" s="6" t="n">
+      <c r="N50" s="6" t="n">
         <v>-0.1535985043633872</v>
       </c>
-      <c r="N50" s="6" t="n">
+      <c r="O50" s="6" t="n">
         <v>0.1710372198784516</v>
       </c>
-      <c r="O50" s="6" t="n">
+      <c r="P50" s="6" t="n">
         <v>0.05403953222290636</v>
       </c>
     </row>
@@ -3206,24 +3359,27 @@
         <v>-0.0160650393471552</v>
       </c>
       <c r="I51" s="6" t="n">
+        <v>0.05140316400968414</v>
+      </c>
+      <c r="J51" s="6" t="n">
         <v>0.007951118267743862</v>
       </c>
-      <c r="J51" s="6" t="n">
+      <c r="K51" s="6" t="n">
         <v>0.0907914997848871</v>
       </c>
-      <c r="K51" s="6" t="n">
+      <c r="L51" s="6" t="n">
         <v>-0.09766096062832919</v>
       </c>
-      <c r="L51" s="6" t="n">
+      <c r="M51" s="6" t="n">
         <v>0.06170921921053307</v>
       </c>
-      <c r="M51" s="6" t="n">
-        <v>-0.03352670957318238</v>
-      </c>
       <c r="N51" s="6" t="n">
+        <v>-0.03352677494094081</v>
+      </c>
+      <c r="O51" s="6" t="n">
         <v>0.3320393086449767</v>
       </c>
-      <c r="O51" s="6" t="n">
+      <c r="P51" s="6" t="n">
         <v>0.1002862364320252</v>
       </c>
     </row>
@@ -3259,25 +3415,28 @@
         <v>-0.004918041330057799</v>
       </c>
       <c r="I52" s="6" t="n">
+        <v>0.03760683054722769</v>
+      </c>
+      <c r="J52" s="6" t="n">
         <v>-0.04509704373959555</v>
       </c>
-      <c r="J52" s="6" t="n">
+      <c r="K52" s="6" t="n">
         <v>-0.1749265324482228</v>
       </c>
-      <c r="K52" s="6" t="n">
+      <c r="L52" s="6" t="n">
         <v>-0.008747308580336233</v>
       </c>
-      <c r="L52" s="6" t="n">
+      <c r="M52" s="6" t="n">
         <v>0.08113588931454596</v>
       </c>
-      <c r="M52" s="6" t="n">
+      <c r="N52" s="6" t="n">
         <v>0.3470668833309982</v>
       </c>
-      <c r="N52" s="6" t="n">
-        <v>0.1306764707031811</v>
-      </c>
       <c r="O52" s="6" t="n">
-        <v>0.04178824205455767</v>
+        <v>0.1306766046082197</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v>0.04178828318058359</v>
       </c>
     </row>
     <row r="53">
@@ -3312,24 +3471,27 @@
         <v>0.01307471047074116</v>
       </c>
       <c r="I53" s="6" t="n">
+        <v>0.006916827444712448</v>
+      </c>
+      <c r="J53" s="6" t="n">
         <v>-0.001869938719937236</v>
       </c>
-      <c r="J53" s="6" t="n">
+      <c r="K53" s="6" t="n">
         <v>-0.00345594323241516</v>
       </c>
-      <c r="K53" s="6" t="n">
+      <c r="L53" s="6" t="n">
         <v>-0.04712009796503425</v>
       </c>
-      <c r="L53" s="6" t="n">
+      <c r="M53" s="6" t="n">
         <v>0.09701398276227624</v>
       </c>
-      <c r="M53" s="6" t="n">
+      <c r="N53" s="6" t="n">
         <v>0.02565690095910922</v>
       </c>
-      <c r="N53" s="6" t="n">
+      <c r="O53" s="6" t="n">
         <v>0.1189501588453845</v>
       </c>
-      <c r="O53" s="6" t="n">
+      <c r="P53" s="6" t="n">
         <v>0.03817423714626678</v>
       </c>
     </row>
@@ -3365,25 +3527,28 @@
         <v>0.02537692582406192</v>
       </c>
       <c r="I54" s="6" t="n">
+        <v>0.06189297474548283</v>
+      </c>
+      <c r="J54" s="6" t="n">
         <v>0.132872753730839</v>
       </c>
-      <c r="J54" s="6" t="n">
+      <c r="K54" s="6" t="n">
         <v>0.1452896847410137</v>
       </c>
-      <c r="K54" s="6" t="n">
+      <c r="L54" s="6" t="n">
         <v>-0.03625527575134335</v>
       </c>
-      <c r="L54" s="6" t="n">
+      <c r="M54" s="6" t="n">
         <v>-0.1021699539265614</v>
       </c>
-      <c r="M54" s="6" t="n">
-        <v>-0.09075488719709224</v>
-      </c>
       <c r="N54" s="6" t="n">
-        <v>0.05914377681299454</v>
+        <v>-0.0907549437557702</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.01933821509274747</v>
+        <v>0.05914362332405099</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0.01933816585261061</v>
       </c>
     </row>
     <row r="55">
@@ -3418,25 +3583,28 @@
         <v>0.01605138163592001</v>
       </c>
       <c r="I55" s="6" t="n">
+        <v>-0.0009018512335106088</v>
+      </c>
+      <c r="J55" s="6" t="n">
         <v>-0.03020348642801807</v>
       </c>
-      <c r="J55" s="6" t="n">
+      <c r="K55" s="6" t="n">
         <v>-0.006838735030247345</v>
       </c>
-      <c r="K55" s="6" t="n">
+      <c r="L55" s="6" t="n">
         <v>-0.03430737565594488</v>
       </c>
-      <c r="L55" s="6" t="n">
-        <v>0.01940347051404068</v>
-      </c>
       <c r="M55" s="6" t="n">
+        <v>0.0194035599785054</v>
+      </c>
+      <c r="N55" s="6" t="n">
         <v>0.06080475800427787</v>
       </c>
-      <c r="N55" s="6" t="n">
-        <v>0.5139823339199088</v>
-      </c>
       <c r="O55" s="6" t="n">
-        <v>0.1482600869593322</v>
+        <v>0.513982432586463</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0.1482601119034506</v>
       </c>
     </row>
     <row r="56">
@@ -3471,25 +3639,28 @@
         <v>0.003456555862949129</v>
       </c>
       <c r="I56" s="6" t="n">
+        <v>0.07155026605400461</v>
+      </c>
+      <c r="J56" s="6" t="n">
         <v>0.05183948035064168</v>
       </c>
-      <c r="J56" s="6" t="n">
+      <c r="K56" s="6" t="n">
         <v>-0.0817393917731184</v>
       </c>
-      <c r="K56" s="6" t="n">
+      <c r="L56" s="6" t="n">
         <v>-0.01515711840146161</v>
       </c>
-      <c r="L56" s="6" t="n">
+      <c r="M56" s="6" t="n">
         <v>0.07885958369319623</v>
       </c>
-      <c r="M56" s="6" t="n">
+      <c r="N56" s="6" t="n">
         <v>0.1183106258960303</v>
       </c>
-      <c r="N56" s="6" t="n">
-        <v>0.4318693310678108</v>
-      </c>
       <c r="O56" s="6" t="n">
-        <v>0.1271138740563336</v>
+        <v>0.4318692274498812</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0.1271138468682826</v>
       </c>
     </row>
     <row r="57">
@@ -3524,25 +3695,28 @@
         <v>-0.02333399866119745</v>
       </c>
       <c r="I57" s="6" t="n">
+        <v>0.04706383945048942</v>
+      </c>
+      <c r="J57" s="6" t="n">
         <v>0.01698755865887613</v>
       </c>
-      <c r="J57" s="6" t="n">
+      <c r="K57" s="6" t="n">
         <v>0.106241755920742</v>
       </c>
-      <c r="K57" s="6" t="n">
-        <v>-0.1271328284836151</v>
-      </c>
       <c r="L57" s="6" t="n">
+        <v>-0.1271327696375528</v>
+      </c>
+      <c r="M57" s="6" t="n">
         <v>0.02251625252414935</v>
       </c>
-      <c r="M57" s="6" t="n">
+      <c r="N57" s="6" t="n">
         <v>-0.09193159405018547</v>
       </c>
-      <c r="N57" s="6" t="n">
-        <v>0.1561783376696857</v>
-      </c>
       <c r="O57" s="6" t="n">
-        <v>0.04956242921501497</v>
+        <v>0.1561785441605237</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v>0.04956249169817051</v>
       </c>
     </row>
     <row r="58">
@@ -3577,25 +3751,28 @@
         <v>0.01528087144487356</v>
       </c>
       <c r="I58" s="6" t="n">
+        <v>0.04351440481734525</v>
+      </c>
+      <c r="J58" s="6" t="n">
         <v>0.01345895057042124</v>
       </c>
-      <c r="J58" s="6" t="n">
+      <c r="K58" s="6" t="n">
         <v>-0.03301310064204388</v>
       </c>
-      <c r="K58" s="6" t="n">
+      <c r="L58" s="6" t="n">
         <v>-0.008507453850260749</v>
       </c>
-      <c r="L58" s="6" t="n">
+      <c r="M58" s="6" t="n">
         <v>0.02374024186537449</v>
       </c>
-      <c r="M58" s="6" t="n">
+      <c r="N58" s="6" t="n">
         <v>0.02851151944584274</v>
       </c>
-      <c r="N58" s="6" t="n">
-        <v>0.7280281235909403</v>
-      </c>
       <c r="O58" s="6" t="n">
-        <v>0.200006510055178</v>
+        <v>0.7280283252907616</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v>0.2000065567444431</v>
       </c>
     </row>
     <row r="59">
@@ -3630,24 +3807,27 @@
         <v>-0.01478670671652849</v>
       </c>
       <c r="I59" s="6" t="n">
+        <v>0.05351711517647817</v>
+      </c>
+      <c r="J59" s="6" t="n">
         <v>-0.05731906015216304</v>
       </c>
-      <c r="J59" s="6" t="n">
+      <c r="K59" s="6" t="n">
         <v>-0.1998459790211022</v>
       </c>
-      <c r="K59" s="6" t="n">
+      <c r="L59" s="6" t="n">
         <v>-0.1027278511108857</v>
       </c>
-      <c r="L59" s="6" t="n">
+      <c r="M59" s="6" t="n">
         <v>0.04968699217466943</v>
       </c>
-      <c r="M59" s="6" t="n">
+      <c r="N59" s="6" t="n">
         <v>0.4191699272676173</v>
       </c>
-      <c r="N59" s="6" t="n">
+      <c r="O59" s="6" t="n">
         <v>-0.1571203978224349</v>
       </c>
-      <c r="O59" s="6" t="n">
+      <c r="P59" s="6" t="n">
         <v>-0.0553842525324878</v>
       </c>
     </row>
@@ -3683,25 +3863,28 @@
         <v>0.02828158839103079</v>
       </c>
       <c r="I60" s="6" t="n">
+        <v>0.0465389342299638</v>
+      </c>
+      <c r="J60" s="6" t="n">
         <v>0.0498234785864009</v>
       </c>
-      <c r="J60" s="6" t="n">
+      <c r="K60" s="6" t="n">
         <v>0.05536584474193385</v>
       </c>
-      <c r="K60" s="6" t="n">
+      <c r="L60" s="6" t="n">
         <v>0.1494979796452061</v>
       </c>
-      <c r="L60" s="6" t="n">
+      <c r="M60" s="6" t="n">
         <v>-0.1064804232815015</v>
       </c>
-      <c r="M60" s="6" t="n">
-        <v>-0.1887067671016402</v>
-      </c>
       <c r="N60" s="6" t="n">
-        <v>0.2084527758041173</v>
+        <v>-0.1887068609290272</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.0651478486663144</v>
+        <v>0.208452879892767</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v>0.06514787924806331</v>
       </c>
     </row>
     <row r="61">
@@ -3736,25 +3919,28 @@
         <v>-0.01600687586192728</v>
       </c>
       <c r="I61" s="6" t="n">
+        <v>-0.01173141679666856</v>
+      </c>
+      <c r="J61" s="6" t="n">
         <v>0.003308370652273629</v>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="K61" s="6" t="n">
         <v>-0.02757582587627139</v>
       </c>
-      <c r="K61" s="6" t="n">
+      <c r="L61" s="6" t="n">
         <v>-0.09813634185194176</v>
       </c>
-      <c r="L61" s="6" t="n">
+      <c r="M61" s="6" t="n">
         <v>0.001522995646940251</v>
       </c>
-      <c r="M61" s="6" t="n">
+      <c r="N61" s="6" t="n">
         <v>0.01151488059390049</v>
       </c>
-      <c r="N61" s="6" t="n">
-        <v>0.2962602918771131</v>
-      </c>
       <c r="O61" s="6" t="n">
-        <v>0.09034534182098719</v>
+        <v>0.296260432782828</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v>0.09034538132845471</v>
       </c>
     </row>
     <row r="62">
@@ -3789,24 +3975,27 @@
         <v>0.000445345309098677</v>
       </c>
       <c r="I62" s="6" t="n">
+        <v>0.149987219250679</v>
+      </c>
+      <c r="J62" s="6" t="n">
         <v>0.0813478009669959</v>
       </c>
-      <c r="J62" s="6" t="n">
+      <c r="K62" s="6" t="n">
         <v>-0.1441904703776041</v>
       </c>
-      <c r="K62" s="6" t="n">
+      <c r="L62" s="6" t="n">
         <v>-0.1344634860865696</v>
       </c>
-      <c r="L62" s="6" t="n">
+      <c r="M62" s="6" t="n">
         <v>0.05195124173176158</v>
       </c>
-      <c r="M62" s="6" t="n">
+      <c r="N62" s="6" t="n">
         <v>0.2061187990351565</v>
       </c>
-      <c r="N62" s="6" t="n">
+      <c r="O62" s="6" t="n">
         <v>1.265852035993138</v>
       </c>
-      <c r="O62" s="6" t="n">
+      <c r="P62" s="6" t="n">
         <v>0.3134408380524516</v>
       </c>
     </row>
@@ -3821,7 +4010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4350,7 +4539,7 @@
     <row r="14"/>
     <row r="15">
       <c r="A15" s="9">
-        <f>== PAST 3 MONTHS LEADERS &amp; LAGGARDS ===</f>
+        <f>== PAST 1 MONTH LEADERS &amp; LAGGARDS ===</f>
         <v/>
       </c>
     </row>
@@ -4377,7 +4566,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Top 10 - 3M</t>
+          <t>Top 10 - 1M</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -4403,7 +4592,7 @@
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>Bottom 10 - 3M</t>
+          <t>Bottom 10 - 1M</t>
         </is>
       </c>
     </row>
@@ -4413,21 +4602,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3490867849739594</v>
+        <v>0.2015224962711435</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4449,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1998459790211022</v>
+        <v>-0.05731906015216304</v>
       </c>
     </row>
     <row r="18">
@@ -4458,21 +4647,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.3018781573806397</v>
+        <v>0.1856216668747503</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4494,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1749265324482228</v>
+        <v>-0.04509704373959555</v>
       </c>
     </row>
     <row r="19">
@@ -4503,12 +4692,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4517,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.27214970370719</v>
+        <v>0.1714756722244206</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4525,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1441904703776041</v>
+        <v>-0.03020348642801807</v>
       </c>
     </row>
     <row r="20">
@@ -4548,21 +4737,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.2168207790765724</v>
+        <v>0.132872753730839</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4570,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1310707883350345</v>
+        <v>-0.02756692060045063</v>
       </c>
     </row>
     <row r="21">
@@ -4593,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.2070791853664002</v>
+        <v>0.1218157579367405</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4615,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.09493844770755866</v>
+        <v>-0.02080590075989186</v>
       </c>
     </row>
     <row r="22">
@@ -4638,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.2036613383840975</v>
+        <v>0.1162790721946345</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4660,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.0817393917731184</v>
+        <v>-0.01831484378483172</v>
       </c>
     </row>
     <row r="23">
@@ -4683,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1976489060938356</v>
+        <v>0.1131828245200317</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4705,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.0800324503850236</v>
+        <v>-0.0118881637320819</v>
       </c>
     </row>
     <row r="24">
@@ -4728,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.1684428674451059</v>
+        <v>0.1116095790257565</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4750,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.0455338478060292</v>
+        <v>-0.005316873608959827</v>
       </c>
     </row>
     <row r="25">
@@ -4773,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.1594266226386121</v>
+        <v>0.09319940470888111</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4795,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.04409912349568212</v>
+        <v>-0.005190771535326544</v>
       </c>
     </row>
     <row r="26">
@@ -4818,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.1573447558606693</v>
+        <v>0.09061063255104385</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -4840,28 +5029,28 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.04236291492091981</v>
+        <v>-0.002902294483186352</v>
       </c>
     </row>
     <row r="27"/>
     <row r="28"/>
     <row r="29">
       <c r="A29" s="9">
-        <f>== PAST 6 MONTHS LEADERS &amp; LAGGARDS ===</f>
+        <f>== PAST 3 MONTHS LEADERS &amp; LAGGARDS ===</f>
         <v/>
       </c>
     </row>
@@ -4888,7 +5077,7 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>Top 10 - 6M</t>
+          <t>Top 10 - 3M</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -4914,7 +5103,7 @@
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>Bottom 10 - 6M</t>
+          <t>Bottom 10 - 3M</t>
         </is>
       </c>
     </row>
@@ -4938,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.5172679577768988</v>
+        <v>0.3490867849739594</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -4946,12 +5135,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4960,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1344634860865696</v>
+        <v>-0.1998459790211022</v>
       </c>
     </row>
     <row r="32">
@@ -4969,12 +5158,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4983,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.5027122941071647</v>
+        <v>0.3018781573806397</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -4991,21 +5180,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1344044727012431</v>
+        <v>-0.1749265324482228</v>
       </c>
     </row>
     <row r="33">
@@ -5028,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.4942238735723645</v>
+        <v>0.27214970370719</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5036,21 +5225,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1271328284836151</v>
+        <v>-0.1441904703776041</v>
       </c>
     </row>
     <row r="34">
@@ -5059,21 +5248,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.448521858340776</v>
+        <v>0.2168207790765724</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5081,12 +5270,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5095,7 +5284,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1177340927147937</v>
+        <v>-0.1310707883350345</v>
       </c>
     </row>
     <row r="35">
@@ -5104,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.4417247266857178</v>
+        <v>0.2070791853664002</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5126,12 +5315,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5140,7 +5329,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1127942168862237</v>
+        <v>-0.09493844770755866</v>
       </c>
     </row>
     <row r="36">
@@ -5149,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.3208050864978083</v>
+        <v>0.2036613383840975</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5171,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.1027278511108857</v>
+        <v>-0.0817393917731184</v>
       </c>
     </row>
     <row r="37">
@@ -5194,12 +5383,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5208,7 +5397,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.2824720777607062</v>
+        <v>0.1976489060938356</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5216,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.09813634185194176</v>
+        <v>-0.0800324503850236</v>
       </c>
     </row>
     <row r="38">
@@ -5239,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.2576963056829229</v>
+        <v>0.1684428674451059</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5261,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.09766096062832919</v>
+        <v>-0.0455338478060292</v>
       </c>
     </row>
     <row r="39">
@@ -5284,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.2514246932755579</v>
+        <v>0.1594266226386121</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5306,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.04712009796503425</v>
+        <v>-0.04409912349568212</v>
       </c>
     </row>
     <row r="40">
@@ -5329,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.2434290676285413</v>
+        <v>0.1573447558606693</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5351,28 +5540,28 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.03625527575134335</v>
+        <v>-0.04236291492091981</v>
       </c>
     </row>
     <row r="41"/>
     <row r="42"/>
     <row r="43">
       <c r="A43" s="9">
-        <f>== PAST 1 YEAR LEADERS &amp; LAGGARDS ===</f>
+        <f>== PAST 6 MONTHS LEADERS &amp; LAGGARDS ===</f>
         <v/>
       </c>
     </row>
@@ -5399,7 +5588,7 @@
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>Top 10 - 1Y</t>
+          <t>Top 10 - 6M</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -5425,7 +5614,7 @@
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>Bottom 10 - 1Y</t>
+          <t>Bottom 10 - 6M</t>
         </is>
       </c>
     </row>
@@ -5435,12 +5624,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5449,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.95299771075168</v>
+        <v>0.5172679577768988</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5457,21 +5646,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1887067671016402</v>
+        <v>-0.1344634860865696</v>
       </c>
     </row>
     <row r="46">
@@ -5494,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.9144533099530932</v>
+        <v>0.5027122941071647</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5502,21 +5691,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1535985043633872</v>
+        <v>-0.1344044727012431</v>
       </c>
     </row>
     <row r="47">
@@ -5525,21 +5714,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.8926345034144225</v>
+        <v>0.4942238735723645</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5561,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.09193159405018547</v>
+        <v>-0.1271327696375528</v>
       </c>
     </row>
     <row r="48">
@@ -5570,21 +5759,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.7887702369085763</v>
+        <v>0.448521858340776</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5592,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.09075488719709224</v>
+        <v>-0.1177340927147937</v>
       </c>
     </row>
     <row r="49">
@@ -5615,21 +5804,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.7654398431849179</v>
+        <v>0.4417247266857178</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5637,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.06989552707371516</v>
+        <v>-0.1127942168862237</v>
       </c>
     </row>
     <row r="50">
@@ -5660,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.7573185118504884</v>
+        <v>0.3208051719641856</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5682,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.05520560798683727</v>
+        <v>-0.1027278511108857</v>
       </c>
     </row>
     <row r="51">
@@ -5705,21 +5894,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.6847379935933298</v>
+        <v>0.2824720777607062</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5727,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.03914048480321919</v>
+        <v>-0.09813634185194176</v>
       </c>
     </row>
     <row r="52">
@@ -5750,21 +5939,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.6708988106605565</v>
+        <v>0.2576963056829229</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5772,12 +5961,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5786,7 +5975,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.03605019350016947</v>
+        <v>-0.09766096062832919</v>
       </c>
     </row>
     <row r="53">
@@ -5795,12 +5984,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5809,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.5886917779864802</v>
+        <v>0.2514247774409466</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -5817,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.03352670957318238</v>
+        <v>-0.04712009796503425</v>
       </c>
     </row>
     <row r="54">
@@ -5840,21 +6029,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.5794660091439812</v>
+        <v>0.2434290676285413</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -5862,28 +6051,28 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.007290436709227133</v>
+        <v>-0.03625527575134335</v>
       </c>
     </row>
     <row r="55"/>
     <row r="56"/>
     <row r="57">
       <c r="A57" s="9">
-        <f>== PAST 3 YEARS LEADERS &amp; LAGGARDS ===</f>
+        <f>== PAST 1 YEAR LEADERS &amp; LAGGARDS ===</f>
         <v/>
       </c>
     </row>
@@ -5910,7 +6099,7 @@
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>Top 10 - 3Y</t>
+          <t>Top 10 - 1Y</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -5936,7 +6125,7 @@
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
-          <t>Bottom 10 - 3Y</t>
+          <t>Bottom 10 - 1Y</t>
         </is>
       </c>
     </row>
@@ -5960,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>2.954814755424023</v>
+        <v>0.95299771075168</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -5968,21 +6157,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1571203978224349</v>
+        <v>-0.1887068609290272</v>
       </c>
     </row>
     <row r="60">
@@ -5991,21 +6180,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>2.610430554875208</v>
+        <v>0.9144535154519131</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6013,21 +6202,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>0.03602311976075834</v>
+        <v>-0.1535985043633872</v>
       </c>
     </row>
     <row r="61">
@@ -6036,12 +6225,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6050,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2.219097928764253</v>
+        <v>0.8926345034144225</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6058,21 +6247,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.05914377681299454</v>
+        <v>-0.09193159405018547</v>
       </c>
     </row>
     <row r="62">
@@ -6081,21 +6270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1.675468032623519</v>
+        <v>0.7887702369085763</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6103,21 +6292,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>0.11391507147122</v>
+        <v>-0.0907549437557702</v>
       </c>
     </row>
     <row r="63">
@@ -6126,21 +6315,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>1.586255904171916</v>
+        <v>0.7654398431849179</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6148,21 +6337,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.1189501588453845</v>
+        <v>-0.06989552707371516</v>
       </c>
     </row>
     <row r="64">
@@ -6171,12 +6360,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6185,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>1.472020837358771</v>
+        <v>0.7573185118504884</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6193,21 +6382,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.1306764707031811</v>
+        <v>-0.05520560798683727</v>
       </c>
     </row>
     <row r="65">
@@ -6216,12 +6405,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6230,7 +6419,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>1.401177922545565</v>
+        <v>0.6847379935933298</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6238,21 +6427,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.1315509675774269</v>
+        <v>-0.03914048480321919</v>
       </c>
     </row>
     <row r="66">
@@ -6261,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>1.356429725046437</v>
+        <v>0.6708988106605565</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6283,12 +6472,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6297,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.1561783376696857</v>
+        <v>-0.03605019350016947</v>
       </c>
     </row>
     <row r="67">
@@ -6306,21 +6495,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>1.317869164743662</v>
+        <v>0.5886919146324345</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6328,12 +6517,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6342,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.1710372198784516</v>
+        <v>-0.03352677494094081</v>
       </c>
     </row>
     <row r="68">
@@ -6351,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>1.289616264418334</v>
+        <v>0.5794661313628906</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6373,20 +6562,531 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
+          <t>WOOD</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Timber &amp; Forestry</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="K68" s="11" t="n">
+        <v>-0.007290436709227133</v>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="9">
+        <f>== PAST 3 YEARS LEADERS &amp; LAGGARDS ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Top 10 - Rank</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Top 10 - Ticker</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Top 10 - Subgroup Name</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Top 10 - Sector</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>Top 10 - 3Y</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>Bottom 10 - Rank</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Bottom 10 - Ticker</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>Bottom 10 - Subgroup Name</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>Bottom 10 - Sector</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>Bottom 10 - 3Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SMH</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Semiconductor Manufacturers</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>2.9548151614259</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="n">
+        <v>52</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>TAN</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Solar Energy</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="n">
+        <v>-0.1571203978224349</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SIL</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Silver Miners</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>2.610430554875208</v>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>53</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>WOOD</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Timber &amp; Forestry</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="K74" s="11" t="n">
+        <v>0.03602300659100766</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Gold Miners</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>2.219097928764253</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>54</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>IHI</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Medical Devices &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="n">
+        <v>0.05914362332405099</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BDRY</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>1.675468032623519</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>55</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Travel Tech &amp; Bookings</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="K76" s="11" t="n">
+        <v>0.1139149554589198</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>5</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>XSD</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Semiconductors - Equal Weight</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>1.586255716658352</v>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>56</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>PBJ</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Food &amp; Beverage Manufacturers</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>0.1189501588453845</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>6</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>XAR</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>1.472020523117808</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>57</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ICLN</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Clean &amp; Renewable Energy</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="n">
+        <v>0.1306766046082197</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>7</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>COPX</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Copper Miners</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>1.401177922545565</v>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>58</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>IHF</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Health Care Providers &amp; Managed Care</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="n">
+        <v>0.1315510530431763</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>8</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NXTG</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>1.356428908937956</v>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>59</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Home Construction</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="K80" s="11" t="n">
+        <v>0.1561785441605237</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>9</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HACK</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>1.317869338161576</v>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="n">
+        <v>60</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>BETZ</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="n">
+        <v>0.1710372198784516</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>10</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>XME</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>1.289616264418334</v>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>61</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>BIZD</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="K68" s="11" t="n">
+      <c r="K82" s="11" t="n">
         <v>0.1818284279947984</v>
       </c>
     </row>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -633,10 +633,10 @@
         <v>0.95299771075168</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.9548151614259</v>
+        <v>2.954815567427861</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5814011980408651</v>
+        <v>0.5814012521564971</v>
       </c>
     </row>
     <row r="3">
@@ -689,10 +689,10 @@
         <v>0.9144535154519131</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.586255716658352</v>
+        <v>1.586255341631304</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.3726415931564593</v>
+        <v>0.3726415268085794</v>
       </c>
     </row>
     <row r="4">
@@ -745,10 +745,10 @@
         <v>0.4347586391378604</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.317869338161576</v>
+        <v>1.317868991325773</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3234158046621174</v>
+        <v>0.3234157386520682</v>
       </c>
     </row>
     <row r="5">
@@ -851,16 +851,16 @@
         <v>0.4942238735723645</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3397633867595804</v>
+        <v>0.3397632492645797</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3960021134484679</v>
+        <v>0.3960019641680483</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.221988076795161</v>
+        <v>1.221987887698371</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3049100463620229</v>
+        <v>0.3049100093449761</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>0.7654398431849179</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.979314708832606</v>
+        <v>0.979314329065486</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2555623493855865</v>
+        <v>0.2555622690848429</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.5572769562876529</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6907129096373184</v>
+        <v>0.6907126023860271</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1913058916038244</v>
+        <v>0.1913058194389419</v>
       </c>
     </row>
     <row r="9">
@@ -1078,13 +1078,13 @@
         <v>0.3629528389571743</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5886919146324345</v>
+        <v>0.5886917779864802</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6435209658821086</v>
+        <v>0.6435211121227156</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1801170442843902</v>
+        <v>0.1801170792866873</v>
       </c>
     </row>
     <row r="11">
@@ -1128,19 +1128,19 @@
         <v>0.06431423521401536</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3208051719641856</v>
+        <v>0.3208050864978083</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4800649400558907</v>
+        <v>0.4800650473755725</v>
       </c>
       <c r="N11" s="6" t="n">
         <v>0.5794661313628906</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.356428908937956</v>
+        <v>1.356429453010214</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3307141676620615</v>
+        <v>0.3307142700775716</v>
       </c>
     </row>
     <row r="12">
@@ -1249,10 +1249,10 @@
         <v>0.8926345034144225</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.401177922545565</v>
+        <v>1.40117766590346</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3390849032738834</v>
+        <v>0.339084855565968</v>
       </c>
     </row>
     <row r="14">
@@ -1302,13 +1302,13 @@
         <v>0.3688010699905064</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.4756981737216881</v>
+        <v>0.4756983578251881</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.3110367399959213</v>
+        <v>0.3110365946855582</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.09447275270777022</v>
+        <v>0.09447271227202592</v>
       </c>
     </row>
     <row r="15">
@@ -1355,16 +1355,16 @@
         <v>0.1503346711088214</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2098626046546102</v>
+        <v>0.2098624919979049</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>0.4479825125455659</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.5568191859772329</v>
+        <v>0.5568190927095242</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1589892071656922</v>
+        <v>0.1589891840210071</v>
       </c>
     </row>
     <row r="16">
@@ -1417,10 +1417,10 @@
         <v>0.5655113038381461</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.7595235911829428</v>
+        <v>0.7595234817904883</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2072531985186861</v>
+        <v>0.2072531734997181</v>
       </c>
     </row>
     <row r="17">
@@ -1520,7 +1520,7 @@
         <v>0.1571561877031578</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1060745059642498</v>
+        <v>0.1060746257359479</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>0.3022682955919407</v>
@@ -1579,10 +1579,10 @@
         <v>0.2396643814929893</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2077640170159634</v>
+        <v>0.2077639196498198</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.3098621497766205</v>
+        <v>0.3098622643002373</v>
       </c>
       <c r="O19" s="6" t="n">
         <v>0.1315510530431763</v>
@@ -1635,16 +1635,16 @@
         <v>0.1019114933429084</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.3471703568961428</v>
+        <v>0.347170232680279</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3210497296615014</v>
+        <v>0.3210496102158449</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.3731334698954882</v>
+        <v>0.3731333408456297</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1114866506712575</v>
+        <v>0.1114866158513359</v>
       </c>
     </row>
     <row r="21">
@@ -1691,7 +1691,7 @@
         <v>0.09679080438402776</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.3026926381261963</v>
+        <v>0.3026925508607157</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>0.3748939037679513</v>
@@ -1750,13 +1750,13 @@
         <v>0.274053897058689</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.2471737907276172</v>
+        <v>0.2471737079378604</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.9106328098003136</v>
+        <v>0.9106331984042819</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2408684537541106</v>
+        <v>0.2408685378809281</v>
       </c>
     </row>
     <row r="23">
@@ -1803,16 +1803,16 @@
         <v>0.07958545804894923</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.231243121798504</v>
+        <v>0.2312432131487518</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>0.2985765057164664</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>1.214322608485292</v>
+        <v>1.214322460753547</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.3034077473801564</v>
+        <v>0.3034077183939097</v>
       </c>
     </row>
     <row r="24">
@@ -1865,10 +1865,10 @@
         <v>0.1887834338245813</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.6631828902998294</v>
+        <v>0.663183043340156</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1848044305192602</v>
+        <v>0.1848044668597919</v>
       </c>
     </row>
     <row r="25">
@@ -1918,13 +1918,13 @@
         <v>0.233698134415397</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2569594331378515</v>
+        <v>0.2569592952828943</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4165680804678447</v>
+        <v>0.4165681680115343</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1230846303424595</v>
+        <v>0.1230846534779448</v>
       </c>
     </row>
     <row r="26">
@@ -1974,13 +1974,13 @@
         <v>0.2621967982854201</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.32906513968907</v>
+        <v>0.3290652522197257</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.236588621295782</v>
+        <v>0.2365888161271297</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.07335095898195876</v>
+        <v>0.0733510153527408</v>
       </c>
     </row>
     <row r="27">
@@ -2089,10 +2089,10 @@
         <v>0.4584814452192709</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.289616264418334</v>
+        <v>1.289616093699974</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3180166618926119</v>
+        <v>0.3180166291346265</v>
       </c>
     </row>
     <row r="29">
@@ -2142,7 +2142,7 @@
         <v>0.2404318849321641</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2378593642696347</v>
+        <v>0.2378592579151184</v>
       </c>
       <c r="O29" s="6" t="n">
         <v>0.7186350938961186</v>
@@ -2257,10 +2257,10 @@
         <v>0.6708988106605565</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2950529816054233</v>
+        <v>0.2950530666495053</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.09000672823763223</v>
+        <v>0.09000675209730469</v>
       </c>
     </row>
     <row r="32">
@@ -2363,7 +2363,7 @@
         <v>0.1033622388388482</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1160803368943923</v>
+        <v>0.1160804673018627</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>0.1328896676160121</v>
@@ -2472,19 +2472,19 @@
         <v>-0.04409912349568212</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.07605573387978715</v>
+        <v>0.07605563983556052</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.2386290768958681</v>
+        <v>0.2386292015036688</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.3167192491771473</v>
+        <v>0.3167193899921932</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.9405794621888182</v>
+        <v>0.9405793092578363</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.2473178676493513</v>
+        <v>0.2473178348836138</v>
       </c>
     </row>
     <row r="36">
@@ -2593,10 +2593,10 @@
         <v>0.1971306573287468</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.4435174528229471</v>
+        <v>0.443517786073083</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1301619453132836</v>
+        <v>0.1301620322829267</v>
       </c>
     </row>
     <row r="38">
@@ -2873,10 +2873,10 @@
         <v>0.3380234749134581</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.5619848712423876</v>
+        <v>0.5619851582619528</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1602696735394098</v>
+        <v>0.1602697446071226</v>
       </c>
     </row>
     <row r="43">
@@ -2929,10 +2929,10 @@
         <v>0.151385429832561</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.3445072479081215</v>
+        <v>0.3445073874574049</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1037084882602277</v>
+        <v>0.1037085264456481</v>
       </c>
     </row>
     <row r="44">
@@ -2979,16 +2979,16 @@
         <v>0.01756439913112762</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1190792393659745</v>
+        <v>0.1190791319507669</v>
       </c>
       <c r="N44" s="6" t="n">
         <v>0.07062307204624085</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.3948477800508428</v>
+        <v>0.3948478634895944</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1173149381635867</v>
+        <v>0.1173149604425678</v>
       </c>
     </row>
     <row r="45">
@@ -3094,13 +3094,13 @@
         <v>0.124195941014893</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.09953649760503391</v>
+        <v>0.09953637435825824</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.2076745111403082</v>
+        <v>0.2076746598215466</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.06491914163171186</v>
+        <v>0.06491918533374386</v>
       </c>
     </row>
     <row r="47">
@@ -3153,10 +3153,10 @@
         <v>-0.03605019350016947</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.7809939976331854</v>
+        <v>0.7809937997512078</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.2121438208721309</v>
+        <v>0.2121437759793303</v>
       </c>
     </row>
     <row r="48">
@@ -3206,13 +3206,13 @@
         <v>0.03069357316529486</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.06989552707371516</v>
+        <v>-0.0698954653670355</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1818284279947984</v>
+        <v>0.1818285276219205</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.0572673257755727</v>
+        <v>0.05726735548448136</v>
       </c>
     </row>
     <row r="49">
@@ -3265,10 +3265,10 @@
         <v>-0.007290436709227133</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.03602300659100766</v>
+        <v>0.03602311976075834</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01186630276114964</v>
+        <v>0.0118663396048142</v>
       </c>
     </row>
     <row r="50">
@@ -3374,13 +3374,13 @@
         <v>0.06170921921053307</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>-0.03352677494094081</v>
+        <v>-0.03352670957318238</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.3320393086449767</v>
+        <v>0.3320391844746136</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1002862364320252</v>
+        <v>0.1002862022431077</v>
       </c>
     </row>
     <row r="52">
@@ -3427,16 +3427,16 @@
         <v>-0.008747308580336233</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.08113588931454596</v>
+        <v>0.08113601174255214</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0.3470668833309982</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.1306766046082197</v>
+        <v>0.1306764707031811</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.04178828318058359</v>
+        <v>0.04178824205455767</v>
       </c>
     </row>
     <row r="53">
@@ -3486,7 +3486,7 @@
         <v>0.09701398276227624</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.02565690095910922</v>
+        <v>0.02565681742549941</v>
       </c>
       <c r="O53" s="6" t="n">
         <v>0.1189501588453845</v>
@@ -3539,16 +3539,16 @@
         <v>-0.03625527575134335</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1021699539265614</v>
+        <v>-0.1021700090740284</v>
       </c>
       <c r="N54" s="6" t="n">
         <v>-0.0907549437557702</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.05914362332405099</v>
+        <v>0.05914385355748286</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.01933816585261061</v>
+        <v>0.01933823971281923</v>
       </c>
     </row>
     <row r="55">
@@ -3595,16 +3595,16 @@
         <v>-0.03430737565594488</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.0194035599785054</v>
+        <v>0.01940347051404068</v>
       </c>
       <c r="N55" s="6" t="n">
         <v>0.06080475800427787</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.513982432586463</v>
+        <v>0.5139823339199088</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.1482601119034506</v>
+        <v>0.1482600869593322</v>
       </c>
     </row>
     <row r="56">
@@ -3704,7 +3704,7 @@
         <v>0.106241755920742</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.1271327696375528</v>
+        <v>-0.1271328284836151</v>
       </c>
       <c r="M57" s="6" t="n">
         <v>0.02251625252414935</v>
@@ -3769,10 +3769,10 @@
         <v>0.02851151944584274</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.7280283252907616</v>
+        <v>0.7280285269906301</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.2000065567444431</v>
+        <v>0.2000066034337153</v>
       </c>
     </row>
     <row r="59">
@@ -3878,13 +3878,13 @@
         <v>-0.1064804232815015</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1887068609290272</v>
+        <v>-0.1887067671016402</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.208452879892767</v>
+        <v>0.2084527758041173</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.06514787924806331</v>
+        <v>0.0651478486663144</v>
       </c>
     </row>
     <row r="61">
@@ -3993,10 +3993,10 @@
         <v>0.2061187990351565</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>1.265852035993138</v>
+        <v>1.265852253943098</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>0.3134408380524516</v>
+        <v>0.3134408801652884</v>
       </c>
     </row>
   </sheetData>
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1271327696375528</v>
+        <v>-0.1271328284836151</v>
       </c>
     </row>
     <row r="48">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3208051719641856</v>
+        <v>0.3208050864978083</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1887068609290272</v>
+        <v>-0.1887067671016402</v>
       </c>
     </row>
     <row r="60">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.06989552707371516</v>
+        <v>-0.0698954653670355</v>
       </c>
     </row>
     <row r="64">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5886919146324345</v>
+        <v>0.5886917779864802</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.03352677494094081</v>
+        <v>-0.03352670957318238</v>
       </c>
     </row>
     <row r="68">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.9548151614259</v>
+        <v>2.954815567427861</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.03602300659100766</v>
+        <v>0.03602311976075834</v>
       </c>
     </row>
     <row r="75">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.05914362332405099</v>
+        <v>0.05914385355748286</v>
       </c>
     </row>
     <row r="76">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.586255716658352</v>
+        <v>1.586255341631304</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1306766046082197</v>
+        <v>0.1306764707031811</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.401177922545565</v>
+        <v>1.40117766590346</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.356428908937956</v>
+        <v>1.356429453010214</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.317869338161576</v>
+        <v>1.317868991325773</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.289616264418334</v>
+        <v>1.289616093699974</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1818284279947984</v>
+        <v>0.1818285276219205</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -633,10 +633,10 @@
         <v>0.95299771075168</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.954815567427861</v>
+        <v>2.954814755424023</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5814012521564971</v>
+        <v>0.5814011439252407</v>
       </c>
     </row>
     <row r="3">
@@ -689,10 +689,10 @@
         <v>0.9144535154519131</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.586255341631304</v>
+        <v>1.586255904171916</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.3726415268085794</v>
+        <v>0.372641626330404</v>
       </c>
     </row>
     <row r="4">
@@ -745,10 +745,10 @@
         <v>0.4347586391378604</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.317868991325773</v>
+        <v>1.317869164743662</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3234157386520682</v>
+        <v>0.3234157716570911</v>
       </c>
     </row>
     <row r="5">
@@ -857,10 +857,10 @@
         <v>0.3960019641680483</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.221987887698371</v>
+        <v>1.221988076795161</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3049100093449761</v>
+        <v>0.3049100463620229</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>0.7654398431849179</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.979314329065486</v>
+        <v>0.9793145189490278</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2555622690848429</v>
+        <v>0.2555623092352122</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.5572769562876529</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6907126023860271</v>
+        <v>0.6907130632630059</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1913058194389419</v>
+        <v>0.1913059276862723</v>
       </c>
     </row>
     <row r="9">
@@ -1078,13 +1078,13 @@
         <v>0.3629528389571743</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5886917779864802</v>
+        <v>0.5886919146324345</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6435211121227156</v>
+        <v>0.6435208196415279</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1801170792866873</v>
+        <v>0.1801170092820972</v>
       </c>
     </row>
     <row r="11">
@@ -1128,10 +1128,10 @@
         <v>0.06431423521401536</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3208050864978083</v>
+        <v>0.3208051719641856</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4800650473755725</v>
+        <v>0.4800649400558907</v>
       </c>
       <c r="N11" s="6" t="n">
         <v>0.5794661313628906</v>
@@ -1243,16 +1243,16 @@
         <v>-0.02216029949244547</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4392069599844457</v>
+        <v>0.4392070521833586</v>
       </c>
       <c r="N13" s="6" t="n">
         <v>0.8926345034144225</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.40117766590346</v>
+        <v>1.401177922545565</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.339084855565968</v>
+        <v>0.3390849032738834</v>
       </c>
     </row>
     <row r="14">
@@ -1299,10 +1299,10 @@
         <v>0.231344858273878</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.3688010699905064</v>
+        <v>0.3688012283877549</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.4756983578251881</v>
+        <v>0.4756982657734323</v>
       </c>
       <c r="O14" s="6" t="n">
         <v>0.3110365946855582</v>
@@ -1352,13 +1352,13 @@
         <v>0.1573447558606693</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1503346711088214</v>
+        <v>0.1503345692653111</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>0.2098624919979049</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.4479825125455659</v>
+        <v>0.4479823511797401</v>
       </c>
       <c r="O15" s="6" t="n">
         <v>0.5568190927095242</v>
@@ -1520,13 +1520,13 @@
         <v>0.1571561877031578</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1060746257359479</v>
+        <v>0.1060745059642498</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>0.3022682955919407</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2751251476180132</v>
+        <v>0.2751252272084794</v>
       </c>
       <c r="O18" s="6" t="n">
         <v>0.8088847221363824</v>
@@ -1585,10 +1585,10 @@
         <v>0.3098622643002373</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1315510530431763</v>
+        <v>0.1315511385089385</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.04205678181883066</v>
+        <v>0.0420568080542576</v>
       </c>
     </row>
     <row r="20">
@@ -1635,16 +1635,16 @@
         <v>0.1019114933429084</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.347170232680279</v>
+        <v>0.3471703568961428</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3210496102158449</v>
+        <v>0.3210497296615014</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.3731333408456297</v>
+        <v>0.3731334698954882</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1114866158513359</v>
+        <v>0.1114866506712575</v>
       </c>
     </row>
     <row r="21">
@@ -1691,10 +1691,10 @@
         <v>0.09679080438402776</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.3026925508607157</v>
+        <v>0.3026926381261963</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3748939037679513</v>
+        <v>0.3748940009748305</v>
       </c>
       <c r="O21" s="6" t="n">
         <v>1.472020523117808</v>
@@ -1750,13 +1750,13 @@
         <v>0.274053897058689</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.2471737079378604</v>
+        <v>0.2471736251481147</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.9106331984042819</v>
+        <v>0.9106328098003136</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2408685378809281</v>
+        <v>0.2408684537541106</v>
       </c>
     </row>
     <row r="23">
@@ -1809,10 +1809,10 @@
         <v>0.2985765057164664</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>1.214322460753547</v>
+        <v>1.214322903948841</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.3034077183939097</v>
+        <v>0.3034078053526579</v>
       </c>
     </row>
     <row r="24">
@@ -1856,7 +1856,7 @@
         <v>0.1594266226386121</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1531784548359023</v>
+        <v>0.1531785284089748</v>
       </c>
       <c r="M24" s="6" t="n">
         <v>0.1963610949333312</v>
@@ -1865,10 +1865,10 @@
         <v>0.1887834338245813</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.663183043340156</v>
+        <v>0.6631831963805108</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1848044668597919</v>
+        <v>0.184804503200328</v>
       </c>
     </row>
     <row r="25">
@@ -1918,13 +1918,13 @@
         <v>0.233698134415397</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2569592952828943</v>
+        <v>0.256959157427967</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4165681680115343</v>
+        <v>0.4165682555552348</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1230846534779448</v>
+        <v>0.1230846766134321</v>
       </c>
     </row>
     <row r="26">
@@ -1968,19 +1968,19 @@
         <v>0.002045241333242798</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1376339895011602</v>
+        <v>0.1376340719497873</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>0.2621967982854201</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.3290652522197257</v>
+        <v>0.3290650271584334</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.2365888161271297</v>
+        <v>0.236588621295782</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.0733510153527408</v>
+        <v>0.07335095898195876</v>
       </c>
     </row>
     <row r="27">
@@ -2027,7 +2027,7 @@
         <v>-0.1177340927147937</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.327070351643459</v>
+        <v>0.3270702016016425</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>0.6847379935933298</v>
@@ -2080,7 +2080,7 @@
         <v>-0.0309982871503458</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>-0.004559294459831276</v>
+        <v>-0.00455935899784865</v>
       </c>
       <c r="M28" s="6" t="n">
         <v>0.2787111694241451</v>
@@ -2089,10 +2089,10 @@
         <v>0.4584814452192709</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.289616093699974</v>
+        <v>1.289616264418334</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3180166291346265</v>
+        <v>0.3180166618926119</v>
       </c>
     </row>
     <row r="29">
@@ -2142,7 +2142,7 @@
         <v>0.2404318849321641</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2378592579151184</v>
+        <v>0.2378593642696347</v>
       </c>
       <c r="O29" s="6" t="n">
         <v>0.7186350938961186</v>
@@ -2201,10 +2201,10 @@
         <v>0.2723625822594464</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.8491257596152417</v>
+        <v>0.8491256483038905</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2274076230404236</v>
+        <v>0.2274075984117752</v>
       </c>
     </row>
     <row r="31">
@@ -2313,10 +2313,10 @@
         <v>0.124953949922479</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.6936872604525228</v>
+        <v>0.6936869323340986</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1920040755467858</v>
+        <v>0.1920039985710393</v>
       </c>
     </row>
     <row r="33">
@@ -2363,10 +2363,10 @@
         <v>0.1033622388388482</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1160804673018627</v>
+        <v>0.1160803368943923</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1328896676160121</v>
+        <v>0.1328895332508482</v>
       </c>
       <c r="O33" s="6" t="n">
         <v>0.6989225872668208</v>
@@ -2478,13 +2478,13 @@
         <v>0.2386292015036688</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.3167193899921932</v>
+        <v>0.3167191083621315</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.9405793092578363</v>
+        <v>0.9405796151198242</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.2473178348836138</v>
+        <v>0.2473179004150921</v>
       </c>
     </row>
     <row r="36">
@@ -2587,16 +2587,16 @@
         <v>0.07742728672366161</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1497681722522</v>
+        <v>0.1497680665420507</v>
       </c>
       <c r="N37" s="6" t="n">
         <v>0.1971306573287468</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.443517786073083</v>
+        <v>0.4435176194479959</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1301620322829267</v>
+        <v>0.1301619887981018</v>
       </c>
     </row>
     <row r="38">
@@ -2758,13 +2758,13 @@
         <v>0.1138930913027458</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.09658321815512561</v>
+        <v>0.09658331413574794</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.089480198205569</v>
+        <v>1.089480372445181</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2784372607729235</v>
+        <v>0.2784372963087802</v>
       </c>
     </row>
     <row r="41">
@@ -2814,13 +2814,13 @@
         <v>0.2035777422773202</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.2167677826073577</v>
+        <v>0.2167678739357963</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.6623434008207847</v>
+        <v>0.66234357128457</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.184605054120125</v>
+        <v>0.1846050946116091</v>
       </c>
     </row>
     <row r="42">
@@ -2873,10 +2873,10 @@
         <v>0.3380234749134581</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.5619851582619528</v>
+        <v>0.5619850625887528</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1602697446071226</v>
+        <v>0.1602697209178832</v>
       </c>
     </row>
     <row r="43">
@@ -2929,10 +2929,10 @@
         <v>0.151385429832561</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.3445073874574049</v>
+        <v>0.3445072479081215</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1037085264456481</v>
+        <v>0.1037084882602277</v>
       </c>
     </row>
     <row r="44">
@@ -2979,16 +2979,16 @@
         <v>0.01756439913112762</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1190791319507669</v>
+        <v>0.1190792393659745</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.07062307204624085</v>
+        <v>0.07062297373180471</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.3948478634895944</v>
+        <v>0.3948477800508428</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1173149604425678</v>
+        <v>0.1173149381635867</v>
       </c>
     </row>
     <row r="45">
@@ -3041,10 +3041,10 @@
         <v>0.1726306199379812</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.3560138803144475</v>
+        <v>0.356013761164383</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1068481538181185</v>
+        <v>0.1068481213993173</v>
       </c>
     </row>
     <row r="46">
@@ -3097,10 +3097,10 @@
         <v>0.09953637435825824</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.2076746598215466</v>
+        <v>0.207674585480923</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.06491918533374386</v>
+        <v>0.06491916348272686</v>
       </c>
     </row>
     <row r="47">
@@ -3206,13 +3206,13 @@
         <v>0.03069357316529486</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.0698954653670355</v>
+        <v>-0.06989552707371516</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1818285276219205</v>
+        <v>0.1818283283676931</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.05726735548448136</v>
+        <v>0.05726729606666758</v>
       </c>
     </row>
     <row r="49">
@@ -3321,10 +3321,10 @@
         <v>-0.1535985043633872</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.1710372198784516</v>
+        <v>0.1710373535388929</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.05403953222290636</v>
+        <v>0.05403957232507151</v>
       </c>
     </row>
     <row r="51">
@@ -3371,16 +3371,16 @@
         <v>-0.09766096062832919</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.06170921921053307</v>
+        <v>0.06170914032541952</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>-0.03352670957318238</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.3320391844746136</v>
+        <v>0.3320393086449767</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1002862022431077</v>
+        <v>0.1002862364320252</v>
       </c>
     </row>
     <row r="52">
@@ -3427,7 +3427,7 @@
         <v>-0.008747308580336233</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.08113601174255214</v>
+        <v>0.08113588931454596</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0.3470668833309982</v>
@@ -3486,13 +3486,13 @@
         <v>0.09701398276227624</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.02565681742549941</v>
+        <v>0.02565690095910922</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.1189501588453845</v>
+        <v>0.1189502582664914</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.03817423714626678</v>
+        <v>0.03817426789426404</v>
       </c>
     </row>
     <row r="54">
@@ -3545,10 +3545,10 @@
         <v>-0.0907549437557702</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.05914385355748286</v>
+        <v>0.05914362332405099</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.01933823971281923</v>
+        <v>0.01933816585261061</v>
       </c>
     </row>
     <row r="55">
@@ -3601,10 +3601,10 @@
         <v>0.06080475800427787</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.5139823339199088</v>
+        <v>0.513982432586463</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.1482600869593322</v>
+        <v>0.1482601119034506</v>
       </c>
     </row>
     <row r="56">
@@ -3657,10 +3657,10 @@
         <v>0.1183106258960303</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.4318692274498812</v>
+        <v>0.4318693310678108</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.1271138468682826</v>
+        <v>0.1271138740563336</v>
       </c>
     </row>
     <row r="57">
@@ -3713,10 +3713,10 @@
         <v>-0.09193159405018547</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.1561785441605237</v>
+        <v>0.1561786474059703</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.04956249169817051</v>
+        <v>0.04956252293975383</v>
       </c>
     </row>
     <row r="58">
@@ -3763,10 +3763,10 @@
         <v>-0.008507453850260749</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.02374024186537449</v>
+        <v>0.02374017107350679</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.02851151944584274</v>
+        <v>0.02851159089912803</v>
       </c>
       <c r="O58" s="6" t="n">
         <v>0.7280285269906301</v>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3208050864978083</v>
+        <v>0.3208051719641856</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.0698954653670355</v>
+        <v>-0.06989552707371516</v>
       </c>
     </row>
     <row r="64">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5886917779864802</v>
+        <v>0.5886919146324345</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.954815567427861</v>
+        <v>2.954814755424023</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.05914385355748286</v>
+        <v>0.05914362332405099</v>
       </c>
     </row>
     <row r="76">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.586255341631304</v>
+        <v>1.586255904171916</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1189501588453845</v>
+        <v>0.1189502582664914</v>
       </c>
     </row>
     <row r="78">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.40117766590346</v>
+        <v>1.401177922545565</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1315510530431763</v>
+        <v>0.1315511385089385</v>
       </c>
     </row>
     <row r="80">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1561785441605237</v>
+        <v>0.1561786474059703</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.317868991325773</v>
+        <v>1.317869164743662</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1710372198784516</v>
+        <v>0.1710373535388929</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.289616093699974</v>
+        <v>1.289616264418334</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1818285276219205</v>
+        <v>0.1818283283676931</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -633,10 +633,10 @@
         <v>0.95299771075168</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.954814755424023</v>
+        <v>2.9548151614259</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5814011439252407</v>
+        <v>0.5814011980408651</v>
       </c>
     </row>
     <row r="3">
@@ -689,10 +689,10 @@
         <v>0.9144535154519131</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.586255904171916</v>
+        <v>1.586255529144814</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.372641626330404</v>
+        <v>0.3726415599825177</v>
       </c>
     </row>
     <row r="4">
@@ -851,16 +851,16 @@
         <v>0.4942238735723645</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3397632492645797</v>
+        <v>0.3397633867595804</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>0.3960019641680483</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.221988076795161</v>
+        <v>1.221987887698371</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3049100463620229</v>
+        <v>0.3049100093449761</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>0.7654398431849179</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.9793145189490278</v>
+        <v>0.9793148987162206</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2555623092352122</v>
+        <v>0.2555623895359658</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.5572769562876529</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6907130632630059</v>
+        <v>0.6907127560116586</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1913059276862723</v>
+        <v>0.1913058555213809</v>
       </c>
     </row>
     <row r="9">
@@ -1078,13 +1078,13 @@
         <v>0.3629528389571743</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5886919146324345</v>
+        <v>0.5886917779864802</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6435208196415279</v>
+        <v>0.6435209658821086</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1801170092820972</v>
+        <v>0.1801170442843902</v>
       </c>
     </row>
     <row r="11">
@@ -1128,13 +1128,13 @@
         <v>0.06431423521401536</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3208051719641856</v>
+        <v>0.3208050864978083</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4800649400558907</v>
+        <v>0.4800650473755725</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5794661313628906</v>
+        <v>0.5794660091439812</v>
       </c>
       <c r="O11" s="6" t="n">
         <v>1.356429453010214</v>
@@ -1243,7 +1243,7 @@
         <v>-0.02216029949244547</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4392070521833586</v>
+        <v>0.4392069599844457</v>
       </c>
       <c r="N13" s="6" t="n">
         <v>0.8926345034144225</v>
@@ -1299,16 +1299,16 @@
         <v>0.231344858273878</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.3688012283877549</v>
+        <v>0.3688010699905064</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.4756982657734323</v>
+        <v>0.4756981737216881</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.3110365946855582</v>
+        <v>0.3110367399959213</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.09447271227202592</v>
+        <v>0.09447275270777022</v>
       </c>
     </row>
     <row r="15">
@@ -1358,13 +1358,13 @@
         <v>0.2098624919979049</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.4479823511797401</v>
+        <v>0.4479825125455659</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.5568190927095242</v>
+        <v>0.5568189994418264</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1589891840210071</v>
+        <v>0.1589891608763236</v>
       </c>
     </row>
     <row r="16">
@@ -1520,19 +1520,19 @@
         <v>0.1571561877031578</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1060745059642498</v>
+        <v>0.1060746257359479</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.3022682955919407</v>
+        <v>0.3022682125769913</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2751252272084794</v>
+        <v>0.2751251476180132</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.8088847221363824</v>
+        <v>0.8088845619678695</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2184385475171322</v>
+        <v>0.2184385115547343</v>
       </c>
     </row>
     <row r="19">
@@ -1579,16 +1579,16 @@
         <v>0.2396643814929893</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2077639196498198</v>
+        <v>0.2077640170159634</v>
       </c>
       <c r="N19" s="6" t="n">
         <v>0.3098622643002373</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1315511385089385</v>
+        <v>0.1315510530431763</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.0420568080542576</v>
+        <v>0.04205678181883066</v>
       </c>
     </row>
     <row r="20">
@@ -1635,16 +1635,16 @@
         <v>0.1019114933429084</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.3471703568961428</v>
+        <v>0.347170232680279</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3210497296615014</v>
+        <v>0.3210496102158449</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.3731334698954882</v>
+        <v>0.3731333408456297</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1114866506712575</v>
+        <v>0.1114866158513359</v>
       </c>
     </row>
     <row r="21">
@@ -1691,16 +1691,16 @@
         <v>0.09679080438402776</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.3026926381261963</v>
+        <v>0.3026925508607157</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3748940009748305</v>
+        <v>0.3748939037679513</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1.472020523117808</v>
+        <v>1.47202068023828</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3521266022186644</v>
+        <v>0.3521266308655093</v>
       </c>
     </row>
     <row r="22">
@@ -1750,7 +1750,7 @@
         <v>0.274053897058689</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.2471736251481147</v>
+        <v>0.2471737079378604</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>0.9106328098003136</v>
@@ -1803,16 +1803,16 @@
         <v>0.07958545804894923</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.2312432131487518</v>
+        <v>0.231243121798504</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>0.2985765057164664</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>1.214322903948841</v>
+        <v>1.214322756217057</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.3034078053526579</v>
+        <v>0.3034077763664058</v>
       </c>
     </row>
     <row r="24">
@@ -1865,10 +1865,10 @@
         <v>0.1887834338245813</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.6631831963805108</v>
+        <v>0.6631833494208939</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.184804503200328</v>
+        <v>0.1848045395408686</v>
       </c>
     </row>
     <row r="25">
@@ -1921,10 +1921,10 @@
         <v>0.256959157427967</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4165682555552348</v>
+        <v>0.4165680804678447</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1230846766134321</v>
+        <v>0.1230846303424595</v>
       </c>
     </row>
     <row r="26">
@@ -1968,13 +1968,13 @@
         <v>0.002045241333242798</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1376340719497873</v>
+        <v>0.1376339895011602</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>0.2621967982854201</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.3290650271584334</v>
+        <v>0.32906513968907</v>
       </c>
       <c r="O26" s="6" t="n">
         <v>0.236588621295782</v>
@@ -2027,16 +2027,16 @@
         <v>-0.1177340927147937</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.3270702016016425</v>
+        <v>0.327070351643459</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>0.6847379935933298</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2.610430554875208</v>
+        <v>2.610430277234953</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.5340976287463735</v>
+        <v>0.5340975894225992</v>
       </c>
     </row>
     <row r="28">
@@ -2089,10 +2089,10 @@
         <v>0.4584814452192709</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.289616264418334</v>
+        <v>1.28961643513672</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3180166618926119</v>
+        <v>0.3180166946506007</v>
       </c>
     </row>
     <row r="29">
@@ -2142,7 +2142,7 @@
         <v>0.2404318849321641</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2378593642696347</v>
+        <v>0.2378592579151184</v>
       </c>
       <c r="O29" s="6" t="n">
         <v>0.7186350938961186</v>
@@ -2201,10 +2201,10 @@
         <v>0.2723625822594464</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.8491256483038905</v>
+        <v>0.8491255369925528</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2274075984117752</v>
+        <v>0.2274075737831289</v>
       </c>
     </row>
     <row r="31">
@@ -2313,10 +2313,10 @@
         <v>0.124953949922479</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.6936869323340986</v>
+        <v>0.6936870963932948</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1920039985710393</v>
+        <v>0.19200403705891</v>
       </c>
     </row>
     <row r="33">
@@ -2366,7 +2366,7 @@
         <v>0.1160803368943923</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1328895332508482</v>
+        <v>0.1328896676160121</v>
       </c>
       <c r="O33" s="6" t="n">
         <v>0.6989225872668208</v>
@@ -2472,19 +2472,19 @@
         <v>-0.04409912349568212</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.07605563983556052</v>
+        <v>0.07605573387978715</v>
       </c>
       <c r="M35" s="6" t="n">
         <v>0.2386292015036688</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.3167191083621315</v>
+        <v>0.3167192491771473</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.9405796151198242</v>
+        <v>0.9405794621888182</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.2473179004150921</v>
+        <v>0.2473178676493513</v>
       </c>
     </row>
     <row r="36">
@@ -2587,16 +2587,16 @@
         <v>0.07742728672366161</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1497680665420507</v>
+        <v>0.1497681722522</v>
       </c>
       <c r="N37" s="6" t="n">
         <v>0.1971306573287468</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.4435176194479959</v>
+        <v>0.4435174528229471</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1301619887981018</v>
+        <v>0.1301619453132836</v>
       </c>
     </row>
     <row r="38">
@@ -2649,10 +2649,10 @@
         <v>-0.05520560798683727</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.1139149554589198</v>
+        <v>0.11391507147122</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.03661465647757489</v>
+        <v>0.03661469246477655</v>
       </c>
     </row>
     <row r="39">
@@ -2758,13 +2758,13 @@
         <v>0.1138930913027458</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.09658331413574794</v>
+        <v>0.09658321815512561</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.089480372445181</v>
+        <v>1.089480546684821</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2784372963087802</v>
+        <v>0.2784373318446405</v>
       </c>
     </row>
     <row r="41">
@@ -2873,10 +2873,10 @@
         <v>0.3380234749134581</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.5619850625887528</v>
+        <v>0.5619851582619528</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1602697209178832</v>
+        <v>0.1602697446071226</v>
       </c>
     </row>
     <row r="43">
@@ -2926,7 +2926,7 @@
         <v>0.1350185150234462</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.151385429832561</v>
+        <v>0.1513855321719377</v>
       </c>
       <c r="O43" s="6" t="n">
         <v>0.3445072479081215</v>
@@ -2985,10 +2985,10 @@
         <v>0.07062297373180471</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.3948477800508428</v>
+        <v>0.3948478634895944</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1173149381635867</v>
+        <v>0.1173149604425678</v>
       </c>
     </row>
     <row r="45">
@@ -3094,13 +3094,13 @@
         <v>0.124195941014893</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.09953637435825824</v>
+        <v>0.09953649760503391</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.207674585480923</v>
+        <v>0.2076744367997028</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.06491916348272686</v>
+        <v>0.06491911978069842</v>
       </c>
     </row>
     <row r="47">
@@ -3206,13 +3206,13 @@
         <v>0.03069357316529486</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.06989552707371516</v>
+        <v>-0.0698954653670355</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1818283283676931</v>
+        <v>0.1818284279947984</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.05726729606666758</v>
+        <v>0.0572673257755727</v>
       </c>
     </row>
     <row r="49">
@@ -3371,7 +3371,7 @@
         <v>-0.09766096062832919</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.06170914032541952</v>
+        <v>0.06170921921053307</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>-0.03352670957318238</v>
@@ -3483,16 +3483,16 @@
         <v>-0.04712009796503425</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.09701398276227624</v>
+        <v>0.09701407832344122</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.02565690095910922</v>
+        <v>0.02565698449273235</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.1189502582664914</v>
+        <v>0.1189501588453845</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.03817426789426404</v>
+        <v>0.03817423714626678</v>
       </c>
     </row>
     <row r="54">
@@ -3542,7 +3542,7 @@
         <v>-0.1021700090740284</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.0907549437557702</v>
+        <v>-0.09075488719709224</v>
       </c>
       <c r="O54" s="6" t="n">
         <v>0.05914362332405099</v>
@@ -3598,13 +3598,13 @@
         <v>0.01940347051404068</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.06080475800427787</v>
+        <v>0.06080485488319431</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.513982432586463</v>
+        <v>0.5139823339199088</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.1482601119034506</v>
+        <v>0.1482600869593322</v>
       </c>
     </row>
     <row r="56">
@@ -3713,10 +3713,10 @@
         <v>-0.09193159405018547</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.1561786474059703</v>
+        <v>0.1561785441605237</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.04956252293975383</v>
+        <v>0.04956249169817051</v>
       </c>
     </row>
     <row r="58">
@@ -3763,16 +3763,16 @@
         <v>-0.008507453850260749</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.02374017107350679</v>
+        <v>0.02374024186537449</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.02851159089912803</v>
+        <v>0.02851151944584274</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.7280285269906301</v>
+        <v>0.7280281235909403</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.2000066034337153</v>
+        <v>0.200006510055178</v>
       </c>
     </row>
     <row r="59">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3208051719641856</v>
+        <v>0.3208050864978083</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.0907549437557702</v>
+        <v>-0.09075488719709224</v>
       </c>
     </row>
     <row r="63">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.06989552707371516</v>
+        <v>-0.0698954653670355</v>
       </c>
     </row>
     <row r="64">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5886919146324345</v>
+        <v>0.5886917779864802</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.5794661313628906</v>
+        <v>0.5794660091439812</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.954814755424023</v>
+        <v>2.9548151614259</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.610430554875208</v>
+        <v>2.610430277234953</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1139149554589198</v>
+        <v>0.11391507147122</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.586255904171916</v>
+        <v>1.586255529144814</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1189502582664914</v>
+        <v>0.1189501588453845</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.472020523117808</v>
+        <v>1.47202068023828</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1315511385089385</v>
+        <v>0.1315510530431763</v>
       </c>
     </row>
     <row r="80">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1561786474059703</v>
+        <v>0.1561785441605237</v>
       </c>
     </row>
     <row r="81">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.289616264418334</v>
+        <v>1.28961643513672</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1818283283676931</v>
+        <v>0.1818284279947984</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -490,13 +490,13 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>587.8200000000001</v>
+        <v>569.77</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.002206660449048492</v>
+        <v>-0.04090424948806892</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.008786674120350613</v>
+        <v>-0.005515461199322225</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.0874881606279283</v>
+        <v>-0.01031769851956543</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>-0.02080590075989186</v>
+        <v>0.02379025306343752</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.01639170734955742</v>
+        <v>0.04322917743455879</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4417247266857178</v>
+        <v>0.3810932890323571</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7092267091658355</v>
+        <v>0.7148516124647184</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.95299771075168</v>
+        <v>0.9252945190915358</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.9548151614259</v>
+        <v>2.952209951066851</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5814011980408651</v>
+        <v>0.5810538756338599</v>
       </c>
     </row>
     <row r="3">
@@ -648,51 +648,51 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>544.29</v>
+        <v>160.11</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.01721230590443379</v>
+        <v>0.003635691315067913</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.0006976791355054468</v>
+        <v>0.01290563162908298</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.1165609712687024</v>
+        <v>0.05418748658777806</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>-0.005190771535326544</v>
+        <v>0.03792302808137582</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>-0.03662597462027972</v>
+        <v>0.2553237014201422</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.5027122941071647</v>
+        <v>0.2760125590262437</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.7585618661923608</v>
+        <v>0.3960529224431304</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.9144535154519131</v>
+        <v>0.7829819284145849</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.586255529144814</v>
+        <v>1.078183955374269</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.3726415599825177</v>
+        <v>0.2761292479898172</v>
       </c>
     </row>
     <row r="4">
@@ -704,12 +704,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>118.18</v>
+        <v>517.74</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.03043727215563286</v>
+        <v>-0.05752363759469459</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.02391268566986571</v>
+        <v>-0.02333477100791426</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1066579201423372</v>
+        <v>-0.01486061790504767</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.03403621802858825</v>
+        <v>0.03508664249046967</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.3490867849739594</v>
+        <v>-0.02845685635460871</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5172679577768988</v>
+        <v>0.440657155471083</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.400937637017968</v>
+        <v>0.7493010396735191</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4347586391378604</v>
+        <v>0.8290293068528991</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.317869164743662</v>
+        <v>1.598944279188865</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3234157716570911</v>
+        <v>0.3748827279269076</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>14.29</v>
+        <v>72.45</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.02858166661757555</v>
+        <v>0.02882702118830904</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.03829937970971975</v>
+        <v>0.03885860578554046</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.06460503883984314</v>
+        <v>0.03796552694301969</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.09061063255104385</v>
+        <v>0.05643037348877811</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1032432365158735</v>
+        <v>0.300342422539678</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2434290676285413</v>
+        <v>0.264879793232532</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.6612789614797654</v>
+        <v>0.3952887933570957</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7573185118504884</v>
+        <v>0.583314992810515</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.675468032623519</v>
+        <v>0.7510938152027176</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3882465048958965</v>
+        <v>0.205322151248412</v>
       </c>
     </row>
     <row r="6">
@@ -816,12 +816,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>99.59999999999999</v>
+        <v>115.28</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.02544029894088773</v>
+        <v>-0.002422973219213698</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.01788451739692998</v>
+        <v>-0.02962966483197282</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.08461283336747982</v>
+        <v>0.01060751369956869</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.05140921508086338</v>
+        <v>0.03818441848712761</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.27214970370719</v>
+        <v>0.2633424523758561</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.4942238735723645</v>
+        <v>0.498505112725717</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3397633867595804</v>
+        <v>0.3997211484991237</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3960019641680483</v>
+        <v>0.3881001899155077</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.221987887698371</v>
+        <v>1.338200490047857</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3049100093449761</v>
+        <v>0.3272739857164206</v>
       </c>
     </row>
     <row r="7">
@@ -872,12 +872,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>157.41</v>
+        <v>35.98</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.003506330802101942</v>
+        <v>0.003346317061972526</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.000254232357903339</v>
+        <v>0.0221590557497402</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.07074355175756319</v>
+        <v>0.09341765871290764</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.01260859924313662</v>
+        <v>0.0969512310714542</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1684428674451059</v>
+        <v>0.2668902632722427</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2824720777607062</v>
+        <v>0.2145113119456794</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3865958298179029</v>
+        <v>0.3824377856966188</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.7654398431849179</v>
+        <v>0.5945374578329099</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.9793148987162206</v>
+        <v>0.7396886100221594</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2555623895359658</v>
+        <v>0.2026996189247852</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>70.98</v>
+        <v>97.44</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01428979639940131</v>
+        <v>-0.003579082430149816</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.006523067722131293</v>
+        <v>-0.02481981358071961</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.04290340733300746</v>
+        <v>-0.005105166301166197</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.05687908705370437</v>
+        <v>0.05500218490129938</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2070791853664002</v>
+        <v>0.2051878070435933</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2514247774409466</v>
+        <v>0.4817743344946215</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.4041424165671308</v>
+        <v>0.3377350316699388</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5572769562876529</v>
+        <v>0.3577773865504552</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6907127560116586</v>
+        <v>1.243970944607723</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1913058555213809</v>
+        <v>0.3091992356919617</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>28.42</v>
+        <v>13.82</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.02370321262763053</v>
+        <v>-0.01285716465541298</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.04178883287955726</v>
+        <v>0.002175470127206536</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.1295707571006663</v>
+        <v>-0.00647017638929992</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.1714756722244206</v>
+        <v>0.09162716124749637</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.3018781573806397</v>
+        <v>0.07548632564659497</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.448521858340776</v>
+        <v>0.1751700192048595</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2228915815917218</v>
+        <v>0.537263631443375</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.3163501563425128</v>
+        <v>0.710396017984787</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4231347548063611</v>
+        <v>1.592870523948319</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.124817354330691</v>
+        <v>0.3738108548949448</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>35.23</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.0002838290509100672</v>
+        <v>-0.02026559099245728</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.01293849277554671</v>
+        <v>-0.03408958988493294</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.08969989319320226</v>
+        <v>0.01881178558448626</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.07343083089035396</v>
+        <v>0.1665985204487019</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1976489060938356</v>
+        <v>0.04900172644567036</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2174311665377875</v>
+        <v>-0.009222426644827308</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.3629528389571743</v>
+        <v>0.4959824875645249</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5886917779864802</v>
+        <v>0.8828801045940886</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6435209658821086</v>
+        <v>1.524177874401354</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1801170442843902</v>
+        <v>0.3615700355542999</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>155.73</v>
+        <v>151.44</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.0008354088619826339</v>
+        <v>-0.02698533130758629</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.02111337837966287</v>
+        <v>-0.003159529576911124</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.07451875800420549</v>
+        <v>-0.0002640169478532739</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.04278826534313485</v>
+        <v>0.0495530493309726</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.06431423521401536</v>
+        <v>0.06374879474760764</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3208050864978083</v>
+        <v>0.290076832502</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4800650473755725</v>
+        <v>0.4819322182227799</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5794660091439812</v>
+        <v>0.5310628550836156</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.356429453010214</v>
+        <v>1.348112825095408</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3307142700775716</v>
+        <v>0.3291469127635811</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>421.33</v>
+        <v>27.75</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.02620741665513315</v>
+        <v>-0.004662810784784366</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.08511895512741763</v>
+        <v>-0.007510697115483023</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.0949039506389413</v>
+        <v>0.03854793088002517</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.09319940470888111</v>
+        <v>0.149544353837042</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.0455338478060292</v>
+        <v>0.2240846893078849</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1049249409408204</v>
+        <v>0.4311501224087011</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.4919701250244364</v>
+        <v>0.2289636888291624</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.7887702369085763</v>
+        <v>0.2562245273116952</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.2896308980675164</v>
+        <v>0.4400622387541164</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.08848339934974181</v>
+        <v>0.1292595035645194</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>85.7</v>
+        <v>203.56</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.00210477446493651</v>
+        <v>0.008072128668026313</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.02646827062779267</v>
+        <v>0.01912482207056132</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.08673594071710888</v>
+        <v>0.07052329262450385</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.08866864353786807</v>
+        <v>0.07272345832230021</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-0.0379142239171999</v>
+        <v>0.2411670694258603</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>-0.02216029949244547</v>
+        <v>0.1658122072144423</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4392069599844457</v>
+        <v>0.2251918881425872</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.8926345034144225</v>
+        <v>0.4747657185080141</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.401177922545565</v>
+        <v>0.636801453483236</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3390849032738834</v>
+        <v>0.178506550135203</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>180.49</v>
+        <v>185.35</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.007367345748221066</v>
+        <v>0.01090809890058497</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.08467555356669632</v>
+        <v>0.03913220371925408</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.01741832978011693</v>
+        <v>0.07792968533350364</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.0882725284948791</v>
+        <v>0.08914099236468731</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.07182741217943756</v>
+        <v>0.05702548623041137</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.231344858273878</v>
+        <v>0.2631341967609662</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.3688010699905064</v>
+        <v>0.4111338456682536</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.4756981737216881</v>
+        <v>0.5359293875216449</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.3110367399959213</v>
+        <v>0.3452460162345199</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.09447275270777022</v>
+        <v>0.1039106033414168</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>198.26</v>
+        <v>420.49</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.003418155857168981</v>
+        <v>-0.01432258739269221</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.00278179037121129</v>
+        <v>0.01249699637360346</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.06356950062726296</v>
+        <v>0.07226825648089008</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.05082947172821406</v>
+        <v>0.10950157278385</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1573447558606693</v>
+        <v>-0.07364738765518553</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1503345692653111</v>
+        <v>0.09186987153946302</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2098624919979049</v>
+        <v>0.5102857171042787</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.4479825125455659</v>
+        <v>0.7897600116800716</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.5568189994418264</v>
+        <v>0.307275271704325</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1589891608763236</v>
+        <v>0.09342504039417232</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>107.96</v>
+        <v>106.69</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.004976966963385676</v>
+        <v>-0.01486611786688619</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.01872384676830086</v>
+        <v>-0.02423627204353629</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.02351152492048203</v>
+        <v>-0.01695380409643588</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.06627159589602627</v>
+        <v>0.06455798385449008</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.01244054714734832</v>
+        <v>0.009079722443891436</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.09381968006631625</v>
+        <v>0.08150026144113354</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.3907936857396435</v>
+        <v>0.4029001279497719</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.5655113038381461</v>
+        <v>0.5600119588401711</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.7595234817904883</v>
+        <v>0.7667548207591359</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2072531734997181</v>
+        <v>0.2089047806087558</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>31.56</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.009416231596420799</v>
+        <v>-0.00697765757573543</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.03011682304893015</v>
+        <v>0.0005207774612521199</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.008951367428083667</v>
+        <v>-0.01271836986569364</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.02301455674856734</v>
+        <v>0.002086269756440329</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.2036613383840975</v>
+        <v>0.1380954097264506</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.07493183957275384</v>
+        <v>0.08921785075022592</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.279392693730635</v>
+        <v>0.3224258952719212</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2526967208876374</v>
+        <v>0.2710577618738432</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5712837279618026</v>
+        <v>0.8679243638543073</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1625675707035459</v>
+        <v>0.231552969107419</v>
       </c>
     </row>
     <row r="18">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>77.93000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.002315116465283262</v>
+        <v>-0.006473390096774945</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.02256923292698954</v>
+        <v>0.001276362716834845</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.02458589017362844</v>
+        <v>-0.009817735591519883</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.03906667073567704</v>
+        <v>0.00512529358343361</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1571561877031578</v>
+        <v>0.1362116957441557</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1060746257359479</v>
+        <v>0.09281808277902259</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.3022682125769913</v>
+        <v>0.2915740331129668</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2751251476180132</v>
+        <v>0.2450559668734342</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.8088845619678695</v>
+        <v>0.9661867609947368</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2184385115547343</v>
+        <v>0.2527803202824712</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>57.15</v>
+        <v>290.43</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.004040818066278096</v>
+        <v>-0.01505749148753399</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.0014018193706411</v>
+        <v>-0.006499483404911244</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.01365733315317597</v>
+        <v>0.02956501983821114</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.002279920502833654</v>
+        <v>0.1232160902235406</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1113738011111118</v>
+        <v>0.1036562285167177</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2396643814929893</v>
+        <v>0.04419042410974883</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2077640170159634</v>
+        <v>0.3008181088649442</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.3098622643002373</v>
+        <v>0.3455786213164014</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1315510530431763</v>
+        <v>1.472650451260571</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.04205678181883066</v>
+        <v>0.3522414435335148</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>111.47</v>
+        <v>56.48</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.007479265926013334</v>
+        <v>0.004088880750868107</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.008450426647530485</v>
+        <v>0.002484902187952942</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.02294209389735258</v>
+        <v>0.0003542411988661787</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.02756692060045063</v>
+        <v>-0.002824856093507466</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.09790039060665423</v>
+        <v>0.1093366873915174</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1019114933429084</v>
+        <v>0.2248664578990269</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.347170232680279</v>
+        <v>0.2039465761312247</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3210496102158449</v>
+        <v>0.237820513892349</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.3731333408456297</v>
+        <v>0.1553915292473569</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1114866158513359</v>
+        <v>0.04932429064823007</v>
       </c>
     </row>
     <row r="21">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>296.73</v>
+        <v>252.16</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01585075243432787</v>
+        <v>0.0038216828245623</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.03451530480606935</v>
+        <v>0.001032194410182763</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.1203278237460554</v>
+        <v>0.006024375832415219</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.1131828245200317</v>
+        <v>0.09287915889304776</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.09377087397512929</v>
+        <v>0.1457886184634014</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.09679080438402776</v>
+        <v>0.05068565335118302</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.3026925508607157</v>
+        <v>0.2453185703698038</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3748939037679513</v>
+        <v>0.2935366445970544</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1.47202068023828</v>
+        <v>1.248331342102369</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3521266308655093</v>
+        <v>0.310046682116025</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>71.67</v>
+        <v>30.74</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.003640869535116664</v>
+        <v>0.0118499216687431</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.02429608287242946</v>
+        <v>0.02262143437315145</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.02900210479271648</v>
+        <v>0.0748251524861856</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.04201802036842062</v>
+        <v>0.09629096888137689</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1550960385161122</v>
+        <v>-0.006554052875376026</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1134711934890489</v>
+        <v>0.1575834489962964</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.274053897058689</v>
+        <v>0.2986137124879005</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.2471737079378604</v>
+        <v>0.3892569594031905</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.9106328098003136</v>
+        <v>0.2710846034100303</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2408684537541106</v>
+        <v>0.08324032644870916</v>
       </c>
     </row>
     <row r="23">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>253.22</v>
+        <v>30.32</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.01413752551075897</v>
+        <v>-0.01717992480038533</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.009850453522245672</v>
+        <v>-0.04353315567514426</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.05658014416836799</v>
+        <v>-0.09221561947140178</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.0762953059135183</v>
+        <v>-0.004596171827194961</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.1289216274514127</v>
+        <v>0.186692782786652</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.07958545804894923</v>
+        <v>0.0006600811309331878</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.231243121798504</v>
+        <v>0.2652458330587368</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2985765057164664</v>
+        <v>0.1889670368629317</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>1.214322756217057</v>
+        <v>0.589617355739664</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.3034077763664058</v>
+        <v>0.1670716834605812</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>68.95</v>
+        <v>108.31</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.001158942959139653</v>
+        <v>-0.02097080134160934</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.02178413630973175</v>
+        <v>-0.01294090727146702</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.03110504136724401</v>
+        <v>-0.05082817475010737</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.05331496963918192</v>
+        <v>-0.0673383267008909</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.1594266226386121</v>
+        <v>0.06930100636138992</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1531785284089748</v>
+        <v>0.0440381552767235</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1963610949333312</v>
+        <v>0.3403840265485849</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1887834338245813</v>
+        <v>0.2898176835681896</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.6631833494208939</v>
+        <v>0.3852412427430851</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1848045395408686</v>
+        <v>0.1147439853383563</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>87.44</v>
+        <v>87.53</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.007941876027791284</v>
+        <v>-0.03516316576810474</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.002407418048734566</v>
+        <v>-0.03601326170217167</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.03003891000226311</v>
+        <v>0.1137549670185696</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.00205432891501256</v>
+        <v>0.2201003817356075</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.09235487425458344</v>
+        <v>-0.03265956873635811</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1001464246337416</v>
+        <v>-0.1279403625885658</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.233698134415397</v>
+        <v>0.3175839725309539</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.256959157427967</v>
+        <v>0.6449003921658587</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4165680804678447</v>
+        <v>2.6679924138275</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1230846303424595</v>
+        <v>0.5422074955923317</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>29.94</v>
+        <v>67.78</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.01491527234093626</v>
+        <v>-0.006595406060330933</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.05534013564966256</v>
+        <v>0.005488727148600825</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.02010221958839864</v>
+        <v>0.008180803137005421</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.08714595275039105</v>
+        <v>0.03181604902138413</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.002045241333242798</v>
+        <v>0.1420538833940521</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1376339895011602</v>
+        <v>0.105422212378617</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.2621967982854201</v>
+        <v>0.1863047357795784</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.32906513968907</v>
+        <v>0.162432259240008</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.236588621295782</v>
+        <v>0.6939586205160762</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.07335095898195876</v>
+        <v>0.1920677325228803</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>89.55</v>
+        <v>55.31</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.009810585741859335</v>
+        <v>0.01133667511703385</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.01186444126280017</v>
+        <v>0.01822543387795528</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.2142373295153601</v>
+        <v>0.0247049761551883</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.1856216668747503</v>
+        <v>0.04310150645993094</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.09493844770755866</v>
+        <v>0.0348655080993483</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.1177340927147937</v>
+        <v>0.1142983115049236</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.327070351643459</v>
+        <v>0.2526000471176872</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.6847379935933298</v>
+        <v>0.2465206149560792</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2.610430277234953</v>
+        <v>0.7227973718377614</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.5340975894225992</v>
+        <v>0.1987944772600587</v>
       </c>
     </row>
     <row r="28">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>117.14</v>
+        <v>113.63</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.01622280559591327</v>
+        <v>-0.03784929109616053</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.01209609082183283</v>
+        <v>-0.03564461098505889</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.163835048323667</v>
+        <v>0.05349524022265428</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.1218157579367405</v>
+        <v>0.1553634877108565</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.0309982871503458</v>
+        <v>0.004396596395755292</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>-0.00455935899784865</v>
+        <v>-0.02828423661679247</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.2787111694241451</v>
+        <v>0.2562630703364925</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.4584814452192709</v>
+        <v>0.441604961215099</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.28961643513672</v>
+        <v>1.258757233255333</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3180166946506007</v>
+        <v>0.3120685291591121</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>54.96</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.01122356260307922</v>
+        <v>-0.01305542136546767</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.03020850457373192</v>
+        <v>-0.009197551401267434</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.01233071181280643</v>
+        <v>-0.01900965507059471</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.04054507984048872</v>
+        <v>-0.0339647888173138</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.03957930884597838</v>
+        <v>0.07460411747884099</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.1126419720670175</v>
+        <v>0.05911137214352813</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.2404318849321641</v>
+        <v>0.2363531746839611</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2378592579151184</v>
+        <v>0.2309658983481357</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.7186350938961186</v>
+        <v>0.4360569671351422</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1978282696883629</v>
+        <v>0.1282115880179038</v>
       </c>
     </row>
     <row r="30">
@@ -2174,37 +2174,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>58.59</v>
+        <v>57.31</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.004801899720501934</v>
+        <v>-0.02417841273647725</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.001703841820769547</v>
+        <v>-0.02367971672201441</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.03956706029252155</v>
+        <v>-0.02167976131899696</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.03315113910185175</v>
+        <v>0.01793964742304333</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.03277745146526279</v>
+        <v>0.04916843640904189</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.0648175693387234</v>
+        <v>0.047828083210121</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.2574699395507958</v>
+        <v>0.2521148932389592</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2723625822594464</v>
+        <v>0.2526576760200443</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.8491255369925528</v>
+        <v>0.8693853091446995</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2274075737831289</v>
+        <v>0.2318739604486779</v>
       </c>
     </row>
     <row r="31">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2230,37 +2230,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>75.23</v>
+        <v>88.95</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.007634605771034808</v>
+        <v>-0.0319948031443501</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.01648427490189053</v>
+        <v>-0.01298275369154067</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.08682464649296961</v>
+        <v>0.1415554291387655</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.05099191719069451</v>
+        <v>0.2471957000680891</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.1310707883350345</v>
+        <v>0.0207711449537693</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.03924886078927092</v>
+        <v>-0.1327028172224362</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1879967419852169</v>
+        <v>0.1846624177881846</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.6708988106605565</v>
+        <v>0.5421001659441715</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2950530666495053</v>
+        <v>2.356515237730709</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.09000675209730469</v>
+        <v>0.4972565019055328</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>133.4</v>
+        <v>74.02</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.0005245172966095168</v>
+        <v>-0.02911858975481563</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.0180346860283862</v>
+        <v>-0.001214464533044191</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.01207142781269444</v>
+        <v>0.03250096418345794</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.009535299777931217</v>
+        <v>0.08248025177226115</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.1376207888196332</v>
+        <v>-0.1046828048547082</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.1071854004799808</v>
+        <v>0.00674685817993903</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.09717071206833539</v>
+        <v>0.1922591229439197</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.124953949922479</v>
+        <v>0.6113283522287294</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.6936870963932948</v>
+        <v>0.3348366261173399</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.19200403705891</v>
+        <v>0.1010559078879396</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>145.75</v>
+        <v>183.76</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.001924787082884905</v>
+        <v>-0.02875265607374411</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01573475015021275</v>
+        <v>-0.01952835181873258</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.009581432638088638</v>
+        <v>-0.01606339734546414</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.002682989735903085</v>
+        <v>0.03323018386561349</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.1141373939239974</v>
+        <v>-0.02493746404612784</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.1033622388388482</v>
+        <v>0.05655083459294974</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1160803368943923</v>
+        <v>0.2429494540490698</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1328896676160121</v>
+        <v>0.2878242178936732</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.6989225872668208</v>
+        <v>0.9516545209159293</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1932310064893175</v>
+        <v>0.2496862190351938</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>291.38</v>
+        <v>144.99</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.01310751944856059</v>
+        <v>0.007644771062489619</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.006911327549427249</v>
+        <v>-0.0056919612492492</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.06037336082828704</v>
+        <v>-0.0163499898447268</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.05794782759774186</v>
+        <v>-0.007597539794523378</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.08610409351656156</v>
+        <v>0.08001047496153446</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.231061734240106</v>
+        <v>0.090716905571675</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.08186989718885429</v>
+        <v>0.1187162706761535</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0745685239254501</v>
+        <v>0.1394841632931274</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.7573126420187357</v>
+        <v>0.7097723563981881</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.206747324042418</v>
+        <v>0.1957657146515595</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>187.87</v>
+        <v>132.46</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.001806554298659613</v>
+        <v>0.006382097157288102</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.007724092141710992</v>
+        <v>-0.01348028227451981</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.04750481585573185</v>
+        <v>-0.01852400619170336</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.02264432121979931</v>
+        <v>-0.007715924315769285</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.04409912349568212</v>
+        <v>0.09375012993237464</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.07605573387978715</v>
+        <v>0.08735068638792964</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.2386292015036688</v>
+        <v>0.09475007571342275</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.3167192491771473</v>
+        <v>0.1327532140990466</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.9405794621888182</v>
+        <v>0.704911384230928</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.2473178676493513</v>
+        <v>0.1946314308883854</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>89.97</v>
+        <v>61.13</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.01925914401595552</v>
+        <v>-0.01577845005000689</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.0008899970141049707</v>
+        <v>-0.00130694359669925</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.2141700819619385</v>
+        <v>-0.008273821002322213</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.2015224962711435</v>
+        <v>-0.004559498127220341</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.04236291492091981</v>
+        <v>0.01845215938172151</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>-0.1344044727012431</v>
+        <v>0.03430674747473694</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.1899084069398547</v>
+        <v>0.2040964274209927</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.5705966851321735</v>
+        <v>0.2157261304073723</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>2.219097928764253</v>
+        <v>0.6795184200464841</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.4765383439015742</v>
+        <v>0.1886707894726596</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>95.41</v>
+        <v>190.4</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.00262715416539594</v>
+        <v>-0.0031413932121237</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.01231878706841305</v>
+        <v>0.01287370052105374</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.007283289395451309</v>
+        <v>0.007407375113673842</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.005316873608959827</v>
+        <v>0.01077665674957418</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.05167862998994366</v>
+        <v>0.06666863848774773</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.07742728672366161</v>
+        <v>0.1086881036984069</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1497681722522</v>
+        <v>0.136569149977839</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1971306573287468</v>
+        <v>0.1074852472029861</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.4435174528229471</v>
+        <v>1.127319830701671</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1301619453132836</v>
+        <v>0.2861084634609588</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>20.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.00196458776913655</v>
+        <v>-0.002008614223147132</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.02076552391816078</v>
+        <v>0.01472646205050698</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0.05480865861319772</v>
+        <v>-0.01379021811523673</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.1162790721946345</v>
+        <v>-0.03486347119753341</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.2168207790765724</v>
+        <v>0.04963588233372929</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.1846001290985122</v>
+        <v>0.06770052396139659</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>-0.04342120349887479</v>
+        <v>0.1331635034663372</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>-0.05520560798683727</v>
+        <v>0.1848941756861824</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.11391507147122</v>
+        <v>0.4633474726110136</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.03661469246477655</v>
+        <v>0.1353135484421581</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>104.08</v>
+        <v>20.07</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.0207000091598678</v>
+        <v>-0.001045239602903925</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.01353587843608772</v>
+        <v>-0.006927233844161829</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.1004440665688457</v>
+        <v>0.007631310012824244</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.1116095790257565</v>
+        <v>0.09283963762348812</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.1484942211907101</v>
+        <v>0.2053330620822484</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.2576963056829229</v>
+        <v>0.1512647877501678</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>-0.03109163410450311</v>
+        <v>-0.0227394919600572</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>-0.03914048480321919</v>
+        <v>-0.07404842439357751</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.5068541449227082</v>
+        <v>0.1530129941141052</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.1464551574243782</v>
+        <v>0.04860373567373588</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>191.17</v>
+        <v>283.76</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.004374753199947179</v>
+        <v>-0.01108243064307712</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.01551127845389266</v>
+        <v>-0.02256204694310171</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0.02636102119035111</v>
+        <v>-0.01499575467925451</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.0118881637320819</v>
+        <v>0.05189798151387826</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.066809600311174</v>
+        <v>0.04940834382657266</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.1369081059890751</v>
+        <v>0.1892707565251146</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1138930913027458</v>
+        <v>0.0736285390519944</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.09658321815512561</v>
+        <v>0.03804516012351722</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.089480546684821</v>
+        <v>0.7736108508212365</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2784373318446405</v>
+        <v>0.2104665120119886</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>61.84</v>
+        <v>231.6</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.007330196569693026</v>
+        <v>-0.01211395797780046</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.01161457667376009</v>
+        <v>-0.02750362360208924</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.02096748331125053</v>
+        <v>0.001990164900414815</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.002902294483186352</v>
+        <v>0.03573187903651465</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.00279584267714017</v>
+        <v>0.02596378579493108</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.03125610303028381</v>
+        <v>-0.03279760017715105</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.2035777422773202</v>
+        <v>0.2153075797975728</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.2167678739357963</v>
+        <v>0.1604833402043191</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.66234357128457</v>
+        <v>0.3691782713798879</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1846050946116091</v>
+        <v>0.1104184422919574</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>24.32</v>
+        <v>97.62</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.002461011813279179</v>
+        <v>-0.003674225331878223</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.01333332061767578</v>
+        <v>0.0128657971415338</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.02486304947194662</v>
+        <v>-0.01314188684216333</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0.0004113627766979544</v>
+        <v>-0.02399514074219622</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.0800324503850236</v>
+        <v>0.03652691904019556</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.05748442346802785</v>
+        <v>0.05471198556486367</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.2211822670477956</v>
+        <v>0.1258977308784577</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.3380234749134581</v>
+        <v>0.1404864822225282</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.5619851582619528</v>
+        <v>0.366679120881938</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1602697446071226</v>
+        <v>0.1097424180825985</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>98.83</v>
+        <v>24.07</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.002536011314226316</v>
+        <v>-0.01109287001113535</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.004063817176051199</v>
+        <v>0.006270887042301165</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.001212684395030972</v>
+        <v>0.006270887042301165</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0.01291382740772229</v>
+        <v>0.001247869307588134</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.04596190841466741</v>
+        <v>-0.0741338575080478</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.06530178563939026</v>
+        <v>0.02225340740011084</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1350185150234462</v>
+        <v>0.2370237900123824</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1513855321719377</v>
+        <v>0.2756846325718179</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.3445072479081215</v>
+        <v>0.5961786662012056</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1037084882602277</v>
+        <v>0.1686752156935332</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>88.95</v>
+        <v>101.96</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.003807861617190711</v>
+        <v>-0.0002941345222592373</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.02059020868603467</v>
+        <v>-0.01886065357012645</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.009244841193360331</v>
+        <v>-0.0003921658385033222</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>0.01332875581243753</v>
+        <v>0.09870685055480011</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.1090062441476574</v>
+        <v>0.0980845701139037</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.01756439913112762</v>
+        <v>0.2436477800952532</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1190792393659745</v>
+        <v>-0.02328216371330638</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.07062297373180471</v>
+        <v>-0.06791782618096098</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.3948478634895944</v>
+        <v>0.5188121487688213</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1173149604425678</v>
+        <v>0.1494798274506262</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>235.48</v>
+        <v>87.13</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.006884169170760179</v>
+        <v>-0.004683615008240771</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.003933877247849216</v>
+        <v>-0.02789244758015053</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.05658007307677781</v>
+        <v>-0.05652410727614587</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0.04319319622797702</v>
+        <v>-0.02560949409997459</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.01058525397406229</v>
+        <v>0.09709767724069773</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.01769376488544872</v>
+        <v>-0.005746060699769018</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.2161038148867669</v>
+        <v>0.11499011717337</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.1726306199379812</v>
+        <v>0.04162779667818928</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.356013761164383</v>
+        <v>0.3934950521561476</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1068481213993173</v>
+        <v>0.1169536294570297</v>
       </c>
     </row>
     <row r="46">
@@ -3070,37 +3070,37 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>74.84</v>
+        <v>74.44</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.005508478181295073</v>
+        <v>0.01086370258539504</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.005238407060238925</v>
+        <v>0.004588447696175058</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.001605930342975626</v>
+        <v>-0.002278490384058918</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.02394308506884935</v>
+        <v>-0.004546621335125733</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.03827851217127076</v>
+        <v>0.02720292758624687</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.002591785716972939</v>
+        <v>0.001323158705051064</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.124195941014893</v>
+        <v>0.1147421189148898</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.09953649760503391</v>
+        <v>0.0897638372196401</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.2076744367997028</v>
+        <v>0.2288020005405369</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.06491911978069842</v>
+        <v>0.07109330139320158</v>
       </c>
     </row>
     <row r="47">
@@ -3138,25 +3138,25 @@
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.01831484378483172</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.02082380059436528</v>
+        <v>0.02694026455734577</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.1822744791212605</v>
+        <v>0.1710899905045671</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>-0.01137043191827602</v>
+        <v>0.01338908028529628</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.03605019350016947</v>
+        <v>-0.0414184240916381</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.7809937997512078</v>
+        <v>0.854123692916507</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.2121437759793303</v>
+        <v>0.228512466375254</v>
       </c>
     </row>
     <row r="48">
@@ -3182,37 +3182,37 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>13.37</v>
+        <v>13.22</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.01255539710287268</v>
+        <v>0.003034898401126807</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.002982845809707202</v>
+        <v>-0.01047899650045769</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.07822583039270925</v>
+        <v>0.02006174599664678</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0.06449040118480354</v>
+        <v>0.03930817527543895</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.07895963973984221</v>
+        <v>0.07622791458668687</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.05517815471448317</v>
+        <v>0.04178738156037065</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.03069357316529486</v>
+        <v>0.04048471774524964</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.0698954653670355</v>
+        <v>-0.0710933626498339</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1818284279947984</v>
+        <v>0.1858759694790073</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.0572673257755727</v>
+        <v>0.05847293149296329</v>
       </c>
     </row>
     <row r="49">
@@ -3238,37 +3238,37 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>72.36</v>
+        <v>70.86</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.0004144050220998841</v>
+        <v>-0.003935883914803928</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.01617950227097653</v>
+        <v>-0.02369800464743432</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.005698452807500587</v>
+        <v>-0.03394680184823773</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.06788663413665286</v>
+        <v>0.02413640858532351</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.08779832427787637</v>
+        <v>0.09442677634153496</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.1127942168862237</v>
+        <v>-0.1137448170443988</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.06441155790935005</v>
+        <v>0.06732870015615022</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.007290436709227133</v>
+        <v>-0.01933225669699301</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.03602311976075834</v>
+        <v>0.03704840956154554</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.0118663396048142</v>
+        <v>0.01220002398244024</v>
       </c>
     </row>
     <row r="50">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -3294,37 +3294,37 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>19.57</v>
+        <v>105.95</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.01683551004303996</v>
+        <v>-0.02070436678636001</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0.02670518323506554</v>
+        <v>-0.03943795088994151</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0.02353683640098003</v>
+        <v>-0.03339114717388048</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0.008711372625436864</v>
+        <v>-0.02124714135573036</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.06295493787803785</v>
+        <v>0.1005381567282113</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.1350928366556123</v>
+        <v>-0.1100916843286661</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.007099014073266963</v>
+        <v>0.06489610822418479</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.1535985043633872</v>
+        <v>-0.05642559552990001</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.1710373535388929</v>
+        <v>0.3618830617101083</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.05403957232507151</v>
+        <v>0.1084427644657147</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>109.02</v>
+        <v>48.07</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.004656278114803292</v>
+        <v>0.00606950445660126</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.0160650393471552</v>
+        <v>0.0182164928411197</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.05140316400968414</v>
+        <v>0.005438157583455894</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>0.007951118267743862</v>
+        <v>-0.01110884403923151</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>0.0907914997848871</v>
+        <v>-0.006736959525904695</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.09766096062832919</v>
+        <v>-0.03279776675414114</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.06170921921053307</v>
+        <v>0.1006885951955736</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>-0.03352670957318238</v>
+        <v>0.02027793635933106</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.3320393086449767</v>
+        <v>0.1294704174714085</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1002862364320252</v>
+        <v>0.04141769719003374</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>18.21</v>
+        <v>44.02</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.008170017477795333</v>
+        <v>-0.003621544733067084</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.004918041330057799</v>
+        <v>0.008938789367425537</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>0.03760683054722769</v>
+        <v>-0.002040357092327305</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.04509704373959555</v>
+        <v>-0.02545932605266898</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.1749265324482228</v>
+        <v>0.008217799065870501</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.008747308580336233</v>
+        <v>-0.02190711338493512</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.08113588931454596</v>
+        <v>0.007510241357272296</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.3470668833309982</v>
+        <v>0.06152653821175003</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.1306764707031811</v>
+        <v>0.5175768174713919</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.04178824205455767</v>
+        <v>0.1491680984093846</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>48.04</v>
+        <v>96.28</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.0002082476886253737</v>
+        <v>-0.01594437466254894</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>0.01307471047074116</v>
+        <v>-0.04199006189754351</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.006916827444712448</v>
+        <v>-0.0322645406914982</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.001869938719937236</v>
+        <v>-0.01078807183812047</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.00345594323241516</v>
+        <v>0.1020243989765355</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.04712009796503425</v>
+        <v>-0.1380675234894067</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.09701407832344122</v>
+        <v>0.03169687715701386</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.02565698449273235</v>
+        <v>-0.1117494386323167</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.1189501588453845</v>
+        <v>0.1866339163188619</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.03817423714626678</v>
+        <v>0.05869838940292271</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>55.76</v>
+        <v>19.17</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.006237788005901135</v>
+        <v>-0.01520675698213059</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.02537692582406192</v>
+        <v>-0.002705376617242239</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>0.06189297474548283</v>
+        <v>-0.004724797621498689</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.132872753730839</v>
+        <v>-0.0005214155292919687</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.1452896847410137</v>
+        <v>0.03571435196416317</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.03625527575134335</v>
+        <v>0.07691019366447338</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1021700090740284</v>
+        <v>0.003054151734082744</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.09075488719709224</v>
+        <v>-0.1763512673480198</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.05914362332405099</v>
+        <v>0.1921619923400917</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.01933816585261061</v>
+        <v>0.0603398673844624</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>44.31</v>
+        <v>55.44</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.006130800457555763</v>
+        <v>0.006535889318931121</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0.01605138163592001</v>
+        <v>-0.009646318684227939</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.0009018512335106088</v>
+        <v>0.02457952321854129</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.03020348642801807</v>
+        <v>0.09760444405071467</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.006838735030247345</v>
+        <v>0.1153844441797525</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.03430737565594488</v>
+        <v>-0.06531829603270711</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.01940347051404068</v>
+        <v>-0.09995574485752268</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.06080485488319431</v>
+        <v>-0.09655974710347048</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.5139823339199088</v>
+        <v>0.09126572218663087</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.1482600869593322</v>
+        <v>0.02954066368961006</v>
       </c>
     </row>
     <row r="56">
@@ -3630,37 +3630,37 @@
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>37.74</v>
+        <v>36.55</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.00211523048659279</v>
+        <v>-0.03358012871527005</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.003456555862949129</v>
+        <v>-0.02481324217007419</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.07155026605400461</v>
+        <v>-0.01455920499611174</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.05183948035064168</v>
+        <v>0.06249993069227666</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.0817393917731184</v>
+        <v>-0.08189113486930832</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.01515711840146161</v>
+        <v>-0.04670813858135725</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.07885958369319623</v>
+        <v>0.08979745503661052</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.1183106258960303</v>
+        <v>0.07796226161212538</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.4318693310678108</v>
+        <v>0.4505463944175534</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.1271138740563336</v>
+        <v>0.13199334757459</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>98.78</v>
+        <v>17.74</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.00753541654976897</v>
+        <v>-0.02043074692233349</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.02333399866119745</v>
+        <v>-0.02527477871088812</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.04706383945048942</v>
+        <v>-0.03796099472158865</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.01698755865887613</v>
+        <v>-0.03429510284886439</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>0.106241755920742</v>
+        <v>-0.1660752929581728</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.1271328284836151</v>
+        <v>-0.06528570340326822</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.02251625252414935</v>
+        <v>0.079879840341331</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.09193159405018547</v>
+        <v>0.2371295184843467</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.1561785441605237</v>
+        <v>0.1629179611776732</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.04956249169817051</v>
+        <v>0.05159785780106207</v>
       </c>
     </row>
     <row r="58">
@@ -3742,37 +3742,37 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>112.95</v>
+        <v>110.48</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.003553921684928074</v>
+        <v>-0.00306800522312678</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>0.01528087144487356</v>
+        <v>-0.007099787094152266</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>0.04351440481734525</v>
+        <v>-0.0139235768104814</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.01345895057042124</v>
+        <v>-0.001536359390881259</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.03301310064204388</v>
+        <v>-0.05310809154870544</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.008507453850260749</v>
+        <v>-0.0302740623649167</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.02374024186537449</v>
+        <v>-0.002945684948866378</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.02851151944584274</v>
+        <v>0.009651798286270719</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.7280281235909403</v>
+        <v>0.756488336977412</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.200006510055178</v>
+        <v>0.2065586109941799</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>51.97</v>
+        <v>45.05</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.009529254590577629</v>
+        <v>-0.004639838538675889</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.01478670671652849</v>
+        <v>-0.0103251585232127</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0.05351711517647817</v>
+        <v>-0.02615648785939151</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.05731906015216304</v>
+        <v>-0.0146544611932159</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.1998459790211022</v>
+        <v>-0.0174481845950788</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.1027278511108857</v>
+        <v>-0.1031256291535526</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.04968699217466943</v>
+        <v>0.003861986165770936</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.4191699272676173</v>
+        <v>0.003435079770780503</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>-0.1571203978224349</v>
+        <v>0.3094616737878297</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>-0.0553842525324878</v>
+        <v>0.09403428092371424</v>
       </c>
     </row>
     <row r="60">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>26.76</v>
+        <v>26</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.01291037895941927</v>
+        <v>-0.01272067955643763</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>0.02828158839103079</v>
+        <v>-0.002110930897393115</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>0.0465389342299638</v>
+        <v>-0.02760119850941756</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.0498234785864009</v>
+        <v>0.02929531925625484</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>0.05536584474193385</v>
+        <v>0.04577300656609307</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>0.1494979796452061</v>
+        <v>0.09043241604886898</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.1064804232815015</v>
+        <v>-0.0989469075241024</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1887067671016402</v>
+        <v>-0.2195222944341353</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2084527758041173</v>
+        <v>0.2580784879602664</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.0651478486663144</v>
+        <v>0.07953297364369294</v>
       </c>
     </row>
     <row r="61">
@@ -3896,51 +3896,51 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>45.49</v>
+        <v>43.62</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.003504925346418775</v>
+        <v>-0.03602212305227037</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.01600687586192728</v>
+        <v>-0.03431479521569214</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.01173141679666856</v>
+        <v>0.02659442713062155</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.003308370652273629</v>
+        <v>0.1262586999082129</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.02757582587627139</v>
+        <v>-0.1039441524562403</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.09813634185194176</v>
+        <v>-0.1768258624228287</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.001522995646940251</v>
+        <v>0.04510131195175404</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.01151488059390049</v>
+        <v>0.1658744950090483</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.296260432782828</v>
+        <v>1.226326884745589</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.09034538132845471</v>
+        <v>0.3057588467310177</v>
       </c>
     </row>
     <row r="62">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>44.93</v>
+        <v>49.87</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.007071816460203717</v>
+        <v>-0.02062056706241033</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>0.000445345309098677</v>
+        <v>-0.05370022372077166</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>0.149987219250679</v>
+        <v>-0.06557991512173333</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0.0813478009669959</v>
+        <v>-0.07476813506321001</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.1441904703776041</v>
+        <v>-0.2034818967300959</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1344634860865696</v>
+        <v>-0.1747476637425495</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.05195124173176158</v>
+        <v>0.03421811840339029</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.2061187990351565</v>
+        <v>0.1962101361148811</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>1.265852253943098</v>
+        <v>-0.120100907802734</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>0.3134408801652884</v>
+        <v>-0.0417526581428419</v>
       </c>
     </row>
   </sheetData>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -4158,17 +4158,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.2015224962711435</v>
+        <v>0.2471957000680891</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.05731906015216304</v>
+        <v>-0.07476813506321001</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1856216668747503</v>
+        <v>0.2201003817356075</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4669,21 +4669,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.04509704373959555</v>
+        <v>-0.0673383267008909</v>
       </c>
     </row>
     <row r="19">
@@ -4692,21 +4692,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1714756722244206</v>
+        <v>0.1665985204487019</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.03020348642801807</v>
+        <v>-0.03486347119753341</v>
       </c>
     </row>
     <row r="20">
@@ -4737,21 +4737,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.132872753730839</v>
+        <v>0.1553634877108565</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.02756692060045063</v>
+        <v>-0.03429510284886439</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1218157579367405</v>
+        <v>0.149544353837042</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.02080590075989186</v>
+        <v>-0.0339647888173138</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1162790721946345</v>
+        <v>0.1262586999082129</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.01831484378483172</v>
+        <v>-0.02560949409997459</v>
       </c>
     </row>
     <row r="23">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1131828245200317</v>
+        <v>0.1232160902235406</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.0118881637320819</v>
+        <v>-0.02545932605266898</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.1116095790257565</v>
+        <v>0.10950157278385</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.005316873608959827</v>
+        <v>-0.02399514074219622</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.09319940470888111</v>
+        <v>0.09870685055480011</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.005190771535326544</v>
+        <v>-0.02124714135573036</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.09061063255104385</v>
+        <v>0.09760444405071467</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.002902294483186352</v>
+        <v>-0.0146544611932159</v>
       </c>
     </row>
     <row r="27"/>
@@ -5113,21 +5113,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3490867849739594</v>
+        <v>0.300342422539678</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1998459790211022</v>
+        <v>-0.2034818967300959</v>
       </c>
     </row>
     <row r="32">
@@ -5158,21 +5158,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.3018781573806397</v>
+        <v>0.2668902632722427</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1749265324482228</v>
+        <v>-0.1660752929581728</v>
       </c>
     </row>
     <row r="33">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.27214970370719</v>
+        <v>0.2633424523758561</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5225,21 +5225,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1441904703776041</v>
+        <v>-0.1046828048547082</v>
       </c>
     </row>
     <row r="34">
@@ -5248,21 +5248,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2168207790765724</v>
+        <v>0.2553237014201422</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1310707883350345</v>
+        <v>-0.1039441524562403</v>
       </c>
     </row>
     <row r="35">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2070791853664002</v>
+        <v>0.2411670694258603</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.09493844770755866</v>
+        <v>-0.08189113486930832</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2036613383840975</v>
+        <v>0.2240846893078849</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.0817393917731184</v>
+        <v>-0.0741338575080478</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1976489060938356</v>
+        <v>0.2053330620822484</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.0800324503850236</v>
+        <v>-0.07364738765518553</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1684428674451059</v>
+        <v>0.2051878070435933</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.0455338478060292</v>
+        <v>-0.05310809154870544</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1594266226386121</v>
+        <v>0.186692782786652</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.04409912349568212</v>
+        <v>-0.03265956873635811</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1573447558606693</v>
+        <v>0.1457886184634014</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.04236291492091981</v>
+        <v>-0.02845685635460871</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5172679577768988</v>
+        <v>0.498505112725717</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1344634860865696</v>
+        <v>-0.1768258624228287</v>
       </c>
     </row>
     <row r="46">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5027122941071647</v>
+        <v>0.4817743344946215</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5691,21 +5691,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1344044727012431</v>
+        <v>-0.1747476637425495</v>
       </c>
     </row>
     <row r="47">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4942238735723645</v>
+        <v>0.440657155471083</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1271328284836151</v>
+        <v>-0.1380675234894067</v>
       </c>
     </row>
     <row r="48">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.448521858340776</v>
+        <v>0.4311501224087011</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1177340927147937</v>
+        <v>-0.1327028172224362</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4417247266857178</v>
+        <v>0.3810932890323571</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.1127942168862237</v>
+        <v>-0.1279403625885658</v>
       </c>
     </row>
     <row r="50">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3208050864978083</v>
+        <v>0.290076832502</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.1027278511108857</v>
+        <v>-0.1137448170443988</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2824720777607062</v>
+        <v>0.2760125590262437</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.09813634185194176</v>
+        <v>-0.1100916843286661</v>
       </c>
     </row>
     <row r="52">
@@ -5939,21 +5939,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2576963056829229</v>
+        <v>0.264879793232532</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.09766096062832919</v>
+        <v>-0.1031256291535526</v>
       </c>
     </row>
     <row r="53">
@@ -5984,21 +5984,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2514247774409466</v>
+        <v>0.2631341967609662</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.04712009796503425</v>
+        <v>-0.06531829603270711</v>
       </c>
     </row>
     <row r="54">
@@ -6029,21 +6029,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2434290676285413</v>
+        <v>0.2436477800952532</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.03625527575134335</v>
+        <v>-0.06528570340326822</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.95299771075168</v>
+        <v>0.9252945190915358</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1887067671016402</v>
+        <v>-0.2195222944341353</v>
       </c>
     </row>
     <row r="60">
@@ -6180,21 +6180,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.9144535154519131</v>
+        <v>0.8828801045940886</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1535985043633872</v>
+        <v>-0.1763512673480198</v>
       </c>
     </row>
     <row r="61">
@@ -6225,21 +6225,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.8926345034144225</v>
+        <v>0.8290293068528991</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.09193159405018547</v>
+        <v>-0.1117494386323167</v>
       </c>
     </row>
     <row r="62">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.7887702369085763</v>
+        <v>0.7897600116800716</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09075488719709224</v>
+        <v>-0.09655974710347048</v>
       </c>
     </row>
     <row r="63">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.7654398431849179</v>
+        <v>0.7829819284145849</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6337,21 +6337,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.0698954653670355</v>
+        <v>-0.07404842439357751</v>
       </c>
     </row>
     <row r="64">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.7573185118504884</v>
+        <v>0.710396017984787</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6382,21 +6382,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.05520560798683727</v>
+        <v>-0.0710933626498339</v>
       </c>
     </row>
     <row r="65">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.6847379935933298</v>
+        <v>0.6449003921658587</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.03914048480321919</v>
+        <v>-0.06791782618096098</v>
       </c>
     </row>
     <row r="66">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.6708988106605565</v>
+        <v>0.6113283522287294</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.03605019350016947</v>
+        <v>-0.05642559552990001</v>
       </c>
     </row>
     <row r="67">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5886917779864802</v>
+        <v>0.5945374578329099</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.03352670957318238</v>
+        <v>-0.0414184240916381</v>
       </c>
     </row>
     <row r="68">
@@ -6540,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.5794660091439812</v>
+        <v>0.583314992810515</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.007290436709227133</v>
+        <v>-0.01933225669699301</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.9548151614259</v>
+        <v>2.952209951066851</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1571203978224349</v>
+        <v>-0.120100907802734</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.610430277234953</v>
+        <v>2.6679924138275</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.03602311976075834</v>
+        <v>0.03704840956154554</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.219097928764253</v>
+        <v>2.356515237730709</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.05914362332405099</v>
+        <v>0.09126572218663087</v>
       </c>
     </row>
     <row r="76">
@@ -6781,21 +6781,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.675468032623519</v>
+        <v>1.598944279188865</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6803,21 +6803,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.11391507147122</v>
+        <v>0.1294704174714085</v>
       </c>
     </row>
     <row r="77">
@@ -6826,21 +6826,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.586255529144814</v>
+        <v>1.592870523948319</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6848,21 +6848,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1189501588453845</v>
+        <v>0.1530129941141052</v>
       </c>
     </row>
     <row r="78">
@@ -6871,21 +6871,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.47202068023828</v>
+        <v>1.524177874401354</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6893,21 +6893,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1306764707031811</v>
+        <v>0.1553915292473569</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.401177922545565</v>
+        <v>1.472650451260571</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6938,21 +6938,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1315510530431763</v>
+        <v>0.1629179611776732</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.356429453010214</v>
+        <v>1.348112825095408</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6983,21 +6983,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1561785441605237</v>
+        <v>0.1858759694790073</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.317869164743662</v>
+        <v>1.338200490047857</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1710373535388929</v>
+        <v>0.1866339163188619</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.28961643513672</v>
+        <v>1.258757233255333</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,21 +7073,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1818284279947984</v>
+        <v>0.1921619923400917</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -489,16 +489,16 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,51 +592,51 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>569.77</v>
+        <v>40.75</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.04090424948806892</v>
+        <v>0.132573666438329</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.005515461199322225</v>
+        <v>0.150480014302423</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.01031769851956543</v>
+        <v>0.2222555432962989</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.02379025306343752</v>
+        <v>0.2423780776786357</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.04322917743455879</v>
+        <v>0.4424329800493492</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.3810932890323571</v>
+        <v>0.3640608026842034</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7148516124647184</v>
+        <v>0.5868382230935685</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9252945190915358</v>
+        <v>0.8253919472093372</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.952209951066851</v>
+        <v>0.9703256892236471</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5810538756338599</v>
+        <v>0.2536587606951883</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>160.11</v>
+        <v>169.55</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.003635691315067913</v>
+        <v>0.05895948039110754</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.01290563162908298</v>
+        <v>0.06374304348462911</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.05418748658777806</v>
+        <v>0.1080975696929585</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.03792302808137582</v>
+        <v>0.09911843050301883</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2553237014201422</v>
+        <v>0.3385632443461823</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2760125590262437</v>
+        <v>0.3390913855539368</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.3960529224431304</v>
+        <v>0.4871433821649793</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7829819284145849</v>
+        <v>0.9180855858616215</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.078183955374269</v>
+        <v>1.200712819471255</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2761292479898172</v>
+        <v>0.3007318993964418</v>
       </c>
     </row>
     <row r="4">
@@ -704,12 +704,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>517.74</v>
+        <v>560.92</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.05752363759469459</v>
+        <v>-0.01553264706411661</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.02333477100791426</v>
+        <v>-0.04088373284713664</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.01486061790504767</v>
+        <v>-0.01541167124582099</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.03508664249046967</v>
+        <v>0.007888080394920616</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.02845685635460871</v>
+        <v>0.03117869007357399</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.440657155471083</v>
+        <v>0.3674304393415166</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.7493010396735191</v>
+        <v>0.6576282247146263</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.8290293068528991</v>
+        <v>0.9344220059162276</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.598944279188865</v>
+        <v>2.890821256959017</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3748827279269076</v>
+        <v>0.5728250832963251</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>72.45</v>
+        <v>74.06</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.02882702118830904</v>
+        <v>0.02222223158272496</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.03885860578554046</v>
+        <v>0.06087953228236165</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.03796552694301969</v>
+        <v>0.05769781646979544</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.05643037348877811</v>
+        <v>0.0799066138994704</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.300342422539678</v>
+        <v>0.3282862101180786</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.264879793232532</v>
+        <v>0.2920878786065719</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3952887933570957</v>
+        <v>0.4254751318468664</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.583314992810515</v>
+        <v>0.6223751306026259</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.7510938152027176</v>
+        <v>0.7900071925259688</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.205322151248412</v>
+        <v>0.2141851734428959</v>
       </c>
     </row>
     <row r="6">
@@ -816,12 +816,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>115.28</v>
+        <v>503.3</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.002422973219213698</v>
+        <v>-0.0278904521840575</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.02962966483197282</v>
+        <v>-0.06829081338364629</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.01060751369956869</v>
+        <v>-0.01145093990519308</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.03818441848712761</v>
+        <v>0.006217607981732431</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2633424523758561</v>
+        <v>-0.06082129291944049</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.498505112725717</v>
+        <v>0.4199375101703102</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3997211484991237</v>
+        <v>0.6826877811046268</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3881001899155077</v>
+        <v>0.8298846855807211</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.338200490047857</v>
+        <v>1.526458741557412</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3272739857164206</v>
+        <v>0.3619800205864627</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>35.98</v>
+        <v>14</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.003346317061972526</v>
+        <v>0.01337918146863082</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.0221590557497402</v>
+        <v>0.02449889542608874</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.09341765871290764</v>
+        <v>0.002498189759613245</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.0969512310714542</v>
+        <v>0.106232239133913</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2668902632722427</v>
+        <v>0.107106751064459</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2145113119456794</v>
+        <v>0.2011063603698098</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3824377856966188</v>
+        <v>0.5735843347092675</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5945374578329099</v>
+        <v>0.80173683323925</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.7396886100221594</v>
+        <v>1.627561009212888</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2026996189247852</v>
+        <v>0.3799105538211582</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>97.44</v>
+        <v>216.96</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.003579082430149816</v>
+        <v>0.06582830279026863</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.02481981358071961</v>
+        <v>0.08090875545236398</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.005105166301166197</v>
+        <v>0.1311783277465324</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.05500218490129938</v>
+        <v>0.1433390229469647</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2051878070435933</v>
+        <v>0.321581790904468</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.4817743344946215</v>
+        <v>0.2406389232985082</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.3377350316699388</v>
+        <v>0.315723744753855</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3577773865504552</v>
+        <v>0.5774326705953017</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.243970944607723</v>
+        <v>0.7445493151706821</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.3091992356919617</v>
+        <v>0.20381869507623</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>13.82</v>
+        <v>88.28</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.01285716465541298</v>
+        <v>0.03166996720974136</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.002175470127206536</v>
+        <v>-0.0002265489441626301</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.00647017638929992</v>
+        <v>0.01798890148333299</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.09162716124749637</v>
+        <v>0.2035446573382451</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.07548632564659497</v>
+        <v>0.1160387316607947</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1751700192048595</v>
+        <v>0.02856469314893251</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.537263631443375</v>
+        <v>0.5147366292770543</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.710396017984787</v>
+        <v>0.9673822938694834</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.592870523948319</v>
+        <v>1.6041182118804</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3738108548949448</v>
+        <v>0.375794487296951</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>85.56999999999999</v>
+        <v>112.29</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.02026559099245728</v>
+        <v>-0.02593683115397905</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.03408958988493294</v>
+        <v>-0.05527511072763724</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01881178558448626</v>
+        <v>-0.02058439231524001</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.1665985204487019</v>
+        <v>0.01125720451813517</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.04900172644567036</v>
+        <v>0.2299013927948101</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>-0.009222426644827308</v>
+        <v>0.4678431492225796</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.4959824875645249</v>
+        <v>0.3614345069440854</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.8828801045940886</v>
+        <v>0.3604456374960496</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.524177874401354</v>
+        <v>1.277555154953971</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3615700355542999</v>
+        <v>0.3156982619672122</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>151.44</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.02698533130758629</v>
+        <v>-0.01949919415305268</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.003159529576911124</v>
+        <v>-0.04831156991341901</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.0002640169478532739</v>
+        <v>-0.02080556303829284</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.0495530493309726</v>
+        <v>0.03443049246601415</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.06374879474760764</v>
+        <v>0.1893302726197357</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.290076832502</v>
+        <v>0.453321689075094</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4819322182227799</v>
+        <v>0.3089690575094233</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5310628550836156</v>
+        <v>0.3387236336222177</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.348112825095408</v>
+        <v>1.200214932908797</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3291469127635811</v>
+        <v>0.300633800002893</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>27.75</v>
+        <v>151.48</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.004662810784784366</v>
+        <v>0.0002753715652108468</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.007510697115483023</v>
+        <v>-0.02017012463449475</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03854793088002517</v>
+        <v>0.01068654775100852</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.149544353837042</v>
+        <v>0.04984206639693856</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.2240846893078849</v>
+        <v>0.06943002290103384</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.4311501224087011</v>
+        <v>0.296030265538876</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2289636888291624</v>
+        <v>0.4840644224903179</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2562245273116952</v>
+        <v>0.5437781998878808</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.4400622387541164</v>
+        <v>1.348758595056241</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1292595035645194</v>
+        <v>0.3292687474085887</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>203.56</v>
+        <v>95.87</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.008072128668026313</v>
+        <v>0.09528166438473407</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.01912482207056132</v>
+        <v>0.04993982378613171</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.07052329262450385</v>
+        <v>0.1444431967100615</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.07272345832230021</v>
+        <v>0.3363535768238257</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.2411670694258603</v>
+        <v>0.1099806162177175</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1658122072144423</v>
+        <v>-0.06992618176857779</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2251918881425872</v>
+        <v>0.4182366352757594</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4747657185080141</v>
+        <v>0.866072247990826</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.636801453483236</v>
+        <v>3.01748515707907</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.178506550135203</v>
+        <v>0.5897106862653985</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>185.35</v>
+        <v>27.85</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.01090809890058497</v>
+        <v>0.003603617350260491</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.03913220371925408</v>
+        <v>0.00288080383101641</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.07792968533350364</v>
+        <v>0.03763041069820749</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.08914099236468731</v>
+        <v>0.153686871815423</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.05702548623041137</v>
+        <v>0.2312112886028335</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.2631341967609662</v>
+        <v>0.4415114296782663</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4111338456682536</v>
+        <v>0.252248231478714</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.5359293875216449</v>
+        <v>0.2682150064915867</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.3452460162345199</v>
+        <v>0.4452516720231456</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1039106033414168</v>
+        <v>0.1306143504621795</v>
       </c>
     </row>
     <row r="15">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>420.49</v>
+        <v>186.33</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.01432258739269221</v>
+        <v>0.00528727108318372</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.01249699637360346</v>
+        <v>0.04339791645501201</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.07226825648089008</v>
+        <v>0.1279738427096815</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.10950157278385</v>
+        <v>0.09489957603912735</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.07364738765518553</v>
+        <v>0.0486294069436648</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.09186987153946302</v>
+        <v>0.2420440996888209</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.5102857171042787</v>
+        <v>0.4359131777031664</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.7897600116800716</v>
+        <v>0.5510847970401243</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.307275271704325</v>
+        <v>0.3523585468272354</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.09342504039417232</v>
+        <v>0.1058527018609225</v>
       </c>
     </row>
     <row r="16">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>106.69</v>
+        <v>97.33</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.01486611786688619</v>
+        <v>0.09421028859268676</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.02423627204353629</v>
+        <v>0.07003081366201802</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.01695380409643588</v>
+        <v>0.1631214325537547</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.06455798385449008</v>
+        <v>0.3646943669030616</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.009079722443891436</v>
+        <v>0.1617331493099305</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.08150026144113354</v>
+        <v>-0.06628929560940189</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.4029001279497719</v>
+        <v>0.2833733468338029</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.5600119588401711</v>
+        <v>0.7321004968851081</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.7667548207591359</v>
+        <v>2.67273350694307</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2089047806087558</v>
+        <v>0.5428716737483894</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>76.84999999999999</v>
+        <v>418.69</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.00697765757573543</v>
+        <v>-0.004280691181175245</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.0005207774612521199</v>
+        <v>0.01318849176223291</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.01271836986569364</v>
+        <v>0.08733705161802763</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.002086269756440329</v>
+        <v>0.104752139185734</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1380954097264506</v>
+        <v>-0.0716819372972084</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.08921785075022592</v>
+        <v>0.06893206319208778</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.3224258952719212</v>
+        <v>0.5074395555000322</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2710577618738432</v>
+        <v>0.7923720645613441</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.8679243638543073</v>
+        <v>0.3016792299773718</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.231552969107419</v>
+        <v>0.09186260385683753</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>70.59999999999999</v>
+        <v>106.7</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.006473390096774945</v>
+        <v>9.367800737858367e-05</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.001276362716834845</v>
+        <v>-0.02654870582889635</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.009817735591519883</v>
+        <v>-0.03000002774325283</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.00512529358343361</v>
+        <v>0.06465770952515659</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1362116957441557</v>
+        <v>0.03241411246812875</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.09281808277902259</v>
+        <v>0.08457003381889372</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2915740331129668</v>
+        <v>0.4070386835025122</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2450559668734342</v>
+        <v>0.5642109802933815</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.9661867609947368</v>
+        <v>0.7669202152134686</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2527803202824712</v>
+        <v>0.2089425032373093</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>290.43</v>
+        <v>117.07</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.01505749148753399</v>
+        <v>0.03027371754427088</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.006499483404911244</v>
+        <v>0.002397455065518805</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.02956501983821114</v>
+        <v>0.04601502510842503</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.1232160902235406</v>
+        <v>0.1903406355987787</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1036562285167177</v>
+        <v>0.0638402649069616</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.04419042410974883</v>
+        <v>-0.000147652305536039</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.3008181088649442</v>
+        <v>0.2850830991872233</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.3455786213164014</v>
+        <v>0.5172770409664631</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>1.472650451260571</v>
+        <v>1.327138035270901</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.3522414435335148</v>
+        <v>0.3251774838117119</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>56.48</v>
+        <v>56.5</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.004088880750868107</v>
+        <v>0.0003541157564761477</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.002484902187952942</v>
+        <v>-0.01016120904780937</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.0003542411988661787</v>
+        <v>-0.0008841598184811117</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.002824856093507466</v>
+        <v>-0.002471740663083866</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.1093366873915174</v>
+        <v>0.1143215220298988</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.2248664578990269</v>
+        <v>0.2268900755187768</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2039465761312247</v>
+        <v>0.2141228794851269</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.237820513892349</v>
+        <v>0.2321156040089518</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1553915292473569</v>
+        <v>0.1558006715927625</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.04932429064823007</v>
+        <v>0.049448136785748</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>252.16</v>
+        <v>31.06</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.0038216828245623</v>
+        <v>0.01040987954479022</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.001032194410182763</v>
+        <v>0.04298182504310266</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.006024375832415219</v>
+        <v>0.1204906289798788</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.09287915889304776</v>
+        <v>0.1077032258134734</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.1457886184634014</v>
+        <v>-0.008006666252026062</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.05068565335118302</v>
+        <v>0.1461384935279264</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2453185703698038</v>
+        <v>0.3209089656969253</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2935366445970544</v>
+        <v>0.4162132757724024</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1.248331342102369</v>
+        <v>0.2843163397313395</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.310046682116025</v>
+        <v>0.08698613033574598</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>30.74</v>
+        <v>29.91</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.0118499216687431</v>
+        <v>-0.01352242254415648</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.02262143437315145</v>
+        <v>-0.05407972632624214</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.0748251524861856</v>
+        <v>-0.1079629902676864</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.09629096888137689</v>
+        <v>-0.01805644299381859</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.006554052875376026</v>
+        <v>0.2055622930774621</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1575834489962964</v>
+        <v>0.0278350328290089</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2986137124879005</v>
+        <v>0.2538454625237314</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.3892569594031905</v>
+        <v>0.171977594583574</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2710846034100303</v>
+        <v>0.5681218781718274</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.08324032644870916</v>
+        <v>0.1617872464509873</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>30.32</v>
+        <v>75</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.01717992480038533</v>
+        <v>-0.0240728498484496</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.04353315567514426</v>
+        <v>-0.03075726722532079</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.09221561947140178</v>
+        <v>-0.03025596649458606</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.004596171827194961</v>
+        <v>-0.02203680255059937</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.186692782786652</v>
+        <v>0.1166167276464529</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0006600811309331878</v>
+        <v>0.06883704605902219</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.2652458330587368</v>
+        <v>0.2769924997604924</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1889670368629317</v>
+        <v>0.2426669987052392</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.589617355739664</v>
+        <v>0.8229581011149818</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1670716834605812</v>
+        <v>0.2215902627405431</v>
       </c>
     </row>
     <row r="24">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>108.31</v>
+        <v>107.7</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.02097080134160934</v>
+        <v>-0.005650443407938077</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.01294090727146702</v>
+        <v>-0.02703048449307843</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.05082817475010737</v>
+        <v>-0.04480711266629711</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.0673383267008909</v>
+        <v>-0.07260827870462039</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.06930100636138992</v>
+        <v>0.07288552803057735</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.0440381552767235</v>
+        <v>0.05650677626565415</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.3403840265485849</v>
+        <v>0.3448889057415858</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2898176835681896</v>
+        <v>0.2736514194487789</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3852412427430851</v>
+        <v>0.3774142843022086</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1147439853383563</v>
+        <v>0.1126404914327344</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>87.53</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.03516316576810474</v>
+        <v>0.004278561828713556</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.03601326170217167</v>
+        <v>-0.006277376717894634</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.1137549670185696</v>
+        <v>0.008593893160664168</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.2201003817356075</v>
+        <v>0.03623073778298092</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.03265956873635811</v>
+        <v>0.1667693346636472</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.1279403625885658</v>
+        <v>0.115773246466621</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.3175839725309539</v>
+        <v>0.1993202024364342</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.6449003921658587</v>
+        <v>0.1684022645241938</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.6679924138275</v>
+        <v>0.701206165021405</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.5422074955923317</v>
+        <v>0.1937653874879193</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>67.78</v>
+        <v>284.1</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.006595406060330933</v>
+        <v>-0.0217952233994374</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.005488727148600825</v>
+        <v>-0.03149925120927488</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.008180803137005421</v>
+        <v>0.007161158633749665</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.03181604902138413</v>
+        <v>0.09873534461127598</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.1420538833940521</v>
+        <v>0.09520535624686244</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.105422212378617</v>
+        <v>-0.0006153435902764848</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1863047357795784</v>
+        <v>0.2686636279429033</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.162432259240008</v>
+        <v>0.3452585591190709</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6939586205160762</v>
+        <v>1.418758482286627</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1920677325228803</v>
+        <v>0.3423450586996399</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>55.31</v>
+        <v>69.12</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.01133667511703385</v>
+        <v>-0.0209631127411648</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.01822543387795528</v>
+        <v>-0.02675294263999195</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.0247049761551883</v>
+        <v>-0.02647883455518263</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.04310150645993094</v>
+        <v>-0.01594526126495233</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.0348655080993483</v>
+        <v>0.1211874638633899</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1142983115049236</v>
+        <v>0.07666618773621936</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.2526000471176872</v>
+        <v>0.252121508221123</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2465206149560792</v>
+        <v>0.2176975271244139</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.7227973718377614</v>
+        <v>0.9249691617488187</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1987944772600587</v>
+        <v>0.2439643245776972</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2048,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>113.63</v>
+        <v>246.15</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.03784929109616053</v>
+        <v>-0.02383411198581009</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.03564461098505889</v>
+        <v>-0.021739135708017</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.05349524022265428</v>
+        <v>-0.02429841807703204</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.1553634877108565</v>
+        <v>0.0668313546330328</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.004396596395755292</v>
+        <v>0.1282648505715887</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>-0.02828423661679247</v>
+        <v>0.01229067288895758</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.2562630703364925</v>
+        <v>0.2134231949922227</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.441604961215099</v>
+        <v>0.280283801237547</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.258757233255333</v>
+        <v>1.194744361113494</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3120685291591121</v>
+        <v>0.2995549484665212</v>
       </c>
     </row>
     <row r="29">
@@ -2118,37 +2118,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>86.18000000000001</v>
+        <v>86.59</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.01305542136546767</v>
+        <v>0.004757438283395032</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.009197551401267434</v>
+        <v>-0.00414031768817491</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.01900965507059471</v>
+        <v>-0.002074453291916356</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.0339647888173138</v>
+        <v>-0.0293689359205257</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.07460411747884099</v>
+        <v>0.088796466817608</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.05911137214352813</v>
+        <v>0.07426095318865378</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.2363531746839611</v>
+        <v>0.2509643300391728</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2309658983481357</v>
+        <v>0.2217958137474481</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4360569671351422</v>
+        <v>0.4428888278089773</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1282115880179038</v>
+        <v>0.1299978666545407</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>57.31</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.02417841273647725</v>
+        <v>0.007430465775484896</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02367971672201441</v>
+        <v>-0.008509498702820362</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.02167976131899696</v>
+        <v>0.02642805407597115</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.01793964742304333</v>
+        <v>0.09052358423569329</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.04916843640904189</v>
+        <v>-0.08424371424920085</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.047828083210121</v>
+        <v>0.02407434745905568</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.2521148932389592</v>
+        <v>0.1891355491104088</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2526576760200443</v>
+        <v>0.6544154257119403</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.8693853091446995</v>
+        <v>0.3447550839835685</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2318739604486779</v>
+        <v>0.1037763004580852</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>88.95</v>
+        <v>54.9</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.0319948031443501</v>
+        <v>-0.00741276147590364</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.01298275369154067</v>
+        <v>0.004207122089574966</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.1415554291387655</v>
+        <v>0.02908386854486422</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.2471957000680891</v>
+        <v>0.03536924379738782</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.0207711449537693</v>
+        <v>0.02007661221043611</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.1327028172224362</v>
+        <v>0.107112047843726</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1846624177881846</v>
+        <v>0.2427835777544449</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.5421001659441715</v>
+        <v>0.2393446220025022</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>2.356515237730709</v>
+        <v>0.7100266858490143</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.4972565019055328</v>
+        <v>0.1958250019514891</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>74.02</v>
+        <v>56.78</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.02911858975481563</v>
+        <v>-0.009247994787889624</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.001214464533044191</v>
+        <v>-0.02923581552570653</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.03250096418345794</v>
+        <v>-0.03188410397153874</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.08248025177226115</v>
+        <v>0.008525746869288753</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.1046828048547082</v>
+        <v>0.05783093621915669</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.00674685817993903</v>
+        <v>0.02874962764115607</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1922591229439197</v>
+        <v>0.2367843170361321</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.6113283522287294</v>
+        <v>0.2365171811879376</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3348366261173399</v>
+        <v>0.8520973587783067</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1010559078879396</v>
+        <v>0.2280647644638434</v>
       </c>
     </row>
     <row r="33">
@@ -2342,37 +2342,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>183.76</v>
+        <v>182.78</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.02875265607374411</v>
+        <v>-0.005333020008893241</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01952835181873258</v>
+        <v>-0.03239806942789636</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.01606339734546414</v>
+        <v>-0.02073396862436427</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.03323018386561349</v>
+        <v>0.02771994662126587</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.02493746404612784</v>
+        <v>-0.008067755666421039</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.05655083459294974</v>
+        <v>0.05115683088237999</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.2429494540490698</v>
+        <v>0.232016907041203</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2878242178936732</v>
+        <v>0.2897402263067095</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.9516545209159293</v>
+        <v>0.9412461510076355</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.2496862190351938</v>
+        <v>0.2474606905674366</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>144.99</v>
+        <v>20.15</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.007644771062489619</v>
+        <v>0.003986045088315793</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.0056919612492492</v>
+        <v>-0.00148665441981255</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.0163499898447268</v>
+        <v>0.002986533871910169</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.007597539794523378</v>
+        <v>0.09719574569335432</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.08001047496153446</v>
+        <v>0.2263404490250014</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.090716905571675</v>
+        <v>0.1644033090541799</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.1187162706761535</v>
+        <v>0.009620174048667218</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1394841632931274</v>
+        <v>-0.07759211481357275</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.7097723563981881</v>
+        <v>0.1576089558960581</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1957657146515595</v>
+        <v>0.0499951491525128</v>
       </c>
     </row>
     <row r="35">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2454,37 +2454,37 @@
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>132.46</v>
+        <v>190.18</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.006382097157288102</v>
+        <v>-0.001155468633169843</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.01348028227451981</v>
+        <v>0.004012218953555857</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.01852400619170336</v>
+        <v>0.001210822486097385</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.007715924315769285</v>
+        <v>0.009608736027559628</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.09375012993237464</v>
+        <v>0.08261673605495234</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.08735068638792964</v>
+        <v>0.1184028769205838</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.09475007571342275</v>
+        <v>0.1289133719364628</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1327532140990466</v>
+        <v>0.1164097135497797</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.704911384230928</v>
+        <v>1.124861598236163</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1946314308883854</v>
+        <v>0.2856128833578462</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>61.13</v>
+        <v>235.32</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.01577845005000689</v>
+        <v>0.01606218101324419</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.00130694359669925</v>
+        <v>-0.0006794139893965268</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.008273821002322213</v>
+        <v>0.00208663922558161</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.004559498127220341</v>
+        <v>0.05236799195878672</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.01845215938172151</v>
+        <v>0.06664536409756305</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.03430674747473694</v>
+        <v>-0.01468843936681408</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.2040964274209927</v>
+        <v>0.2298500321180317</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.2157261304073723</v>
+        <v>0.1734460065604306</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.6795184200464841</v>
+        <v>0.3911702606141925</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1886707894726596</v>
+        <v>0.1163321394566896</v>
       </c>
     </row>
     <row r="37">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2566,37 +2566,37 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>190.4</v>
+        <v>132.9</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.0031413932121237</v>
+        <v>0.003321660579163499</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.01287370052105374</v>
+        <v>-0.001352629486726542</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.007407375113673842</v>
+        <v>-0.02387073188171418</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0.01077665674957418</v>
+        <v>-0.004419893418237231</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.06666863848774773</v>
+        <v>0.1000063211248901</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.1086881036984069</v>
+        <v>0.09122786993394372</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.136569149977839</v>
+        <v>0.1091089660891356</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1074852472029861</v>
+        <v>0.1212934070311236</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.127319830701671</v>
+        <v>0.710574353190186</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2861084634609588</v>
+        <v>0.1959526499391073</v>
       </c>
     </row>
     <row r="38">
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>94.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.002008614223147132</v>
+        <v>0.009533914314950209</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.01472646205050698</v>
+        <v>0.01718433737215941</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.01379021811523673</v>
+        <v>-0.0135596475553007</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.03486347119753341</v>
+        <v>-0.02566194222970208</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.04963588233372929</v>
+        <v>0.05196537107300347</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.06770052396139659</v>
+        <v>0.08201809045644004</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1331635034663372</v>
+        <v>0.1508985202793596</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1848941756861824</v>
+        <v>0.1783935000238677</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.4633474726110136</v>
+        <v>0.4772985525949782</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1353135484421581</v>
+        <v>0.1389100469215299</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>20.07</v>
+        <v>286.29</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.001045239602903925</v>
+        <v>0.008915980730993533</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.006927233844161829</v>
+        <v>-0.0173674187492413</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.007631310012824244</v>
+        <v>-0.003792874658538281</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.09283963762348812</v>
+        <v>0.06127668364802696</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.2053330620822484</v>
+        <v>0.0706432875078904</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.1512647877501678</v>
+        <v>0.2054823441955855</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>-0.0227394919600572</v>
+        <v>0.08934215290304248</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>-0.07404842439357751</v>
+        <v>0.06151277562848434</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.1530129941141052</v>
+        <v>0.7894243309914397</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.04860373567373588</v>
+        <v>0.2140533716147381</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>283.76</v>
+        <v>144.3</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.01108243064307712</v>
+        <v>-0.004758965551172278</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.02256204694310171</v>
+        <v>-0.0004848103331503983</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.01499575467925451</v>
+        <v>-0.02605291924232533</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0.05189798151387826</v>
+        <v>-0.01232034891553979</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.04940834382657266</v>
+        <v>0.07936012081909438</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.1892707565251146</v>
+        <v>0.09271043773378063</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0736285390519944</v>
+        <v>0.1210848371768589</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.03804516012351722</v>
+        <v>0.1202626458959595</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.7736108508212365</v>
+        <v>0.7016357617472957</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2104665120119886</v>
+        <v>0.1938658641478461</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>231.6</v>
+        <v>88.83</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.01211395797780046</v>
+        <v>0.01951112855762238</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.02750362360208924</v>
+        <v>0.0005632242897650741</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.001990164900414815</v>
+        <v>-0.02833074152008053</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.03573187903651465</v>
+        <v>-0.006598035674032499</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.02596378579493108</v>
+        <v>0.1250053626317904</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>-0.03279760017715105</v>
+        <v>0.01411364743718502</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.2153075797975728</v>
+        <v>0.1418242570744921</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1604833402043191</v>
+        <v>0.0628333755827013</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.3691782713798879</v>
+        <v>0.4206835399126552</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1104184422919574</v>
+        <v>0.1241711860634513</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>97.62</v>
+        <v>60.83</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.003674225331878223</v>
+        <v>-0.004907561456219622</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.0128657971415338</v>
+        <v>-0.00847590311327806</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.01314188684216333</v>
+        <v>-0.00847590311327806</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.02399514074219622</v>
+        <v>-0.009444683566171119</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.03652691904019556</v>
+        <v>0.01869984109626066</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.05471198556486367</v>
+        <v>0.02527157330722418</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.1258977308784577</v>
+        <v>0.2040377974763274</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.1404864822225282</v>
+        <v>0.2017746166334586</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.366679120881938</v>
+        <v>0.6712766056679036</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1097424180825985</v>
+        <v>0.1867232325943777</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>24.07</v>
+        <v>102.81</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.01109287001113535</v>
+        <v>0.008336587698641207</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.006270887042301165</v>
+        <v>-0.00261936619775649</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.006270887042301165</v>
+        <v>0.01480604122147433</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0.001247869307588134</v>
+        <v>0.1078663165695481</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.0741338575080478</v>
+        <v>0.1183172914496335</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.02225340740011084</v>
+        <v>0.2573889907669633</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.2370237900123824</v>
+        <v>-0.01021005739682135</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.2756846325718179</v>
+        <v>-0.03519164948036568</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.5961786662012056</v>
+        <v>0.5314738594447945</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1686752156935332</v>
+        <v>0.1526652384250935</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>101.96</v>
+        <v>98.61</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.0002941345222592373</v>
+        <v>0.0101413423060388</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.01886065357012645</v>
+        <v>0.01335939866790192</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.0003921658385033222</v>
+        <v>-0.003133820909138163</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>0.09870685055480011</v>
+        <v>-0.01409714137210571</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.0980845701139037</v>
+        <v>0.0440716647005015</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.2436477800952532</v>
+        <v>0.06767095670430345</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>-0.02328216371330638</v>
+        <v>0.1463104264768147</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>-0.06791782618096098</v>
+        <v>0.1325630508534874</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5188121487688213</v>
+        <v>0.3805387867546137</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1494798274506262</v>
+        <v>0.1134811541763183</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>87.13</v>
+        <v>24.02</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.004683615008240771</v>
+        <v>-0.002077242945345725</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.02789244758015053</v>
+        <v>-0.02397399991691684</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.05652410727614587</v>
+        <v>0.02430702244261962</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.02560949409997459</v>
+        <v>-0.000831965765473619</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.09709767724069773</v>
+        <v>-0.05837226998835732</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.005746060699769018</v>
+        <v>0.03457811775004904</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.11499011717337</v>
+        <v>0.2344541910713545</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.04162779667818928</v>
+        <v>0.2817680491471724</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.3934950521561476</v>
+        <v>0.5928630153273278</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1169536294570297</v>
+        <v>0.1678654472901409</v>
       </c>
     </row>
     <row r="46">
@@ -3070,37 +3070,37 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>74.44</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.01086370258539504</v>
+        <v>0.008463154658194139</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.004588447696175058</v>
+        <v>0.01624471238154523</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.002278490384058918</v>
+        <v>0.004280932372230373</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.004546621335125733</v>
+        <v>0.00387805456353707</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.02720292758624687</v>
+        <v>0.03846113254143724</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.001323158705051064</v>
+        <v>0.01073946797882197</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.1147421189148898</v>
+        <v>0.1298121858722365</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.0897638372196401</v>
+        <v>0.08583547006071113</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.2288020005405369</v>
+        <v>0.2392014638825493</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.07109330139320158</v>
+        <v>0.07410640400622825</v>
       </c>
     </row>
     <row r="47">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -3126,37 +3126,37 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>61.15</v>
+        <v>108.23</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0</v>
+        <v>0.02151964581750021</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0</v>
+        <v>-0.001107476870118806</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0</v>
+        <v>-0.02389965694558749</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0</v>
+        <v>-0.0001847264948398042</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.02694026455734577</v>
+        <v>0.1425909909602245</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.1710899905045671</v>
+        <v>-0.0775193576649057</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.01338908028529628</v>
+        <v>0.09097274752818651</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.0414184240916381</v>
+        <v>-0.04997509067509931</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.854123692916507</v>
+        <v>0.3911900299794939</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.228512466375254</v>
+        <v>0.1163374273484619</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>13.22</v>
+        <v>61.15</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.003034898401126807</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.01047899650045769</v>
+        <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.02006174599664678</v>
+        <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0.03930817527543895</v>
+        <v>0</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.07622791458668687</v>
+        <v>0.03398115367615806</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.04178738156037065</v>
+        <v>0.1725337670954961</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.04048471774524964</v>
+        <v>0.0236637935190982</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.0710933626498339</v>
+        <v>-0.02106958931696834</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1858759694790073</v>
+        <v>0.8541234784503668</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.05847293149296329</v>
+        <v>0.2285124190079832</v>
       </c>
     </row>
     <row r="49">
@@ -3238,37 +3238,37 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>70.86</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.003935883914803928</v>
+        <v>0.01392746713363247</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.02369800464743432</v>
+        <v>-0.006129478074066053</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.03394680184823773</v>
+        <v>-0.01349857018257117</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.02413640858532351</v>
+        <v>0.03840003475625187</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.09442677634153496</v>
+        <v>0.1223787650530612</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.1137448170443988</v>
+        <v>-0.09183597008158906</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.06732870015615022</v>
+        <v>0.08698872082858977</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.01933225669699301</v>
+        <v>-0.01234557931289804</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.03704840956154554</v>
+        <v>0.05149186720169974</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01220002398244024</v>
+        <v>0.01687750310335212</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>105.95</v>
+        <v>13.26</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.02070436678636001</v>
+        <v>0.003025715661503225</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.03943795088994151</v>
+        <v>-0.002257316257133324</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.03339114717388048</v>
+        <v>0.04245282629849845</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.02124714135573036</v>
+        <v>0.04245282629849845</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.1005381567282113</v>
+        <v>0.08905272406948228</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.1100916843286661</v>
+        <v>0.06393845492716244</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.06489610822418479</v>
+        <v>0.03987611339429686</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.05642559552990001</v>
+        <v>-0.06886727500065792</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.3618830617101083</v>
+        <v>0.1894639912166562</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1084427644657147</v>
+        <v>0.05953937243061636</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>48.07</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.00606950445660126</v>
+        <v>0.03095142703278042</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0.0182164928411197</v>
+        <v>0.01110322896624005</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.005438157583455894</v>
+        <v>-0.01605863561948706</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.01110884403923151</v>
+        <v>0.01982944897633798</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.006736959525904695</v>
+        <v>0.1529984172889229</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.03279776675414114</v>
+        <v>-0.09688813148710862</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.1006885951955736</v>
+        <v>0.06351599004774133</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.02027793635933106</v>
+        <v>-0.1005814603407325</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.1294704174714085</v>
+        <v>0.2233616993267387</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.04141769719003374</v>
+        <v>0.06951027151631628</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>44.02</v>
+        <v>48.44</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.003621544733067084</v>
+        <v>0.007647170577042228</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0.008938789367425537</v>
+        <v>0.02318544626115759</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.002040357092327305</v>
+        <v>0.01674222927580016</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.02545932605266898</v>
+        <v>-0.003546624687471023</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.008217799065870501</v>
+        <v>0.003339215686119612</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.02190711338493512</v>
+        <v>-0.02462131716104055</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.007510241357272296</v>
+        <v>0.1136554954614877</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.06152653821175003</v>
+        <v>0.02421858684807487</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.5175768174713919</v>
+        <v>0.1381077724258786</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.1491680984093846</v>
+        <v>0.04406562310018769</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>96.28</v>
+        <v>45.01</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.01594437466254894</v>
+        <v>0.03186610324816841</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.04199006189754351</v>
+        <v>-0.004203593765468194</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.0322645406914982</v>
+        <v>0.04942874707516154</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.01078807183812047</v>
+        <v>0.1621481759236358</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.1020243989765355</v>
+        <v>-0.04639835605947273</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.1380675234894067</v>
+        <v>-0.1652448099032714</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.03169687715701386</v>
+        <v>0.04471943515685006</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>-0.1117494386323167</v>
+        <v>0.2759371282738932</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.1866339163188619</v>
+        <v>1.297271247119065</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.05869838940292271</v>
+        <v>0.3194838905026109</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>19.17</v>
+        <v>56.64</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.01520675698213059</v>
+        <v>0.02164503594271983</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.002705376617242239</v>
+        <v>0.009985690804376057</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.004724797621498689</v>
+        <v>0.05435588426271254</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.0005214155292919687</v>
+        <v>0.1213621316930815</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.03571435196416317</v>
+        <v>0.1281951762740852</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0.07691019366447338</v>
+        <v>-0.03975688403875677</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.003054151734082744</v>
+        <v>-0.08225622826260492</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.1763512673480198</v>
+        <v>-0.08088220683312941</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.1921619923400917</v>
+        <v>0.1148862079664186</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.0603398673844624</v>
+        <v>0.03691585305103917</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>55.44</v>
+        <v>19.44</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.006535889318931121</v>
+        <v>0.01416347357338665</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.009646318684227939</v>
+        <v>0.01639041341707581</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.02457952321854129</v>
+        <v>0.03269585506055783</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.09760444405071467</v>
+        <v>0.01363467298902465</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>0.1153844441797525</v>
+        <v>0.04670760282743158</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.06531829603270711</v>
+        <v>0.08545507677424435</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.09995574485752268</v>
+        <v>0.01451890578224013</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-0.09655974710347048</v>
+        <v>-0.1573436222674325</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.09126572218663087</v>
+        <v>0.2090471472137965</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.02954066368961006</v>
+        <v>0.06532244924504638</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>36.55</v>
+        <v>44.02</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.03358012871527005</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.02481324217007419</v>
+        <v>0.004105846362894239</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.01455920499611174</v>
+        <v>0.008245547677731002</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.06249993069227666</v>
+        <v>-0.02545932605266898</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.08189113486930832</v>
+        <v>-0.0008775109063307029</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.04670813858135725</v>
+        <v>-0.03251318647119028</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.08979745503661052</v>
+        <v>0.01605137991238914</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.07796226161212538</v>
+        <v>0.05129102610203051</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.4505463944175534</v>
+        <v>0.5175767176826889</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.13199334757459</v>
+        <v>0.1491680732214236</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>17.74</v>
+        <v>26.66</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.02043074692233349</v>
+        <v>0.02538460951585031</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.02527477871088812</v>
+        <v>0.02550294701030786</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.03796099472158865</v>
+        <v>0.009198623318389609</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.03429510284886439</v>
+        <v>0.0554235790120674</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.1660752929581728</v>
+        <v>0.07925309527690416</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.06528570340326822</v>
+        <v>0.1202231290855231</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.079879840341331</v>
+        <v>-0.07128193492038548</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.2371295184843467</v>
+        <v>-0.1836314386442651</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.1629179611776732</v>
+        <v>0.2900144381755552</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.05159785780106207</v>
+        <v>0.08859129473328076</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>110.48</v>
+        <v>17.83</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.00306800522312678</v>
+        <v>0.005073289388335622</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.007099787094152266</v>
+        <v>-0.0315046131729102</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.0139235768104814</v>
+        <v>-0.01491715204824473</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.001536359390881259</v>
+        <v>-0.02939580244188378</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.05310809154870544</v>
+        <v>-0.1482679317565084</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.0302740623649167</v>
+        <v>-0.0495556993888846</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.002945684948866378</v>
+        <v>0.08798015949266991</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.009651798286270719</v>
+        <v>0.2572889174561326</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.756488336977412</v>
+        <v>0.1688177805296209</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.2065586109941799</v>
+        <v>0.0533732122991657</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>45.05</v>
+        <v>36.38</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.004639838538675889</v>
+        <v>-0.004651112790528877</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.0103251585232127</v>
+        <v>-0.03782068905678304</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.02615648785939151</v>
+        <v>-0.02466483077112824</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.0146544611932159</v>
+        <v>0.05755812367469781</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.0174481845950788</v>
+        <v>-0.06407313514334689</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.1031256291535526</v>
+        <v>-0.05801773002675481</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.003861986165770936</v>
+        <v>0.08024104936806786</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.003435079770780503</v>
+        <v>0.09185665223993333</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.3094616737878297</v>
+        <v>0.4437997395292224</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.09403428092371424</v>
+        <v>0.130235610026934</v>
       </c>
     </row>
     <row r="60">
@@ -3840,51 +3840,51 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>26</v>
+        <v>111.32</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.01272067955643763</v>
+        <v>0.007603152718748563</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.002110930897393115</v>
+        <v>0.009522110127168748</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.02760119850941756</v>
+        <v>0.004058779986420236</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.02929531925625484</v>
+        <v>0.006055112152787645</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>0.04577300656609307</v>
+        <v>-0.03660246849020388</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>0.09043241604886898</v>
+        <v>-0.02756849921047488</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.0989469075241024</v>
+        <v>0.01023687255691885</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.2195222944341353</v>
+        <v>0.02305304761575555</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2580784879602664</v>
+        <v>0.7698429713747155</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.07953297364369294</v>
+        <v>0.2096087279338876</v>
       </c>
     </row>
     <row r="61">
@@ -3896,51 +3896,51 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>43.62</v>
+        <v>45.5</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.03602212305227037</v>
+        <v>0.009988918325424923</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.03431479521569214</v>
+        <v>-0.005899070462383471</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0.02659442713062155</v>
+        <v>-0.01451154852754499</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.1262586999082129</v>
+        <v>-0.004811925083753166</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.1039441524562403</v>
+        <v>-0.001974120471302077</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.1768258624228287</v>
+        <v>-0.0910907161046135</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.04510131195175404</v>
+        <v>0.01974627130578588</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.1658744950090483</v>
+        <v>0.007460113537789193</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>1.226326884745589</v>
+        <v>0.3225419261426619</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.3057588467310177</v>
+        <v>0.09766499904031223</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>49.87</v>
+        <v>50.47</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.02062056706241033</v>
+        <v>0.0120313274848447</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.05370022372077166</v>
+        <v>-0.03554367562142458</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.06557991512173333</v>
+        <v>-0.01560365184157908</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.07476813506321001</v>
+        <v>-0.06363636749674195</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2034818967300959</v>
+        <v>-0.1722158404096373</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1747476637425495</v>
+        <v>-0.137559794499157</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.03421811840339029</v>
+        <v>0.05984885243057181</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.1962101361148811</v>
+        <v>0.2309756395293445</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.120100907802734</v>
+        <v>-0.1095144937359003</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.0417526581428419</v>
+        <v>-0.03792495061522139</v>
       </c>
     </row>
   </sheetData>
@@ -4091,17 +4091,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -4158,17 +4158,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.2471957000680891</v>
+        <v>0.3646943669030616</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4624,21 +4624,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.07476813506321001</v>
+        <v>-0.07260827870462039</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.2201003817356075</v>
+        <v>0.3363535768238257</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4669,21 +4669,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.0673383267008909</v>
+        <v>-0.06363636749674195</v>
       </c>
     </row>
     <row r="19">
@@ -4692,21 +4692,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1665985204487019</v>
+        <v>0.2423780776786357</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.03486347119753341</v>
+        <v>-0.02939580244188378</v>
       </c>
     </row>
     <row r="20">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1553634877108565</v>
+        <v>0.2035446573382451</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.03429510284886439</v>
+        <v>-0.0293689359205257</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.149544353837042</v>
+        <v>0.1903406355987787</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.0339647888173138</v>
+        <v>-0.02566194222970208</v>
       </c>
     </row>
     <row r="22">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1262586999082129</v>
+        <v>0.1621481759236358</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.02560949409997459</v>
+        <v>-0.02545932605266898</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1232160902235406</v>
+        <v>0.153686871815423</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.02545932605266898</v>
+        <v>-0.02203680255059937</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.10950157278385</v>
+        <v>0.1433390229469647</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.02399514074219622</v>
+        <v>-0.01805644299381859</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.09870685055480011</v>
+        <v>0.1213621316930815</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.02124714135573036</v>
+        <v>-0.01594526126495233</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.09760444405071467</v>
+        <v>0.1078663165695481</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.0146544611932159</v>
+        <v>-0.01409714137210571</v>
       </c>
     </row>
     <row r="27"/>
@@ -5113,12 +5113,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.300342422539678</v>
+        <v>0.4424329800493492</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2034818967300959</v>
+        <v>-0.1722158404096373</v>
       </c>
     </row>
     <row r="32">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2668902632722427</v>
+        <v>0.3385632443461823</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1660752929581728</v>
+        <v>-0.1482679317565084</v>
       </c>
     </row>
     <row r="33">
@@ -5203,21 +5203,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2633424523758561</v>
+        <v>0.3282862101180786</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1046828048547082</v>
+        <v>-0.08424371424920085</v>
       </c>
     </row>
     <row r="34">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2553237014201422</v>
+        <v>0.321581790904468</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1039441524562403</v>
+        <v>-0.0716819372972084</v>
       </c>
     </row>
     <row r="35">
@@ -5293,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2411670694258603</v>
+        <v>0.2312112886028335</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.08189113486930832</v>
+        <v>-0.06407313514334689</v>
       </c>
     </row>
     <row r="36">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2240846893078849</v>
+        <v>0.2299013927948101</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.0741338575080478</v>
+        <v>-0.06082129291944049</v>
       </c>
     </row>
     <row r="37">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.2053330620822484</v>
+        <v>0.2263404490250014</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.07364738765518553</v>
+        <v>-0.05837226998835732</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.2051878070435933</v>
+        <v>0.2055622930774621</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.05310809154870544</v>
+        <v>-0.04639835605947273</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.186692782786652</v>
+        <v>0.1893302726197357</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.03265956873635811</v>
+        <v>-0.03660246849020388</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1457886184634014</v>
+        <v>0.1667693346636472</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.02845685635460871</v>
+        <v>-0.008067755666421039</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.498505112725717</v>
+        <v>0.4678431492225796</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1768258624228287</v>
+        <v>-0.1652448099032714</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4817743344946215</v>
+        <v>0.453321689075094</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1747476637425495</v>
+        <v>-0.137559794499157</v>
       </c>
     </row>
     <row r="47">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.440657155471083</v>
+        <v>0.4415114296782663</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1380675234894067</v>
+        <v>-0.09688813148710862</v>
       </c>
     </row>
     <row r="48">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4311501224087011</v>
+        <v>0.4199375101703102</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1327028172224362</v>
+        <v>-0.09183597008158906</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.3810932890323571</v>
+        <v>0.3674304393415166</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.1279403625885658</v>
+        <v>-0.0910907161046135</v>
       </c>
     </row>
     <row r="50">
@@ -5849,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.290076832502</v>
+        <v>0.3640608026842034</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.1137448170443988</v>
+        <v>-0.0775193576649057</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2760125590262437</v>
+        <v>0.3390913855539368</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.1100916843286661</v>
+        <v>-0.06992618176857779</v>
       </c>
     </row>
     <row r="52">
@@ -5939,21 +5939,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.264879793232532</v>
+        <v>0.296030265538876</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.1031256291535526</v>
+        <v>-0.06628929560940189</v>
       </c>
     </row>
     <row r="53">
@@ -5984,21 +5984,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2631341967609662</v>
+        <v>0.2920878786065719</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.06531829603270711</v>
+        <v>-0.05801773002675481</v>
       </c>
     </row>
     <row r="54">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2436477800952532</v>
+        <v>0.2573889907669633</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.06528570340326822</v>
+        <v>-0.0495556993888846</v>
       </c>
     </row>
     <row r="55"/>
@@ -6135,21 +6135,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9252945190915358</v>
+        <v>0.9673822938694834</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2195222944341353</v>
+        <v>-0.1836314386442651</v>
       </c>
     </row>
     <row r="60">
@@ -6180,21 +6180,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8828801045940886</v>
+        <v>0.9344220059162276</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1763512673480198</v>
+        <v>-0.1573436222674325</v>
       </c>
     </row>
     <row r="61">
@@ -6225,21 +6225,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.8290293068528991</v>
+        <v>0.9180855858616215</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1117494386323167</v>
+        <v>-0.1005814603407325</v>
       </c>
     </row>
     <row r="62">
@@ -6270,21 +6270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.7897600116800716</v>
+        <v>0.866072247990826</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09655974710347048</v>
+        <v>-0.08088220683312941</v>
       </c>
     </row>
     <row r="63">
@@ -6315,21 +6315,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.7829819284145849</v>
+        <v>0.8298846855807211</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.07404842439357751</v>
+        <v>-0.07759211481357275</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.710396017984787</v>
+        <v>0.8253919472093372</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.0710933626498339</v>
+        <v>-0.06886727500065792</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.6449003921658587</v>
+        <v>0.80173683323925</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6427,21 +6427,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06791782618096098</v>
+        <v>-0.04997509067509931</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.6113283522287294</v>
+        <v>0.7923720645613441</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6472,21 +6472,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.05642559552990001</v>
+        <v>-0.03519164948036568</v>
       </c>
     </row>
     <row r="67">
@@ -6495,21 +6495,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5945374578329099</v>
+        <v>0.7321004968851081</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.0414184240916381</v>
+        <v>-0.02106958931696834</v>
       </c>
     </row>
     <row r="68">
@@ -6540,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.583314992810515</v>
+        <v>0.6544154257119403</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.01933225669699301</v>
+        <v>-0.01234557931289804</v>
       </c>
     </row>
     <row r="69"/>
@@ -6646,21 +6646,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.952209951066851</v>
+        <v>3.01748515707907</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.120100907802734</v>
+        <v>-0.1095144937359003</v>
       </c>
     </row>
     <row r="74">
@@ -6691,21 +6691,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.6679924138275</v>
+        <v>2.890821256959017</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.03704840956154554</v>
+        <v>0.05149186720169974</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.356515237730709</v>
+        <v>2.67273350694307</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.09126572218663087</v>
+        <v>0.1148862079664186</v>
       </c>
     </row>
     <row r="76">
@@ -6781,21 +6781,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.598944279188865</v>
+        <v>1.627561009212888</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1294704174714085</v>
+        <v>0.1381077724258786</v>
       </c>
     </row>
     <row r="77">
@@ -6826,21 +6826,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.592870523948319</v>
+        <v>1.6041182118804</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6848,21 +6848,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1530129941141052</v>
+        <v>0.1558006715927625</v>
       </c>
     </row>
     <row r="78">
@@ -6871,21 +6871,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.524177874401354</v>
+        <v>1.526458741557412</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6893,21 +6893,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1553915292473569</v>
+        <v>0.1576089558960581</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.472650451260571</v>
+        <v>1.418758482286627</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1629179611776732</v>
+        <v>0.1688177805296209</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.348112825095408</v>
+        <v>1.348758595056241</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1858759694790073</v>
+        <v>0.1894639912166562</v>
       </c>
     </row>
     <row r="81">
@@ -7006,21 +7006,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.338200490047857</v>
+        <v>1.327138035270901</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1866339163188619</v>
+        <v>0.2090471472137965</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.258757233255333</v>
+        <v>1.297271247119065</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1921619923400917</v>
+        <v>0.2233616993267387</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -489,12 +489,12 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>40.75</v>
+        <v>39.29</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.132573666438329</v>
+        <v>-0.03582819839196705</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.150480014302423</v>
+        <v>0.1149261930806114</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.2222555432962989</v>
+        <v>0.1700766131748668</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.2423780776786357</v>
+        <v>0.2179170167315752</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.4424329800493492</v>
+        <v>0.3512215111005108</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.3640608026842034</v>
+        <v>0.3316122609599257</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.5868382230935685</v>
+        <v>0.5364410761223668</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8253919472093372</v>
+        <v>0.7623360157144299</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.9703256892236471</v>
+        <v>0.8997324695333531</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.2536587606951883</v>
+        <v>0.2385041947685302</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>169.55</v>
+        <v>163.38</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.05895948039110754</v>
+        <v>-0.03639043384187868</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.06374304348462911</v>
+        <v>0.04156575447590982</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.1080975696929585</v>
+        <v>0.0574757597593043</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.09911843050301883</v>
+        <v>0.08241686922083735</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3385632443461823</v>
+        <v>0.241670166880777</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3390913855539368</v>
+        <v>0.3106297919870251</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4871433821649793</v>
+        <v>0.4414602549005644</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.9180855858616215</v>
+        <v>0.839585106525542</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.200712819471255</v>
+        <v>1.120627715208933</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.3007318993964418</v>
+        <v>0.2847584349537717</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>560.92</v>
+        <v>562.65</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.01553264706411661</v>
+        <v>0.003084292869957039</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.04088373284713664</v>
+        <v>-0.04493137378210976</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.01541167124582099</v>
+        <v>-0.01545103303084183</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.007888080394920616</v>
+        <v>0.006835723220652623</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.03117869007357399</v>
+        <v>-0.003559573594840715</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.3674304393415166</v>
+        <v>0.3556851940075456</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.6576282247146263</v>
+        <v>0.7360835839964324</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.9344220059162276</v>
+        <v>0.9532141786388142</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.890821256959017</v>
+        <v>2.902822102304913</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5728250832963251</v>
+        <v>0.5744404969646537</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>74.06</v>
+        <v>14.19</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.02222223158272496</v>
+        <v>0.01320952977013001</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.06087953228236165</v>
+        <v>0.0215982166771338</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.05769781646979544</v>
+        <v>0.01793400340928319</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.0799066138994704</v>
+        <v>0.1640689145895042</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.3282862101180786</v>
+        <v>0.1717588755305355</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2920878786065719</v>
+        <v>0.2097186815130918</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4254751318468664</v>
+        <v>0.5908071142392768</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6223751306026259</v>
+        <v>0.7649253293171467</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.7900071925259688</v>
+        <v>1.662288889962444</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2141851734428959</v>
+        <v>0.3859632878566497</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>503.3</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.0278904521840575</v>
+        <v>0.01869054767438283</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.06829081338364629</v>
+        <v>0.0515669297850343</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.01145093990519308</v>
+        <v>0.04460453166026057</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.006217607981732431</v>
+        <v>0.217573782318274</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.06082129291944049</v>
+        <v>0.09628973145270292</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.4199375101703102</v>
+        <v>0.01285903278117173</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.6826877811046268</v>
+        <v>0.6080691139416476</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.8298846855807211</v>
+        <v>0.995924098936483</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.526458741557412</v>
+        <v>1.652790905981059</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3619800205864627</v>
+        <v>0.3843131360242578</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>14</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.01337918146863082</v>
+        <v>-0.0238994963734106</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.02449889542608874</v>
+        <v>0.03300939479541865</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.002498189759613245</v>
+        <v>0.0277225572812021</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.106232239133913</v>
+        <v>0.07798991272500233</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.107106751064459</v>
+        <v>0.2639291968772322</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2011063603698098</v>
+        <v>0.2702747088483035</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5735843347092675</v>
+        <v>0.4188758870786717</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.80173683323925</v>
+        <v>0.5719672005632088</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.627561009212888</v>
+        <v>0.7472267610254193</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3799105538211582</v>
+        <v>0.2044342335876361</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>216.96</v>
+        <v>496.74</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.06582830279026863</v>
+        <v>-0.01303397122531258</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.08090875545236398</v>
+        <v>-0.07165288486008103</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1311783277465324</v>
+        <v>-0.04550169757772216</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.1433390229469647</v>
+        <v>-0.009234706759287281</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.321581790904468</v>
+        <v>-0.1183387139529989</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2406389232985082</v>
+        <v>0.3927933371855714</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.315723744753855</v>
+        <v>0.728374684899157</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5774326705953017</v>
+        <v>0.8173752459129875</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7445493151706821</v>
+        <v>1.493528760024005</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.20381869507623</v>
+        <v>0.356036753242245</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>88.28</v>
+        <v>210.83</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.03166996720974136</v>
+        <v>-0.02825407767845856</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.0002265489441626301</v>
+        <v>0.05976676004691606</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.01798890148333299</v>
+        <v>0.09255324919610053</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.2035446573382451</v>
+        <v>0.1302739677841829</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1160387316607947</v>
+        <v>0.2557896526849146</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.02856469314893251</v>
+        <v>0.2100101805125285</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.5147366292770543</v>
+        <v>0.2861781246611053</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.9673822938694834</v>
+        <v>0.5269943576065113</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.6041182118804</v>
+        <v>0.6952587873050629</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.375794487296951</v>
+        <v>0.1923726377504384</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>112.29</v>
+        <v>109.77</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.02593683115397905</v>
+        <v>-0.02244192939633749</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.05527511072763724</v>
+        <v>-0.09943393885693408</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.02058439231524001</v>
+        <v>-0.03021473385081197</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.01125720451813517</v>
+        <v>-0.00281618080334034</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.2299013927948101</v>
+        <v>0.1810845035459363</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.4678431492225796</v>
+        <v>0.4799784192124557</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.3614345069440854</v>
+        <v>0.3607201338119321</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3604456374960496</v>
+        <v>0.3313651556957473</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.277555154953971</v>
+        <v>1.226442078438445</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3156982619672122</v>
+        <v>0.3057813670222351</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>95.54000000000001</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.01949919415305268</v>
+        <v>0.01658492012453094</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.04831156991341901</v>
+        <v>0.09900765391387156</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.02080556303829284</v>
+        <v>0.1705500430447753</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.03443049246601415</v>
+        <v>0.36479476384883</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1893302726197357</v>
+        <v>0.08946650986558158</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.453321689075094</v>
+        <v>-0.09425140055093906</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.3089690575094233</v>
+        <v>0.5239469154493241</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.3387236336222177</v>
+        <v>0.8605259185200824</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.200214932908797</v>
+        <v>3.084114827510716</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.300633800002893</v>
+        <v>0.5984509522647237</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>151.48</v>
+        <v>187.45</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.0002753715652108468</v>
+        <v>0.006010814716800095</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.02017012463449475</v>
+        <v>0.04621308736906604</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.01068654775100852</v>
+        <v>0.122119087242182</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.04984206639693856</v>
+        <v>0.1023876990680239</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.06943002290103384</v>
+        <v>0.07805609247499001</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.296030265538876</v>
+        <v>0.2453957335439825</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.4840644224903179</v>
+        <v>0.4818489911770398</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.5437781998878808</v>
+        <v>0.5454462653766565</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.348758595056241</v>
+        <v>0.3604876248207709</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3292687474085887</v>
+        <v>0.1080640509628346</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>95.87</v>
+        <v>27.67</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.09528166438473407</v>
+        <v>-0.006463206560512136</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.04993982378613171</v>
+        <v>-0.0494675542378914</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.1444431967100615</v>
+        <v>0.05369382464290062</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.3363535768238257</v>
+        <v>0.1386831664625621</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1099806162177175</v>
+        <v>0.2162637396173164</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>-0.06992618176857779</v>
+        <v>0.4617009841636663</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4182366352757594</v>
+        <v>0.2640475490090151</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.866072247990826</v>
+        <v>0.2681026793440959</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>3.01748515707907</v>
+        <v>0.4359107119349344</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5897106862653985</v>
+        <v>0.1281732858201774</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>27.85</v>
+        <v>150.7</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.003603617350260491</v>
+        <v>-0.005149186699871744</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.00288080383101641</v>
+        <v>-0.03149106017395409</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.03763041069820749</v>
+        <v>0.003061710851036015</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.153686871815423</v>
+        <v>0.04951598852068062</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.2312112886028335</v>
+        <v>0.04386786455166347</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.4415114296782663</v>
+        <v>0.2778204633315782</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.252248231478714</v>
+        <v>0.5072315646645533</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.2682150064915867</v>
+        <v>0.5399838115970526</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.4452516720231456</v>
+        <v>1.336638589614314</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1306143504621795</v>
+        <v>0.3269783835225826</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>186.33</v>
+        <v>93.45</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.00528727108318372</v>
+        <v>-0.02187569549149426</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.04339791645501201</v>
+        <v>-0.08561644091272647</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.1279738427096815</v>
+        <v>-0.03050111484617335</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.09489957603912735</v>
+        <v>0.01808471528660838</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.0486294069436648</v>
+        <v>0.1453631071360175</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2420440996888209</v>
+        <v>0.4662440475289116</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.4359131777031664</v>
+        <v>0.3139991196864858</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.5510847970401243</v>
+        <v>0.3067064318124866</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.3523585468272354</v>
+        <v>1.152083890080423</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1058527018609225</v>
+        <v>0.2910797382051873</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>97.33</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.09421028859268676</v>
+        <v>0.02589126266986641</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.07003081366201802</v>
+        <v>0.1311884249625639</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1631214325537547</v>
+        <v>0.1898236493416738</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.3646943669030616</v>
+        <v>0.4115069478290252</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1617331493099305</v>
+        <v>0.156206551278701</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>-0.06628929560940189</v>
+        <v>-0.06032376748770851</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2833733468338029</v>
+        <v>0.378308588972174</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7321004968851081</v>
+        <v>0.7245401964579796</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>2.67273350694307</v>
+        <v>2.767825214887752</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.5428716737483894</v>
+        <v>0.5560740111690905</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>418.69</v>
+        <v>416.06</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.004280691181175245</v>
+        <v>-0.006281508675814562</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.01318849176223291</v>
+        <v>0.01337163001787345</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.08733705161802763</v>
+        <v>0.06116101766879734</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.104752139185734</v>
+        <v>0.1089610471796658</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.0716819372972084</v>
+        <v>-0.0775541200860993</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.06893206319208778</v>
+        <v>0.06805290873148251</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.5074395555000322</v>
+        <v>0.5425149952627484</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.7923720645613441</v>
+        <v>0.789698346825636</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.3016792299773718</v>
+        <v>0.2935027206011414</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.09186260385683753</v>
+        <v>0.0895716187190605</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>106.7</v>
+        <v>31.62</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>9.367800737858367e-05</v>
+        <v>0.01802966461429145</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.02654870582889635</v>
+        <v>0.0718644352282507</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.03000002774325283</v>
+        <v>0.1181046701376185</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.06465770952515659</v>
+        <v>0.1296892139263572</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.03241411246812875</v>
+        <v>0.03451783992405799</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.08457003381889372</v>
+        <v>0.1570831264162118</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.4070386835025122</v>
+        <v>0.3658518319013904</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.5642109802933815</v>
+        <v>0.4315534206105514</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7669202152134686</v>
+        <v>0.30747213259535</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2089425032373093</v>
+        <v>0.09347992345984135</v>
       </c>
     </row>
     <row r="19">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>117.07</v>
+        <v>104.8</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.03027371754427088</v>
+        <v>-0.01780687863942509</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.002397455065518805</v>
+        <v>-0.03410135436167916</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.04601502510842503</v>
+        <v>-0.0367647048511307</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.1903406355987787</v>
+        <v>0.05858588941169507</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.0638402649069616</v>
+        <v>-0.003612828031141158</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>-0.000147652305536039</v>
+        <v>0.05623867932275717</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2850830991872233</v>
+        <v>0.4040384919272886</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.5172770409664631</v>
+        <v>0.5522629686010287</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>1.327138035270901</v>
+        <v>0.7354569910048714</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.3251774838117119</v>
+        <v>0.2017236782508203</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>56.5</v>
+        <v>56.4</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.0003541157564761477</v>
+        <v>-0.001769884497718421</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.01016120904780937</v>
+        <v>-0.009135570270452087</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.0008841598184811117</v>
+        <v>0.007322733258102287</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.002471740663083866</v>
+        <v>-0.001062656031998621</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.1143215220298988</v>
+        <v>0.1169711842578531</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.2268900755187768</v>
+        <v>0.2300388639422584</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2141228794851269</v>
+        <v>0.2179418067053136</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.2321156040089518</v>
+        <v>0.2320609192131269</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1558006715927625</v>
+        <v>0.1537550379016577</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.049448136785748</v>
+        <v>0.0488286371647968</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>31.06</v>
+        <v>114.7</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01040987954479022</v>
+        <v>-0.02024432179687463</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.04298182504310266</v>
+        <v>-0.004944909442387013</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.1204906289798788</v>
+        <v>0.03942001390368155</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.1077032258134734</v>
+        <v>0.1735215823117939</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>-0.008006666252026062</v>
+        <v>0.01403361968587813</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1461384935279264</v>
+        <v>-0.02222375711538427</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.3209089656969253</v>
+        <v>0.3150804830804286</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.4162132757724024</v>
+        <v>0.493116439869717</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2843163397313395</v>
+        <v>1.280026876911797</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.08698613033574598</v>
+        <v>0.3161740447464823</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>29.91</v>
+        <v>67.59</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01352242254415648</v>
+        <v>-0.007051613913406474</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.05407972632624214</v>
+        <v>-0.02086053117297937</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.1079629902676864</v>
+        <v>0.01532216685807963</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.01805644299381859</v>
+        <v>0.0279847351770437</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.2055622930774621</v>
+        <v>0.1291625665302303</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.0278350328290089</v>
+        <v>0.1035789447721345</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2538454625237314</v>
+        <v>0.21820970741618</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.171977594583574</v>
+        <v>0.1635397278646835</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.5681218781718274</v>
+        <v>0.6892099159585674</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1617872464509873</v>
+        <v>0.190952775067176</v>
       </c>
     </row>
     <row r="23">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>75</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.0240728498484496</v>
+        <v>-0.00386667887369796</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.03075726722532079</v>
+        <v>-0.03909969023186299</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.03025596649458606</v>
+        <v>-0.02327100050998943</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.02203680255059937</v>
+        <v>-0.01554882480782749</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.1166167276464529</v>
+        <v>0.08640914216028617</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.06883704605902219</v>
+        <v>0.0512288379090351</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.2769924997604924</v>
+        <v>0.2763240668179678</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2426669987052392</v>
+        <v>0.233472431468446</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8229581011149818</v>
+        <v>0.8159094759096965</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2215902627405431</v>
+        <v>0.2200137676287623</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>107.7</v>
+        <v>74.58</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.005650443407938077</v>
+        <v>0.000134130833732149</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02703048449307843</v>
+        <v>-0.001071548715919635</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.04480711266629711</v>
+        <v>0.02996820962848301</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.07260827870462039</v>
+        <v>0.1144650907307414</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.07288552803057735</v>
+        <v>-0.1028793924870881</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.05650677626565415</v>
+        <v>0.02435166100926933</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.3448889057415858</v>
+        <v>0.2247877387287385</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2736514194487789</v>
+        <v>0.6704623110202306</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3774142843022086</v>
+        <v>0.3449354571041487</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1126404914327344</v>
+        <v>0.1038256483969355</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>68.06999999999999</v>
+        <v>106.64</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.004278561828713556</v>
+        <v>-0.009842131742149984</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.006277376717894634</v>
+        <v>-0.05048524879530147</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.008593893160664168</v>
+        <v>-0.04229904938496531</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.03623073778298092</v>
+        <v>-0.07639008976928319</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.1667693346636472</v>
+        <v>0.02022141568084312</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.115773246466621</v>
+        <v>0.02863210614424649</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1993202024364342</v>
+        <v>0.3543762745558203</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1684022645241938</v>
+        <v>0.2889663881525353</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.701206165021405</v>
+        <v>0.3638829049853698</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1937653874879193</v>
+        <v>0.1089850595959378</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>284.1</v>
+        <v>68.62</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.0217952233994374</v>
+        <v>-0.007233796008851101</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.03149925120927488</v>
+        <v>-0.03907016905822869</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.007161158633749665</v>
+        <v>-0.02181038839653404</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.09873534461127598</v>
+        <v>-0.01251971713818534</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.09520535624686244</v>
+        <v>0.0888338899474248</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>-0.0006153435902764848</v>
+        <v>0.05908964431639729</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.2686636279429033</v>
+        <v>0.2483960362122755</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.3452585591190709</v>
+        <v>0.2074350030269239</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.418758482286627</v>
+        <v>0.9110447335607466</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.3423450586996399</v>
+        <v>0.2409576225481818</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>69.12</v>
+        <v>86.27</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.0209631127411648</v>
+        <v>-0.003695573488368353</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.02675294263999195</v>
+        <v>-0.02121627818846628</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.02647883455518263</v>
+        <v>0.0002318451370018071</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.01594526126495233</v>
+        <v>-0.02254708186039311</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.1211874638633899</v>
+        <v>0.06093599263960114</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.07666618773621936</v>
+        <v>0.05262589064126177</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.252121508221123</v>
+        <v>0.275424098738718</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2176975271244139</v>
+        <v>0.235745154727955</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.9249691617488187</v>
+        <v>0.43755661749006</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2439643245776972</v>
+        <v>0.1286041755775855</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2048,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>246.15</v>
+        <v>54.91</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.02383411198581009</v>
+        <v>0.0001821187842496741</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.021739135708017</v>
+        <v>0.0103036134133041</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.02429841807703204</v>
+        <v>0.01673980189493274</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.0668313546330328</v>
+        <v>0.02719272906220027</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.1282648505715887</v>
+        <v>0.02851443988893387</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.01229067288895758</v>
+        <v>0.1013268874197724</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.2134231949922227</v>
+        <v>0.243541145296629</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.280283801237547</v>
+        <v>0.2367332357246432</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.194744361113494</v>
+        <v>0.7103379106072287</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2995549484665212</v>
+        <v>0.1958975442445685</v>
       </c>
     </row>
     <row r="29">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2118,37 +2118,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>86.59</v>
+        <v>29.26</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.004757438283395032</v>
+        <v>-0.02173184961037411</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.00414031768817491</v>
+        <v>-0.08160704116951478</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.002074453291916356</v>
+        <v>-0.1035538977932257</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.0293689359205257</v>
+        <v>-0.04316545775400527</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.088796466817608</v>
+        <v>0.1066565672414321</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.07426095318865378</v>
+        <v>-0.00712585983595504</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.2509643300391728</v>
+        <v>0.2457626017538341</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2217958137474481</v>
+        <v>0.1696930459358288</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4428888278089773</v>
+        <v>0.5340436893446598</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1299978666545407</v>
+        <v>0.1533096064362873</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>74.56999999999999</v>
+        <v>56.04</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.007430465775484896</v>
+        <v>-0.01303272067063432</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.008509498702820362</v>
+        <v>-0.03892986459100733</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.02642805407597115</v>
+        <v>-0.03958864814055241</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.09052358423569329</v>
+        <v>0.006104131919763223</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.08424371424920085</v>
+        <v>0.03024905566376623</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.02407434745905568</v>
+        <v>0.008955328029041532</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1891355491104088</v>
+        <v>0.241855016783858</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.6544154257119403</v>
+        <v>0.2321085704494394</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.3447550839835685</v>
+        <v>0.8279592637917723</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1037763004580852</v>
+        <v>0.2227063595652798</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>54.9</v>
+        <v>20.05</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.00741276147590364</v>
+        <v>-0.004962798181780803</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.004207122089574966</v>
+        <v>-0.01522600019635578</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.02908386854486422</v>
+        <v>0.01416281096680105</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.03536924379738782</v>
+        <v>0.09772788979252556</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.02007661221043611</v>
+        <v>0.2125793421279389</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.107112047843726</v>
+        <v>0.1522988319900958</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.2427835777544449</v>
+        <v>0.03377152687999474</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2393446220025022</v>
+        <v>-0.07441609132309601</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.7100266858490143</v>
+        <v>0.151863976274524</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1958250019514891</v>
+        <v>0.04825529645212523</v>
       </c>
     </row>
     <row r="32">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2286,37 +2286,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>56.78</v>
+        <v>271.78</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.009247994787889624</v>
+        <v>-0.04336503716838991</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.02923581552570653</v>
+        <v>-0.06956524101207195</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03188410397153874</v>
+        <v>-0.03934114997257399</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.008525746869288753</v>
+        <v>0.0480891648532964</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.05783093621915669</v>
+        <v>0.02003489498688937</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.02874962764115607</v>
+        <v>-0.03564795343573046</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.2367843170361321</v>
+        <v>0.2438297083371015</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.2365171811879376</v>
+        <v>0.2860112409361613</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.8520973587783067</v>
+        <v>1.313868780503996</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.2280647644638434</v>
+        <v>0.3226539771151147</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>182.78</v>
+        <v>237.56</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.005333020008893241</v>
+        <v>-0.03489740625995319</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.03239806942789636</v>
+        <v>-0.0485802585774695</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.02073396862436427</v>
+        <v>-0.04972201952653743</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.02771994662126587</v>
+        <v>0.0361582114173169</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.008067755666421039</v>
+        <v>0.06470245776182404</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.05115683088237999</v>
+        <v>-0.02367716137196763</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.232016907041203</v>
+        <v>0.1967653188059659</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2897402263067095</v>
+        <v>0.2288012158624717</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.9412461510076355</v>
+        <v>1.118153619596244</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.2474606905674366</v>
+        <v>0.2842586061956147</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>20.15</v>
+        <v>133.67</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.003986045088315793</v>
+        <v>0.005793862361353375</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.00148665441981255</v>
+        <v>0.001498441195872058</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.002986533871910169</v>
+        <v>-0.02288015214172379</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.09719574569335432</v>
+        <v>0.0005988609420448654</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.2263404490250014</v>
+        <v>0.1077492716491038</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.1644033090541799</v>
+        <v>0.09188320876568068</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.009620174048667218</v>
+        <v>0.1085327898776529</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.07759211481357275</v>
+        <v>0.1137018929900209</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.1576089558960581</v>
+        <v>0.7204855234513499</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.0499951491525128</v>
+        <v>0.1982580102861293</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>190.18</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.001155468633169843</v>
+        <v>0.004826852777988222</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.004012218953555857</v>
+        <v>0.006305153962073762</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.001210822486097385</v>
+        <v>-0.002188174239882712</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.009608736027559628</v>
+        <v>-0.01925437592349355</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.08261673605495234</v>
+        <v>0.04727047868980705</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.1184028769205838</v>
+        <v>0.08320454330486315</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1289133719364628</v>
+        <v>0.1546702515251839</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1164097135497797</v>
+        <v>0.1775293588303151</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>1.124861598236163</v>
+        <v>0.484429430777253</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.2856128833578462</v>
+        <v>0.1407396018250597</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>235.32</v>
+        <v>181.16</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.01606218101324419</v>
+        <v>-0.008863087471313591</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.0006794139893965268</v>
+        <v>-0.03745817331846668</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.00208663922558161</v>
+        <v>-0.02386978157872188</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.05236799195878672</v>
+        <v>0.02304044380430526</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.06664536409756305</v>
+        <v>-0.03501059801616579</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>-0.01468843936681408</v>
+        <v>0.03514433209639156</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.2298500321180317</v>
+        <v>0.2449343579699745</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.1734460065604306</v>
+        <v>0.2843304250335186</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.3911702606141925</v>
+        <v>0.9240411842789535</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1163321394566896</v>
+        <v>0.2437643981864017</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>132.9</v>
+        <v>234.6</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.003321660579163499</v>
+        <v>-0.003059668529208914</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.001352629486726542</v>
+        <v>0.003121439267839143</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.02387073188171418</v>
+        <v>0.006996629927766174</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.004419893418237231</v>
+        <v>0.0601952611971226</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.1000063211248901</v>
+        <v>0.04627390358550887</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.09122786993394372</v>
+        <v>-0.02104024613014799</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1091089660891356</v>
+        <v>0.2461825454560191</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1212934070311236</v>
+        <v>0.1700854400990452</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.710574353190186</v>
+        <v>0.3869136156393398</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1959526499391073</v>
+        <v>0.1151924073272814</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>95.3</v>
+        <v>284.02</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.009533914314950209</v>
+        <v>-0.007929091003865074</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.01718433737215941</v>
+        <v>-0.03803560029238995</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.0135596475553007</v>
+        <v>0.001975578831139968</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.02566194222970208</v>
+        <v>0.04982619961184676</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.05196537107300347</v>
+        <v>0.05583639038539734</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.08201809045644004</v>
+        <v>0.1918589398926021</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1508985202793596</v>
+        <v>0.1111023958961606</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1783935000238677</v>
+        <v>0.05780256615892698</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.4772985525949782</v>
+        <v>0.7752358226264782</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1389100469215299</v>
+        <v>0.210836073265686</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>286.29</v>
+        <v>188.85</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.008915980730993533</v>
+        <v>-0.006993304361584407</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.0173674187492413</v>
+        <v>-0.01645741624771413</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.003792874658538281</v>
+        <v>0.009623111587224731</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.06127668364802696</v>
+        <v>0.005966070428095493</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.0706432875078904</v>
+        <v>0.05839923417793935</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.2054823441955855</v>
+        <v>0.105223597834752</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.08934215290304248</v>
+        <v>0.1428621820647504</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.06151277562848434</v>
+        <v>0.1068683577362404</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.7894243309914397</v>
+        <v>1.110001794353455</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.2140533716147381</v>
+        <v>0.2826089759630093</v>
       </c>
     </row>
     <row r="40">
@@ -2734,37 +2734,37 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>144.3</v>
+        <v>144.14</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.004758965551172278</v>
+        <v>-0.001108826463794177</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.0004848103331503983</v>
+        <v>-0.009142791090218316</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.02605291924232533</v>
+        <v>-0.03578838656046657</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.01232034891553979</v>
+        <v>-0.0156388267477634</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.07936012081909438</v>
+        <v>0.07439706504893739</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.09271043773378063</v>
+        <v>0.0820046082527035</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1210848371768589</v>
+        <v>0.1136692935813541</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.1202626458959595</v>
+        <v>0.1069738341767936</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.7016357617472957</v>
+        <v>0.6997489429829316</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.1938658641478461</v>
+        <v>0.1934244375976786</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>88.83</v>
+        <v>101.91</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.01951112855762238</v>
+        <v>-0.008753953096550249</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.0005632242897650741</v>
+        <v>-0.04111775656172445</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.02833074152008053</v>
+        <v>0.02504531823600287</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.006598035674032499</v>
+        <v>0.09604215941889249</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.1250053626317904</v>
+        <v>0.09225366589513451</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.01411364743718502</v>
+        <v>0.2618112714978287</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1418242570744921</v>
+        <v>0.01120149079671795</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.0628333755827013</v>
+        <v>-0.0413889551324278</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.4206835399126552</v>
+        <v>0.5180674091106219</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1241711860634513</v>
+        <v>0.1492919167481073</v>
       </c>
     </row>
     <row r="42">
@@ -2846,37 +2846,37 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>60.83</v>
+        <v>60.24</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.004907561456219622</v>
+        <v>-0.009699163814371081</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.00847590311327806</v>
+        <v>-0.01873265552394765</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.00847590311327806</v>
+        <v>-0.01148665841839047</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.009444683566171119</v>
+        <v>-0.01067495020031395</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.01869984109626066</v>
+        <v>0.002791537374437159</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.02527157330722418</v>
+        <v>0.00673990302332661</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.2040377974763274</v>
+        <v>0.2024584541638124</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.2017746166334586</v>
+        <v>0.1954564259675411</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.6712766056679036</v>
+        <v>0.6550662731651089</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1867232325943777</v>
+        <v>0.1828739372649748</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>102.81</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.008336587698641207</v>
+        <v>-0.000101431256146034</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.00261936619775649</v>
+        <v>0.0002028468522516924</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.01480604122147433</v>
+        <v>0.005711929348881206</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0.1078663165695481</v>
+        <v>-0.00884604798066857</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.1183172914496335</v>
+        <v>0.03087430371090694</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.2573889907669633</v>
+        <v>0.0595739747682047</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>-0.01021005739682135</v>
+        <v>0.1510058889340729</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-0.03519164948036568</v>
+        <v>0.1292019168220842</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.5314738594447945</v>
+        <v>0.3803989044136944</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1526652384250935</v>
+        <v>0.1134435452821561</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>98.61</v>
+        <v>23.93</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.0101413423060388</v>
+        <v>-0.003746883883126717</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.01335939866790192</v>
+        <v>-0.01845770595082619</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.003133820909138163</v>
+        <v>0.01098437803311336</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.01409714137210571</v>
+        <v>-0.006641753690272201</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.0440716647005015</v>
+        <v>-0.07455305857775096</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.06767095670430345</v>
+        <v>0.02192973989289393</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1463104264768147</v>
+        <v>0.2431619814870487</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.1325630508534874</v>
+        <v>0.2830590490694809</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.3805387867546137</v>
+        <v>0.5868945418504425</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1134811541763183</v>
+        <v>0.1664049538122361</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>24.02</v>
+        <v>86.73</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.002077242945345725</v>
+        <v>-0.02364064427371138</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.02397399991691684</v>
+        <v>-0.02867059617364809</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.02430702244261962</v>
+        <v>-0.03472448714716592</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.000831965765473619</v>
+        <v>-0.02484820130209242</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.05837226998835732</v>
+        <v>0.07358126206115889</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.03457811775004904</v>
+        <v>-0.01700815949269874</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.2344541910713545</v>
+        <v>0.1299779140962816</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.2817680491471724</v>
+        <v>0.04352888852578363</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.5928630153273278</v>
+        <v>0.3870979195986841</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1678654472901409</v>
+        <v>0.1152418036439458</v>
       </c>
     </row>
     <row r="46">
@@ -3070,37 +3070,37 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>75.06999999999999</v>
+        <v>74.98</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.008463154658194139</v>
+        <v>-0.001198832266637528</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.01624471238154523</v>
+        <v>0.007389534455229052</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.004280932372230373</v>
+        <v>0.005767944836665428</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.00387805456353707</v>
+        <v>0.006578138101979825</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.03846113254143724</v>
+        <v>0.040795262559429</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.01073946797882197</v>
+        <v>0.004042003572663599</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.1298121858722365</v>
+        <v>0.1284578601417952</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.08583547006071113</v>
+        <v>0.07469917752170407</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.2392014638825493</v>
+        <v>0.2377160250614165</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.07410640400622825</v>
+        <v>0.07367705297070337</v>
       </c>
     </row>
     <row r="47">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -3126,37 +3126,37 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>108.23</v>
+        <v>61.15</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.02151964581750021</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.001107476870118806</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.02389965694558749</v>
+        <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.0001847264948398042</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.1425909909602245</v>
+        <v>0.01733224247203835</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.0775193576649057</v>
+        <v>0.1727788613367855</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.09097274752818651</v>
+        <v>0.05368904063349733</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.04997509067509931</v>
+        <v>-0.0156525820938912</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.3911900299794939</v>
+        <v>0.854123692916507</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.1163374273484619</v>
+        <v>0.228512466375254</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>61.15</v>
+        <v>13.29</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0</v>
+        <v>0.002262423261943036</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>-0.0184638109825952</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0</v>
+        <v>0.01295732300128005</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0</v>
+        <v>0.05727925891082353</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.03398115367615806</v>
+        <v>0.08279139017840342</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.1725337670954961</v>
+        <v>0.06958665462679803</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0236637935190982</v>
+        <v>0.04826632854733814</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.02106958931696834</v>
+        <v>-0.0667605961663692</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.8541234784503668</v>
+        <v>0.1921552661916834</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.2285124190079832</v>
+        <v>0.06033787324362971</v>
       </c>
     </row>
     <row r="49">
@@ -3238,37 +3238,37 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>71.84999999999999</v>
+        <v>71.47</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.01392746713363247</v>
+        <v>-0.005288757988698323</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.006129478074066053</v>
+        <v>-0.01270891251142725</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.01349857018257117</v>
+        <v>-0.01420687971443968</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.03840003475625187</v>
+        <v>0.04442497299386106</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.1223787650530612</v>
+        <v>0.09446930415906274</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.09183597008158906</v>
+        <v>-0.1035605552772438</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.08698872082858977</v>
+        <v>0.094051324335088</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.01234557931289804</v>
+        <v>-0.01726293765672415</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.05149186720169974</v>
+        <v>0.04597587438440431</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01687750310335212</v>
+        <v>0.01509624796383835</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>13.26</v>
+        <v>48.4</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.003025715661503225</v>
+        <v>-0.0008257040042115582</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.002257316257133324</v>
+        <v>0.00770357601469529</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0.04245282629849845</v>
+        <v>0.02195947850769309</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0.04245282629849845</v>
+        <v>-0.002884206572061565</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.08905272406948228</v>
+        <v>-0.002384397977841846</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.06393845492716244</v>
+        <v>-0.03042316438079384</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.03987611339429686</v>
+        <v>0.1232866646245048</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.06886727500065792</v>
+        <v>0.01747828095981174</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.1894639912166562</v>
+        <v>0.1372243639678699</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.05953937243061636</v>
+        <v>0.0437954157820597</v>
       </c>
     </row>
     <row r="51">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -3350,37 +3350,37 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>99.26000000000001</v>
+        <v>19.49</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.03095142703278042</v>
+        <v>0.002469026065070379</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0.01110322896624005</v>
+        <v>0.01267859031233431</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.01605863561948706</v>
+        <v>0.0386378375521208</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>0.01982944897633798</v>
+        <v>0.001850676352346925</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>0.1529984172889229</v>
+        <v>0.04773939553218365</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.09688813148710862</v>
+        <v>0.08858853004071454</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.06351599004774133</v>
+        <v>0.03089190215280802</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>-0.1005814603407325</v>
+        <v>-0.1614988007811355</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.2233616993267387</v>
+        <v>0.2120634718788934</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.06951027151631628</v>
+        <v>0.06620763387480766</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>48.44</v>
+        <v>26.81</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0.007647170577042228</v>
+        <v>0.005663952641663528</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0.02318544626115759</v>
+        <v>-0.0110291324103764</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>0.01674222927580016</v>
+        <v>0.02830517665963583</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.003546624687471023</v>
+        <v>0.04673227487176557</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.003339215686119612</v>
+        <v>0.07236500864311779</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.02462131716104055</v>
+        <v>0.1279875144231475</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.1136554954614877</v>
+        <v>-0.04115538684279185</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.02421858684807487</v>
+        <v>-0.178882683039299</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.1381077724258786</v>
+        <v>0.2973207793955348</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.04406562310018769</v>
+        <v>0.0906426027052003</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>45.01</v>
+        <v>105.62</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.03186610324816841</v>
+        <v>-0.02411531487940544</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.004203593765468194</v>
+        <v>-0.03569794646481728</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.04942874707516154</v>
+        <v>-0.02931711132788073</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.1621481759236358</v>
+        <v>-0.004242452621258441</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.04639835605947273</v>
+        <v>0.06927232873758227</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.1652448099032714</v>
+        <v>-0.1077902739274449</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.04471943515685006</v>
+        <v>0.06830246182626309</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.2759371282738932</v>
+        <v>-0.05249727000918158</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>1.297271247119065</v>
+        <v>0.3576413106327292</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.3194838905026109</v>
+        <v>0.1072907741893858</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>56.64</v>
+        <v>43.77</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.02164503594271983</v>
+        <v>-0.005679236651527808</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.009985690804376057</v>
+        <v>-0.006130800457555763</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>0.05435588426271254</v>
+        <v>0.00899030382770305</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.1213621316930815</v>
+        <v>-0.02603467300174667</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.1281951762740852</v>
+        <v>-0.01034613087670544</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.03975688403875677</v>
+        <v>-0.04257584349636578</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.08225622826260492</v>
+        <v>0.01544597814896598</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.08088220683312941</v>
+        <v>0.0442288507136932</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.1148862079664186</v>
+        <v>0.5089581395880995</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.03691585305103917</v>
+        <v>0.1469885011765455</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>19.44</v>
+        <v>43.84</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.01416347357338665</v>
+        <v>-0.02599418379417207</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0.01639041341707581</v>
+        <v>-0.03116021762236709</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.03269585506055783</v>
+        <v>0.01481480042466754</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.01363467298902465</v>
+        <v>0.1336954287159613</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>0.04670760282743158</v>
+        <v>-0.08742715826181302</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.08545507677424435</v>
+        <v>-0.1935246567263722</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.01451890578224013</v>
+        <v>0.09078086305036903</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-0.1573436222674325</v>
+        <v>0.2601585846354728</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.2090471472137965</v>
+        <v>1.237555556096386</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.06532244924504638</v>
+        <v>0.3079504021445061</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>44.02</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0</v>
+        <v>-0.02538791273651531</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.004105846362894239</v>
+        <v>-0.02803175876364716</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.008245547677731002</v>
+        <v>-0.01756883655415109</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.02545932605266898</v>
+        <v>0.01393977728342066</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.0008775109063307029</v>
+        <v>0.07498245298421358</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.03251318647119028</v>
+        <v>-0.1246572641634346</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.01605137991238914</v>
+        <v>0.0369575926963619</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.05129102610203051</v>
+        <v>-0.09941534714282763</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.5175767176826889</v>
+        <v>0.192303211372401</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.1491680732214236</v>
+        <v>0.06038173369088407</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>26.66</v>
+        <v>45.69</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.02538460951585031</v>
+        <v>0.004175793993604016</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0.02550294701030786</v>
+        <v>0.0008761686635958554</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.009198623318389609</v>
+        <v>-0.004575226409339495</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.0554235790120674</v>
+        <v>0.004175793993604016</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>0.07925309527690416</v>
+        <v>-0.006955003401390103</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.1202231290855231</v>
+        <v>-0.09846096385988345</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.07128193492038548</v>
+        <v>0.03195278783033539</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.1836314386442651</v>
+        <v>0.006772669526038388</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.2900144381755552</v>
+        <v>0.3280645887741378</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.08859129473328076</v>
+        <v>0.09919075156752521</v>
       </c>
     </row>
     <row r="58">
@@ -3742,37 +3742,37 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>17.83</v>
+        <v>17.63</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.005073289388335622</v>
+        <v>-0.01121709275351934</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.0315046131729102</v>
+        <v>-0.03976042621552955</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.01491715204824473</v>
+        <v>-0.0270420339830143</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.02939580244188378</v>
+        <v>-0.02811467729005912</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.1482679317565084</v>
+        <v>-0.1785632779843298</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.0495556993888846</v>
+        <v>-0.06518674072061104</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.08798015949266991</v>
+        <v>0.1078887839049232</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.2572889174561326</v>
+        <v>0.238002228704753</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1688177805296209</v>
+        <v>0.1557070430734575</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.0533732122991657</v>
+        <v>0.04941979829830001</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>36.38</v>
+        <v>55.45</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.004651112790528877</v>
+        <v>-0.02100986298609442</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.03782068905678304</v>
+        <v>-0.01176260631318449</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.02466483077112824</v>
+        <v>0.02476437141883059</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>0.05755812367469781</v>
+        <v>0.09628309125316648</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.06407313514334689</v>
+        <v>0.09103840266390817</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.05801773002675481</v>
+        <v>-0.06373227890306632</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.08024104936806786</v>
+        <v>-0.09007570597469305</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.09185665223993333</v>
+        <v>-0.1102560935330482</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.4437997395292224</v>
+        <v>0.09146268344711217</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.130235610026934</v>
+        <v>0.02960260015602056</v>
       </c>
     </row>
     <row r="60">
@@ -3840,51 +3840,51 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>111.32</v>
+        <v>35.81</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0.007603152718748563</v>
+        <v>-0.01566794057419052</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>0.009522110127168748</v>
+        <v>-0.05314643939059249</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>0.004058779986420236</v>
+        <v>-0.03059007296770555</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.006055112152787645</v>
+        <v>0.0455474853515625</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.03660246849020388</v>
+        <v>-0.08718701043532728</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.02756849921047488</v>
+        <v>-0.08180651201624145</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.01023687255691885</v>
+        <v>0.08774519488419918</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>0.02305304761575555</v>
+        <v>0.08446696032087009</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.7698429713747155</v>
+        <v>0.4211783710092467</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.2096087279338876</v>
+        <v>0.1243016890392368</v>
       </c>
     </row>
     <row r="61">
@@ -3896,51 +3896,51 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>45.5</v>
+        <v>110.68</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.009988918325424923</v>
+        <v>-0.005749186052847244</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.005899070462383471</v>
+        <v>-0.01661486180255445</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.01451154852754499</v>
+        <v>-0.004497211716383842</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.004811925083753166</v>
+        <v>-0.001083057249790631</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.001974120471302077</v>
+        <v>-0.04420379453830892</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.0910907161046135</v>
+        <v>-0.04690027156056464</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.01974627130578588</v>
+        <v>0.01557193371047583</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.007460113537789193</v>
+        <v>0.02022703860463615</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.3225419261426619</v>
+        <v>0.7596676014047938</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.09766499904031223</v>
+        <v>0.2072861339600116</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>50.47</v>
+        <v>49.73</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.0120313274848447</v>
+        <v>-0.01466220845192379</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.03554367562142458</v>
+        <v>-0.05222034714544033</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.01560365184157908</v>
+        <v>-0.02965854551733993</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.06363636749674195</v>
+        <v>-0.05617762690493233</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.1722158404096373</v>
+        <v>-0.2096312620876556</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.137559794499157</v>
+        <v>-0.1679772601410985</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.05984885243057181</v>
+        <v>0.08913709392083802</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.2309756395293445</v>
+        <v>0.2120399956562842</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1095144937359003</v>
+        <v>-0.1225709778521613</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.03792495061522139</v>
+        <v>-0.04265016876995342</v>
       </c>
     </row>
   </sheetData>
@@ -4158,17 +4158,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3646943669030616</v>
+        <v>0.4115069478290252</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.07260827870462039</v>
+        <v>-0.07639008976928319</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.3363535768238257</v>
+        <v>0.36479476384883</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.06363636749674195</v>
+        <v>-0.05617762690493233</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.2423780776786357</v>
+        <v>0.2179170167315752</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.02939580244188378</v>
+        <v>-0.04316545775400527</v>
       </c>
     </row>
     <row r="20">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.2035446573382451</v>
+        <v>0.217573782318274</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.0293689359205257</v>
+        <v>-0.02811467729005912</v>
       </c>
     </row>
     <row r="21">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1903406355987787</v>
+        <v>0.1735215823117939</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.02566194222970208</v>
+        <v>-0.02603467300174667</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1621481759236358</v>
+        <v>0.1640689145895042</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.02545932605266898</v>
+        <v>-0.02484820130209242</v>
       </c>
     </row>
     <row r="23">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.153686871815423</v>
+        <v>0.1386831664625621</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.02203680255059937</v>
+        <v>-0.02254708186039311</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.1433390229469647</v>
+        <v>0.1336954287159613</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.01805644299381859</v>
+        <v>-0.01925437592349355</v>
       </c>
     </row>
     <row r="25">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.1213621316930815</v>
+        <v>0.1302739677841829</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.01594526126495233</v>
+        <v>-0.0156388267477634</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.1078663165695481</v>
+        <v>0.1296892139263572</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.01409714137210571</v>
+        <v>-0.01554882480782749</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.4424329800493492</v>
+        <v>0.3512215111005108</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.1722158404096373</v>
+        <v>-0.2096312620876556</v>
       </c>
     </row>
     <row r="32">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.3385632443461823</v>
+        <v>0.2639291968772322</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1482679317565084</v>
+        <v>-0.1785632779843298</v>
       </c>
     </row>
     <row r="33">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.3282862101180786</v>
+        <v>0.2557896526849146</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5225,21 +5225,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.08424371424920085</v>
+        <v>-0.1183387139529989</v>
       </c>
     </row>
     <row r="34">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.321581790904468</v>
+        <v>0.241670166880777</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.0716819372972084</v>
+        <v>-0.1028793924870881</v>
       </c>
     </row>
     <row r="35">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2312112886028335</v>
+        <v>0.2162637396173164</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.06407313514334689</v>
+        <v>-0.08742715826181302</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2299013927948101</v>
+        <v>0.2125793421279389</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.06082129291944049</v>
+        <v>-0.08718701043532728</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.2263404490250014</v>
+        <v>0.1810845035459363</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.05837226998835732</v>
+        <v>-0.0775541200860993</v>
       </c>
     </row>
     <row r="38">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.2055622930774621</v>
+        <v>0.1717588755305355</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.04639835605947273</v>
+        <v>-0.07455305857775096</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1893302726197357</v>
+        <v>0.156206551278701</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.03660246849020388</v>
+        <v>-0.04420379453830892</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1667693346636472</v>
+        <v>0.1453631071360175</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.008067755666421039</v>
+        <v>-0.03501059801616579</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4678431492225796</v>
+        <v>0.4799784192124557</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1652448099032714</v>
+        <v>-0.1935246567263722</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.453321689075094</v>
+        <v>0.4662440475289116</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.137559794499157</v>
+        <v>-0.1679772601410985</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4415114296782663</v>
+        <v>0.4617009841636663</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.09688813148710862</v>
+        <v>-0.1246572641634346</v>
       </c>
     </row>
     <row r="48">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4199375101703102</v>
+        <v>0.3927933371855714</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.09183597008158906</v>
+        <v>-0.1077902739274449</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.3674304393415166</v>
+        <v>0.3556851940075456</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.0910907161046135</v>
+        <v>-0.1035605552772438</v>
       </c>
     </row>
     <row r="50">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3640608026842034</v>
+        <v>0.3316122609599257</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.0775193576649057</v>
+        <v>-0.09846096385988345</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3390913855539368</v>
+        <v>0.3106297919870251</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.06992618176857779</v>
+        <v>-0.09425140055093906</v>
       </c>
     </row>
     <row r="52">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.296030265538876</v>
+        <v>0.2778204633315782</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.06628929560940189</v>
+        <v>-0.08180651201624145</v>
       </c>
     </row>
     <row r="53">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2920878786065719</v>
+        <v>0.2702747088483035</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.05801773002675481</v>
+        <v>-0.06518674072061104</v>
       </c>
     </row>
     <row r="54">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2573889907669633</v>
+        <v>0.2618112714978287</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.0495556993888846</v>
+        <v>-0.06373227890306632</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9673822938694834</v>
+        <v>0.995924098936483</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1836314386442651</v>
+        <v>-0.178882683039299</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.9344220059162276</v>
+        <v>0.9532141786388142</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1573436222674325</v>
+        <v>-0.1614988007811355</v>
       </c>
     </row>
     <row r="61">
@@ -6225,21 +6225,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.9180855858616215</v>
+        <v>0.8605259185200824</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6247,21 +6247,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1005814603407325</v>
+        <v>-0.1102560935330482</v>
       </c>
     </row>
     <row r="62">
@@ -6270,21 +6270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.866072247990826</v>
+        <v>0.839585106525542</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6292,21 +6292,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.08088220683312941</v>
+        <v>-0.09941534714282763</v>
       </c>
     </row>
     <row r="63">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.8298846855807211</v>
+        <v>0.8173752459129875</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.07759211481357275</v>
+        <v>-0.07441609132309601</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.8253919472093372</v>
+        <v>0.789698346825636</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.06886727500065792</v>
+        <v>-0.0667605961663692</v>
       </c>
     </row>
     <row r="65">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.80173683323925</v>
+        <v>0.7649253293171467</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.04997509067509931</v>
+        <v>-0.05249727000918158</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.7923720645613441</v>
+        <v>0.7623360157144299</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.03519164948036568</v>
+        <v>-0.0413889551324278</v>
       </c>
     </row>
     <row r="67">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.7321004968851081</v>
+        <v>0.7245401964579796</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.02106958931696834</v>
+        <v>-0.01726293765672415</v>
       </c>
     </row>
     <row r="68">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.6544154257119403</v>
+        <v>0.6704623110202306</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.01234557931289804</v>
+        <v>-0.0156525820938912</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.01748515707907</v>
+        <v>3.084114827510716</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1095144937359003</v>
+        <v>-0.1225709778521613</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.890821256959017</v>
+        <v>2.902822102304913</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.05149186720169974</v>
+        <v>0.04597587438440431</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.67273350694307</v>
+        <v>2.767825214887752</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1148862079664186</v>
+        <v>0.09146268344711217</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.627561009212888</v>
+        <v>1.662288889962444</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1381077724258786</v>
+        <v>0.1372243639678699</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.6041182118804</v>
+        <v>1.652790905981059</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6848,21 +6848,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1558006715927625</v>
+        <v>0.151863976274524</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.526458741557412</v>
+        <v>1.493528760024005</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6893,21 +6893,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1576089558960581</v>
+        <v>0.1537550379016577</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.418758482286627</v>
+        <v>1.336638589614314</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1688177805296209</v>
+        <v>0.1557070430734575</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.348758595056241</v>
+        <v>1.313868780503996</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1894639912166562</v>
+        <v>0.1921552661916834</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.327138035270901</v>
+        <v>1.280026876911797</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2090471472137965</v>
+        <v>0.192303211372401</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.297271247119065</v>
+        <v>1.237555556096386</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2233616993267387</v>
+        <v>0.2120634718788934</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -490,11 +490,11 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>39.29</v>
+        <v>39.67</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.03582819839196705</v>
+        <v>-0.01022963182081738</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.1149261930806114</v>
+        <v>0.1062464443320152</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.1700766131748668</v>
+        <v>0.1250709034979998</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.2179170167315752</v>
+        <v>0.2385263715522423</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3512215111005108</v>
+        <v>0.3527085481915295</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.3316122609599257</v>
+        <v>0.2813531471064719</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.5364410761223668</v>
+        <v>0.4968864681086271</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.7623360157144299</v>
+        <v>0.7445211595022221</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.8997324695333531</v>
+        <v>0.8811853731296575</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.2385041947685302</v>
+        <v>0.2344604992499379</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>163.38</v>
+        <v>164.17</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.03639043384187868</v>
+        <v>-0.009412886012248434</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.04156575447590982</v>
+        <v>0.02908543487214388</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.0574757597593043</v>
+        <v>0.03885337870706107</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.08241686922083735</v>
+        <v>0.09097556373003579</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.241670166880777</v>
+        <v>0.2481479135518203</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3106297919870251</v>
+        <v>0.2723068130390858</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4414602549005644</v>
+        <v>0.3787824731453153</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.839585106525542</v>
+        <v>0.8139175228184441</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.120627715208933</v>
+        <v>1.122940826059083</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2847584349537717</v>
+        <v>0.2852253892741008</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>562.65</v>
+        <v>94.53</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.003084292869957039</v>
+        <v>-0.0006342907380969542</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.04493137378210976</v>
+        <v>0.08232199156032038</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.01545103303084183</v>
+        <v>0.05608308036264131</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.006835723220652623</v>
+        <v>0.2162892086280088</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.003559573594840715</v>
+        <v>0.1379872850941843</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.3556851940075456</v>
+        <v>0.01586415064019131</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.7360835839964324</v>
+        <v>0.6176515189347465</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.9532141786388142</v>
+        <v>1.013591892676134</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.902822102304913</v>
+        <v>1.754785208663779</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5744404969646537</v>
+        <v>0.4018318212799878</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>14.19</v>
+        <v>14.69</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.01320952977013001</v>
+        <v>-0.004067825058759245</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.0215982166771338</v>
+        <v>0.04928568431309288</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.01793400340928319</v>
+        <v>0.06449270850343702</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.1640689145895042</v>
+        <v>0.1686555240277376</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1717588755305355</v>
+        <v>0.1589743084281259</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2097186815130918</v>
+        <v>0.2375736918291802</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5908071142392768</v>
+        <v>0.5984766323319684</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7649253293171467</v>
+        <v>0.7467300650312909</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.662288889962444</v>
+        <v>1.903162005237858</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3859632878566497</v>
+        <v>0.4265612526648261</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>89.93000000000001</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.01869054767438283</v>
+        <v>-0.00164838930702671</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.0515669297850343</v>
+        <v>0.03209318652364179</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.04460453166026057</v>
+        <v>0.03665667768436398</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.217573782318274</v>
+        <v>0.06961005988766211</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.09628973145270292</v>
+        <v>0.258873820678748</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.01285903278117173</v>
+        <v>0.2551196553764945</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.6080691139416476</v>
+        <v>0.3695122742781598</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.995924098936483</v>
+        <v>0.5457126745004974</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.652790905981059</v>
+        <v>0.7521557281617683</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3843131360242578</v>
+        <v>0.2055657491939105</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>72.29000000000001</v>
+        <v>546.8</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.0238994963734106</v>
+        <v>-0.02430319319889596</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.03300939479541865</v>
+        <v>-0.07956977956884459</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.0277225572812021</v>
+        <v>-0.03970774383648434</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.07798991272500233</v>
+        <v>-0.0256419654410005</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2639291968772322</v>
+        <v>-0.05122157682553441</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2702747088483035</v>
+        <v>0.3045137489638723</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4188758870786717</v>
+        <v>0.6174257845455791</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5719672005632088</v>
+        <v>0.8679382482486457</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.7472267610254193</v>
+        <v>2.724319714352051</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2044342335876361</v>
+        <v>0.5500616991536957</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>496.74</v>
+        <v>212.53</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.01303397122531258</v>
+        <v>-0.004822994901066524</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.07165288486008103</v>
+        <v>0.052493470450103</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.04550169757772216</v>
+        <v>0.06254371682641913</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.009234706759287281</v>
+        <v>0.1296375011628197</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-0.1183387139529989</v>
+        <v>0.2593156439456339</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.3927933371855714</v>
+        <v>0.2061416699479359</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.728374684899157</v>
+        <v>0.2547593660352556</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.8173752459129875</v>
+        <v>0.5236763655541357</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.493528760024005</v>
+        <v>0.6893953383835563</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.356036753242245</v>
+        <v>0.1909963499301843</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>210.83</v>
+        <v>109.57</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.02825407767845856</v>
+        <v>-0.01836591113881325</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.05976676004691606</v>
+        <v>-0.05183452743439487</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.09255324919610053</v>
+        <v>-0.08071149047346671</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.1302739677841829</v>
+        <v>0.04173796707464361</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2557896526849146</v>
+        <v>0.1551924244333998</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2100101805125285</v>
+        <v>0.5380404685630704</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2861781246611053</v>
+        <v>0.3346007876635313</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.5269943576065113</v>
+        <v>0.3171267595971754</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.6952587873050629</v>
+        <v>1.186163089851748</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1923726377504384</v>
+        <v>0.2978590183107437</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>109.77</v>
+        <v>100.37</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.02244192939633749</v>
+        <v>0.008237063482538387</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.09943393885693408</v>
+        <v>0.1063712675929362</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.03021473385081197</v>
+        <v>0.1117634482024275</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.00281618080334034</v>
+        <v>0.3304612870941879</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1810845035459363</v>
+        <v>0.140715273389949</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.4799784192124557</v>
+        <v>-0.1001930977010621</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.3607201338119321</v>
+        <v>0.4798319323950051</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3313651556957473</v>
+        <v>0.8360829737134441</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.226442078438445</v>
+        <v>3.065531159540543</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3057813670222351</v>
+        <v>0.5960228250563313</v>
       </c>
     </row>
     <row r="11">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>97.45999999999999</v>
+        <v>103.54</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.01658492012453094</v>
+        <v>0.006904590798696653</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.09900765391387156</v>
+        <v>0.1267820394304116</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1705500430447753</v>
+        <v>0.1442148674973367</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.36479476384883</v>
+        <v>0.3763125919890651</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.08946650986558158</v>
+        <v>0.2178311574183212</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>-0.09425140055093906</v>
+        <v>-0.06467927940470042</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.5239469154493241</v>
+        <v>0.337762742004565</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.8605259185200824</v>
+        <v>0.7330007848257154</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>3.084114827510716</v>
+        <v>2.739504322336177</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.5984509522647237</v>
+        <v>0.5521654536871292</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>187.45</v>
+        <v>27.7</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.006010814716800095</v>
+        <v>-0.01247766430091968</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.04621308736906604</v>
+        <v>-0.006456183760595202</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.122119087242182</v>
+        <v>-0.01388392266037453</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.1023876990680239</v>
+        <v>0.2006935903494607</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.07805609247499001</v>
+        <v>0.2111936924558484</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2453957335439825</v>
+        <v>0.4924569806033121</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.4818489911770398</v>
+        <v>0.2338529987342681</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.5454462653766565</v>
+        <v>0.2311111450195313</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.3604876248207709</v>
+        <v>0.4263646062881807</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1080640509628346</v>
+        <v>0.1256676481502936</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>27.67</v>
+        <v>186.24</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.006463206560512136</v>
+        <v>-0.0174105091793848</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.0494675542378914</v>
+        <v>0.01576219958245773</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.05369382464290062</v>
+        <v>0.05860292870234463</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.1386831664625621</v>
+        <v>0.07003735838936631</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.2162637396173164</v>
+        <v>0.08841423612300114</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.4617009841636663</v>
+        <v>0.2563854170076443</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2640475490090151</v>
+        <v>0.4467384680705093</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2681026793440959</v>
+        <v>0.4816300057442271</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.4359107119349344</v>
+        <v>0.3872569344519201</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1281732858201774</v>
+        <v>0.1152844185723247</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>150.7</v>
+        <v>93.23</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.005149186699871744</v>
+        <v>-0.01707954816287638</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.03149106017395409</v>
+        <v>-0.04663050941714131</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.003061710851036015</v>
+        <v>-0.07326038995003958</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.04951598852068062</v>
+        <v>0.05463802881995106</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.04386786455166347</v>
+        <v>0.107144918343389</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.2778204633315782</v>
+        <v>0.5179024107879282</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.5072315646645533</v>
+        <v>0.2937166171564909</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.5399838115970526</v>
+        <v>0.2914165351631244</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.336638589614314</v>
+        <v>1.102566833491946</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3269783835225826</v>
+        <v>0.2811007039001339</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>93.45</v>
+        <v>149.66</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.02187569549149426</v>
+        <v>-0.009223460491253221</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.08561644091272647</v>
+        <v>-0.03844256037461879</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.03050111484617335</v>
+        <v>-0.01072976914323431</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.01808471528660838</v>
+        <v>0.03161778286766359</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1453631071360175</v>
+        <v>0.001932784063071624</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.4662440475289116</v>
+        <v>0.258787546998823</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.3139991196864858</v>
+        <v>0.4570062148404634</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3067064318124866</v>
+        <v>0.5021193436436537</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.152083890080423</v>
+        <v>1.306897648685217</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2910797382051873</v>
+        <v>0.3213243611856211</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>99.84999999999999</v>
+        <v>481.6</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.02589126266986641</v>
+        <v>-0.03337816774603897</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1311884249625639</v>
+        <v>-0.1233116420438366</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1898236493416738</v>
+        <v>-0.08336508617294713</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.4115069478290252</v>
+        <v>-0.02571259233649537</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.156206551278701</v>
+        <v>-0.2022644751892749</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>-0.06032376748770851</v>
+        <v>0.3440925851826981</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.378308588972174</v>
+        <v>0.5647982905389661</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7245401964579796</v>
+        <v>0.6872002562489001</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>2.767825214887752</v>
+        <v>1.403044777355776</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.5560740111690905</v>
+        <v>0.3394318482025291</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>416.06</v>
+        <v>107.65</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.006281508675814562</v>
+        <v>0.004244420186638287</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.01337163001787345</v>
+        <v>-0.005955717952774942</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.06116101766879734</v>
+        <v>-0.02194059164370932</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.1089610471796658</v>
+        <v>0.0402454440187543</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.0775541200860993</v>
+        <v>0.009234092315174802</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.06805290873148251</v>
+        <v>0.07838321952036686</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.5425149952627484</v>
+        <v>0.4025170760410619</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.789698346825636</v>
+        <v>0.5395503184539641</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2935027206011414</v>
+        <v>0.7857397907577623</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.0895716187190605</v>
+        <v>0.2132195276134305</v>
       </c>
     </row>
     <row r="18">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>31.62</v>
+        <v>408.71</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.01802966461429145</v>
+        <v>-0.01593912149667442</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.0718644352282507</v>
+        <v>-0.04193627377514952</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.1181046701376185</v>
+        <v>-0.00639374946814586</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.1296892139263572</v>
+        <v>0.04353262430053495</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.03451783992405799</v>
+        <v>-0.07939904648720297</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1570831264162118</v>
+        <v>0.01948116158018798</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.3658518319013904</v>
+        <v>0.4712995921701681</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.4315534206105514</v>
+        <v>0.6487726177322406</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.30747213259535</v>
+        <v>0.2985232393772841</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.09347992345984135</v>
+        <v>0.09097946339194896</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>104.8</v>
+        <v>57.27</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.01780687863942509</v>
+        <v>0.005442439927558329</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.03410135436167916</v>
+        <v>0.01813334147135426</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.0367647048511307</v>
+        <v>-0.0005235389126754253</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.05858588941169507</v>
+        <v>0.01380773156525139</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.003612828031141158</v>
+        <v>0.1315144572520734</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.05623867932275717</v>
+        <v>0.2838703735345112</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.4040384919272886</v>
+        <v>0.1982497222265898</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.5522629686010287</v>
+        <v>0.2311151019404041</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.7354569910048714</v>
+        <v>0.1815290792320881</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2017236782508203</v>
+        <v>0.05717805213150662</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>56.4</v>
+        <v>31.13</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.001769884497718421</v>
+        <v>-0.01174605838836185</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.009135570270452087</v>
+        <v>0.02468729495452271</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.007322733258102287</v>
+        <v>0.04428043336036636</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.001062656031998621</v>
+        <v>0.06865774313834083</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.1169711842578531</v>
+        <v>0.03191399164015563</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.2300388639422584</v>
+        <v>0.1618765108462719</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2179418067053136</v>
+        <v>0.3261034893215953</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.2320609192131269</v>
+        <v>0.3606666589967518</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1537550379016577</v>
+        <v>0.3179066412426645</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.0488286371647968</v>
+        <v>0.09638112146179978</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>114.7</v>
+        <v>68.81</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.02024432179687463</v>
+        <v>0.01250733498487189</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.004944909442387013</v>
+        <v>0.008500574133435412</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.03942001390368155</v>
+        <v>0.02563722335056551</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.1735215823117939</v>
+        <v>0.05812700061898646</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.01403361968587813</v>
+        <v>0.1368365777188796</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>-0.02222375711538427</v>
+        <v>0.139630682168179</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.3150804830804286</v>
+        <v>0.2217861386846798</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.493116439869717</v>
+        <v>0.1620604077722079</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1.280026876911797</v>
+        <v>0.7390423418808807</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3161740447464823</v>
+        <v>0.2025506722090289</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>67.59</v>
+        <v>77.03</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.007051613913406474</v>
+        <v>0.005482289069301594</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.02086053117297937</v>
+        <v>0.01036202698928412</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01532216685807963</v>
+        <v>0.03063956356677155</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.0279847351770437</v>
+        <v>0.135968169188271</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1291625665302303</v>
+        <v>-0.09285734308861049</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1035789447721345</v>
+        <v>0.02343075605018141</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.21820970741618</v>
+        <v>0.2862077285516247</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1635397278646835</v>
+        <v>0.6678391318130437</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6892099159585674</v>
+        <v>0.3854695983281289</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.190952775067176</v>
+        <v>0.114805236770116</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>74.70999999999999</v>
+        <v>117.87</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.00386667887369796</v>
+        <v>-0.01231769428873253</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.03909969023186299</v>
+        <v>-0.001947465965373874</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.02327100050998943</v>
+        <v>0.002807570431208717</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.01554882480782749</v>
+        <v>0.158541431310139</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.08640914216028617</v>
+        <v>0.007522380825803587</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0512288379090351</v>
+        <v>-0.01127809756820264</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.2763240668179678</v>
+        <v>0.2925911842182873</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.233472431468446</v>
+        <v>0.4763618985477249</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8159094759096965</v>
+        <v>1.380239069138207</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2200137676287623</v>
+        <v>0.3351811523429973</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>74.58</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.000134130833732149</v>
+        <v>-0.001335806482845037</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.001071548715919635</v>
+        <v>-0.03398368360459958</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.02996820962848301</v>
+        <v>-0.01670388877360118</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.1144650907307414</v>
+        <v>-0.01280867790446649</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.1028793924870881</v>
+        <v>0.08400195628146778</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.02435166100926933</v>
+        <v>0.1014116112321484</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.2247877387287385</v>
+        <v>0.2343019534053656</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.6704623110202306</v>
+        <v>0.1809970100076792</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3449354571041487</v>
+        <v>0.8506220696700277</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1038256483969355</v>
+        <v>0.2277386059736752</v>
       </c>
     </row>
     <row r="25">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>106.64</v>
+        <v>86.83</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.009842131742149984</v>
+        <v>-0.002298023107519143</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.05048524879530147</v>
+        <v>-0.00561151930235948</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.04229904938496531</v>
+        <v>-0.0009205134930809766</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.07639008976928319</v>
+        <v>-0.01351959619854703</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.02022141568084312</v>
+        <v>0.06795401888126174</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.02863210614424649</v>
+        <v>0.08070570260462739</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.3543762745558203</v>
+        <v>0.2463884138370906</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2889663881525353</v>
+        <v>0.206813048870969</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.3638829049853698</v>
+        <v>0.4608836582299571</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1089850595959378</v>
+        <v>0.134676020846948</v>
       </c>
     </row>
     <row r="26">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>68.62</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.007233796008851101</v>
+        <v>0.0007274229460541015</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.03907016905822869</v>
+        <v>-0.0319447892071012</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.02181038839653404</v>
+        <v>-0.01644268638455293</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.01251971713818534</v>
+        <v>-0.008217988607386872</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.0888338899474248</v>
+        <v>0.08843918536212958</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.05908964431639729</v>
+        <v>0.1094650834678874</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.2483960362122755</v>
+        <v>0.212691397039005</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.2074350030269239</v>
+        <v>0.1609558667881472</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.9110447335607466</v>
+        <v>0.9462596674123076</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2409576225481818</v>
+        <v>0.248533676303065</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>86.27</v>
+        <v>136.35</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.003695573488368353</v>
+        <v>0.01729765852781084</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.02121627818846628</v>
+        <v>0.03592469980922464</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.0002318451370018071</v>
+        <v>0.009091243767520796</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.02254708186039311</v>
+        <v>0.01028747145619557</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.06093599263960114</v>
+        <v>0.1350039626633848</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.05262589064126177</v>
+        <v>0.1157420861975609</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.275424098738718</v>
+        <v>0.1260633799094044</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.235745154727955</v>
+        <v>0.1353688215038973</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.43755661749006</v>
+        <v>0.7581728692870191</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1286041755775855</v>
+        <v>0.2069441980630615</v>
       </c>
     </row>
     <row r="28">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>54.91</v>
+        <v>54.92</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.0001821187842496741</v>
+        <v>0.003104989387128887</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.0103036134133041</v>
+        <v>0.004205513768727798</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.01673980189493274</v>
+        <v>0.0165554314561529</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.02719272906220027</v>
+        <v>0.01766453451381045</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.02851443988893387</v>
+        <v>0.02643758282308917</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1013268874197724</v>
+        <v>0.1060121507362417</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.243541145296629</v>
+        <v>0.2400573475838088</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.2367332357246432</v>
+        <v>0.2315769006083825</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7103379106072287</v>
+        <v>0.7216200722229225</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1958975442445685</v>
+        <v>0.1985213435941513</v>
       </c>
     </row>
     <row r="29">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2118,37 +2118,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>29.26</v>
+        <v>107.24</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.02173184961037411</v>
+        <v>-0.008322559006460062</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.08160704116951478</v>
+        <v>-0.03064267806030074</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.1035538977932257</v>
+        <v>-0.02818305984010416</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.04316545775400527</v>
+        <v>-0.05606903188416701</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.1066565672414321</v>
+        <v>0.01051328684661201</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>-0.00712585983595504</v>
+        <v>0.06229411485523006</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.2457626017538341</v>
+        <v>0.3001099660667417</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1696930459358288</v>
+        <v>0.2347690140478842</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.5340436893446598</v>
+        <v>0.3913186314791934</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1533096064362873</v>
+        <v>0.1163718243373277</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>56.04</v>
+        <v>194.76</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01303272067063432</v>
+        <v>0.001182314959041308</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.03892986459100733</v>
+        <v>0.01968583511432431</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.03958864814055241</v>
+        <v>0.03469159500353491</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.006104131919763223</v>
+        <v>0.04205457927786171</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.03024905566376623</v>
+        <v>0.08545375456726778</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.008955328029041532</v>
+        <v>0.1562775876233875</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.241855016783858</v>
+        <v>0.1586215554522143</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2321085704494394</v>
+        <v>0.1239939565402435</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.8279592637917723</v>
+        <v>1.184007155803418</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2227063595652798</v>
+        <v>0.2974322403380472</v>
       </c>
     </row>
     <row r="31">
@@ -2230,37 +2230,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>20.05</v>
+        <v>20.25</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.004962798181780803</v>
+        <v>0.009632024742090017</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.01522600019635578</v>
+        <v>0.007973725657356878</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.01416281096680105</v>
+        <v>0.003031163279524796</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.09772788979252556</v>
+        <v>0.1383473119787493</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.2125793421279389</v>
+        <v>0.2307766585696509</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.1522988319900958</v>
+        <v>0.207945151181703</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.03377152687999474</v>
+        <v>0.01540310240618181</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.07441609132309601</v>
+        <v>-0.08448467658413183</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.151863976274524</v>
+        <v>0.1640894703759932</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.04825529645212523</v>
+        <v>0.05195086152384798</v>
       </c>
     </row>
     <row r="32">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2286,37 +2286,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>271.78</v>
+        <v>29.67</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.04336503716838991</v>
+        <v>0.003381818819809812</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.06956524101207195</v>
+        <v>-0.03824960423289192</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03934114997257399</v>
+        <v>-0.05629772352727236</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.0480891648532964</v>
+        <v>-0.01428572424339569</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.02003489498688937</v>
+        <v>0.09362333188717908</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.03564795343573046</v>
+        <v>0.02949342090459428</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.2438297083371015</v>
+        <v>0.1960422472357963</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.2860112409361613</v>
+        <v>0.140847368749152</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>1.313868780503996</v>
+        <v>0.5768590857544742</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.3226539771151147</v>
+        <v>0.1639409867605022</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>237.56</v>
+        <v>146.36</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.03489740625995319</v>
+        <v>0.01631835423342154</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.0485802585774695</v>
+        <v>0.01716589916728295</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.04972201952653743</v>
+        <v>-0.001637145178524757</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.0361582114173169</v>
+        <v>-0.01208230415037015</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.06470245776182404</v>
+        <v>0.09452387119743388</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.02367716137196763</v>
+        <v>0.1038771417878395</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1967653188059659</v>
+        <v>0.122515508851476</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2288012158624717</v>
+        <v>0.1219262485632111</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>1.118153619596244</v>
+        <v>0.7242043854297402</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.2842586061956147</v>
+        <v>0.1991207414271283</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>133.67</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.005793862361353375</v>
+        <v>0.006972690434744466</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.001498441195872058</v>
+        <v>0.02294117647058824</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.02288015214172379</v>
+        <v>0.01777640103956224</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.0005988609420448654</v>
+        <v>-0.0257752473465539</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.1077492716491038</v>
+        <v>0.05717202479958172</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.09188320876568068</v>
+        <v>0.0887593912540936</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.1085327898776529</v>
+        <v>0.1468654761536587</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1137018929900209</v>
+        <v>0.1791873800766897</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.7204855234513499</v>
+        <v>0.4909287187703559</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1982580102861293</v>
+        <v>0.1424020141156066</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>95.76000000000001</v>
+        <v>239.35</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.004826852777988222</v>
+        <v>-0.001335136094940514</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.006305153962073762</v>
+        <v>0.02094354039830093</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.002188174239882712</v>
+        <v>0.006052719176329324</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.01925437592349355</v>
+        <v>0.05538168873939808</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.04727047868980705</v>
+        <v>0.05447683239395773</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.08320454330486315</v>
+        <v>-0.009467685343217291</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1546702515251839</v>
+        <v>0.2358375219152578</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1775293588303151</v>
+        <v>0.1671080574287651</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.484429430777253</v>
+        <v>0.4196295524341567</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1407396018250597</v>
+        <v>0.1238931144045428</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>181.16</v>
+        <v>286.5</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.008863087471313591</v>
+        <v>-0.0006976358511168179</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.03745817331846668</v>
+        <v>-0.00153343011661855</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.02386978157872188</v>
+        <v>-0.02258459070504848</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.02304044380430526</v>
+        <v>0.1055799328740505</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.03501059801616579</v>
+        <v>0.04611678938179486</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.03514433209639156</v>
+        <v>0.2211755647868956</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.2449343579699745</v>
+        <v>0.08745164082665036</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.2843304250335186</v>
+        <v>0.0507205995936586</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.9240411842789535</v>
+        <v>0.7888361229338565</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.2437643981864017</v>
+        <v>0.2139203317642531</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>234.6</v>
+        <v>55.92</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.003059668529208914</v>
+        <v>-0.008334832874451248</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.003121439267839143</v>
+        <v>-0.04784609901571979</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.006996629927766174</v>
+        <v>-0.0408233464710287</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0.0601952611971226</v>
+        <v>-0.03068123591433414</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.04627390358550887</v>
+        <v>0.01962247982538745</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-0.02104024613014799</v>
+        <v>0.006613779775656692</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.2461825454560191</v>
+        <v>0.2004213690859413</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1700854400990452</v>
+        <v>0.202981971632322</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.3869136156393398</v>
+        <v>0.8275472690532513</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1151924073272814</v>
+        <v>0.2226144927409983</v>
       </c>
     </row>
     <row r="38">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>284.02</v>
+        <v>102.45</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.007929091003865074</v>
+        <v>-0.008900123574488994</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.03803560029238995</v>
+        <v>0.00451023722038979</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0.001975578831139968</v>
+        <v>-0.02437867951537764</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.04982619961184676</v>
+        <v>0.1644691184268776</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.05583639038539734</v>
+        <v>0.08998196313583473</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.1918589398926021</v>
+        <v>0.3068384784713125</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1111023958961606</v>
+        <v>0.00233985587347707</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.05780256615892698</v>
+        <v>-0.0464432907076564</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.7752358226264782</v>
+        <v>0.5107213271704421</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.210836073265686</v>
+        <v>0.1474350717044821</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>188.85</v>
+        <v>233.4</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.006993304361584407</v>
+        <v>-0.01660066782758784</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.01645741624771413</v>
+        <v>-0.07085988562103906</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.009623111587224731</v>
+        <v>-0.07060092637915438</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.005966070428095493</v>
+        <v>-0.02806698388562834</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.05839923417793935</v>
+        <v>0.03635729344793615</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.105223597834752</v>
+        <v>-0.03864331453663938</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1428621820647504</v>
+        <v>0.1645593809786907</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1068683577362404</v>
+        <v>0.1980348787483377</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.110001794353455</v>
+        <v>1.103075590049285</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.2826089759630093</v>
+        <v>0.2812040245669016</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>144.14</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.001108826463794177</v>
+        <v>0.006091355067219251</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.009142791090218316</v>
+        <v>0.01143085403975186</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.03578838656046657</v>
+        <v>0.0204922031846575</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.0156388267477634</v>
+        <v>-0.01696259424546409</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.07439706504893739</v>
+        <v>0.03310390288919463</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.0820046082527035</v>
+        <v>0.06214841859354925</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1136692935813541</v>
+        <v>0.1353313369903819</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.1069738341767936</v>
+        <v>0.1167061950066108</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.6997489429829316</v>
+        <v>0.3798510756620408</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.1934244375976786</v>
+        <v>0.1132962310781305</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>101.91</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.008753953096550249</v>
+        <v>0.01299737089896125</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.04111775656172445</v>
+        <v>0.01496455957154774</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.02504531823600287</v>
+        <v>-0.01920739523246617</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.09604215941889249</v>
+        <v>0.02114695199075811</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.09225366589513451</v>
+        <v>0.07877038254291868</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.2618112714978287</v>
+        <v>0.02177123671661962</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.01120149079671795</v>
+        <v>0.1244246443396357</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>-0.0413889551324278</v>
+        <v>0.05023309260234221</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.5180674091106219</v>
+        <v>0.4918811068163833</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1492919167481073</v>
+        <v>0.1426452134094596</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>60.24</v>
+        <v>76.23</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.009699163814371081</v>
+        <v>0.01208183305624622</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.01873265552394765</v>
+        <v>0.03517115682715821</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.01148665841839047</v>
+        <v>0.02749697868170986</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.01067495020031395</v>
+        <v>0.02349623954249047</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.002791537374437159</v>
+        <v>0.05190327847969334</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.00673990302332661</v>
+        <v>0.0015329290562478</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.2024584541638124</v>
+        <v>0.1438972779541685</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.1954564259675411</v>
+        <v>0.09628604677036434</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.6550662731651089</v>
+        <v>0.2686617488912595</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1828739372649748</v>
+        <v>0.08255162247368819</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>98.59999999999999</v>
+        <v>178.2</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.000101431256146034</v>
+        <v>-0.01508868533715746</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.0002028468522516924</v>
+        <v>-0.05813953582149989</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.005711929348881206</v>
+        <v>-0.0376410935336503</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.00884604798066857</v>
+        <v>0.004509600221433097</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.03087430371090694</v>
+        <v>-0.07055111628032462</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.0595739747682047</v>
+        <v>0.01247242005609195</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1510058889340729</v>
+        <v>0.2130841319533854</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1292019168220842</v>
+        <v>0.2430705703620042</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.3803989044136944</v>
+        <v>0.8807956970683557</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1134435452821561</v>
+        <v>0.2343752563793724</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>23.93</v>
+        <v>265.61</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.003746883883126717</v>
+        <v>-0.02614213220688844</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.01845770595082619</v>
+        <v>-0.09923020398869831</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.01098437803311336</v>
+        <v>-0.07867086101190823</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.006641753690272201</v>
+        <v>-0.01263902565196284</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.07455305857775096</v>
+        <v>-0.02032622819584862</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.02192973989289393</v>
+        <v>-0.06053907208309173</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.2431619814870487</v>
+        <v>0.1890655525833309</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.2830590490694809</v>
+        <v>0.2330343532957873</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5868945418504425</v>
+        <v>1.276406973381285</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1664049538122361</v>
+        <v>0.3154771309262718</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>86.73</v>
+        <v>23.76</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.02364064427371138</v>
+        <v>-0.004191130717169478</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.02867059617364809</v>
+        <v>-0.02382908463722366</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.03472448714716592</v>
+        <v>0.002954820314317264</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.02484820130209242</v>
+        <v>-0.01164728269476301</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.07358126206115889</v>
+        <v>-0.08920004044723295</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.01700815949269874</v>
+        <v>0.005258993889079688</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.1299779140962816</v>
+        <v>0.2324219289109892</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.04352888852578363</v>
+        <v>0.2487830536346594</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.3870979195986841</v>
+        <v>0.5567693396090245</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1152418036439458</v>
+        <v>0.1589768374955602</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>74.98</v>
+        <v>59.71</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.001198832266637528</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.007389534455229052</v>
+        <v>-0.03864114478013558</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.005767944836665428</v>
+        <v>-0.01744283964631099</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.006578138101979825</v>
+        <v>-0.04753548584329848</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.040795262559429</v>
+        <v>-0.01728553615310358</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.004042003572663599</v>
+        <v>-0.00294423046188319</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.1284578601417952</v>
+        <v>0.1642460844733846</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.07469917752170407</v>
+        <v>0.1582853761292966</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.2377160250614165</v>
+        <v>0.6525166628167181</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.07367705297070337</v>
+        <v>0.1822662239177246</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>61.15</v>
+        <v>13.44</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0</v>
+        <v>0.01128665304445642</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0</v>
+        <v>0.01972680342848077</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0</v>
+        <v>0.009009000623754648</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0</v>
+        <v>0.08914095739007943</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.01733224247203835</v>
+        <v>0.1065110411937404</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.1727788613367855</v>
+        <v>0.08165879111829111</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.05368904063349733</v>
+        <v>0.02880882940286233</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.0156525820938912</v>
+        <v>-0.05622751001056292</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.854123692916507</v>
+        <v>0.2095047083865942</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.228512466375254</v>
+        <v>0.06545682192352476</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>13.29</v>
+        <v>72.41</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.002262423261943036</v>
+        <v>-0.001100784104757557</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.0184638109825952</v>
+        <v>0.01785497115007817</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.01295732300128005</v>
+        <v>-0.01065446630724387</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0.05727925891082353</v>
+        <v>0.04427755769578634</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.08279139017840342</v>
+        <v>0.1120730927980731</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.06958665462679803</v>
+        <v>-0.07627087878723882</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.04826632854733814</v>
+        <v>0.09357293510830078</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.0667605961663692</v>
+        <v>-0.03415296264530521</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1921552661916834</v>
+        <v>0.05958893404188803</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.06033787324362971</v>
+        <v>0.01948100408496667</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>71.47</v>
+        <v>61.15</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.005288757988698323</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.01270891251142725</v>
+        <v>0</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.01420687971443968</v>
+        <v>0</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.04442497299386106</v>
+        <v>0</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.09446930415906274</v>
+        <v>-0.006834612586222644</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.1035605552772438</v>
+        <v>0.1737265728073003</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.094051324335088</v>
+        <v>0.02625609124376327</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.01726293765672415</v>
+        <v>-0.02589689989407251</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.04597587438440431</v>
+        <v>0.8552509686293264</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01509624796383835</v>
+        <v>0.2287613875065113</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>48.4</v>
+        <v>27.42</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.0008257040042115582</v>
+        <v>-0.004823439932708062</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0.00770357601469529</v>
+        <v>0.04120372932118221</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0.02195947850769309</v>
+        <v>0.05433534396887807</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.002884206572061565</v>
+        <v>0.09527059818445704</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.002384397977841846</v>
+        <v>0.1068031300230829</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.03042316438079384</v>
+        <v>0.1783583966227018</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.1232866646245048</v>
+        <v>-0.05796319288236795</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.01747828095981174</v>
+        <v>-0.1872819951666668</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.1372243639678699</v>
+        <v>0.3440913718502245</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.0437954157820597</v>
+        <v>0.103594678716546</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>19.49</v>
+        <v>48.99</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.002469026065070379</v>
+        <v>0.007714461947983198</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0.01267859031233431</v>
+        <v>0.02521979618753822</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.0386378375521208</v>
+        <v>0.04156925115454824</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>0.001850676352346925</v>
+        <v>0.02201127265717662</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>0.04773939553218365</v>
+        <v>0.01363135907226432</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.08858853004071454</v>
+        <v>-0.03219143929175883</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.03089190215280802</v>
+        <v>0.117581570221321</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>-0.1614988007811355</v>
+        <v>0.02530926856735238</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.2120634718788934</v>
+        <v>0.1693809289207941</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.06620763387480766</v>
+        <v>0.05354236047446004</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>26.81</v>
+        <v>19.85</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0.005663952641663528</v>
+        <v>0.01014758025400053</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.0110291324103764</v>
+        <v>0.01974823586176</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>0.02830517665963583</v>
+        <v>0.04251043131321341</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.04673227487176557</v>
+        <v>0.04928898656134395</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.07236500864311779</v>
+        <v>0.07672363122771064</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0.1279875144231475</v>
+        <v>0.1182760319239657</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.04115538684279185</v>
+        <v>0.02278815764308639</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.178882683039299</v>
+        <v>-0.1674072831927558</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.2973207793955348</v>
+        <v>0.2333863303303019</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.0906426027052003</v>
+        <v>0.07242363540522123</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>105.62</v>
+        <v>45.69</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.02411531487940544</v>
+        <v>-0.008248341016549365</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.03569794646481728</v>
+        <v>0.009723726557104628</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.02931711132788073</v>
+        <v>0.0295177450893509</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.004242452621258441</v>
+        <v>0.1453998326850228</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.06927232873758227</v>
+        <v>-0.06678922628494766</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.1077902739274449</v>
+        <v>-0.168516870021152</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.06830246182626309</v>
+        <v>0.1058233978089897</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>-0.05249727000918158</v>
+        <v>0.2137701680510042</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.3576413106327292</v>
+        <v>1.259292493118767</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.1072907741893858</v>
+        <v>0.3121721616852913</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>43.77</v>
+        <v>106.29</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.005679236651527808</v>
+        <v>-0.001971822389414624</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.006130800457555763</v>
+        <v>-0.01756171072191182</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>0.00899030382770305</v>
+        <v>-0.01801549322549367</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.02603467300174667</v>
+        <v>-0.01982664586383265</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-0.01034613087670544</v>
+        <v>0.06432737324271098</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.04257584349636578</v>
+        <v>-0.08918572542508529</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.01544597814896598</v>
+        <v>0.0338218759108877</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>0.0442288507136932</v>
+        <v>-0.0846274176488514</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.5089581395880995</v>
+        <v>0.3653953000070467</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.1469885011765455</v>
+        <v>0.1093948220242442</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>43.84</v>
+        <v>112.32</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.02599418379417207</v>
+        <v>0.008258511277772218</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.03116021762236709</v>
+        <v>0.01353546295010544</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.01481480042466754</v>
+        <v>0.004381631545618658</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.1336954287159613</v>
+        <v>0.05663213988935878</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.08742715826181302</v>
+        <v>-0.02466479907488284</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.1935246567263722</v>
+        <v>-0.02744869830656449</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.09078086305036903</v>
+        <v>0.002896149069998577</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.2601585846354728</v>
+        <v>0.02176421993280453</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1.237555556096386</v>
+        <v>0.778905969723813</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.3079504021445061</v>
+        <v>0.2116699319683837</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>96.73999999999999</v>
+        <v>45.8</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.02538791273651531</v>
+        <v>0.001968937965226569</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.02803175876364716</v>
+        <v>0.01193108562866274</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.01756883655415109</v>
+        <v>0.005267731706220413</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.01393977728342066</v>
+        <v>0.01103752777971234</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>0.07498245298421358</v>
+        <v>0.004165722959141194</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.1246572641634346</v>
+        <v>-0.09217049465923488</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.0369575926963619</v>
+        <v>0.02014043654266207</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.09941534714282763</v>
+        <v>0.002448804219735035</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.192303211372401</v>
+        <v>0.3248729771352223</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.06038173369088407</v>
+        <v>0.09830951830926038</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>45.69</v>
+        <v>55.88</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.004175793993604016</v>
+        <v>-0.005162846898407181</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0.0008761686635958554</v>
+        <v>0.0145243139154998</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.004575226409339495</v>
+        <v>0.007754739391512722</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.004175793993604016</v>
+        <v>0.1124826115343294</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.006955003401390103</v>
+        <v>0.1066740300855091</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.09846096385988345</v>
+        <v>-0.05726583152427001</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.03195278783033539</v>
+        <v>-0.1150088592110421</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.006772669526038388</v>
+        <v>-0.107349672683052</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.3280645887741378</v>
+        <v>0.1063651880999674</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.09919075156752521</v>
+        <v>0.0342673954305599</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>17.63</v>
+        <v>97.81</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.01121709275351934</v>
+        <v>0.003282384878819933</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.03976042621552955</v>
+        <v>-0.0003066105930060736</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.0270420339830143</v>
+        <v>-0.005894926665846789</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.02811467729005912</v>
+        <v>0.007415812626023754</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.1785632779843298</v>
+        <v>0.07695581299329257</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.06518674072061104</v>
+        <v>-0.1088690528488604</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.1078887839049232</v>
+        <v>0.003792521207997446</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.238002228704753</v>
+        <v>-0.1282404319741842</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1557070430734575</v>
+        <v>0.2101333972185575</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.04941979829830001</v>
+        <v>0.06564139465946117</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>55.45</v>
+        <v>43.22</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.02100986298609442</v>
+        <v>0.01052141122569861</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.01176260631318449</v>
+        <v>-0.02172926839840217</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0.02476437141883059</v>
+        <v>0.002086718069998605</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>0.09628309125316648</v>
+        <v>-0.06632101175427785</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>0.09103840266390817</v>
+        <v>-0.04088235142238517</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.06373227890306632</v>
+        <v>-0.07203221405533422</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.09007570597469305</v>
+        <v>-0.01002309041821914</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1102560935330482</v>
+        <v>0.03266533758399159</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.09146268344711217</v>
+        <v>0.4980192325236705</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.02960260015602056</v>
+        <v>0.1442101511038905</v>
       </c>
     </row>
     <row r="60">
@@ -3840,51 +3840,51 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>35.81</v>
+        <v>17.43</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.01566794057419052</v>
+        <v>-0.009096068563056225</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.05314643939059249</v>
+        <v>-0.03754833143335723</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.03059007296770555</v>
+        <v>-0.03595130648634626</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.0455474853515625</v>
+        <v>-0.01968506006485204</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.08718701043532728</v>
+        <v>-0.2201346271664504</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.08180651201624145</v>
+        <v>-0.08927657585516668</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.08774519488419918</v>
+        <v>0.08120048305549288</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>0.08446696032087009</v>
+        <v>0.2005969390778188</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.4211783710092467</v>
+        <v>0.1498006985616074</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.1243016890392368</v>
+        <v>0.04762902618657017</v>
       </c>
     </row>
     <row r="61">
@@ -3896,51 +3896,51 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>110.68</v>
+        <v>35.25</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.005749186052847244</v>
+        <v>-0.02192011363648394</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.01661486180255445</v>
+        <v>-0.06795345625494364</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.004497211716383842</v>
+        <v>-0.05799033338131443</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.001083057249790631</v>
+        <v>0.04197452237918031</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.04420379453830892</v>
+        <v>-0.1246555795986607</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.04690027156056464</v>
+        <v>-0.09593356895645044</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.01557193371047583</v>
+        <v>0.03962162831725791</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.02022703860463615</v>
+        <v>0.04761629431557335</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.7596676014047938</v>
+        <v>0.3864096067395713</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.2072861339600116</v>
+        <v>0.1150573027826047</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>49.73</v>
+        <v>48.32</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.01466220845192379</v>
+        <v>-0.02027575032821716</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.05222034714544033</v>
+        <v>-0.05106045890839717</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.02965854551733993</v>
+        <v>-0.06826071874015249</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.05617762690493233</v>
+        <v>-0.05772229241291804</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2096312620876556</v>
+        <v>-0.2673237008222162</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1679772601410985</v>
+        <v>-0.2017181452289877</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.08913709392083802</v>
+        <v>0.04003445215247958</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.2120399956562842</v>
+        <v>0.1534972642364067</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1225709778521613</v>
+        <v>-0.1242533357651183</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.04265016876995342</v>
+        <v>-0.04326242552526005</v>
       </c>
     </row>
   </sheetData>
@@ -4158,17 +4158,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.4115069478290252</v>
+        <v>0.3763125919890651</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4624,21 +4624,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.07639008976928319</v>
+        <v>-0.06632101175427785</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.36479476384883</v>
+        <v>0.3304612870941879</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.05617762690493233</v>
+        <v>-0.05772229241291804</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.2179170167315752</v>
+        <v>0.2385263715522423</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.04316545775400527</v>
+        <v>-0.05606903188416701</v>
       </c>
     </row>
     <row r="20">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.217573782318274</v>
+        <v>0.2162892086280088</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.02811467729005912</v>
+        <v>-0.04753548584329848</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1735215823117939</v>
+        <v>0.2006935903494607</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.02603467300174667</v>
+        <v>-0.03068123591433414</v>
       </c>
     </row>
     <row r="22">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1640689145895042</v>
+        <v>0.1686555240277376</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.02484820130209242</v>
+        <v>-0.02806698388562834</v>
       </c>
     </row>
     <row r="23">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1386831664625621</v>
+        <v>0.1644691184268776</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.02254708186039311</v>
+        <v>-0.0257752473465539</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.1336954287159613</v>
+        <v>0.158541431310139</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.01925437592349355</v>
+        <v>-0.02571259233649537</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.1302739677841829</v>
+        <v>0.1453998326850228</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.0156388267477634</v>
+        <v>-0.0256419654410005</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.1296892139263572</v>
+        <v>0.1383473119787493</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.01554882480782749</v>
+        <v>-0.01982664586383265</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3512215111005108</v>
+        <v>0.3527085481915295</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2096312620876556</v>
+        <v>-0.2673237008222162</v>
       </c>
     </row>
     <row r="32">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2639291968772322</v>
+        <v>0.2593156439456339</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1785632779843298</v>
+        <v>-0.2201346271664504</v>
       </c>
     </row>
     <row r="33">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2557896526849146</v>
+        <v>0.258873820678748</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1183387139529989</v>
+        <v>-0.2022644751892749</v>
       </c>
     </row>
     <row r="34">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.241670166880777</v>
+        <v>0.2481479135518203</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1028793924870881</v>
+        <v>-0.1246555795986607</v>
       </c>
     </row>
     <row r="35">
@@ -5293,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2162637396173164</v>
+        <v>0.2307766585696509</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.08742715826181302</v>
+        <v>-0.09285734308861049</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2125793421279389</v>
+        <v>0.2178311574183212</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.08718701043532728</v>
+        <v>-0.08920004044723295</v>
       </c>
     </row>
     <row r="37">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1810845035459363</v>
+        <v>0.2111936924558484</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.0775541200860993</v>
+        <v>-0.07939904648720297</v>
       </c>
     </row>
     <row r="38">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1717588755305355</v>
+        <v>0.1589743084281259</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.07455305857775096</v>
+        <v>-0.07055111628032462</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.156206551278701</v>
+        <v>0.1551924244333998</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.04420379453830892</v>
+        <v>-0.06678922628494766</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1453631071360175</v>
+        <v>0.140715273389949</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.03501059801616579</v>
+        <v>-0.05122157682553441</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4799784192124557</v>
+        <v>0.5380404685630704</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1935246567263722</v>
+        <v>-0.2017181452289877</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4662440475289116</v>
+        <v>0.5179024107879282</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1679772601410985</v>
+        <v>-0.168516870021152</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4617009841636663</v>
+        <v>0.4924569806033121</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1246572641634346</v>
+        <v>-0.1088690528488604</v>
       </c>
     </row>
     <row r="48">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3927933371855714</v>
+        <v>0.3440925851826981</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1077902739274449</v>
+        <v>-0.1001930977010621</v>
       </c>
     </row>
     <row r="49">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.3556851940075456</v>
+        <v>0.3068384784713125</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.1035605552772438</v>
+        <v>-0.09593356895645044</v>
       </c>
     </row>
     <row r="50">
@@ -5849,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3316122609599257</v>
+        <v>0.3045137489638723</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.09846096385988345</v>
+        <v>-0.09217049465923488</v>
       </c>
     </row>
     <row r="51">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3106297919870251</v>
+        <v>0.2838703735345112</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.09425140055093906</v>
+        <v>-0.08927657585516668</v>
       </c>
     </row>
     <row r="52">
@@ -5939,21 +5939,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2778204633315782</v>
+        <v>0.2813531471064719</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.08180651201624145</v>
+        <v>-0.08918572542508529</v>
       </c>
     </row>
     <row r="53">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2702747088483035</v>
+        <v>0.2723068130390858</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.06518674072061104</v>
+        <v>-0.07627087878723882</v>
       </c>
     </row>
     <row r="54">
@@ -6029,21 +6029,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2618112714978287</v>
+        <v>0.258787546998823</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.06373227890306632</v>
+        <v>-0.07203221405533422</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.995924098936483</v>
+        <v>1.013591892676134</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.178882683039299</v>
+        <v>-0.1872819951666668</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.9532141786388142</v>
+        <v>0.8679382482486457</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1614988007811355</v>
+        <v>-0.1674072831927558</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.8605259185200824</v>
+        <v>0.8360829737134441</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6247,21 +6247,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1102560935330482</v>
+        <v>-0.1282404319741842</v>
       </c>
     </row>
     <row r="62">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.839585106525542</v>
+        <v>0.8139175228184441</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6292,21 +6292,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09941534714282763</v>
+        <v>-0.107349672683052</v>
       </c>
     </row>
     <row r="63">
@@ -6315,21 +6315,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.8173752459129875</v>
+        <v>0.7467300650312909</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.07441609132309601</v>
+        <v>-0.0846274176488514</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.789698346825636</v>
+        <v>0.7445211595022221</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6382,21 +6382,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.0667605961663692</v>
+        <v>-0.08448467658413183</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.7649253293171467</v>
+        <v>0.7330007848257154</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6427,21 +6427,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.05249727000918158</v>
+        <v>-0.05622751001056292</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.7623360157144299</v>
+        <v>0.6872002562489001</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.0413889551324278</v>
+        <v>-0.0464432907076564</v>
       </c>
     </row>
     <row r="67">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.7245401964579796</v>
+        <v>0.6678391318130437</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.01726293765672415</v>
+        <v>-0.03415296264530521</v>
       </c>
     </row>
     <row r="68">
@@ -6540,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.6704623110202306</v>
+        <v>0.6487726177322406</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.0156525820938912</v>
+        <v>-0.02589689989407251</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.084114827510716</v>
+        <v>3.065531159540543</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1225709778521613</v>
+        <v>-0.1242533357651183</v>
       </c>
     </row>
     <row r="74">
@@ -6691,21 +6691,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.902822102304913</v>
+        <v>2.739504322336177</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.04597587438440431</v>
+        <v>0.05958893404188803</v>
       </c>
     </row>
     <row r="75">
@@ -6736,21 +6736,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.767825214887752</v>
+        <v>2.724319714352051</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.09146268344711217</v>
+        <v>0.1063651880999674</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.662288889962444</v>
+        <v>1.903162005237858</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6803,21 +6803,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1372243639678699</v>
+        <v>0.1498006985616074</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.652790905981059</v>
+        <v>1.754785208663779</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.151863976274524</v>
+        <v>0.1640894703759932</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.493528760024005</v>
+        <v>1.403044777355776</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6893,21 +6893,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1537550379016577</v>
+        <v>0.1693809289207941</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.336638589614314</v>
+        <v>1.380239069138207</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6938,21 +6938,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1557070430734575</v>
+        <v>0.1815290792320881</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.313868780503996</v>
+        <v>1.306897648685217</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1921552661916834</v>
+        <v>0.2095047083865942</v>
       </c>
     </row>
     <row r="81">
@@ -7006,21 +7006,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.280026876911797</v>
+        <v>1.276406973381285</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.192303211372401</v>
+        <v>0.2101333972185575</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.237555556096386</v>
+        <v>1.259292493118767</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2120634718788934</v>
+        <v>0.2333863303303019</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -490,12 +490,12 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>39.67</v>
+        <v>41.48</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.01022963182081738</v>
+        <v>0.04562645467193227</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.1062464443320152</v>
+        <v>0.152862703445664</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.1250709034979998</v>
+        <v>0.1784090523631128</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.2385263715522423</v>
+        <v>0.2950359389038635</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3527085481915295</v>
+        <v>0.4144278434499256</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.2813531471064719</v>
+        <v>0.3524758010776912</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.4968864681086271</v>
+        <v>0.5376138514779003</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.7445211595022221</v>
+        <v>0.8933565217451869</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.8811853731296575</v>
+        <v>0.9580436441610367</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.2344604992499379</v>
+        <v>0.2510484311422119</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>164.17</v>
+        <v>169.1</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.009412886012248434</v>
+        <v>0.03002989577606563</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.02908543487214388</v>
+        <v>0.05614893172752145</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.03885337870706107</v>
+        <v>0.06977920078584643</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.09097556373003579</v>
+        <v>0.1237374462030834</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2481479135518203</v>
+        <v>0.2856296653088952</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2723068130390858</v>
+        <v>0.3195041526595619</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.3787824731453153</v>
+        <v>0.3992418279461551</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.8139175228184441</v>
+        <v>0.913210517865559</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.122940826059083</v>
+        <v>1.162516074268487</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2852253892741008</v>
+        <v>0.2931625375630991</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>94.53</v>
+        <v>15.06</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.0006342907380969542</v>
+        <v>0.02552757050454701</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.08232199156032038</v>
+        <v>0.09008682438866855</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.05608308036264131</v>
+        <v>0.09245827571118759</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.2162892086280088</v>
+        <v>0.198488460312884</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1379872850941843</v>
+        <v>0.1885601067994833</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.01586415064019131</v>
+        <v>0.2898115742092504</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.6176515189347465</v>
+        <v>0.6321777169593679</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1.013591892676134</v>
+        <v>0.7723528918098002</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.754785208663779</v>
+        <v>2.049595021434023</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4018318212799878</v>
+        <v>0.4501537722664573</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>14.69</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.004067825058759245</v>
+        <v>0.01893579751023311</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.04928568431309288</v>
+        <v>0.1256281411515563</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.06449270850343702</v>
+        <v>0.08725593945676025</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.1686555240277376</v>
+        <v>0.2393206147964704</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1589743084281259</v>
+        <v>0.1595359818939477</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2375736918291802</v>
+        <v>0.01669811957409162</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5984766323319684</v>
+        <v>0.6314276402811283</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7467300650312909</v>
+        <v>1.051295153891555</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.903162005237858</v>
+        <v>1.805408934991207</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.4265612526648261</v>
+        <v>0.4103667431223594</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>72.68000000000001</v>
+        <v>555.8200000000001</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.00164838930702671</v>
+        <v>0.01649601267852474</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.03209318652364179</v>
+        <v>-0.02448358412839613</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.03665667768436398</v>
+        <v>-0.02986400706943781</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.06961005988766211</v>
+        <v>-0.009568942949492731</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.258873820678748</v>
+        <v>-0.03557051592773763</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.2551196553764945</v>
+        <v>0.3042519301386932</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3695122742781598</v>
+        <v>0.6398031563836784</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5457126745004974</v>
+        <v>0.8969428710457421</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.7521557281617683</v>
+        <v>2.778900488309921</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2055657491939105</v>
+        <v>0.55759717866082</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>546.8</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.02430319319889596</v>
+        <v>0.01224545109949671</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.07956977956884459</v>
+        <v>0.01545897575926958</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.03970774383648434</v>
+        <v>0.05491829578968765</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.0256419654410005</v>
+        <v>0.08270791757154616</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.05122157682553441</v>
+        <v>0.2742892984903063</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3045137489638723</v>
+        <v>0.2622236364783486</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.6174257845455791</v>
+        <v>0.3627560864586408</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.8679382482486457</v>
+        <v>0.5939460258242291</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.724319714352051</v>
+        <v>0.7617223539453544</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5500616991536957</v>
+        <v>0.2077558645915345</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>212.53</v>
+        <v>216.4</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.004822994901066524</v>
+        <v>0.01820917112603149</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.052493470450103</v>
+        <v>0.06307720815429207</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.06254371682641913</v>
+        <v>0.08340837060751194</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.1296375011628197</v>
+        <v>0.1502072637318761</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2593156439456339</v>
+        <v>0.2822467380079285</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2061416699479359</v>
+        <v>0.2355305092267588</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.2547593660352556</v>
+        <v>0.2581835886505053</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5236763655541357</v>
+        <v>0.5827732277882587</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6893953383835563</v>
+        <v>0.7104499920670619</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1909963499301843</v>
+        <v>0.1959236667657247</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>109.57</v>
+        <v>102.8</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.01836591113881325</v>
+        <v>0.02421042381866956</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.05183452743439487</v>
+        <v>0.1744545239965511</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.08071149047346671</v>
+        <v>0.1321585858665639</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.04173796707464361</v>
+        <v>0.3626723187290708</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1551924244333998</v>
+        <v>0.1683324736151492</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.5380404685630704</v>
+        <v>-0.09118230728315335</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.3346007876635313</v>
+        <v>0.5001443452564853</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.3171267595971754</v>
+        <v>0.8925066973774203</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.186163089851748</v>
+        <v>3.185095936388366</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2978590183107437</v>
+        <v>0.6115179203700585</v>
       </c>
     </row>
     <row r="10">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>100.37</v>
+        <v>105.52</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.008237063482538387</v>
+        <v>0.01912300280115353</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1063712675929362</v>
+        <v>0.1862844324150554</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1117634482024275</v>
+        <v>0.1708831938209017</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.3304612870941879</v>
+        <v>0.4026318215409348</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.140715273389949</v>
+        <v>0.2411197460529637</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>-0.1001930977010621</v>
+        <v>-0.0507377368948887</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.4798319323950051</v>
+        <v>0.3661485350224098</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.8360829737134441</v>
+        <v>0.7637963039479443</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>3.065531159540543</v>
+        <v>2.848588569227107</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.5960228250563313</v>
+        <v>0.5671136563157424</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>103.54</v>
+        <v>108.09</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.006904590798696653</v>
+        <v>-0.01350737757648734</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.1267820394304116</v>
+        <v>-0.06236990386486285</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1442148674973367</v>
+        <v>-0.09015156934971746</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.3763125919890651</v>
+        <v>0.02766681901760415</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.2178311574183212</v>
+        <v>0.13958880418308</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>-0.06467927940470042</v>
+        <v>0.4882280108141392</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.337762742004565</v>
+        <v>0.293277165483135</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.7330007848257154</v>
+        <v>0.3098777268755866</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>2.739504322336177</v>
+        <v>1.124955763122969</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.5521654536871292</v>
+        <v>0.2856318740540713</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>27.7</v>
+        <v>151.96</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.01247766430091968</v>
+        <v>0.01536818786234018</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.006456183760595202</v>
+        <v>0.003433731273625229</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.01388392266037453</v>
+        <v>0.0002633527211959308</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.2006935903494607</v>
+        <v>0.04749430648507436</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.2111936924558484</v>
+        <v>0.01735245767999705</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.4924569806033121</v>
+        <v>0.2650421786539643</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2338529987342681</v>
+        <v>0.4713513239589857</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2311111450195313</v>
+        <v>0.5340298159845249</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.4263646062881807</v>
+        <v>1.337276181745597</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1256676481502936</v>
+        <v>0.3270990688575082</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>186.24</v>
+        <v>27.48</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.0174105091793848</v>
+        <v>-0.007942282117099131</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.01576219958245773</v>
+        <v>-0.009729746225717872</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.05860292870234463</v>
+        <v>-0.01716736616428904</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.07003735838936631</v>
+        <v>0.1911573431187126</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.08841423612300114</v>
+        <v>0.2015740504519132</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2563854170076443</v>
+        <v>0.4617021626290732</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4467384680705093</v>
+        <v>0.1979075371614945</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4816300057442271</v>
+        <v>0.23728053466909</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3872569344519201</v>
+        <v>0.396341418501359</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1152844185723247</v>
+        <v>0.1177136123041</v>
       </c>
     </row>
     <row r="14">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>93.23</v>
+        <v>490.93</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.01707954816287638</v>
+        <v>0.01937289546101084</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.04663050941714131</v>
+        <v>-0.05178274435872177</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.07326038995003958</v>
+        <v>-0.07390917688486387</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.05463802881995106</v>
+        <v>-0.006837824238850931</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.107144918343389</v>
+        <v>-0.1868100282615821</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.5179024107879282</v>
+        <v>0.3522220957617839</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2937166171564909</v>
+        <v>0.5832994268475196</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.2914165351631244</v>
+        <v>0.7363982642919</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.102566833491946</v>
+        <v>1.435969464511421</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2811007039001339</v>
+        <v>0.3455214120630428</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>149.66</v>
+        <v>182.73</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.009223460491253221</v>
+        <v>-0.01884670136435229</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.03844256037461879</v>
+        <v>-0.01413547499164003</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.01072976914323431</v>
+        <v>0.02444357644057282</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.03161778286766359</v>
+        <v>0.04987068384710147</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.001932784063071624</v>
+        <v>0.06790121805408122</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.258787546998823</v>
+        <v>0.2424260407272048</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.4570062148404634</v>
+        <v>0.4261214722663904</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.5021193436436537</v>
+        <v>0.4387169636823891</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.306897648685217</v>
+        <v>0.3437666422421484</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.3213243611856211</v>
+        <v>0.103505796184862</v>
       </c>
     </row>
     <row r="16">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>481.6</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.03337816774603897</v>
+        <v>-0.00825918958205929</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.1233116420438366</v>
+        <v>-0.05110840755497958</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.08336508617294713</v>
+        <v>-0.0746597199877771</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.02571259233649537</v>
+        <v>0.04592757339947773</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.2022644751892749</v>
+        <v>0.09800079856797761</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.3440925851826981</v>
+        <v>0.4782399370984411</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.5647982905389661</v>
+        <v>0.2628125974937807</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.6872002562489001</v>
+        <v>0.2883834095393756</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>1.403044777355776</v>
+        <v>1.059073505723657</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.3394318482025291</v>
+        <v>0.2722055431320056</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>107.65</v>
+        <v>108.91</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.004244420186638287</v>
+        <v>0.01161062565001503</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.005955717952774942</v>
+        <v>0.02080795922675449</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.02194059164370932</v>
+        <v>-0.003932620177272139</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.0402454440187543</v>
+        <v>0.05237226698443398</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.009234092315174802</v>
+        <v>0.02099939562777831</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.07838321952036686</v>
+        <v>0.07110546159750131</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.4025170760410619</v>
+        <v>0.3868506441618464</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5395503184539641</v>
+        <v>0.55640223043893</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.7857397907577623</v>
+        <v>0.8024145448705204</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2132195276134305</v>
+        <v>0.2169840727429497</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>408.71</v>
+        <v>405.69</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.01593912149667442</v>
+        <v>-0.007389075571458847</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.04193627377514952</v>
+        <v>-0.03519700382099333</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.00639374946814586</v>
+        <v>-0.02313986427650261</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.04353262430053495</v>
+        <v>0.03582188287829546</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.07939904648720297</v>
+        <v>-0.08620143650386614</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.01948116158018798</v>
+        <v>0.01924478980378752</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.4712995921701681</v>
+        <v>0.4478761219728882</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.6487726177322406</v>
+        <v>0.6384739186884369</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.2985232393772841</v>
+        <v>0.2900960251108557</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.09097946339194896</v>
+        <v>0.08861424356046865</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>57.27</v>
+        <v>57</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.005442439927558329</v>
+        <v>-0.004714518170168214</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.01813334147135426</v>
+        <v>0.009206807046356458</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.0005235389126754253</v>
+        <v>0.01171458724928298</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.01380773156525139</v>
+        <v>0.00902811659373004</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1315144572520734</v>
+        <v>0.1261799117835503</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2838703735345112</v>
+        <v>0.2581545246874235</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1982497222265898</v>
+        <v>0.1683656159367792</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2311151019404041</v>
+        <v>0.2355568499146774</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1815290792320881</v>
+        <v>0.1745032738567558</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05717805213150662</v>
+        <v>0.05507842872297086</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>31.13</v>
+        <v>120.94</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.01174605838836185</v>
+        <v>0.02604564030955903</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02468729495452271</v>
+        <v>0.06433164978157557</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.04428043336036636</v>
+        <v>0.02639396216602541</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.06865774313834083</v>
+        <v>0.1887163847137645</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.03191399164015563</v>
+        <v>0.03376394636062297</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1618765108462719</v>
+        <v>0.01353976017393776</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.3261034893215953</v>
+        <v>0.3052691731774988</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3606666589967518</v>
+        <v>0.5050476356131941</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.3179066412426645</v>
+        <v>1.442718457972188</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.09638112146179978</v>
+        <v>0.3467628810591052</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>68.81</v>
+        <v>30.54</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01250733498487189</v>
+        <v>-0.01895272281223948</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.008500574133435412</v>
+        <v>-0.006506143691605626</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.02563722335056551</v>
+        <v>0.01596811237900386</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.05812700061898646</v>
+        <v>0.04840376915148648</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.1368365777188796</v>
+        <v>0.01235641179052815</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.139630682168179</v>
+        <v>0.1466329746792341</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2217861386846798</v>
+        <v>0.3108508453815095</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1620604077722079</v>
+        <v>0.3230254977141271</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.7390423418808807</v>
+        <v>0.281903651127311</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.2025506722090289</v>
+        <v>0.08630504086901247</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>77.03</v>
+        <v>68.78</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.005482289069301594</v>
+        <v>-0.0004359654172539917</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01036202698928412</v>
+        <v>0.01475361490129523</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.03063956356677155</v>
+        <v>0.02032332061654474</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.135968169188271</v>
+        <v>0.05766569383965381</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.09285734308861049</v>
+        <v>0.136340956285925</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.02343075605018141</v>
+        <v>0.1385701700372501</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2862077285516247</v>
+        <v>0.1895080199573169</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.6678391318130437</v>
+        <v>0.1680276072854574</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.3854695983281289</v>
+        <v>0.7439504280402232</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.114805236770116</v>
+        <v>0.2036809261537262</v>
       </c>
     </row>
     <row r="23">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>117.87</v>
+        <v>76.59</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.01231769428873253</v>
+        <v>-0.005712092021018078</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.001947465965373874</v>
+        <v>0.03472034330421647</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.002807570431208717</v>
+        <v>0.03346371214565425</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.158541431310139</v>
+        <v>0.1294794144729203</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.007522380825803587</v>
+        <v>-0.09803902542107912</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.01127809756820264</v>
+        <v>-0.002215167321317324</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.2925911842182873</v>
+        <v>0.2567720258793178</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.4763618985477249</v>
+        <v>0.6622435344435043</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>1.380239069138207</v>
+        <v>0.3756289130531152</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.3351811523429973</v>
+        <v>0.1121595576378009</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>74.76000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.001335806482845037</v>
+        <v>0.005412889678588328</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.03398368360459958</v>
+        <v>0.01299608659336204</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.01670388877360118</v>
+        <v>0.003679003017636795</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.01280867790446649</v>
+        <v>-0.008179886602680431</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.08400195628146778</v>
+        <v>0.07373473616727111</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1014116112321484</v>
+        <v>0.09114795530851771</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.2343019534053656</v>
+        <v>0.2308607301097951</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1809970100076792</v>
+        <v>0.2368227885412648</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.8506220696700277</v>
+        <v>0.4690301752000299</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2277386059736752</v>
+        <v>0.1367812599682521</v>
       </c>
     </row>
     <row r="25">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>86.83</v>
+        <v>107.79</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.002298023107519143</v>
+        <v>0.005128711886552839</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.00561151930235948</v>
+        <v>-0.004801003183340424</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.0009205134930809766</v>
+        <v>-0.01767978111780188</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.01351959619854703</v>
+        <v>-0.05122788190790595</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.06795401888126174</v>
+        <v>0.01569591835238193</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.08070570260462739</v>
+        <v>0.07720547001441247</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.2463884138370906</v>
+        <v>0.2709337364841999</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.206813048870969</v>
+        <v>0.2655334574838295</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4608836582299571</v>
+        <v>0.4037770549920487</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.134676020846948</v>
+        <v>0.1196940743400747</v>
       </c>
     </row>
     <row r="26">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>68.79000000000001</v>
+        <v>196.78</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.0007274229460541015</v>
+        <v>0.01037176180650401</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.0319447892071012</v>
+        <v>0.03350843008052373</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.01644268638455293</v>
+        <v>0.04681350809536489</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.008217988607386872</v>
+        <v>0.05286252116350831</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.08843918536212958</v>
+        <v>0.09671182236161502</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1094650834678874</v>
+        <v>0.1429961410219822</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.212691397039005</v>
+        <v>0.1564612905453211</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1609558667881472</v>
+        <v>0.1419696337227867</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.9462596674123076</v>
+        <v>1.196951974691782</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.248533676303065</v>
+        <v>0.2999905274835979</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>136.35</v>
+        <v>30.09</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.01729765852781084</v>
+        <v>0.01415571537627058</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.03592469980922464</v>
+        <v>-0.007585736957497091</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.009091243767520796</v>
+        <v>-0.05078866156475992</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.01028747145619557</v>
+        <v>-0.0003322335134584575</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.1350039626633848</v>
+        <v>0.1091043525022228</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1157420861975609</v>
+        <v>0.0408163373021051</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1260633799094044</v>
+        <v>0.1799478456701546</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1353688215038973</v>
+        <v>0.1767438654761651</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.7581728692870191</v>
+        <v>0.6042547795391398</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2069441980630615</v>
+        <v>0.1706429318856573</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2048,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>54.92</v>
+        <v>74.33</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.003104989387128887</v>
+        <v>-0.005751742815526151</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.004205513768727798</v>
+        <v>-0.03279110856345691</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.0165554314561529</v>
+        <v>-0.0322874079724742</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.01766453451381045</v>
+        <v>-0.01848674849887921</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.02643758282308917</v>
+        <v>0.0777670558174095</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1060121507362417</v>
+        <v>0.07626890400568609</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.2400573475838088</v>
+        <v>0.1933340437546009</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.2315769006083825</v>
+        <v>0.1805769491882383</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7216200722229225</v>
+        <v>0.8530512750235897</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1985213435941513</v>
+        <v>0.2282755650930859</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>107.24</v>
+        <v>54.61</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.008322559006460062</v>
+        <v>-0.005644529660036257</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.03064267806030074</v>
+        <v>-0.01265595273113629</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02818305984010416</v>
+        <v>0.005338820917155207</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.05606903188416701</v>
+        <v>0.01192029686478024</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.01051328684661201</v>
+        <v>0.02064382544266841</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.06229411485523006</v>
+        <v>0.1051255768726911</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.3001099660667417</v>
+        <v>0.2273043348992754</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2347690140478842</v>
+        <v>0.2315138939787311</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.3913186314791934</v>
+        <v>0.7030806739856179</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1163718243373277</v>
+        <v>0.1942036848510362</v>
       </c>
     </row>
     <row r="30">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2174,37 +2174,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>194.76</v>
+        <v>135.22</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.001182314959041308</v>
+        <v>-0.008287530856101455</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.01968583511432431</v>
+        <v>0.02083643641056065</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.03469159500353491</v>
+        <v>0.007075273091631473</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.04205457927786171</v>
+        <v>0.001926455941775096</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.08545375456726778</v>
+        <v>0.1256108087256458</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.1562775876233875</v>
+        <v>0.1038320010806912</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1586215554522143</v>
+        <v>0.1065929027806558</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.1239939565402435</v>
+        <v>0.1397368893534949</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>1.184007155803418</v>
+        <v>0.7438356904336645</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2974322403380472</v>
+        <v>0.2036545281370556</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>20.25</v>
+        <v>68.44</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.009632024742090017</v>
+        <v>-0.005087926580359947</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.007973725657356878</v>
+        <v>-0.03059484531726453</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.003031163279524796</v>
+        <v>-0.02935753272032005</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.1383473119787493</v>
+        <v>-0.01326410266507416</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.2307766585696509</v>
+        <v>0.08290128669982044</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.207945151181703</v>
+        <v>0.0849588089478881</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.01540310240618181</v>
+        <v>0.1743853064768288</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.08448467658413183</v>
+        <v>0.1619426606594883</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.1640894703759932</v>
+        <v>0.944471617876778</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.05195086152384798</v>
+        <v>0.248151212081726</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>29.67</v>
+        <v>20.25</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.003381818819809812</v>
+        <v>-0.0002962131061631235</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.03824960423289192</v>
+        <v>0.008719538967123741</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.05629772352727236</v>
+        <v>0.001731902837523336</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.01428572424339569</v>
+        <v>0.1379988643824801</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.09362333188717908</v>
+        <v>0.2303999183922816</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.02949342090459428</v>
+        <v>0.1986383404869261</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1960422472357963</v>
+        <v>-0.002709280782963841</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.140847368749152</v>
+        <v>-0.07851609139889915</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.5768590857544742</v>
+        <v>0.1637331431167057</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1639409867605022</v>
+        <v>0.05184351667638598</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>146.36</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.01631835423342154</v>
+        <v>-0.0002067411328988689</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.01716589916728295</v>
+        <v>0.0247880963990148</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.001637145178524757</v>
+        <v>0.03987959941044616</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.01208230415037015</v>
+        <v>-0.02597665967561558</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.09452387119743388</v>
+        <v>0.05695346385750555</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.1038771417878395</v>
+        <v>0.09024239502942044</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.122515508851476</v>
+        <v>0.1351132364505137</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1219262485632111</v>
+        <v>0.186297876202153</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.7242043854297402</v>
+        <v>0.4861606697055834</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1991207414271283</v>
+        <v>0.141182897974649</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>96.76000000000001</v>
+        <v>240.65</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.006972690434744466</v>
+        <v>0.00543132550582226</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.02294117647058824</v>
+        <v>0.03907593935435294</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.01777640103956224</v>
+        <v>0.01049758582436344</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.0257752473465539</v>
+        <v>0.06111381022382623</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.05717202479958172</v>
+        <v>0.06020403930903795</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.0887593912540936</v>
+        <v>0.0008882900248843306</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.1468654761536587</v>
+        <v>0.2233106703797991</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1791873800766897</v>
+        <v>0.1797381037389376</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.4909287187703559</v>
+        <v>0.4217998446870961</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1424020141156066</v>
+        <v>0.1244655488556823</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>239.35</v>
+        <v>145.33</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.001335136094940514</v>
+        <v>-0.007037433554260453</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.02094354039830093</v>
+        <v>0.002344963963096358</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.006052719176329324</v>
+        <v>-0.003360344730161557</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.05538168873939808</v>
+        <v>-0.01903470929199014</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.05447683239395773</v>
+        <v>0.08682123218032989</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>-0.009467685343217291</v>
+        <v>0.09505436096064179</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.2358375219152578</v>
+        <v>0.1058302788845547</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1671080574287651</v>
+        <v>0.127492313585811</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.4196295524341567</v>
+        <v>0.710552362205785</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1238931144045428</v>
+        <v>0.1959475248985569</v>
       </c>
     </row>
     <row r="36">
@@ -2510,37 +2510,37 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>286.5</v>
+        <v>287.55</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.0006976358511168179</v>
+        <v>0.003664878858529619</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.00153343011661855</v>
+        <v>0.01335627959159624</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.02258459070504848</v>
+        <v>-0.009507112358636327</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.1055799328740505</v>
+        <v>0.1096317493964554</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.04611678938179486</v>
+        <v>0.04995068068675312</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.2211755647868956</v>
+        <v>0.1984745407863062</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.08745164082665036</v>
+        <v>0.07427045753334482</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0507205995936586</v>
+        <v>0.05445535357975539</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.7888361229338565</v>
+        <v>0.7733579933190686</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.2139203317642531</v>
+        <v>0.2104089852843209</v>
       </c>
     </row>
     <row r="37">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2566,37 +2566,37 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>55.92</v>
+        <v>234.3</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.008334832874451248</v>
+        <v>0.003856080457622424</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.04784609901571979</v>
+        <v>-0.07082804707713952</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.0408233464710287</v>
+        <v>-0.06986896098123407</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.03068123591433414</v>
+        <v>-0.02431913197607161</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.01962247982538745</v>
+        <v>0.04035357055431543</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.006613779775656692</v>
+        <v>-0.0273747364725867</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.2004213690859413</v>
+        <v>0.1591732751004542</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.202981971632322</v>
+        <v>0.205424750314386</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.8275472690532513</v>
+        <v>1.099709460892496</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2226144927409983</v>
+        <v>0.2805201053863298</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>102.45</v>
+        <v>55.63</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.008900123574488994</v>
+        <v>-0.005185928296240983</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.00451023722038979</v>
+        <v>-0.02931426042433727</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.02437867951537764</v>
+        <v>-0.0522998237635881</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.1644691184268776</v>
+        <v>-0.03570805352108342</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.08998196313583473</v>
+        <v>0.01433479075577759</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.3068384784713125</v>
+        <v>0.01194032419265323</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.00233985587347707</v>
+        <v>0.1693066477521565</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>-0.0464432907076564</v>
+        <v>0.2057453988754698</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.5107213271704421</v>
+        <v>0.8047864912580656</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1474350717044821</v>
+        <v>0.2175176820728026</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>233.4</v>
+        <v>99.25</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.01660066782758784</v>
+        <v>0.001513638024102315</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.07085988562103906</v>
+        <v>0.01669736946893341</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.07060092637915438</v>
+        <v>0.02977799157885164</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.02806698388562834</v>
+        <v>-0.01547463144899919</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.03635729344793615</v>
+        <v>0.03466764823945634</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>-0.03864331453663938</v>
+        <v>0.06667138960949304</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1645593809786907</v>
+        <v>0.1266377255263733</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1980348787483377</v>
+        <v>0.1248641142218756</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.103075590049285</v>
+        <v>0.3809152986554412</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.2812040245669016</v>
+        <v>0.113582370890384</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>99.09999999999999</v>
+        <v>24.01</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.006091355067219251</v>
+        <v>0.01052188542052734</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.01143085403975186</v>
+        <v>-0.002492707382762638</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0.0204922031846575</v>
+        <v>0.003762548173111613</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.01696259424546409</v>
+        <v>-0.001247948648210317</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.03310390288919463</v>
+        <v>-0.07961670763179773</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.06214841859354925</v>
+        <v>-0.008001924711047104</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1353313369903819</v>
+        <v>0.2377330688647203</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.1167061950066108</v>
+        <v>0.3011463446021128</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.3798510756620408</v>
+        <v>0.5594016247778781</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.1132962310781305</v>
+        <v>0.159629693724636</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>88.84999999999999</v>
+        <v>101.85</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.01299737089896125</v>
+        <v>-0.005856500653916186</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.01496455957154774</v>
+        <v>-0.001078860448600283</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.01920739523246617</v>
+        <v>-0.01991916600555521</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.02114695199075811</v>
+        <v>0.1576494042733454</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.07877038254291868</v>
+        <v>0.08359848305597284</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.02177123671661962</v>
+        <v>0.2599765138576169</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1244246443396357</v>
+        <v>-0.01280076552278242</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.05023309260234221</v>
+        <v>-0.04518615414094007</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.4918811068163833</v>
+        <v>0.4726927596512758</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1426452134094596</v>
+        <v>0.1377252165163672</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>76.23</v>
+        <v>179.41</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.01208183305624622</v>
+        <v>0.00679016124909726</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.03517115682715821</v>
+        <v>-0.02367213199151863</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.02749697868170986</v>
+        <v>-0.04273820608842138</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0.02349623954249047</v>
+        <v>0.01133038238320272</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.05190327847969334</v>
+        <v>-0.06424000848707467</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.0015329290562478</v>
+        <v>0.009075125707277865</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.1438972779541685</v>
+        <v>0.2121418993403217</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.09628604677036434</v>
+        <v>0.2647218240249103</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.2686617488912595</v>
+        <v>0.8715526030321288</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.08255162247368819</v>
+        <v>0.2323498391217607</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>178.2</v>
+        <v>76</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.01508868533715746</v>
+        <v>-0.003017228739406463</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.05813953582149989</v>
+        <v>0.02095644152915854</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.0376410935336503</v>
+        <v>0.02564104676118806</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0.004509600221433097</v>
+        <v>0.02040811727386838</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.07055111628032462</v>
+        <v>0.04872944567678861</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.01247242005609195</v>
+        <v>0.003600843101631446</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.2130841319533854</v>
+        <v>0.1257163656893932</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.2430705703620042</v>
+        <v>0.1105443761914848</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.8807956970683557</v>
+        <v>0.2568520646958581</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.2343752563793724</v>
+        <v>0.07918206951582207</v>
       </c>
     </row>
     <row r="44">
@@ -2958,37 +2958,37 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>265.61</v>
+        <v>264.85</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.02614213220688844</v>
+        <v>-0.002861260080418093</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.09923020398869831</v>
+        <v>-0.0880762566448211</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.07867086101190823</v>
+        <v>-0.09400328988130269</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.01263902565196284</v>
+        <v>-0.01546412219282767</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.02032622819584862</v>
+        <v>-0.0231293296509445</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.06053907208309173</v>
+        <v>-0.0553132259773147</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1890655525833309</v>
+        <v>0.1647262067607254</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.2330343532957873</v>
+        <v>0.2292218553950622</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>1.276406973381285</v>
+        <v>1.262451053271168</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.3154771309262718</v>
+        <v>0.3127833625811696</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>23.76</v>
+        <v>59.56</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.004191130717169478</v>
+        <v>-0.002512103726034831</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.02382908463722366</v>
+        <v>-0.02568296527714464</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.002954820314317264</v>
+        <v>-0.02695634268683078</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.01164728269476301</v>
+        <v>-0.04992817549822748</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.08920004044723295</v>
+        <v>-0.01975421681936163</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.005258993889079688</v>
+        <v>-0.001810235415633632</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.2324219289109892</v>
+        <v>0.1455623820699603</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.2487830536346594</v>
+        <v>0.164700235822508</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.5567693396090245</v>
+        <v>0.6414971371858842</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1589768374955602</v>
+        <v>0.1796324473329909</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>59.71</v>
+        <v>48.14</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>0.05362225512318708</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.03864114478013558</v>
+        <v>0.1036222046869355</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.01744283964631099</v>
+        <v>0.06575163473761259</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.04753548584329848</v>
+        <v>0.2068187547313149</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.01728553615310358</v>
+        <v>-0.01674836009309233</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.00294423046188319</v>
+        <v>-0.1277405220598924</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.1642460844733846</v>
+        <v>0.1486689048497891</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.1582853761292966</v>
+        <v>0.2772359198122183</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.6525166628167181</v>
+        <v>1.337933479301196</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.1822662239177246</v>
+        <v>0.3272234611199185</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>13.44</v>
+        <v>87.89</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.01128665304445642</v>
+        <v>-0.01080471694945806</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0.01972680342848077</v>
+        <v>0.00872262320885886</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.009009000623754648</v>
+        <v>-0.01941311968190629</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0.08914095739007943</v>
+        <v>0.01011374821069611</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.1065110411937404</v>
+        <v>0.06711457390608389</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.08165879111829111</v>
+        <v>0.01877603446741949</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.02880882940286233</v>
+        <v>0.06386917566729178</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.05622751001056292</v>
+        <v>0.04723604532128056</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.2095047083865942</v>
+        <v>0.469811208934066</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.06545682192352476</v>
+        <v>0.1369826870105073</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>72.41</v>
+        <v>13.39</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.001100784104757557</v>
+        <v>-0.003720181445059256</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0.01785497115007817</v>
+        <v>0.01285930959607717</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.01065446630724387</v>
+        <v>0.002245560435363725</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0.04427755769578634</v>
+        <v>0.0850891554093427</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.1120730927980731</v>
+        <v>0.1023946193495382</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.07627087878723882</v>
+        <v>0.05833388107709148</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.09357293510830078</v>
+        <v>0.01288101078367587</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.03415296264530521</v>
+        <v>-0.05260626120229872</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.05958893404188803</v>
+        <v>0.2042272045919782</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.01948100408496667</v>
+        <v>0.06390490551087069</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>61.15</v>
+        <v>72.62</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0</v>
+        <v>0.002900139122386847</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0</v>
+        <v>0.02483773809018786</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0</v>
+        <v>0.0005511286100605695</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0</v>
+        <v>0.04730323885089471</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.006834612586222644</v>
+        <v>0.1152952041756332</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.1737265728073003</v>
+        <v>-0.06663434001913127</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.02625609124376327</v>
+        <v>0.07767596181552316</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.02589689989407251</v>
+        <v>-0.02691996359760507</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.8552509686293264</v>
+        <v>0.0511495176955401</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.2287613875065113</v>
+        <v>0.01676713125602602</v>
       </c>
     </row>
     <row r="50">
@@ -3294,37 +3294,37 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>27.42</v>
+        <v>27.9</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.004823439932708062</v>
+        <v>0.01732313567279631</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0.04120372932118221</v>
+        <v>0.07288463299091053</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0.05433534396887807</v>
+        <v>0.07061984766979168</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0.09527059818445704</v>
+        <v>0.1142400889867472</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.1068031300230829</v>
+        <v>0.1259723580017409</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.1783583966227018</v>
+        <v>0.1532503887534342</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.05796319288236795</v>
+        <v>-0.05218462324131812</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.1872819951666668</v>
+        <v>-0.1623628481445768</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.3440913718502245</v>
+        <v>0.3497732014023969</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.103594678716546</v>
+        <v>0.1051475547794232</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>48.99</v>
+        <v>61.15</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.007714461947983198</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0.02521979618753822</v>
+        <v>0</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.04156925115454824</v>
+        <v>0</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>0.02201127265717662</v>
+        <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>0.01363135907226432</v>
+        <v>-0.006834612586222644</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.03219143929175883</v>
+        <v>0.1571975827818108</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.117581570221321</v>
+        <v>0.02477194685476913</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.02530926856735238</v>
+        <v>-0.02692906852609112</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.1693809289207941</v>
+        <v>0.8546842624351416</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.05354236047446004</v>
+        <v>0.2286362620085851</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>19.85</v>
+        <v>48.71</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0.01014758025400053</v>
+        <v>-0.005715504886729006</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0.01974823586176</v>
+        <v>0.01331390459146076</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>0.04251043131321341</v>
+        <v>0.03177293008025805</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.04928898656134395</v>
+        <v>0.01627370695452823</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.07672363122771064</v>
+        <v>0.007940838158711827</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0.1182760319239657</v>
+        <v>-0.02557111613972429</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.02278815764308639</v>
+        <v>0.09083274936191699</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.1674072831927558</v>
+        <v>0.03126962043984038</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.2333863303303019</v>
+        <v>0.1501995976969406</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.07242363540522123</v>
+        <v>0.04775016312085945</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>45.69</v>
+        <v>19.89</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.008248341016549365</v>
+        <v>0.002166318986434934</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>0.009723726557104628</v>
+        <v>0.0377171239583538</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.0295177450893509</v>
+        <v>0.03490970831588491</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.1453998326850228</v>
+        <v>0.05154096267416386</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.06678922628494766</v>
+        <v>0.07903448736809571</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.168516870021152</v>
+        <v>0.09296699804926445</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.1058233978089897</v>
+        <v>0.002840687546005416</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.2137701680510042</v>
+        <v>-0.1622255860929829</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>1.259292493118767</v>
+        <v>0.2323295259510725</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.3121721616852913</v>
+        <v>0.0721172523969158</v>
       </c>
     </row>
     <row r="54">
@@ -3518,37 +3518,37 @@
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>106.29</v>
+        <v>106.38</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.001971822389414624</v>
+        <v>0.0008467055895704512</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.01756171072191182</v>
+        <v>0.004058521166223628</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.01801549322549367</v>
+        <v>-0.03553948948215713</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.01982664586383265</v>
+        <v>-0.01899672760613746</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.06432737324271098</v>
+        <v>0.06522854517876842</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.08918572542508529</v>
+        <v>-0.06356974536991022</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.0338218759108877</v>
+        <v>-0.007147487040026212</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.0846274176488514</v>
+        <v>-0.06945679356906309</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.3653953000070467</v>
+        <v>0.371547005753273</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.1093948220242442</v>
+        <v>0.111058429796375</v>
       </c>
     </row>
     <row r="55">
@@ -3574,37 +3574,37 @@
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>112.32</v>
+        <v>113.18</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.008258511277772218</v>
+        <v>0.007656700611540224</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0.01353546295010544</v>
+        <v>0.02443878408945332</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.004381631545618658</v>
+        <v>0.01716548683142594</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.05663213988935878</v>
+        <v>0.06472245584102265</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.02466479907488284</v>
+        <v>-0.01719694944550276</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.02744869830656449</v>
+        <v>-0.02286221433676694</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.002896149069998577</v>
+        <v>-0.0008304002045388392</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.02176421993280453</v>
+        <v>0.02792515182354194</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.778905969723813</v>
+        <v>0.7906073655598655</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.2116699319683837</v>
+        <v>0.2143208600056745</v>
       </c>
     </row>
     <row r="56">
@@ -3630,37 +3630,37 @@
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>45.8</v>
+        <v>45.88</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0.001968937965226569</v>
+        <v>0.00174676489928749</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.01193108562866274</v>
+        <v>0.01842401431989105</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.005267731706220413</v>
+        <v>0.007908624928191665</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.01103752777971234</v>
+        <v>0.01280357264510013</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>0.004165722959141194</v>
+        <v>0.005919764397073868</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.09217049465923488</v>
+        <v>-0.09471190229196469</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.02014043654266207</v>
+        <v>0.01202370460324298</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.002448804219735035</v>
+        <v>0.01394524181588008</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.3248729771352223</v>
+        <v>0.3208482128492025</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.09830951830926038</v>
+        <v>0.09719622398410688</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>55.88</v>
+        <v>98.16</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.005162846898407181</v>
+        <v>0.003578428711297654</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0.0145243139154998</v>
+        <v>0.01952643234990115</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.007754739391512722</v>
+        <v>-0.02328354565065294</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.1124826115343294</v>
+        <v>0.01102077829413983</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>0.1066740300855091</v>
+        <v>0.08080962259530677</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.05726583152427001</v>
+        <v>-0.07442143372282706</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.1150088592110421</v>
+        <v>-0.03817795747299568</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.107349672683052</v>
+        <v>-0.1142172571252481</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.1063651880999674</v>
+        <v>0.2277621749875063</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.0342673954305599</v>
+        <v>0.07079109255142657</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>97.81</v>
+        <v>55.71</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.003282384878819933</v>
+        <v>-0.003042268797299297</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.0003066105930060736</v>
+        <v>0.00487013824768745</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.005894926665846789</v>
+        <v>-0.00482315934211397</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.007415812626023754</v>
+        <v>0.1090981403977203</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.07695581299329257</v>
+        <v>0.1033072302149984</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.1088690528488604</v>
+        <v>-0.06422910711989271</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.003792521207997446</v>
+        <v>-0.1330288692720052</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.1282404319741842</v>
+        <v>-0.09786861881636555</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.2101333972185575</v>
+        <v>0.09255354780009029</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.06564139465946117</v>
+        <v>0.02994549867148399</v>
       </c>
     </row>
     <row r="59">
@@ -3798,37 +3798,37 @@
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>43.22</v>
+        <v>43.31</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.01052141122569861</v>
+        <v>0.002082372745162653</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.02172926839840217</v>
+        <v>-0.016129011292353</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0.002086718069998605</v>
+        <v>-0.007334395759574619</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.06632101175427785</v>
+        <v>-0.0643767440764238</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.04088235142238517</v>
+        <v>-0.03888511097158265</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.07203221405533422</v>
+        <v>-0.07324135177078628</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.01002309041821914</v>
+        <v>-0.004163521819501526</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.03266533758399159</v>
+        <v>0.04661503770308184</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.4980192325236705</v>
+        <v>0.4898145102722269</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.1442101511038905</v>
+        <v>0.1421173612832982</v>
       </c>
     </row>
     <row r="60">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>17.43</v>
+        <v>17.65</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.009096068563056225</v>
+        <v>0.01262187662091807</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.03754833143335723</v>
+        <v>-0.005073289388335622</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.03595130648634626</v>
+        <v>-0.03021984183259729</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.01968506006485204</v>
+        <v>-0.007311645843347869</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.2201346271664504</v>
+        <v>-0.2102912626496191</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.08927657585516668</v>
+        <v>-0.07295058859736248</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.08120048305549288</v>
+        <v>0.0855180317830484</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>0.2005969390778188</v>
+        <v>0.2394066877214975</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.1498006985616074</v>
+        <v>0.1512473465757025</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.04762902618657017</v>
+        <v>0.04806820817927115</v>
       </c>
     </row>
     <row r="61">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>35.25</v>
+        <v>35.85</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.02192011363648394</v>
+        <v>0.01702123330839989</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.06795345625494364</v>
+        <v>-0.01915186805885549</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.05799033338131443</v>
+        <v>-0.04348989028877603</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.04197452237918031</v>
+        <v>0.05971021382600461</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.1246555795986607</v>
+        <v>-0.1097561379938035</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.09593356895645044</v>
+        <v>-0.09561452249997449</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.03962162831725791</v>
+        <v>0.04262811822276213</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.04761629431557335</v>
+        <v>0.06987838293670334</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.3864096067395713</v>
+        <v>0.4028976576504761</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.1150573027826047</v>
+        <v>0.119460214394556</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>48.32</v>
+        <v>48.85</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.02027575032821716</v>
+        <v>0.01096851785273589</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.05106045890839717</v>
+        <v>-0.0204531878806905</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.06826071874015249</v>
+        <v>-0.07305507083646612</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.05772229241291804</v>
+        <v>-0.0473869025550141</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2673237008222162</v>
+        <v>-0.2592873277544082</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.2017181452289877</v>
+        <v>-0.1763615352718633</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.04003445215247958</v>
+        <v>0.03759550922317278</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.1534972642364067</v>
+        <v>0.172306230397838</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1242533357651183</v>
+        <v>-0.1252082165189478</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.04326242552526005</v>
+        <v>-0.04361028203661199</v>
       </c>
     </row>
   </sheetData>
@@ -4181,17 +4181,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3763125919890651</v>
+        <v>0.4026318215409348</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.06632101175427785</v>
+        <v>-0.0643767440764238</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.3304612870941879</v>
+        <v>0.3626723187290708</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4669,21 +4669,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.05772229241291804</v>
+        <v>-0.05122788190790595</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.2385263715522423</v>
+        <v>0.2950359389038635</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.05606903188416701</v>
+        <v>-0.04992817549822748</v>
       </c>
     </row>
     <row r="20">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.2162892086280088</v>
+        <v>0.2393206147964704</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.04753548584329848</v>
+        <v>-0.0473869025550141</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.2006935903494607</v>
+        <v>0.2068187547313149</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.03068123591433414</v>
+        <v>-0.03570805352108342</v>
       </c>
     </row>
     <row r="22">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1686555240277376</v>
+        <v>0.198488460312884</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.02806698388562834</v>
+        <v>-0.02597665967561558</v>
       </c>
     </row>
     <row r="23">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1644691184268776</v>
+        <v>0.1911573431187126</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.0257752473465539</v>
+        <v>-0.02431913197607161</v>
       </c>
     </row>
     <row r="24">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.158541431310139</v>
+        <v>0.1887163847137645</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.02571259233649537</v>
+        <v>-0.01903470929199014</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.1453998326850228</v>
+        <v>0.1576494042733454</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.0256419654410005</v>
+        <v>-0.01899672760613746</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.1383473119787493</v>
+        <v>0.1502072637318761</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.01982664586383265</v>
+        <v>-0.01848674849887921</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3527085481915295</v>
+        <v>0.4144278434499256</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2673237008222162</v>
+        <v>-0.2592873277544082</v>
       </c>
     </row>
     <row r="32">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2593156439456339</v>
+        <v>0.2856296653088952</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.2201346271664504</v>
+        <v>-0.2102912626496191</v>
       </c>
     </row>
     <row r="33">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.258873820678748</v>
+        <v>0.2822467380079285</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.2022644751892749</v>
+        <v>-0.1868100282615821</v>
       </c>
     </row>
     <row r="34">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2481479135518203</v>
+        <v>0.2742892984903063</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1246555795986607</v>
+        <v>-0.1097561379938035</v>
       </c>
     </row>
     <row r="35">
@@ -5293,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2307766585696509</v>
+        <v>0.2411197460529637</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.09285734308861049</v>
+        <v>-0.09803902542107912</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2178311574183212</v>
+        <v>0.2303999183922816</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.08920004044723295</v>
+        <v>-0.08620143650386614</v>
       </c>
     </row>
     <row r="37">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.2111936924558484</v>
+        <v>0.2015740504519132</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.07939904648720297</v>
+        <v>-0.07961670763179773</v>
       </c>
     </row>
     <row r="38">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1589743084281259</v>
+        <v>0.1885601067994833</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.07055111628032462</v>
+        <v>-0.06424000848707467</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1551924244333998</v>
+        <v>0.1683324736151492</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.06678922628494766</v>
+        <v>-0.03888511097158265</v>
       </c>
     </row>
     <row r="40">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.140715273389949</v>
+        <v>0.1595359818939477</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.05122157682553441</v>
+        <v>-0.03557051592773763</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5380404685630704</v>
+        <v>0.4882280108141392</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.2017181452289877</v>
+        <v>-0.1763615352718633</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5179024107879282</v>
+        <v>0.4782399370984411</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.168516870021152</v>
+        <v>-0.1277405220598924</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4924569806033121</v>
+        <v>0.4617021626290732</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5736,21 +5736,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1088690528488604</v>
+        <v>-0.09561452249997449</v>
       </c>
     </row>
     <row r="48">
@@ -5759,21 +5759,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3440925851826981</v>
+        <v>0.3524758010776912</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1001930977010621</v>
+        <v>-0.09471190229196469</v>
       </c>
     </row>
     <row r="49">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.3068384784713125</v>
+        <v>0.3522220957617839</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.09593356895645044</v>
+        <v>-0.09118230728315335</v>
       </c>
     </row>
     <row r="50">
@@ -5849,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3045137489638723</v>
+        <v>0.3195041526595619</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.09217049465923488</v>
+        <v>-0.07442143372282706</v>
       </c>
     </row>
     <row r="51">
@@ -5894,21 +5894,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2838703735345112</v>
+        <v>0.3042519301386932</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.08927657585516668</v>
+        <v>-0.07324135177078628</v>
       </c>
     </row>
     <row r="52">
@@ -5939,21 +5939,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2813531471064719</v>
+        <v>0.2898115742092504</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.08918572542508529</v>
+        <v>-0.07295058859736248</v>
       </c>
     </row>
     <row r="53">
@@ -5984,21 +5984,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2723068130390858</v>
+        <v>0.2650421786539643</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.07627087878723882</v>
+        <v>-0.06663434001913127</v>
       </c>
     </row>
     <row r="54">
@@ -6029,21 +6029,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.258787546998823</v>
+        <v>0.2622236364783486</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.07203221405533422</v>
+        <v>-0.06422910711989271</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>1.013591892676134</v>
+        <v>1.051295153891555</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1872819951666668</v>
+        <v>-0.1623628481445768</v>
       </c>
     </row>
     <row r="60">
@@ -6180,21 +6180,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8679382482486457</v>
+        <v>0.913210517865559</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1674072831927558</v>
+        <v>-0.1622255860929829</v>
       </c>
     </row>
     <row r="61">
@@ -6225,21 +6225,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.8360829737134441</v>
+        <v>0.8969428710457421</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1282404319741842</v>
+        <v>-0.1142172571252481</v>
       </c>
     </row>
     <row r="62">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.8139175228184441</v>
+        <v>0.8933565217451869</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.107349672683052</v>
+        <v>-0.09786861881636555</v>
       </c>
     </row>
     <row r="63">
@@ -6315,21 +6315,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.7467300650312909</v>
+        <v>0.8925066973774203</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.0846274176488514</v>
+        <v>-0.07851609139889915</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.7445211595022221</v>
+        <v>0.7723528918098002</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.08448467658413183</v>
+        <v>-0.06945679356906309</v>
       </c>
     </row>
     <row r="65">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.7330007848257154</v>
+        <v>0.7637963039479443</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.05622751001056292</v>
+        <v>-0.05260626120229872</v>
       </c>
     </row>
     <row r="66">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.6872002562489001</v>
+        <v>0.7363982642919</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.0464432907076564</v>
+        <v>-0.04518615414094007</v>
       </c>
     </row>
     <row r="67">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.6678391318130437</v>
+        <v>0.6622435344435043</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.03415296264530521</v>
+        <v>-0.02692906852609112</v>
       </c>
     </row>
     <row r="68">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.6487726177322406</v>
+        <v>0.6384739186884369</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.02589689989407251</v>
+        <v>-0.02691996359760507</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.065531159540543</v>
+        <v>3.185095936388366</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1242533357651183</v>
+        <v>-0.1252082165189478</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.739504322336177</v>
+        <v>2.848588569227107</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.05958893404188803</v>
+        <v>0.0511495176955401</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.724319714352051</v>
+        <v>2.778900488309921</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1063651880999674</v>
+        <v>0.09255354780009029</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.903162005237858</v>
+        <v>2.049595021434023</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6803,21 +6803,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1498006985616074</v>
+        <v>0.1501995976969406</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.754785208663779</v>
+        <v>1.805408934991207</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6848,21 +6848,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1640894703759932</v>
+        <v>0.1512473465757025</v>
       </c>
     </row>
     <row r="78">
@@ -6871,21 +6871,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.403044777355776</v>
+        <v>1.442718457972188</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6893,21 +6893,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1693809289207941</v>
+        <v>0.1637331431167057</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.380239069138207</v>
+        <v>1.435969464511421</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1815290792320881</v>
+        <v>0.1745032738567558</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.306897648685217</v>
+        <v>1.337933479301196</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2095047083865942</v>
+        <v>0.2042272045919782</v>
       </c>
     </row>
     <row r="81">
@@ -7006,21 +7006,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.276406973381285</v>
+        <v>1.337276181745597</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2101333972185575</v>
+        <v>0.2277621749875063</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.259292493118767</v>
+        <v>1.262451053271168</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2333863303303019</v>
+        <v>0.2323295259510725</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -492,10 +492,10 @@
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>41.48</v>
+        <v>40.6</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.04562645467193227</v>
+        <v>-0.0007384344869655335</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.152862703445664</v>
+        <v>0.03334175434126907</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.1784090523631128</v>
+        <v>0.1520997883189514</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.2950359389038635</v>
+        <v>0.2593050980278939</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.4144278434499256</v>
+        <v>0.3675183606502821</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.3524758010776912</v>
+        <v>0.3097074275398546</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.5376138514779003</v>
+        <v>0.4913115329741946</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8933565217451869</v>
+        <v>0.8321598701053672</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.9580436441610367</v>
+        <v>0.9165034398504042</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.2510484311422119</v>
+        <v>0.2421380560400708</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>169.1</v>
+        <v>168.23</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.03002989577606563</v>
+        <v>-0.0009501969397787136</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.05614893172752145</v>
+        <v>0.02968533908543658</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.06977920078584643</v>
+        <v>0.07248498707730566</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1237374462030834</v>
+        <v>0.1171392510699594</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2856296653088952</v>
+        <v>0.2524740777631889</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3195041526595619</v>
+        <v>0.3220941573732861</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.3992418279461551</v>
+        <v>0.3752725956834628</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.913210517865559</v>
+        <v>0.8717461366268007</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.162516074268487</v>
+        <v>1.15139025605556</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2931625375630991</v>
+        <v>0.2909410148233977</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>15.06</v>
+        <v>118.58</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.02552757050454701</v>
+        <v>0.08183560962279568</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.09008682438866855</v>
+        <v>0.08025877250078928</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.09245827571118759</v>
+        <v>-0.02715561223372076</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.198488460312884</v>
+        <v>0.119524205824818</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1885601067994833</v>
+        <v>0.2918618656533372</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2898115742092504</v>
+        <v>0.6208309991169259</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.6321777169593679</v>
+        <v>0.4299006343259106</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.7723528918098002</v>
+        <v>0.4165865066930616</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.049595021434023</v>
+        <v>1.331180015934649</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4501537722664573</v>
+        <v>0.3259442688139391</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>96.31999999999999</v>
+        <v>14.82</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.01893579751023311</v>
+        <v>-0.01593630266303725</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.1256281411515563</v>
+        <v>0.0443974723799041</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.08725593945676025</v>
+        <v>0.06695459528541603</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.2393206147964704</v>
+        <v>0.1970920482898146</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1595359818939477</v>
+        <v>0.1510679374620751</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.01669811957409162</v>
+        <v>0.2278376196794136</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.6314276402811283</v>
+        <v>0.6108695654427396</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1.051295153891555</v>
+        <v>0.7855420908745894</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.805408934991207</v>
+        <v>1.999999903474261</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.4103667431223594</v>
+        <v>0.442249554839163</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>555.8200000000001</v>
+        <v>573</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.01649601267852474</v>
+        <v>0.03100199698300066</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.02448358412839613</v>
+        <v>0.01839505045203871</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.02986400706943781</v>
+        <v>-0.02736283821767227</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-0.009568942949492731</v>
+        <v>0.04457207684098807</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.03557051592773763</v>
+        <v>-0.03778337531486142</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.3042519301386932</v>
+        <v>0.4100450497944867</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.6398031563836784</v>
+        <v>0.6530527402671746</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.8969428710457421</v>
+        <v>0.9310050622889963</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.778900488309921</v>
+        <v>2.895703557390161</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.55759717866082</v>
+        <v>0.5734826818148677</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>73.56999999999999</v>
+        <v>96.45</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.01224545109949671</v>
+        <v>0.009524764747693704</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.01545897575926958</v>
+        <v>0.07250079640766072</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.05491829578968765</v>
+        <v>0.1278063696704079</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.08270791757154616</v>
+        <v>0.2381257388833407</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2742892984903063</v>
+        <v>0.1241463903056188</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2622236364783486</v>
+        <v>0.01126188174680198</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3627560864586408</v>
+        <v>0.5908603163349453</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5939460258242291</v>
+        <v>1.043047874174863</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.7617223539453544</v>
+        <v>1.809194600799145</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2077558645915345</v>
+        <v>0.4110008488192307</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>216.4</v>
+        <v>100.79</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01820917112603149</v>
+        <v>0.07612638238986569</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.06307720815429207</v>
+        <v>0.07854472131604728</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.08340837060751194</v>
+        <v>-0.01379643908824102</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.1502072637318761</v>
+        <v>0.1312009275151849</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2822467380079285</v>
+        <v>0.22960351112463</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2355305092267588</v>
+        <v>0.6062961058276495</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.2581835886505053</v>
+        <v>0.388847105516134</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5827732277882587</v>
+        <v>0.3860159216002093</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7104499920670619</v>
+        <v>1.244581684858332</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1959236667657247</v>
+        <v>0.309317999579662</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>102.8</v>
+        <v>28.92</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.02421042381866956</v>
+        <v>0.05240176703221411</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.1744545239965511</v>
+        <v>0.04517527996217563</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.1321585858665639</v>
+        <v>-0.006526984887456622</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.3626723187290708</v>
+        <v>0.2130872437580336</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1683324736151492</v>
+        <v>0.2991913647319246</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>-0.09118230728315335</v>
+        <v>0.5415778104186986</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.5001443452564853</v>
+        <v>0.2819149273453181</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.8925066973774203</v>
+        <v>0.28934461358971</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>3.185095936388366</v>
+        <v>0.4695121762110985</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.6115179203700585</v>
+        <v>0.1369055754996991</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>105.52</v>
+        <v>72.41</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.01912300280115353</v>
+        <v>-0.0054936672146223</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1862844324150554</v>
+        <v>0.001660018606477243</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1708831938209017</v>
+        <v>0.03472420961144485</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.4026318215409348</v>
+        <v>0.05646341836720503</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.2411197460529637</v>
+        <v>0.243225832058245</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>-0.0507377368948887</v>
+        <v>0.2655044537686493</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.3661485350224098</v>
+        <v>0.3273128517246395</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7637963039479443</v>
+        <v>0.5406216200729459</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>2.848588569227107</v>
+        <v>0.7339450086017405</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.5671136563157424</v>
+        <v>0.2013745842291661</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>108.09</v>
+        <v>214.8</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.01350737757648734</v>
+        <v>-0.001997828761403642</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.06236990386486285</v>
+        <v>0.01883034286498009</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.09015156934971746</v>
+        <v>0.07972253149550856</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.02766681901760415</v>
+        <v>0.1405511653127289</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.13958880418308</v>
+        <v>0.264599691098145</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.4882280108141392</v>
+        <v>0.2259060402450779</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.293277165483135</v>
+        <v>0.2393162475932735</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.3098777268755866</v>
+        <v>0.5538399861273877</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.124955763122969</v>
+        <v>0.6978034837266827</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2856318740540713</v>
+        <v>0.1929689497471709</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>151.96</v>
+        <v>103.14</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.01536818786234018</v>
+        <v>0.02494288189146521</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.003433731273625229</v>
+        <v>0.05828032381010684</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.0002633527211959308</v>
+        <v>0.1630581758537579</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.04749430648507436</v>
+        <v>0.3610451445114873</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.01735245767999705</v>
+        <v>0.1637435987183533</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2650421786539643</v>
+        <v>-0.1249492365973937</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.4713513239589857</v>
+        <v>0.4222635707587059</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.5340298159845249</v>
+        <v>0.8658471463941766</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.337276181745597</v>
+        <v>3.198938195973668</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3270990688575082</v>
+        <v>0.6132926706737631</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>27.48</v>
+        <v>185.47</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.007942282117099131</v>
+        <v>0.00547541185121303</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.009729746225717872</v>
+        <v>-0.0105627941305636</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.01716736616428904</v>
+        <v>0.03516215391048516</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.1911573431187126</v>
+        <v>0.09693635682607438</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.2015740504519132</v>
+        <v>0.1409098998436606</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.4617021626290732</v>
+        <v>0.217330839307921</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1979075371614945</v>
+        <v>0.4314566256098578</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.23728053466909</v>
+        <v>0.4442873474210509</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.396341418501359</v>
+        <v>0.3639161965975486</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1177136123041</v>
+        <v>0.1089940827557185</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>490.93</v>
+        <v>500.26</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.01937289546101084</v>
+        <v>0.01946163411555712</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.05178274435872177</v>
+        <v>0.00708624149545356</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.07390917688486387</v>
+        <v>-0.06507439301059192</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.006837824238850931</v>
+        <v>0.01503500775153288</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>-0.1868100282615821</v>
+        <v>-0.1946778897260528</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.3522220957617839</v>
+        <v>0.4263975415784478</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.5832994268475196</v>
+        <v>0.5863166145717411</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7363982642919</v>
+        <v>0.736123342185601</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.435969464511421</v>
+        <v>1.482264719107691</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3455214120630428</v>
+        <v>0.3539917917103961</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>182.73</v>
+        <v>103.69</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.01884670136435229</v>
+        <v>0.01239996382704511</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01413547499164003</v>
+        <v>0.03845772684994486</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.02444357644057282</v>
+        <v>0.1746913604255935</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.04987068384710147</v>
+        <v>0.369206362670955</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.06790121805408122</v>
+        <v>0.2136001811623969</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2424260407272048</v>
+        <v>-0.1048860003503831</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.4261214722663904</v>
+        <v>0.2807243524244734</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.4387169636823891</v>
+        <v>0.6988138925974754</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.3437666422421484</v>
+        <v>2.781843923754035</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.103505796184862</v>
+        <v>0.5580014847029853</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>92.45999999999999</v>
+        <v>152.89</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.00825918958205929</v>
+        <v>0.006119983118534567</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.05110840755497958</v>
+        <v>0.01453219964004648</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.0746597199877771</v>
+        <v>-0.01741649490723229</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.04592757339947773</v>
+        <v>0.04934799308170468</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.09800079856797761</v>
+        <v>-0.01365679608037851</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.4782399370984411</v>
+        <v>0.2727842154315607</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2628125974937807</v>
+        <v>0.4592480425549732</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2883834095393756</v>
+        <v>0.5429578001045752</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>1.059073505723657</v>
+        <v>1.351580272521233</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2722055431320056</v>
+        <v>0.329800839366452</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>108.91</v>
+        <v>414.95</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.01161062565001503</v>
+        <v>0.02487158467391692</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.02080795922675449</v>
+        <v>-0.002667849247886878</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.003932620177272139</v>
+        <v>0.01066810727690037</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.05237226698443398</v>
+        <v>0.07589198321691426</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.02099939562777831</v>
+        <v>-0.02486308040000951</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.07110546159750131</v>
+        <v>0.04529312273229369</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.3868506441618464</v>
+        <v>0.4768315772644252</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.55640223043893</v>
+        <v>0.6652294244766919</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.8024145448705204</v>
+        <v>0.3195427695907054</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2169840727429497</v>
+        <v>0.09683463826636607</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>405.69</v>
+        <v>109.73</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.007389075571458847</v>
+        <v>0.01040520164539216</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.03519700382099333</v>
+        <v>0.04704198627495271</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.02313986427650261</v>
+        <v>0.01133643646943394</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.03582188287829546</v>
+        <v>0.05408266056999134</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.08620143650386614</v>
+        <v>-0.005798671502418307</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.01924478980378752</v>
+        <v>0.08557579510471847</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.4478761219728882</v>
+        <v>0.3772645215508754</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.6384739186884369</v>
+        <v>0.5698875424821077</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.2900960251108557</v>
+        <v>0.8159850787144027</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.08861424356046865</v>
+        <v>0.220030698572333</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>57</v>
+        <v>30.94</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.004714518170168214</v>
+        <v>0.01111111595912861</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.009206807046356458</v>
+        <v>-0.02150538542465985</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.01171458724928298</v>
+        <v>0.04881357742568193</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.00902811659373004</v>
+        <v>0.1061852446769662</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1261799117835503</v>
+        <v>0.0876331567687727</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2581545246874235</v>
+        <v>0.1192277973310563</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1683656159367792</v>
+        <v>0.3065201767782184</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2355568499146774</v>
+        <v>0.333026239170555</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1745032738567558</v>
+        <v>0.2986938822173852</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05507842872297086</v>
+        <v>0.09102725092836406</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>120.94</v>
+        <v>57.26</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.02604564030955903</v>
+        <v>-0.002612811814624472</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.06433164978157557</v>
+        <v>0.01524816972318144</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.02639396216602541</v>
+        <v>0.005973298726727361</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.1887163847137645</v>
+        <v>0.009520400021306274</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.03376394636062297</v>
+        <v>0.1362512251684804</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.01353976017393776</v>
+        <v>0.2460882207347193</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.3052691731774988</v>
+        <v>0.1677623735262805</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.5050476356131941</v>
+        <v>0.2358929665320748</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>1.442718457972188</v>
+        <v>0.1798605298851956</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.3467628810591052</v>
+        <v>0.05668017053599561</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>30.54</v>
+        <v>123</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.01895272281223948</v>
+        <v>0.02235892690543984</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.006506143691605626</v>
+        <v>0.07236271379765724</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01596811237900386</v>
+        <v>0.06705997728853541</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.04840376915148648</v>
+        <v>0.1929007785075274</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.01235641179052815</v>
+        <v>0.001416854141543578</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1466329746792341</v>
+        <v>0.03192644568444858</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.3108508453815095</v>
+        <v>0.2933886966188599</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3230254977141271</v>
+        <v>0.5235052538342884</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.281903651127311</v>
+        <v>1.484325816647351</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.08630504086901247</v>
+        <v>0.3543664411293408</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>68.78</v>
+        <v>110.32</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.0004359654172539917</v>
+        <v>0.07744897306814025</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01475361490129523</v>
+        <v>0.08252375361106701</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.02032332061654474</v>
+        <v>0.03801280543780283</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.05766569383965381</v>
+        <v>0.213507812680958</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.136340956285925</v>
+        <v>0.1858213621099751</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1385701700372501</v>
+        <v>0.3527115622104939</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1895080199573169</v>
+        <v>0.07158087244109468</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1680276072854574</v>
+        <v>0.02690261788790416</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7439504280402232</v>
+        <v>0.5951641357813047</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2036809261537262</v>
+        <v>0.1684275600745069</v>
       </c>
     </row>
     <row r="23">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>76.59</v>
+        <v>77.13</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.005712092021018078</v>
+        <v>0.01593781761927904</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.03472034330421647</v>
+        <v>0.03419141002623949</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.03346371214565425</v>
+        <v>0.03308322354881077</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.1294794144729203</v>
+        <v>0.1238525475764416</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.09803902542107912</v>
+        <v>-0.094334708998008</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.002215167321317324</v>
+        <v>0.0273415206988894</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.2567720258793178</v>
+        <v>0.2366166656198008</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.6622435344435043</v>
+        <v>0.6603653939958316</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.3756289130531152</v>
+        <v>0.3853279361325146</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1121595576378009</v>
+        <v>0.1147672397519746</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>87.3</v>
+        <v>55.31</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.005412889678588328</v>
+        <v>-0.003064134288896181</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.01299608659336204</v>
+        <v>0.007284675414140684</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.003679003017636795</v>
+        <v>0.01766334730675356</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.008179886602680431</v>
+        <v>0.03925456459093635</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.07373473616727111</v>
+        <v>0.06962949050167255</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.09114795530851771</v>
+        <v>0.1040204899446253</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.2308607301097951</v>
+        <v>0.2367409651420747</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2368227885412648</v>
+        <v>0.2421240624434589</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.4690301752000299</v>
+        <v>0.7249110669138941</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1367812599682521</v>
+        <v>0.1992845427118632</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>107.79</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.005128711886552839</v>
+        <v>-0.00308398164771595</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.004801003183340424</v>
+        <v>-0.004818640272562735</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.01767978111780188</v>
+        <v>-0.04372992316242963</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.05122788190790595</v>
+        <v>-0.01549256118846409</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.01569591835238193</v>
+        <v>0.07480331894998149</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.07720547001441247</v>
+        <v>0.126541043098632</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.2709337364841999</v>
+        <v>0.1981901005493547</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2655334574838295</v>
+        <v>0.1582644817186409</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4037770549920487</v>
+        <v>0.8535499687737067</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1196940743400747</v>
+        <v>0.2283857398475233</v>
       </c>
     </row>
     <row r="26">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>196.78</v>
+        <v>195.35</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.01037176180650401</v>
+        <v>0.002000407141044214</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.03350843008052373</v>
+        <v>0.03441884982750332</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.04681350809536489</v>
+        <v>0.01739498824141039</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.05286252116350831</v>
+        <v>0.03551557075961354</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.09671182236161502</v>
+        <v>0.1025320730022015</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1429961410219822</v>
+        <v>0.1523063754411451</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1564612905453211</v>
+        <v>0.1301589907852347</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1419696337227867</v>
+        <v>0.1323071529322364</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.196951974691782</v>
+        <v>1.180986437720687</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2999905274835979</v>
+        <v>0.2968338013187954</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>30.09</v>
+        <v>68.42</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.01415571537627058</v>
+        <v>-0.004075673824379122</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.007585736957497091</v>
+        <v>-0.002914668750092386</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.05078866156475992</v>
+        <v>-0.04187096120750622</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.0003322335134584575</v>
+        <v>-0.01155739725006732</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.1091043525022228</v>
+        <v>0.08156350063015205</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0408163373021051</v>
+        <v>0.1333218079574128</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1799478456701546</v>
+        <v>0.1772173724357906</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1767438654761651</v>
+        <v>0.1434055713817428</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.6042547795391398</v>
+        <v>0.9439032698544372</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1706429318856573</v>
+        <v>0.2480295931985996</v>
       </c>
     </row>
     <row r="28">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>74.33</v>
+        <v>133.78</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.005751742815526151</v>
+        <v>-0.01320357341754086</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.03279110856345691</v>
+        <v>0.0008229266990229522</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.0322874079724742</v>
+        <v>0.002322601002161973</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.01848674849887921</v>
+        <v>-0.01820046842446221</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.0777670558174095</v>
+        <v>0.1387338883824909</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.07626890400568609</v>
+        <v>0.07126149403816884</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.1933340437546009</v>
+        <v>0.08963670743614971</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1805769491882383</v>
+        <v>0.1216701120997679</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.8530512750235897</v>
+        <v>0.7252648386173806</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2282755650930859</v>
+        <v>0.1993665264426143</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>54.61</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.005644529660036257</v>
+        <v>-0.009401509783854234</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.01265595273113629</v>
+        <v>0.00150695360926445</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.005338820917155207</v>
+        <v>-0.01974129652619316</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.01192029686478024</v>
+        <v>-0.008946992160661527</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.02064382544266841</v>
+        <v>0.02297696711730346</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.1051255768726911</v>
+        <v>0.06220449560621866</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.2273043348992754</v>
+        <v>0.2015233810482282</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2315138939787311</v>
+        <v>0.2223582362394017</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.7030806739856179</v>
+        <v>0.4538853224177233</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1942036848510362</v>
+        <v>0.1328612384498735</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>135.22</v>
+        <v>293.83</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.008287530856101455</v>
+        <v>0.01935814942676717</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.02083643641056065</v>
+        <v>0.03453981387951366</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.007075273091631473</v>
+        <v>-0.004809528967770982</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.001926455941775096</v>
+        <v>0.1128237277051727</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.1256108087256458</v>
+        <v>0.07069195938580974</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.1038320010806912</v>
+        <v>0.206892214200902</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1065929027806558</v>
+        <v>0.101229212602586</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.1397368893534949</v>
+        <v>0.07229398712808988</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.7438356904336645</v>
+        <v>0.8120875586331813</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2036545281370556</v>
+        <v>0.2191572515920148</v>
       </c>
     </row>
     <row r="31">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2230,37 +2230,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>68.44</v>
+        <v>144.62</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.005087926580359947</v>
+        <v>-0.01094245718888065</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.03059484531726453</v>
+        <v>0.003330066113303554</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02935753272032005</v>
+        <v>-0.005843171075705311</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.01326410266507416</v>
+        <v>-0.02985182792238505</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.08290128669982044</v>
+        <v>0.105415123044259</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.0849588089478881</v>
+        <v>0.07837410613987705</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1743853064768288</v>
+        <v>0.09618904411916929</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1619426606594883</v>
+        <v>0.1194475363644438</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.944471617876778</v>
+        <v>0.7021954940692297</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.248151212081726</v>
+        <v>0.193996752334034</v>
       </c>
     </row>
     <row r="32">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2286,37 +2286,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>20.25</v>
+        <v>66.86</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.0002962131061631235</v>
+        <v>-0.01849680101919393</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.008719538967123741</v>
+        <v>-0.01080035163620552</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.001731902837523336</v>
+        <v>-0.03143558173719874</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.1379988643824801</v>
+        <v>0.003150773888446423</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.2303999183922816</v>
+        <v>0.07087356402039879</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.1986383404869261</v>
+        <v>0.08811896223178595</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.002709280782963841</v>
+        <v>0.1456529443701386</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.07851609139889915</v>
+        <v>0.1272357546581819</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1637331431167057</v>
+        <v>0.6952676097207109</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.05184351667638598</v>
+        <v>0.1923747061836572</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>96.73999999999999</v>
+        <v>107.01</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.0002067411328988689</v>
+        <v>-0.007604559778353503</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.0247880963990148</v>
+        <v>0.003469643179854875</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.03987959941044616</v>
+        <v>-0.04719077141461248</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.02597665967561558</v>
+        <v>-0.05275736053882962</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.05695346385750555</v>
+        <v>-0.03227196371513608</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.09024239502942044</v>
+        <v>0.04924480786706842</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1351132364505137</v>
+        <v>0.2471182760515491</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.186297876202153</v>
+        <v>0.2483778937130097</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4861606697055834</v>
+        <v>0.3936189291918937</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.141182897974649</v>
+        <v>0.1169867262866195</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>240.65</v>
+        <v>19.94</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.00543132550582226</v>
+        <v>-0.004592241164112942</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.03907593935435294</v>
+        <v>-0.005386523977323421</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.01049758582436344</v>
+        <v>-0.02053050895854269</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.06111381022382623</v>
+        <v>0.07911255029238795</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.06020403930903795</v>
+        <v>0.1934171470993917</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.0008882900248843306</v>
+        <v>0.165517166805937</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.2233106703797991</v>
+        <v>-0.01447991925322045</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1797381037389376</v>
+        <v>-0.0943688001426094</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.4217998446870961</v>
+        <v>0.1463158666827324</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1244655488556823</v>
+        <v>0.04656956560216963</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>145.33</v>
+        <v>239.51</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.007037433554260453</v>
+        <v>-0.00424065304800858</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.002344963963096358</v>
+        <v>0.02092919128550164</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.003360344730161557</v>
+        <v>0.02411595975286329</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.01903470929199014</v>
+        <v>0.0533004756133495</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.08682123218032989</v>
+        <v>0.0354973132794707</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.09505436096064179</v>
+        <v>-0.0118506579760792</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1058302788845547</v>
+        <v>0.2015091998176057</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.127492313585811</v>
+        <v>0.1679441495001655</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.710552362205785</v>
+        <v>0.4150646678888199</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1959475248985569</v>
+        <v>0.1226871774513179</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>287.55</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.003664878858529619</v>
+        <v>-0.01361602298159847</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.01335627959159624</v>
+        <v>-0.008980791469992866</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.009507112358636327</v>
+        <v>-0.002732262780838823</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.1096317493964554</v>
+        <v>-0.03947369843537185</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.04995068068675312</v>
+        <v>0.03967447518882583</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.1984745407863062</v>
+        <v>0.06532686169843749</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.07427045753334482</v>
+        <v>0.1068792791381836</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.05445535357975539</v>
+        <v>0.1521247659623972</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.7733579933190686</v>
+        <v>0.457893698644009</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.2104089852843209</v>
+        <v>0.1339013863516594</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>234.3</v>
+        <v>24.18</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.003856080457622424</v>
+        <v>0.01086957475136097</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.07082804707713952</v>
+        <v>0.01044713735109859</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.06986896098123407</v>
+        <v>-0.008203398788982241</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.02431913197607161</v>
+        <v>0.01129236551596602</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.04035357055431543</v>
+        <v>-0.0699026218591392</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-0.0273747364725867</v>
+        <v>-0.008326910457219339</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1591732751004542</v>
+        <v>0.2288695777599072</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.205424750314386</v>
+        <v>0.3110617438643799</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.099709460892496</v>
+        <v>0.5704427906528478</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2805201053863298</v>
+        <v>0.1623601350278336</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>55.63</v>
+        <v>181.71</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.005185928296240983</v>
+        <v>0.004866476104085082</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.02931426042433727</v>
+        <v>0.003036007069108004</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.0522998237635881</v>
+        <v>-0.0345358895283493</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.03570805352108342</v>
+        <v>0.02975178397512446</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.01433479075577759</v>
+        <v>-0.06054030020464729</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.01194032419265323</v>
+        <v>0.02643597684195131</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1693066477521565</v>
+        <v>0.2072660329993872</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.2057453988754698</v>
+        <v>0.2698392065852875</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.8047864912580656</v>
+        <v>0.8955457119824488</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.2175176820728026</v>
+        <v>0.2375936927561551</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>99.25</v>
+        <v>56.06</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.001513638024102315</v>
+        <v>-0.002668523636803921</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.01669736946893341</v>
+        <v>0.0003568960998736603</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.02977799157885164</v>
+        <v>-0.03858686240797482</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.01547463144899919</v>
+        <v>-0.0247042132959987</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.03466764823945634</v>
+        <v>-0.00990292923562841</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.06667138960949304</v>
+        <v>0.01939202841685472</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1266377255263733</v>
+        <v>0.1705380751625702</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1248641142218756</v>
+        <v>0.2065085551166912</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.3809152986554412</v>
+        <v>0.8187368548589553</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.113582370890384</v>
+        <v>0.2206466282003032</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>24.01</v>
+        <v>234.26</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.01052188542052734</v>
+        <v>-0.008968653575532226</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.002492707382762638</v>
+        <v>-0.01389124046839529</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0.003762548173111613</v>
+        <v>-0.06179665899194831</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.001247948648210317</v>
+        <v>-0.03956381046446</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.07961670763179773</v>
+        <v>0.01711405769960672</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>-0.008001924711047104</v>
+        <v>-0.03751605632718502</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.2377330688647203</v>
+        <v>0.1515788162993894</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.3011463446021128</v>
+        <v>0.1817485548610145</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.5594016247778781</v>
+        <v>1.099350919197255</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.159629693724636</v>
+        <v>0.2804472149867825</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>101.85</v>
+        <v>29.35</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.005856500653916186</v>
+        <v>-0.01377687648719195</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.001078860448600283</v>
+        <v>0.00307587668776077</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.01991916600555521</v>
+        <v>-0.07878217767724449</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.1576494042733454</v>
+        <v>-0.052308652496037</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.08359848305597284</v>
+        <v>0.00928474754030395</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.2599765138576169</v>
+        <v>0.03163443214042583</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>-0.01280076552278242</v>
+        <v>0.1268238933470183</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>-0.04518615414094007</v>
+        <v>0.1324300054723355</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.4726927596512758</v>
+        <v>0.5648015338211572</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1377252165163672</v>
+        <v>0.1609666768189806</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>179.41</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.00679016124909726</v>
+        <v>-0.009735311616780207</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.02367213199151863</v>
+        <v>-0.009634857636346972</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.04273820608842138</v>
+        <v>-0.009433965184638571</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0.01133038238320272</v>
+        <v>-0.02874477186524582</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.06424000848707467</v>
+        <v>0.01641237789962102</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.009075125707277865</v>
+        <v>0.04048231066887786</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.2121418993403217</v>
+        <v>0.1036049579521161</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.2647218240249103</v>
+        <v>0.1027594616569694</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.8715526030321288</v>
+        <v>0.3586537130560541</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.2323498391217607</v>
+        <v>0.1075659439066485</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>76</v>
+        <v>59.85</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.003017228739406463</v>
+        <v>-0.005483579750435896</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.02095644152915854</v>
+        <v>-0.006474156598257785</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.02564104676118806</v>
+        <v>-0.0250855339768421</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0.02040811727386838</v>
+        <v>-0.03296172137090936</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.04872944567678861</v>
+        <v>-0.02994454553492321</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.003600843101631446</v>
+        <v>-0.0006064779694855416</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1257163656893932</v>
+        <v>0.1375388476614838</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1105443761914848</v>
+        <v>0.1645529124886174</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.2568520646958581</v>
+        <v>0.6494893982844774</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.07918206951582207</v>
+        <v>0.1815438468699599</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>264.85</v>
+        <v>74.69</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.002861260080418093</v>
+        <v>-0.01425358650532527</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.0880762566448211</v>
+        <v>-0.003867710089939913</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.09400328988130269</v>
+        <v>0.003493243788316835</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.01546412219282767</v>
+        <v>-0.009022161077294366</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.0231293296509445</v>
+        <v>0.03448509793657073</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.0553132259773147</v>
+        <v>-0.0280530010592388</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1647262067607254</v>
+        <v>0.1013580550388324</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.2292218553950622</v>
+        <v>0.09529676924548602</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>1.262451053271168</v>
+        <v>0.2351877886365707</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.3127833625811696</v>
+        <v>0.07294550126446375</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>59.56</v>
+        <v>13.39</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.002512103726034831</v>
+        <v>0.001495920563565178</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.02568296527714464</v>
+        <v>0.007524483202164145</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.02695634268683078</v>
+        <v>-0.01107825841601739</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.04992817549822748</v>
+        <v>0.07463886856569291</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.01975421681936163</v>
+        <v>0.08573156099566237</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.001810235415633632</v>
+        <v>0.1184284398340698</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.1455623820699603</v>
+        <v>0.002438978766084121</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.164700235822508</v>
+        <v>-0.06209200339854237</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.6414971371858842</v>
+        <v>0.204227307876776</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1796324473329909</v>
+        <v>0.06390493592738999</v>
       </c>
     </row>
     <row r="46">
@@ -3070,37 +3070,37 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>48.14</v>
+        <v>48.37</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.05362225512318708</v>
+        <v>0.006659723203021439</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.1036222046869355</v>
+        <v>0.1033302637666498</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.06575163473761259</v>
+        <v>0.06895025263833743</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.2068187547313149</v>
+        <v>0.1996527603668088</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.01674836009309233</v>
+        <v>-0.03568582378334462</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.1277405220598924</v>
+        <v>-0.1098638425458085</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.1486689048497891</v>
+        <v>0.1314808437876374</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.2772359198122183</v>
+        <v>0.27719331644162</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>1.337933479301196</v>
+        <v>1.349103258312145</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.3272234611199185</v>
+        <v>0.3293337644048264</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>87.89</v>
+        <v>266.05</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.01080471694945806</v>
+        <v>-0.002250163574909148</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0.00872262320885886</v>
+        <v>-0.02108326960064955</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.01941311968190629</v>
+        <v>-0.08918184788162986</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0.01011374821069611</v>
+        <v>-0.02570776483304904</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.06711457390608389</v>
+        <v>-0.04586581025154646</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.01877603446741949</v>
+        <v>-0.05908252104130807</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.06386917566729178</v>
+        <v>0.1615841488119443</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.04723604532128056</v>
+        <v>0.2157839606918286</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.469811208934066</v>
+        <v>1.272701908487517</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.1369826870105073</v>
+        <v>0.3147630560933352</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>13.39</v>
+        <v>27.86</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.003720181445059256</v>
+        <v>0.008433466028960002</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0.01285930959607717</v>
+        <v>0.03916300043979071</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.002245560435363725</v>
+        <v>0.02770193411197619</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0.0850891554093427</v>
+        <v>0.08577553494588286</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.1023946193495382</v>
+        <v>0.117709168731817</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.05833388107709148</v>
+        <v>0.1428827612355619</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.01288101078367587</v>
+        <v>-0.06469605029817671</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.05260626120229872</v>
+        <v>-0.1654236264747735</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.2042272045919782</v>
+        <v>0.348128002492625</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.06390490551087069</v>
+        <v>0.1046983615957591</v>
       </c>
     </row>
     <row r="49">
@@ -3238,37 +3238,37 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>72.62</v>
+        <v>72.44</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.002900139122386847</v>
+        <v>0.0004142905369381999</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0.02483773809018786</v>
+        <v>0.01357214501379</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.0005511286100605695</v>
+        <v>0.0006907452987900964</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.04730323885089471</v>
+        <v>0.03411847659567613</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.1152952041756332</v>
+        <v>0.08207087916771694</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.06663434001913127</v>
+        <v>-0.0671659541357007</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.07767596181552316</v>
+        <v>0.06192877822542142</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.02691996359760507</v>
+        <v>-0.01633652057566171</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.0511495176955401</v>
+        <v>0.04854419109303687</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01676713125602602</v>
+        <v>0.01592640022844583</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>27.9</v>
+        <v>61.15</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.01732313567279631</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0.07288463299091053</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0.07061984766979168</v>
+        <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0.1142400889867472</v>
+        <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.1259723580017409</v>
+        <v>-0.01411178572315996</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.1532503887534342</v>
+        <v>0.1534804029332366</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.05218462324131812</v>
+        <v>0.02092262599480477</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.1623628481445768</v>
+        <v>-0.02790664672684995</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.3497732014023969</v>
+        <v>0.8546844770310331</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1051475547794232</v>
+        <v>0.2286363093949586</v>
       </c>
     </row>
     <row r="51">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -3350,37 +3350,37 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>61.15</v>
+        <v>86.59</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>-0.0185878607802874</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0</v>
+        <v>-0.001614285871370025</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0</v>
+        <v>-0.03023859950669117</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>0</v>
+        <v>-0.03294622009686787</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.006834612586222644</v>
+        <v>0.03354970184710826</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.1571975827818108</v>
+        <v>0.0003605856206634339</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.02477194685476913</v>
+        <v>0.03273779625803841</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>-0.02692906852609112</v>
+        <v>0.01388907624042024</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.8546842624351416</v>
+        <v>0.4480707698675348</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.2286362620085851</v>
+        <v>0.1313489958298475</v>
       </c>
     </row>
     <row r="52">
@@ -3406,37 +3406,37 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>48.71</v>
+        <v>47.82</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.005715504886729006</v>
+        <v>-0.01503603612168725</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0.01331390459146076</v>
+        <v>-0.01198350852829144</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>0.03177293008025805</v>
+        <v>-0.004372248382466637</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.01627370695452823</v>
+        <v>-0.008500929946164804</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.007940838158711827</v>
+        <v>-0.01352839709025433</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.02557111613972429</v>
+        <v>-0.05595011066244671</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.09083274936191699</v>
+        <v>0.05868177725274171</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.03126962043984038</v>
+        <v>0.01881310068191921</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.1501995976969406</v>
+        <v>0.1291837505681623</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.04775016312085945</v>
+        <v>0.04132958355072414</v>
       </c>
     </row>
     <row r="53">
@@ -3462,37 +3462,37 @@
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>19.89</v>
+        <v>19.55</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.002166318986434934</v>
+        <v>-0.001481522912788691</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>0.0377171239583538</v>
+        <v>0.002873403198657476</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.03490970831588491</v>
+        <v>0.01558842421294981</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.05154096267416386</v>
+        <v>0.003336783140917676</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.07903448736809571</v>
+        <v>0.04855154057290867</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.09296699804926445</v>
+        <v>0.06616841017940644</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.002840687546005416</v>
+        <v>-0.02135404514820882</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>-0.1622255860929829</v>
+        <v>-0.190727699206089</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.2323295259510725</v>
+        <v>0.2108325175219736</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.0721172523969158</v>
+        <v>0.06584656986662885</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>106.38</v>
+        <v>45.53</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.0008467055895704512</v>
+        <v>-0.002847154370338889</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.004058521166223628</v>
+        <v>-0.003501857128938024</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.03553948948215713</v>
+        <v>-0.002628756682822919</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.01899672760613746</v>
+        <v>-0.005678142193316749</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.06522854517876842</v>
+        <v>-0.007844859776415025</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.06356974536991022</v>
+        <v>-0.1021494852829112</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.007147487040026212</v>
+        <v>-0.002418601323448066</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.06945679356906309</v>
+        <v>0.008337524384908201</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.371547005753273</v>
+        <v>0.3107719293505926</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.111058429796375</v>
+        <v>0.09439905847200736</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>113.18</v>
+        <v>54.62</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.007656700611540224</v>
+        <v>-0.01390143466778182</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0.02443878408945332</v>
+        <v>-0.01496847285184222</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.01716548683142594</v>
+        <v>-0.02655501091176093</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.06472245584102265</v>
+        <v>0.06326649927147976</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.01719694944550276</v>
+        <v>0.1125198395015694</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.02286221433676694</v>
+        <v>-0.09061540551572755</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.0008304002045388392</v>
+        <v>-0.1481419144635615</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.02792515182354194</v>
+        <v>-0.1165165132553329</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.7906073655598655</v>
+        <v>0.07117691017305372</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.2143208600056745</v>
+        <v>0.02318398575317437</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>45.88</v>
+        <v>111.41</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0.00174676489928749</v>
+        <v>-0.01065622006694034</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.01842401431989105</v>
+        <v>0.006595621204560587</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.007908624928191665</v>
+        <v>-0.0101288259328095</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.01280357264510013</v>
+        <v>0.03483187695004508</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>0.005919764397073868</v>
+        <v>-0.03922384863474582</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.09471190229196469</v>
+        <v>-0.05077272795230825</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.01202370460324298</v>
+        <v>-0.01783103545430709</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.01394524181588008</v>
+        <v>0.01457970075220483</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.3208482128492025</v>
+        <v>0.7626047776603397</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.09719622398410688</v>
+        <v>0.2079574806451752</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>98.16</v>
+        <v>43.18</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.003578428711297654</v>
+        <v>-0.007584418043843133</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0.01952643234990115</v>
+        <v>-0.01347955554986158</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.02328354565065294</v>
+        <v>-0.01952771554208454</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.01102077829413983</v>
+        <v>-0.05472854604418065</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>0.08080962259530677</v>
+        <v>-0.03731223899373526</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.07442143372282706</v>
+        <v>-0.08318578049921332</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.03817795747299568</v>
+        <v>-0.02017155211277166</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.1142172571252481</v>
+        <v>0.04090398098682568</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.2277621749875063</v>
+        <v>0.4853427196754951</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.07079109255142657</v>
+        <v>0.1409734989274538</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>55.71</v>
+        <v>17.83</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.003042268797299297</v>
+        <v>0.008484141173140225</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>0.00487013824768745</v>
+        <v>0.01134434330459477</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.00482315934211397</v>
+        <v>-0.02886713883586078</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.1090981403977203</v>
+        <v>0.001122990362909304</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.1033072302149984</v>
+        <v>-0.2277383548660169</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.06422910711989271</v>
+        <v>-0.01877840099188033</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.1330288692720052</v>
+        <v>0.07243764284457255</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.09786861881636555</v>
+        <v>0.2564121432298727</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.09255354780009029</v>
+        <v>0.1629881328757132</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.02994549867148399</v>
+        <v>0.0516190088841173</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>43.31</v>
+        <v>36.14</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.002082372745162653</v>
+        <v>0.01431373298468941</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.016129011292353</v>
+        <v>0.009215247241055824</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.007334395759574619</v>
+        <v>-0.04442094972850286</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.0643767440764238</v>
+        <v>0.0524169839563875</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.03888511097158265</v>
+        <v>-0.0976273614468619</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.07324135177078628</v>
+        <v>-0.07334513200934378</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.004163521819501526</v>
+        <v>0.04141666058415017</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.04661503770308184</v>
+        <v>0.07438463962708841</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.4898145102722269</v>
+        <v>0.4142460990012753</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.1421173612832982</v>
+        <v>0.1224706563563254</v>
       </c>
     </row>
     <row r="60">
@@ -3840,51 +3840,51 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>17.65</v>
+        <v>104.52</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0.01262187662091807</v>
+        <v>-0.0139622958201282</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.005073289388335622</v>
+        <v>-0.0104147517033768</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.03021984183259729</v>
+        <v>-0.0457409129194426</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.007311645843347869</v>
+        <v>-0.04320762827722979</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.2102912626496191</v>
+        <v>0.01317224611168433</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.07295058859736248</v>
+        <v>-0.08975434158564388</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.0855180317830484</v>
+        <v>-0.03674762415027688</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>0.2394066877214975</v>
+        <v>-0.08325970781190706</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.1512473465757025</v>
+        <v>0.3475663305073708</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.04806820817927115</v>
+        <v>0.1045449230719151</v>
       </c>
     </row>
     <row r="61">
@@ -3896,51 +3896,51 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>35.85</v>
+        <v>95.63</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.01702123330839989</v>
+        <v>-0.01726441627094066</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.01915186805885549</v>
+        <v>-0.01147406072837298</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.04348989028877603</v>
+        <v>-0.03918418138964286</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.05971021382600461</v>
+        <v>-0.0239845481016645</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.1097561379938035</v>
+        <v>0.02369446729182312</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.09561452249997449</v>
+        <v>-0.107418873869659</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.04262811822276213</v>
+        <v>-0.07469361221629744</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.06987838293670334</v>
+        <v>-0.1312054046189869</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.4028976576504761</v>
+        <v>0.1961179080901518</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.119460214394556</v>
+        <v>0.0615114039487239</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>48.85</v>
+        <v>49.74</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.01096851785273589</v>
+        <v>0.01968025672803764</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.0204531878806905</v>
+        <v>0.000201128822090002</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.07305507083646612</v>
+        <v>-0.05202972134026085</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.0473869025550141</v>
+        <v>-0.03529867428915567</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2592873277544082</v>
+        <v>-0.2945681439299139</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1763615352718633</v>
+        <v>-0.0956363331187855</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.03759550922317278</v>
+        <v>0.03841336313097599</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.172306230397838</v>
+        <v>0.2143555368711547</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1252082165189478</v>
+        <v>-0.1092702940060968</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.04361028203661199</v>
+        <v>-0.03783701469231271</v>
       </c>
     </row>
   </sheetData>
@@ -4158,17 +4158,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.4026318215409348</v>
+        <v>0.369206362670955</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.0643767440764238</v>
+        <v>-0.05472854604418065</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.3626723187290708</v>
+        <v>0.3610451445114873</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.05122788190790595</v>
+        <v>-0.05275736053882962</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.2950359389038635</v>
+        <v>0.2593050980278939</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.04992817549822748</v>
+        <v>-0.052308652496037</v>
       </c>
     </row>
     <row r="20">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.2393206147964704</v>
+        <v>0.2381257388833407</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.0473869025550141</v>
+        <v>-0.04320762827722979</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.2068187547313149</v>
+        <v>0.213507812680958</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.03570805352108342</v>
+        <v>-0.03956381046446</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.198488460312884</v>
+        <v>0.2130872437580336</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.02597665967561558</v>
+        <v>-0.03947369843537185</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1911573431187126</v>
+        <v>0.1996527603668088</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.02431913197607161</v>
+        <v>-0.03529867428915567</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.1887163847137645</v>
+        <v>0.1970920482898146</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.01903470929199014</v>
+        <v>-0.03296172137090936</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.1576494042733454</v>
+        <v>0.1929007785075274</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.01899672760613746</v>
+        <v>-0.03294622009686787</v>
       </c>
     </row>
     <row r="26">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.1502072637318761</v>
+        <v>0.1405511653127289</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.01848674849887921</v>
+        <v>-0.02985182792238505</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.4144278434499256</v>
+        <v>0.3675183606502821</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2592873277544082</v>
+        <v>-0.2945681439299139</v>
       </c>
     </row>
     <row r="32">
@@ -5158,21 +5158,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2856296653088952</v>
+        <v>0.2991913647319246</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.2102912626496191</v>
+        <v>-0.2277383548660169</v>
       </c>
     </row>
     <row r="33">
@@ -5203,21 +5203,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2822467380079285</v>
+        <v>0.2918618656533372</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1868100282615821</v>
+        <v>-0.1946778897260528</v>
       </c>
     </row>
     <row r="34">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2742892984903063</v>
+        <v>0.264599691098145</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1097561379938035</v>
+        <v>-0.0976273614468619</v>
       </c>
     </row>
     <row r="35">
@@ -5293,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2411197460529637</v>
+        <v>0.2524740777631889</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.09803902542107912</v>
+        <v>-0.094334708998008</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2303999183922816</v>
+        <v>0.243225832058245</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.08620143650386614</v>
+        <v>-0.0699026218591392</v>
       </c>
     </row>
     <row r="37">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.2015740504519132</v>
+        <v>0.22960351112463</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.07961670763179773</v>
+        <v>-0.06054030020464729</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1885601067994833</v>
+        <v>0.2136001811623969</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.06424000848707467</v>
+        <v>-0.04586581025154646</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1683324736151492</v>
+        <v>0.1934171470993917</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.03888511097158265</v>
+        <v>-0.03922384863474582</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1595359818939477</v>
+        <v>0.1858213621099751</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.03557051592773763</v>
+        <v>-0.03778337531486142</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4882280108141392</v>
+        <v>0.6208309991169259</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5646,21 +5646,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1763615352718633</v>
+        <v>-0.1249492365973937</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4782399370984411</v>
+        <v>0.6062961058276495</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1277405220598924</v>
+        <v>-0.1098638425458085</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4617021626290732</v>
+        <v>0.5415778104186986</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5736,21 +5736,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.09561452249997449</v>
+        <v>-0.107418873869659</v>
       </c>
     </row>
     <row r="48">
@@ -5759,21 +5759,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3524758010776912</v>
+        <v>0.4263975415784478</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.09471190229196469</v>
+        <v>-0.1048860003503831</v>
       </c>
     </row>
     <row r="49">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.3522220957617839</v>
+        <v>0.4100450497944867</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.09118230728315335</v>
+        <v>-0.1021494852829112</v>
       </c>
     </row>
     <row r="50">
@@ -5849,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3195041526595619</v>
+        <v>0.3527115622104939</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.07442143372282706</v>
+        <v>-0.0956363331187855</v>
       </c>
     </row>
     <row r="51">
@@ -5894,21 +5894,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3042519301386932</v>
+        <v>0.3220941573732861</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.07324135177078628</v>
+        <v>-0.09061540551572755</v>
       </c>
     </row>
     <row r="52">
@@ -5939,21 +5939,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2898115742092504</v>
+        <v>0.3097074275398546</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.07295058859736248</v>
+        <v>-0.08975434158564388</v>
       </c>
     </row>
     <row r="53">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2650421786539643</v>
+        <v>0.2727842154315607</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.06663434001913127</v>
+        <v>-0.08318578049921332</v>
       </c>
     </row>
     <row r="54">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2622236364783486</v>
+        <v>0.2655044537686493</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.06422910711989271</v>
+        <v>-0.07334513200934378</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>1.051295153891555</v>
+        <v>1.043047874174863</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6157,21 +6157,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1623628481445768</v>
+        <v>-0.190727699206089</v>
       </c>
     </row>
     <row r="60">
@@ -6180,21 +6180,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.913210517865559</v>
+        <v>0.9310050622889963</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6202,21 +6202,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1622255860929829</v>
+        <v>-0.1654236264747735</v>
       </c>
     </row>
     <row r="61">
@@ -6225,21 +6225,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.8969428710457421</v>
+        <v>0.8717461366268007</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1142172571252481</v>
+        <v>-0.1312054046189869</v>
       </c>
     </row>
     <row r="62">
@@ -6270,21 +6270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.8933565217451869</v>
+        <v>0.8658471463941766</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.09786861881636555</v>
+        <v>-0.1165165132553329</v>
       </c>
     </row>
     <row r="63">
@@ -6315,21 +6315,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.8925066973774203</v>
+        <v>0.8321598701053672</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.07851609139889915</v>
+        <v>-0.0943688001426094</v>
       </c>
     </row>
     <row r="64">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.7723528918098002</v>
+        <v>0.7855420908745894</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.06945679356906309</v>
+        <v>-0.08325970781190706</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.7637963039479443</v>
+        <v>0.736123342185601</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.05260626120229872</v>
+        <v>-0.06209200339854237</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.7363982642919</v>
+        <v>0.6988138925974754</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6472,21 +6472,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.04518615414094007</v>
+        <v>-0.02790664672684995</v>
       </c>
     </row>
     <row r="67">
@@ -6495,21 +6495,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.6622435344435043</v>
+        <v>0.6652294244766919</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.02692906852609112</v>
+        <v>-0.01633652057566171</v>
       </c>
     </row>
     <row r="68">
@@ -6540,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.6384739186884369</v>
+        <v>0.6603653939958316</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.02691996359760507</v>
+        <v>0.008337524384908201</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.185095936388366</v>
+        <v>3.198938195973668</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1252082165189478</v>
+        <v>-0.1092702940060968</v>
       </c>
     </row>
     <row r="74">
@@ -6691,21 +6691,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.848588569227107</v>
+        <v>2.895703557390161</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.0511495176955401</v>
+        <v>0.04854419109303687</v>
       </c>
     </row>
     <row r="75">
@@ -6736,21 +6736,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.778900488309921</v>
+        <v>2.781843923754035</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.09255354780009029</v>
+        <v>0.07117691017305372</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>2.049595021434023</v>
+        <v>1.999999903474261</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1501995976969406</v>
+        <v>0.1291837505681623</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.805408934991207</v>
+        <v>1.809194600799145</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6848,21 +6848,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1512473465757025</v>
+        <v>0.1463158666827324</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.442718457972188</v>
+        <v>1.484325816647351</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6893,21 +6893,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1637331431167057</v>
+        <v>0.1629881328757132</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.435969464511421</v>
+        <v>1.482264719107691</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1745032738567558</v>
+        <v>0.1798605298851956</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.337933479301196</v>
+        <v>1.351580272521233</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6983,21 +6983,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.2042272045919782</v>
+        <v>0.1961179080901518</v>
       </c>
     </row>
     <row r="81">
@@ -7006,21 +7006,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.337276181745597</v>
+        <v>1.349103258312145</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,21 +7028,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2277621749875063</v>
+        <v>0.204227307876776</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.262451053271168</v>
+        <v>1.331180015934649</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2323295259510725</v>
+        <v>0.2108325175219736</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -630,13 +630,13 @@
         <v>0.4913115329741946</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8321598701053672</v>
+        <v>0.8321597124057059</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.9165034398504042</v>
+        <v>0.9165036124037205</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.2421380560400708</v>
+        <v>0.2421380933189037</v>
       </c>
     </row>
     <row r="3">
@@ -686,13 +686,13 @@
         <v>0.3752725956834628</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.8717461366268007</v>
+        <v>0.8717462955109481</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.15139025605556</v>
+        <v>1.151390465961669</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2909410148233977</v>
+        <v>0.2909410568080935</v>
       </c>
     </row>
     <row r="4">
@@ -745,10 +745,10 @@
         <v>0.4165865066930616</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.331180015934649</v>
+        <v>1.331180190758338</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3259442688139391</v>
+        <v>0.3259443019597366</v>
       </c>
     </row>
     <row r="5">
@@ -857,10 +857,10 @@
         <v>0.9310050622889963</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.895703557390161</v>
+        <v>2.895703961535242</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5734826818148677</v>
+        <v>0.5734827362265424</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>1.043047874174863</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.809194600799145</v>
+        <v>1.809195225039157</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.4110008488192307</v>
+        <v>0.4110009533335426</v>
       </c>
     </row>
     <row r="8">
@@ -963,16 +963,16 @@
         <v>0.6062961058276495</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.388847105516134</v>
+        <v>0.3888472515257795</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3860159216002093</v>
+        <v>0.386016067015176</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.244581684858332</v>
+        <v>1.244581875542</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.309317999579662</v>
+        <v>0.3093180366564372</v>
       </c>
     </row>
     <row r="9">
@@ -1078,13 +1078,13 @@
         <v>0.3273128517246395</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5406216200729459</v>
+        <v>0.5406217451142574</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.7339450086017405</v>
+        <v>0.7339448502101542</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2013745842291661</v>
+        <v>0.2013745476482998</v>
       </c>
     </row>
     <row r="11">
@@ -1131,16 +1131,16 @@
         <v>0.2259060402450779</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2393162475932735</v>
+        <v>0.2393161384869218</v>
       </c>
       <c r="N11" s="6" t="n">
         <v>0.5538399861273877</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6978034837266827</v>
+        <v>0.6978033813430333</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1929689497471709</v>
+        <v>0.1929689257670659</v>
       </c>
     </row>
     <row r="12">
@@ -1240,19 +1240,19 @@
         <v>0.1409098998436606</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.217330839307921</v>
+        <v>0.217330961224758</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4314566256098578</v>
+        <v>0.4314567941886087</v>
       </c>
       <c r="N13" s="6" t="n">
         <v>0.4442873474210509</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3639161965975486</v>
+        <v>0.3639163496434898</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1089940827557185</v>
+        <v>0.1089941242360377</v>
       </c>
     </row>
     <row r="14">
@@ -1296,19 +1296,19 @@
         <v>-0.1946778897260528</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.4263975415784478</v>
+        <v>0.4263976656966508</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.5863166145717411</v>
+        <v>0.5863167680808199</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.736123342185601</v>
+        <v>0.7361231583136925</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.482264719107691</v>
+        <v>1.482264343226667</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3539917917103961</v>
+        <v>0.3539917233669136</v>
       </c>
     </row>
     <row r="15">
@@ -1417,10 +1417,10 @@
         <v>0.5429578001045752</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>1.351580272521233</v>
+        <v>1.351580548471401</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.329800839366452</v>
+        <v>0.32980089138236</v>
       </c>
     </row>
     <row r="17">
@@ -1473,10 +1473,10 @@
         <v>0.6652294244766919</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.3195427695907054</v>
+        <v>0.3195428976470995</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.09683463826636607</v>
+        <v>0.09683467374751586</v>
       </c>
     </row>
     <row r="18">
@@ -1579,16 +1579,16 @@
         <v>0.1192277973310563</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.3065201767782184</v>
+        <v>0.3065200715476364</v>
       </c>
       <c r="N19" s="6" t="n">
         <v>0.333026239170555</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2986938822173852</v>
+        <v>0.2986936742700874</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.09102725092836406</v>
+        <v>0.09102719269647852</v>
       </c>
     </row>
     <row r="20">
@@ -1635,16 +1635,16 @@
         <v>0.2460882207347193</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1677623735262805</v>
+        <v>0.1677624643747753</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>0.2358929665320748</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1798605298851956</v>
+        <v>0.179860437144562</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05668017053599561</v>
+        <v>0.05668014284990086</v>
       </c>
     </row>
     <row r="21">
@@ -1697,10 +1697,10 @@
         <v>0.5235052538342884</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1.484325816647351</v>
+        <v>1.484326008060648</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3543664411293408</v>
+        <v>0.3543664759132565</v>
       </c>
     </row>
     <row r="22">
@@ -1865,10 +1865,10 @@
         <v>0.2421240624434589</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7249110669138941</v>
+        <v>0.7249112721198103</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1992845427118632</v>
+        <v>0.1992845902699236</v>
       </c>
     </row>
     <row r="25">
@@ -1915,16 +1915,16 @@
         <v>0.126541043098632</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1981901005493547</v>
+        <v>0.198190174209165</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1582644817186409</v>
+        <v>0.1582643440533249</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8535499687737067</v>
+        <v>0.8535497924999462</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2283857398475233</v>
+        <v>0.2283857009074384</v>
       </c>
     </row>
     <row r="26">
@@ -1968,7 +1968,7 @@
         <v>0.1025320730022015</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1523063754411451</v>
+        <v>0.152306271725916</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>0.1301589907852347</v>
@@ -1977,10 +1977,10 @@
         <v>0.1323071529322364</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.180986437720687</v>
+        <v>1.180986251947711</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2968338013187954</v>
+        <v>0.2968337644980437</v>
       </c>
     </row>
     <row r="27">
@@ -2027,10 +2027,10 @@
         <v>0.1333218079574128</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1772173724357906</v>
+        <v>0.1772172951694551</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1434055713817428</v>
+        <v>0.1434056442733718</v>
       </c>
       <c r="O27" s="6" t="n">
         <v>0.9439032698544372</v>
@@ -2083,16 +2083,16 @@
         <v>0.07126149403816884</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.08963670743614971</v>
+        <v>0.08963663972466906</v>
       </c>
       <c r="N28" s="6" t="n">
         <v>0.1216701120997679</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7252648386173806</v>
+        <v>0.7252650083676495</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1993665264426143</v>
+        <v>0.1993665657781758</v>
       </c>
     </row>
     <row r="29">
@@ -2139,16 +2139,16 @@
         <v>0.06220449560621866</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.2015233810482282</v>
+        <v>0.2015232535686169</v>
       </c>
       <c r="N29" s="6" t="n">
         <v>0.2223582362394017</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4538853224177233</v>
+        <v>0.4538854157445846</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1328612384498735</v>
+        <v>0.1328612626898371</v>
       </c>
     </row>
     <row r="30">
@@ -2257,10 +2257,10 @@
         <v>0.1194475363644438</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.7021954940692297</v>
+        <v>0.7021951883586124</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.193996752334034</v>
+        <v>0.1939966808542879</v>
       </c>
     </row>
     <row r="32">
@@ -2310,13 +2310,13 @@
         <v>0.1456529443701386</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1272357546581819</v>
+        <v>0.1272356821606562</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.6952676097207109</v>
+        <v>0.6952679376651796</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1923747061836572</v>
+        <v>0.1923747830707636</v>
       </c>
     </row>
     <row r="33">
@@ -2363,10 +2363,10 @@
         <v>0.04924480786706842</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.2471182760515491</v>
+        <v>0.2471183869386495</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2483778937130097</v>
+        <v>0.2483780048242201</v>
       </c>
       <c r="O33" s="6" t="n">
         <v>0.3936189291918937</v>
@@ -2475,16 +2475,16 @@
         <v>-0.0118506579760792</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.2015091998176057</v>
+        <v>0.201509107846672</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1679441495001655</v>
+        <v>0.1679442364043346</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.4150646678888199</v>
+        <v>0.4150645403186999</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1226871774513179</v>
+        <v>0.1226871437140276</v>
       </c>
     </row>
     <row r="36">
@@ -2590,7 +2590,7 @@
         <v>0.2288695777599072</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.3110617438643799</v>
+        <v>0.3110616082767637</v>
       </c>
       <c r="O37" s="6" t="n">
         <v>0.5704427906528478</v>
@@ -2643,10 +2643,10 @@
         <v>0.02643597684195131</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.2072660329993872</v>
+        <v>0.2072659106090462</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.2698392065852875</v>
+        <v>0.2698390711790588</v>
       </c>
       <c r="O38" s="6" t="n">
         <v>0.8955457119824488</v>
@@ -2870,13 +2870,13 @@
         <v>0.1036049579521161</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.1027594616569694</v>
+        <v>0.1027595566691841</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.3586537130560541</v>
+        <v>0.358653857279353</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1075659439066485</v>
+        <v>0.107565983096622</v>
       </c>
     </row>
     <row r="43">
@@ -2929,10 +2929,10 @@
         <v>0.1645529124886174</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.6494893982844774</v>
+        <v>0.6494897451212038</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1815438468699599</v>
+        <v>0.1815439296840258</v>
       </c>
     </row>
     <row r="44">
@@ -2976,7 +2976,7 @@
         <v>0.03448509793657073</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.0280530010592388</v>
+        <v>-0.02805290456246157</v>
       </c>
       <c r="M44" s="6" t="n">
         <v>0.1013580550388324</v>
@@ -2985,10 +2985,10 @@
         <v>0.09529676924548602</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.2351877886365707</v>
+        <v>0.2351878665592024</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.07294550126446375</v>
+        <v>0.07294552382695341</v>
       </c>
     </row>
     <row r="45">
@@ -3041,10 +3041,10 @@
         <v>-0.06209200339854237</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.204227307876776</v>
+        <v>0.2042271013071979</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.06390493592738999</v>
+        <v>0.06390487509435472</v>
       </c>
     </row>
     <row r="46">
@@ -3153,10 +3153,10 @@
         <v>0.2157839606918286</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>1.272701908487517</v>
+        <v>1.272701760368182</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.3147630560933352</v>
+        <v>0.3147630275308808</v>
       </c>
     </row>
     <row r="48">
@@ -3259,16 +3259,16 @@
         <v>-0.0671659541357007</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.06192877822542142</v>
+        <v>0.06192865945662662</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>-0.01633652057566171</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.04854419109303687</v>
+        <v>0.04854395950560098</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01592640022844583</v>
+        <v>0.01592632543401207</v>
       </c>
     </row>
     <row r="50">
@@ -3321,10 +3321,10 @@
         <v>-0.02790664672684995</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.8546844770310331</v>
+        <v>0.8546842624351416</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.2286363093949586</v>
+        <v>0.2286362620085851</v>
       </c>
     </row>
     <row r="51">
@@ -3374,13 +3374,13 @@
         <v>0.03273779625803841</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.01388907624042024</v>
+        <v>0.01388916681436414</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.4480707698675348</v>
+        <v>0.4480709546249946</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1313489958298475</v>
+        <v>0.1313490439456262</v>
       </c>
     </row>
     <row r="52">
@@ -3427,16 +3427,16 @@
         <v>-0.05595011066244671</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.05868177725274171</v>
+        <v>0.05868168784371908</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0.01881310068191921</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.1291837505681623</v>
+        <v>0.129183648854402</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.04132958355072414</v>
+        <v>0.04132955228402335</v>
       </c>
     </row>
     <row r="53">
@@ -3595,16 +3595,16 @@
         <v>-0.09061540551572755</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.1481419144635615</v>
+        <v>-0.1481418131020827</v>
       </c>
       <c r="N55" s="6" t="n">
         <v>-0.1165165132553329</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.07117691017305372</v>
+        <v>0.0711769903096382</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.02318398575317437</v>
+        <v>0.02318401126855751</v>
       </c>
     </row>
     <row r="56">
@@ -3648,7 +3648,7 @@
         <v>-0.03922384863474582</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.05077272795230825</v>
+        <v>-0.05077266624930143</v>
       </c>
       <c r="M56" s="6" t="n">
         <v>-0.01783103545430709</v>
@@ -3657,10 +3657,10 @@
         <v>0.01457970075220483</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.7626047776603397</v>
+        <v>0.7626048840368653</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.2079574806451752</v>
+        <v>0.2079575049460129</v>
       </c>
     </row>
     <row r="57">
@@ -3713,10 +3713,10 @@
         <v>0.04090398098682568</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.4853427196754951</v>
+        <v>0.4853426222212511</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.1409734989274538</v>
+        <v>0.1409734739741302</v>
       </c>
     </row>
     <row r="58">
@@ -3825,10 +3825,10 @@
         <v>0.07438463962708841</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.4142460990012753</v>
+        <v>0.4142462045594697</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.1224706563563254</v>
+        <v>0.1224706842830945</v>
       </c>
     </row>
     <row r="60">
@@ -3881,10 +3881,10 @@
         <v>-0.08325970781190706</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.3475663305073708</v>
+        <v>0.3475660654005512</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.1045449230719151</v>
+        <v>0.1045448506395099</v>
       </c>
     </row>
     <row r="61">
@@ -3928,19 +3928,19 @@
         <v>0.02369446729182312</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.107418873869659</v>
+        <v>-0.1074189374307434</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.07469361221629744</v>
+        <v>-0.07469354390900318</v>
       </c>
       <c r="N61" s="6" t="n">
         <v>-0.1312054046189869</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1961179080901518</v>
+        <v>0.1961176798070168</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.0615114039487239</v>
+        <v>0.06151133641770956</v>
       </c>
     </row>
     <row r="62">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.107418873869659</v>
+        <v>-0.1074189374307434</v>
       </c>
     </row>
     <row r="48">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4263975415784478</v>
+        <v>0.4263976656966508</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.8717461366268007</v>
+        <v>0.8717462955109481</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.8321598701053672</v>
+        <v>0.8321597124057059</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.736123342185601</v>
+        <v>0.7361231583136925</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.895703557390161</v>
+        <v>2.895703961535242</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.04854419109303687</v>
+        <v>0.04854395950560098</v>
       </c>
     </row>
     <row r="75">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.07117691017305372</v>
+        <v>0.0711769903096382</v>
       </c>
     </row>
     <row r="76">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1291837505681623</v>
+        <v>0.129183648854402</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.809194600799145</v>
+        <v>1.809195225039157</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.484325816647351</v>
+        <v>1.484326008060648</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.482264719107691</v>
+        <v>1.482264343226667</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1798605298851956</v>
+        <v>0.179860437144562</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.351580272521233</v>
+        <v>1.351580548471401</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1961179080901518</v>
+        <v>0.1961176798070168</v>
       </c>
     </row>
     <row r="81">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.204227307876776</v>
+        <v>0.2042271013071979</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.331180015934649</v>
+        <v>1.331180190758338</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -630,7 +630,7 @@
         <v>0.4913115329741946</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8321597124057059</v>
+        <v>0.8321598701053672</v>
       </c>
       <c r="O2" s="6" t="n">
         <v>0.9165036124037205</v>
@@ -689,10 +689,10 @@
         <v>0.8717462955109481</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.151390465961669</v>
+        <v>1.15139025605556</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2909410568080935</v>
+        <v>0.2909410148233977</v>
       </c>
     </row>
     <row r="4">
@@ -857,10 +857,10 @@
         <v>0.9310050622889963</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.895703961535242</v>
+        <v>2.895703557390161</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5734827362265424</v>
+        <v>0.5734826818148677</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         <v>1.043047874174863</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.809195225039157</v>
+        <v>1.809194912919116</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.4110009533335426</v>
+        <v>0.4110009010763827</v>
       </c>
     </row>
     <row r="8">
@@ -960,19 +960,19 @@
         <v>0.22960351112463</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.6062961058276495</v>
+        <v>0.6062960081727999</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>0.3888472515257795</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.386016067015176</v>
+        <v>0.3860159216002093</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.244581875542</v>
+        <v>1.244582066225699</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.3093180366564372</v>
+        <v>0.3093180737332164</v>
       </c>
     </row>
     <row r="9">
@@ -1078,13 +1078,13 @@
         <v>0.3273128517246395</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5406217451142574</v>
+        <v>0.5406216200729459</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.7339448502101542</v>
+        <v>0.7339446918185966</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2013745476482998</v>
+        <v>0.2013745110674376</v>
       </c>
     </row>
     <row r="11">
@@ -1134,13 +1134,13 @@
         <v>0.2393161384869218</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5538399861273877</v>
+        <v>0.5538398146138817</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6978033813430333</v>
+        <v>0.6978036884940182</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1929689257670659</v>
+        <v>0.1929689977073865</v>
       </c>
     </row>
     <row r="12">
@@ -1193,10 +1193,10 @@
         <v>0.8658471463941766</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>3.198938195973668</v>
+        <v>3.198937543877196</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.6132926706737631</v>
+        <v>0.6132925871587993</v>
       </c>
     </row>
     <row r="13">
@@ -1240,13 +1240,13 @@
         <v>0.1409098998436606</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.217330961224758</v>
+        <v>0.217330839307921</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4314567941886087</v>
+        <v>0.4314566256098578</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4442873474210509</v>
+        <v>0.4442875190354245</v>
       </c>
       <c r="O13" s="6" t="n">
         <v>0.3639163496434898</v>
@@ -1305,10 +1305,10 @@
         <v>0.7361231583136925</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.482264343226667</v>
+        <v>1.482264719107691</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3539917233669136</v>
+        <v>0.3539917917103961</v>
       </c>
     </row>
     <row r="15">
@@ -1361,10 +1361,10 @@
         <v>0.6988138925974754</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>2.781843923754035</v>
+        <v>2.781843660666441</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.5580014847029853</v>
+        <v>0.5580014485750293</v>
       </c>
     </row>
     <row r="16">
@@ -1414,7 +1414,7 @@
         <v>0.4592480425549732</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.5429578001045752</v>
+        <v>0.5429579189053095</v>
       </c>
       <c r="O16" s="6" t="n">
         <v>1.351580548471401</v>
@@ -1585,10 +1585,10 @@
         <v>0.333026239170555</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2986936742700874</v>
+        <v>0.298693778243728</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.09102719269647852</v>
+        <v>0.09102722181241973</v>
       </c>
     </row>
     <row r="20">
@@ -1635,7 +1635,7 @@
         <v>0.2460882207347193</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1677624643747753</v>
+        <v>0.1677623735262805</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>0.2358929665320748</v>
@@ -1694,13 +1694,13 @@
         <v>0.2933886966188599</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.5235052538342884</v>
+        <v>0.5235049658937658</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1.484326008060648</v>
+        <v>1.484326390887332</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3543664759132565</v>
+        <v>0.3543665454810989</v>
       </c>
     </row>
     <row r="22">
@@ -1809,10 +1809,10 @@
         <v>0.6603653939958316</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.3853279361325146</v>
+        <v>0.3853278412159706</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1147672397519746</v>
+        <v>0.1147672142923335</v>
       </c>
     </row>
     <row r="24">
@@ -1918,7 +1918,7 @@
         <v>0.198190174209165</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1582643440533249</v>
+        <v>0.1582644817186409</v>
       </c>
       <c r="O25" s="6" t="n">
         <v>0.8535497924999462</v>
@@ -1968,7 +1968,7 @@
         <v>0.1025320730022015</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.152306271725916</v>
+        <v>0.1523063754411451</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>0.1301589907852347</v>
@@ -1977,10 +1977,10 @@
         <v>0.1323071529322364</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.180986251947711</v>
+        <v>1.180986623493694</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2968337644980437</v>
+        <v>0.2968338381395514</v>
       </c>
     </row>
     <row r="27">
@@ -2030,13 +2030,13 @@
         <v>0.1772172951694551</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1434056442733718</v>
+        <v>0.1434055713817428</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.9439032698544372</v>
+        <v>0.9439034805359205</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2480295931985996</v>
+        <v>0.2480296382860141</v>
       </c>
     </row>
     <row r="28">
@@ -2083,16 +2083,16 @@
         <v>0.07126149403816884</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.08963663972466906</v>
+        <v>0.08963670743614971</v>
       </c>
       <c r="N28" s="6" t="n">
         <v>0.1216701120997679</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7252650083676495</v>
+        <v>0.7252648386173806</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1993665657781758</v>
+        <v>0.1993665264426143</v>
       </c>
     </row>
     <row r="29">
@@ -2145,10 +2145,10 @@
         <v>0.2223582362394017</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4538854157445846</v>
+        <v>0.4538853224177233</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1328612626898371</v>
+        <v>0.1328612384498735</v>
       </c>
     </row>
     <row r="30">
@@ -2257,10 +2257,10 @@
         <v>0.1194475363644438</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.7021951883586124</v>
+        <v>0.7021953412139073</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1939966808542879</v>
+        <v>0.1939967165941587</v>
       </c>
     </row>
     <row r="32">
@@ -2307,16 +2307,16 @@
         <v>0.08811896223178595</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1456529443701386</v>
+        <v>0.145653019256009</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1272356821606562</v>
+        <v>0.1272357546581819</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.6952679376651796</v>
+        <v>0.6952676097207109</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1923747830707636</v>
+        <v>0.1923747061836572</v>
       </c>
     </row>
     <row r="33">
@@ -2363,16 +2363,16 @@
         <v>0.04924480786706842</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.2471183869386495</v>
+        <v>0.2471182760515491</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2483780048242201</v>
+        <v>0.2483778937130097</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3936189291918937</v>
+        <v>0.3936192061307255</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1169867262866195</v>
+        <v>0.1169868002755157</v>
       </c>
     </row>
     <row r="34">
@@ -2478,13 +2478,13 @@
         <v>0.201509107846672</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1679442364043346</v>
+        <v>0.1679440625960094</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.4150645403186999</v>
+        <v>0.4150646678888199</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1226871437140276</v>
+        <v>0.1226871774513179</v>
       </c>
     </row>
     <row r="36">
@@ -2537,10 +2537,10 @@
         <v>0.1521247659623972</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.457893698644009</v>
+        <v>0.4578938695178663</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1339013863516594</v>
+        <v>0.1339014306516646</v>
       </c>
     </row>
     <row r="37">
@@ -2593,10 +2593,10 @@
         <v>0.3110616082767637</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.5704427906528478</v>
+        <v>0.5704425961087913</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1623601350278336</v>
+        <v>0.1623600870306985</v>
       </c>
     </row>
     <row r="38">
@@ -2643,16 +2643,16 @@
         <v>0.02643597684195131</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.2072659106090462</v>
+        <v>0.2072660329993872</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.2698390711790588</v>
+        <v>0.2698392065852875</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.8955457119824488</v>
+        <v>0.8955458628444235</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.2375936927561551</v>
+        <v>0.2375937255885336</v>
       </c>
     </row>
     <row r="39">
@@ -2705,10 +2705,10 @@
         <v>0.2065085551166912</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.8187368548589553</v>
+        <v>0.818736742316422</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.2206466282003032</v>
+        <v>0.2206466030226337</v>
       </c>
     </row>
     <row r="40">
@@ -2873,10 +2873,10 @@
         <v>0.1027595566691841</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.358653857279353</v>
+        <v>0.3586535688327857</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.107565983096622</v>
+        <v>0.1075659047166808</v>
       </c>
     </row>
     <row r="43">
@@ -2929,10 +2929,10 @@
         <v>0.1645529124886174</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.6494897451212038</v>
+        <v>0.6494895717028224</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1815439296840258</v>
+        <v>0.18154388827699</v>
       </c>
     </row>
     <row r="44">
@@ -2979,16 +2979,16 @@
         <v>-0.02805290456246157</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1013580550388324</v>
+        <v>0.1013579311350352</v>
       </c>
       <c r="N44" s="6" t="n">
         <v>0.09529676924548602</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.2351878665592024</v>
+        <v>0.2351877107139491</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.07294552382695341</v>
+        <v>0.0729454787019761</v>
       </c>
     </row>
     <row r="45">
@@ -3038,13 +3038,13 @@
         <v>0.002438978766084121</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>-0.06209200339854237</v>
+        <v>-0.06209206605126483</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.2042271013071979</v>
+        <v>0.2042272045919782</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.06390487509435472</v>
+        <v>0.06390490551087069</v>
       </c>
     </row>
     <row r="46">
@@ -3097,10 +3097,10 @@
         <v>0.27719331644162</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>1.349103258312145</v>
+        <v>1.349103040712502</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.3293337644048264</v>
+        <v>0.3293337233590132</v>
       </c>
     </row>
     <row r="47">
@@ -3203,16 +3203,16 @@
         <v>0.1428827612355619</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>-0.06469605029817671</v>
+        <v>-0.06469611018604993</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.1654236264747735</v>
+        <v>-0.1654237218411977</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.348128002492625</v>
+        <v>0.3481278780710768</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.1046983615957591</v>
+        <v>0.1046983276107851</v>
       </c>
     </row>
     <row r="49">
@@ -3265,10 +3265,10 @@
         <v>-0.01633652057566171</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.04854395950560098</v>
+        <v>0.04854419109303687</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01592632543401207</v>
+        <v>0.01592640022844583</v>
       </c>
     </row>
     <row r="50">
@@ -3377,10 +3377,10 @@
         <v>0.01388916681436414</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.4480709546249946</v>
+        <v>0.4480708622462588</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1313490439456262</v>
+        <v>0.1313490198877358</v>
       </c>
     </row>
     <row r="52">
@@ -3433,10 +3433,10 @@
         <v>0.01881310068191921</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.129183648854402</v>
+        <v>0.1291837505681623</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.04132955228402335</v>
+        <v>0.04132958355072414</v>
       </c>
     </row>
     <row r="53">
@@ -3489,10 +3489,10 @@
         <v>-0.190727699206089</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.2108325175219736</v>
+        <v>0.2108326605965962</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.06584656986662885</v>
+        <v>0.06584661184754892</v>
       </c>
     </row>
     <row r="54">
@@ -3545,10 +3545,10 @@
         <v>0.008337524384908201</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.3107719293505926</v>
+        <v>0.3107720733022772</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.09439905847200736</v>
+        <v>0.09439909853506201</v>
       </c>
     </row>
     <row r="55">
@@ -3654,7 +3654,7 @@
         <v>-0.01783103545430709</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.01457970075220483</v>
+        <v>0.01457977124394838</v>
       </c>
       <c r="O56" s="6" t="n">
         <v>0.7626048840368653</v>
@@ -3707,10 +3707,10 @@
         <v>-0.08318578049921332</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.02017155211277166</v>
+        <v>-0.02017163692871327</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.04090398098682568</v>
+        <v>0.04090407670597185</v>
       </c>
       <c r="O57" s="6" t="n">
         <v>0.4853426222212511</v>
@@ -3769,10 +3769,10 @@
         <v>0.2564121432298727</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1629881328757132</v>
+        <v>0.1629882052191838</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.0516190088841173</v>
+        <v>0.0516190306893749</v>
       </c>
     </row>
     <row r="59">
@@ -3825,10 +3825,10 @@
         <v>0.07438463962708841</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.4142462045594697</v>
+        <v>0.4142460990012753</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.1224706842830945</v>
+        <v>0.1224706563563254</v>
       </c>
     </row>
     <row r="60">
@@ -3881,10 +3881,10 @@
         <v>-0.08325970781190706</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.3475660654005512</v>
+        <v>0.3475664630608197</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.1045448506395099</v>
+        <v>0.1045449592881247</v>
       </c>
     </row>
     <row r="61">
@@ -3934,13 +3934,13 @@
         <v>-0.07469354390900318</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.1312054046189869</v>
+        <v>-0.1312053444004524</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1961176798070168</v>
+        <v>0.1961177939485734</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.06151133641770956</v>
+        <v>0.06151137018321462</v>
       </c>
     </row>
     <row r="62">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.6062961058276495</v>
+        <v>0.6062960081727999</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1654236264747735</v>
+        <v>-0.1654237218411977</v>
       </c>
     </row>
     <row r="61">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1312054046189869</v>
+        <v>-0.1312053444004524</v>
       </c>
     </row>
     <row r="62">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.8321597124057059</v>
+        <v>0.8321598701053672</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06209200339854237</v>
+        <v>-0.06209206605126483</v>
       </c>
     </row>
     <row r="66">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.198938195973668</v>
+        <v>3.198937543877196</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.895703961535242</v>
+        <v>2.895703557390161</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.04854395950560098</v>
+        <v>0.04854419109303687</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.781843923754035</v>
+        <v>2.781843660666441</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.129183648854402</v>
+        <v>0.1291837505681623</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.809195225039157</v>
+        <v>1.809194912919116</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.484326008060648</v>
+        <v>1.484326390887332</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1629881328757132</v>
+        <v>0.1629882052191838</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.482264343226667</v>
+        <v>1.482264719107691</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1961176798070168</v>
+        <v>0.1961177939485734</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.349103258312145</v>
+        <v>1.349103040712502</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2042271013071979</v>
+        <v>0.2042272045919782</v>
       </c>
     </row>
     <row r="82">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2108325175219736</v>
+        <v>0.2108326605965962</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>56.06</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.002668523636803921</v>
+        <v>0.01180358812076632</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.0003568960998736603</v>
+        <v>0.02486850605252533</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.03858686240797482</v>
+        <v>0.0003112536720988324</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.0247042132959987</v>
+        <v>0.05307128122779647</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.00990292923562841</v>
+        <v>0.03653690241905228</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.01939202841685472</v>
+        <v>0.2126816226462667</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1705380751625702</v>
+        <v>0.07339530527866356</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.2065085551166912</v>
+        <v>0.02211628757177997</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.818736742316422</v>
+        <v>0.9501667853320555</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.2206466030226337</v>
+        <v>0.2493685953203773</v>
       </c>
     </row>
     <row r="40">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2734,37 +2734,37 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>234.26</v>
+        <v>56.06</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.008968653575532226</v>
+        <v>-0.002668523636803921</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.01389124046839529</v>
+        <v>0.0003568960998736603</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.06179665899194831</v>
+        <v>-0.03858686240797482</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.03956381046446</v>
+        <v>-0.0247042132959987</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.01711405769960672</v>
+        <v>-0.00990292923562841</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>-0.03751605632718502</v>
+        <v>0.01939202841685472</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1515788162993894</v>
+        <v>0.1705380751625702</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.1817485548610145</v>
+        <v>0.2065085551166912</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.099350919197255</v>
+        <v>0.818736742316422</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2804472149867825</v>
+        <v>0.2206466030226337</v>
       </c>
     </row>
     <row r="41">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2790,37 +2790,37 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>29.35</v>
+        <v>234.26</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.01377687648719195</v>
+        <v>-0.008968653575532226</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.00307587668776077</v>
+        <v>-0.01389124046839529</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.07878217767724449</v>
+        <v>-0.06179665899194831</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.052308652496037</v>
+        <v>-0.03956381046446</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.00928474754030395</v>
+        <v>0.01711405769960672</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.03163443214042583</v>
+        <v>-0.03751605632718502</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1268238933470183</v>
+        <v>0.1515788162993894</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1324300054723355</v>
+        <v>0.1817485548610145</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.5648015338211572</v>
+        <v>1.099350919197255</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1609666768189806</v>
+        <v>0.2804472149867825</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>97.65000000000001</v>
+        <v>29.35</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.009735311616780207</v>
+        <v>-0.01377687648719195</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.009634857636346972</v>
+        <v>0.00307587668776077</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.009433965184638571</v>
+        <v>-0.07878217767724449</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.02874477186524582</v>
+        <v>-0.052308652496037</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.01641237789962102</v>
+        <v>0.00928474754030395</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.04048231066887786</v>
+        <v>0.03163443214042583</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.1036049579521161</v>
+        <v>0.1268238933470183</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.1027595566691841</v>
+        <v>0.1324300054723355</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.3586535688327857</v>
+        <v>0.5648015338211572</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1075659047166808</v>
+        <v>0.1609666768189806</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>59.85</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.005483579750435896</v>
+        <v>-0.009735311616780207</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.006474156598257785</v>
+        <v>-0.009634857636346972</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.0250855339768421</v>
+        <v>-0.009433965184638571</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.03296172137090936</v>
+        <v>-0.02874477186524582</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.02994454553492321</v>
+        <v>0.01641237789962102</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>-0.0006064779694855416</v>
+        <v>0.04048231066887786</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1375388476614838</v>
+        <v>0.1036049579521161</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1645529124886174</v>
+        <v>0.1027595566691841</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.6494895717028224</v>
+        <v>0.3586535688327857</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.18154388827699</v>
+        <v>0.1075659047166808</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>74.69</v>
+        <v>59.85</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.01425358650532527</v>
+        <v>-0.005483579750435896</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.003867710089939913</v>
+        <v>-0.006474156598257785</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.003493243788316835</v>
+        <v>-0.0250855339768421</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.009022161077294366</v>
+        <v>-0.03296172137090936</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.03448509793657073</v>
+        <v>-0.02994454553492321</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.02805290456246157</v>
+        <v>-0.0006064779694855416</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1013579311350352</v>
+        <v>0.1375388476614838</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.09529676924548602</v>
+        <v>0.1645529124886174</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.2351877107139491</v>
+        <v>0.6494895717028224</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.0729454787019761</v>
+        <v>0.18154388827699</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>13.39</v>
+        <v>74.69</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.001495920563565178</v>
+        <v>-0.01425358650532527</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.007524483202164145</v>
+        <v>-0.003867710089939913</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.01107825841601739</v>
+        <v>0.003493243788316835</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0.07463886856569291</v>
+        <v>-0.009022161077294366</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.08573156099566237</v>
+        <v>0.03448509793657073</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.1184284398340698</v>
+        <v>-0.02805290456246157</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.002438978766084121</v>
+        <v>0.1013579311350352</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>-0.06209206605126483</v>
+        <v>0.09529676924548602</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.2042272045919782</v>
+        <v>0.2351877107139491</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.06390490551087069</v>
+        <v>0.0729454787019761</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>48.37</v>
+        <v>13.39</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.006659723203021439</v>
+        <v>0.001495920563565178</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.1033302637666498</v>
+        <v>0.007524483202164145</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.06895025263833743</v>
+        <v>-0.01107825841601739</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.1996527603668088</v>
+        <v>0.07463886856569291</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.03568582378334462</v>
+        <v>0.08573156099566237</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.1098638425458085</v>
+        <v>0.1184284398340698</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.1314808437876374</v>
+        <v>0.002438978766084121</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.27719331644162</v>
+        <v>-0.06209206605126483</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>1.349103040712502</v>
+        <v>0.2042272045919782</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.3293337233590132</v>
+        <v>0.06390490551087069</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>266.05</v>
+        <v>48.37</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.002250163574909148</v>
+        <v>0.006659723203021439</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.02108326960064955</v>
+        <v>0.1033302637666498</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.08918184788162986</v>
+        <v>0.06895025263833743</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.02570776483304904</v>
+        <v>0.1996527603668088</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-0.04586581025154646</v>
+        <v>-0.03568582378334462</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.05908252104130807</v>
+        <v>-0.1098638425458085</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.1615841488119443</v>
+        <v>0.1314808437876374</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.2157839606918286</v>
+        <v>0.27719331644162</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>1.272701760368182</v>
+        <v>1.349103040712502</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.3147630275308808</v>
+        <v>0.3293337233590132</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>27.86</v>
+        <v>266.05</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.008433466028960002</v>
+        <v>-0.002250163574909148</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0.03916300043979071</v>
+        <v>-0.02108326960064955</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.02770193411197619</v>
+        <v>-0.08918184788162986</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0.08577553494588286</v>
+        <v>-0.02570776483304904</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.117709168731817</v>
+        <v>-0.04586581025154646</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.1428827612355619</v>
+        <v>-0.05908252104130807</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>-0.06469611018604993</v>
+        <v>0.1615841488119443</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.1654237218411977</v>
+        <v>0.2157839606918286</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.3481278780710768</v>
+        <v>1.272701760368182</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.1046983276107851</v>
+        <v>0.3147630275308808</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>72.44</v>
+        <v>27.86</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.0004142905369381999</v>
+        <v>0.008433466028960002</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0.01357214501379</v>
+        <v>0.03916300043979071</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.0006907452987900964</v>
+        <v>0.02770193411197619</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.03411847659567613</v>
+        <v>0.08577553494588286</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.08207087916771694</v>
+        <v>0.117709168731817</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.0671659541357007</v>
+        <v>0.1428827612355619</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.06192865945662662</v>
+        <v>-0.06469611018604993</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.01633652057566171</v>
+        <v>-0.1654237218411977</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.04854419109303687</v>
+        <v>0.3481278780710768</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01592640022844583</v>
+        <v>0.1046983276107851</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>61.15</v>
+        <v>72.44</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0</v>
+        <v>0.0004142905369381999</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>0.01357214501379</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0</v>
+        <v>0.0006907452987900964</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0</v>
+        <v>0.03411847659567613</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.01411178572315996</v>
+        <v>0.08207087916771694</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.1534804029332366</v>
+        <v>-0.0671659541357007</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.02092262599480477</v>
+        <v>0.06192865945662662</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.02790664672684995</v>
+        <v>-0.01633652057566171</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.8546842624351416</v>
+        <v>0.04854419109303687</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.2286362620085851</v>
+        <v>0.01592640022844583</v>
       </c>
     </row>
     <row r="51">
@@ -6472,21 +6472,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.02790664672684995</v>
+        <v>-0.01633652057566171</v>
       </c>
     </row>
     <row r="67">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.01633652057566171</v>
+        <v>0.008337524384908201</v>
       </c>
     </row>
     <row r="68">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.008337524384908201</v>
+        <v>0.01388916681436414</v>
       </c>
     </row>
     <row r="69"/>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -492,11 +492,11 @@
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
@@ -592,51 +592,51 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>40.6</v>
+        <v>15.47</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.0007384344869655335</v>
+        <v>0.04385968863626877</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.03334175434126907</v>
+        <v>0.05309739339183528</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.1520997883189514</v>
+        <v>0.1050000190734863</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.2593050980278939</v>
+        <v>0.152757092330881</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3675183606502821</v>
+        <v>0.195517833747145</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.3097074275398546</v>
+        <v>0.2816901953744504</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.4913115329741946</v>
+        <v>0.7639680113510074</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8321598701053672</v>
+        <v>0.8482676796351563</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>0.9165036124037205</v>
+        <v>2.16359932298873</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.2421380933189037</v>
+        <v>0.4680037263200747</v>
       </c>
     </row>
     <row r="3">
@@ -648,12 +648,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>168.23</v>
+        <v>39.26</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.0009501969397787136</v>
+        <v>-0.03300493110712854</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.02968533908543658</v>
+        <v>-0.01033526257465445</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.07248498707730566</v>
+        <v>0.094813096857566</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1171392510699594</v>
+        <v>0.2143518743578259</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2524740777631889</v>
+        <v>0.3194625597125427</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3220941573732861</v>
+        <v>0.266480624123407</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.3752725956834628</v>
+        <v>0.4394737385007925</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.8717462955109481</v>
+        <v>0.7897597987467058</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.15139025605556</v>
+        <v>0.8056374078355901</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2909410148233977</v>
+        <v>0.2177089961532312</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>118.58</v>
+        <v>162.5</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.08183560962279568</v>
+        <v>-0.03406048786221938</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.08025877250078928</v>
+        <v>-0.01017237124670456</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.02715561223372076</v>
+        <v>0.01861719578404819</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.119524205824818</v>
+        <v>0.1053670231410271</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2918618656533372</v>
+        <v>0.1899883913110376</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.6208309991169259</v>
+        <v>0.2770629853733622</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4299006343259106</v>
+        <v>0.3250863827018096</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4165865066930616</v>
+        <v>0.8168475521495351</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.331180190758338</v>
+        <v>1.064730871609922</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3259443019597366</v>
+        <v>0.2733696185660617</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>14.82</v>
+        <v>116.97</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.01593630266303725</v>
+        <v>-0.0135773366966665</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.0443974723799041</v>
+        <v>0.06753674862178949</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.06695459528541603</v>
+        <v>0.01220148573812874</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.1970920482898146</v>
+        <v>0.0953272798754663</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1510679374620751</v>
+        <v>0.1773528235249215</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2278376196794136</v>
+        <v>0.5988244309135209</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.6108695654427396</v>
+        <v>0.3976866662272542</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7855420908745894</v>
+        <v>0.3870868717720912</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.999999903474261</v>
+        <v>1.222486343295206</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.442249554839163</v>
+        <v>0.3050075782935981</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>573</v>
+        <v>556.63</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.03100199698300066</v>
+        <v>-0.02856892690608637</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.01839505045203871</v>
+        <v>0.01797735425986446</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.02736283821767227</v>
+        <v>-0.06302287942466867</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.04457207684098807</v>
+        <v>0.02978553403754547</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.03778337531486142</v>
+        <v>-0.07062593009241236</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.4100450497944867</v>
+        <v>0.3697615758326191</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.6530527402671746</v>
+        <v>0.5849948869035908</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.9310050622889963</v>
+        <v>0.923462653161536</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.895703557390161</v>
+        <v>2.6116842591124</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5734826818148677</v>
+        <v>0.5342751774802219</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>96.45</v>
+        <v>100.15</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.009524764747693704</v>
+        <v>-0.006349830179928517</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.07250079640766072</v>
+        <v>0.07422501254721525</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.1278063696704079</v>
+        <v>0.02413335298350372</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.2381257388833407</v>
+        <v>0.09060219458702656</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1241463903056188</v>
+        <v>0.125742584616398</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.01126188174680198</v>
+        <v>0.5960963983369636</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5908603163349453</v>
+        <v>0.3670992475406898</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>1.043047874174863</v>
+        <v>0.3766502254135238</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.809194912919116</v>
+        <v>1.151349983541433</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.4110009010763827</v>
+        <v>0.2909329596035206</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>100.79</v>
+        <v>92.86</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.07612638238986569</v>
+        <v>-0.03722132142541301</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.07854472131604728</v>
+        <v>-0.01766633016513974</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.01379643908824102</v>
+        <v>0.06320133391242422</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.1312009275151849</v>
+        <v>0.1775297982709156</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.22960351112463</v>
+        <v>0.05713141721587411</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.6062960081727999</v>
+        <v>-0.02637862179896378</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.3888472515257795</v>
+        <v>0.4830527866977201</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.3860159216002093</v>
+        <v>0.9144810780686863</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.244582066225699</v>
+        <v>1.602476911986245</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.3093180737332164</v>
+        <v>0.3755053854805361</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>28.92</v>
+        <v>70.62</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.05240176703221411</v>
+        <v>-0.02472035388756666</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.04517527996217563</v>
+        <v>-0.02834338951491511</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.006526984887456622</v>
+        <v>0.002840167322312181</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.2130872437580336</v>
+        <v>0.03761394769055548</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2991913647319246</v>
+        <v>0.2135335737595909</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.5415778104186986</v>
+        <v>0.2342206535407039</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2819149273453181</v>
+        <v>0.2940286933299185</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.28934461358971</v>
+        <v>0.4971559260941103</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4695121762110985</v>
+        <v>0.6736711062572551</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1369055754996991</v>
+        <v>0.1872897164139793</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>72.41</v>
+        <v>188.96</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.0054936672146223</v>
+        <v>0.01881708885638633</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.001660018606477243</v>
+        <v>0.01460481712025596</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.03472420961144485</v>
+        <v>0.03059722074502824</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.05646341836720503</v>
+        <v>0.06516354687209436</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.243225832058245</v>
+        <v>0.1579130290056037</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2655044537686493</v>
+        <v>0.2402374618787975</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.3273128517246395</v>
+        <v>0.4329287921225777</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5406216200729459</v>
+        <v>0.4536533424611577</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.7339446918185966</v>
+        <v>0.3641599439164334</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2013745110674376</v>
+        <v>0.1090601421010695</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>214.8</v>
+        <v>28.82</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.001997828761403642</v>
+        <v>-0.003457827842528238</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.01883034286498009</v>
+        <v>0.04043317332262464</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.07972253149550856</v>
+        <v>0.03371594556503466</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.1405511653127289</v>
+        <v>0.1454689932276994</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.264599691098145</v>
+        <v>0.1874742130713498</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.2259060402450779</v>
+        <v>0.5362472997444092</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2393161384869218</v>
+        <v>0.2712836170195403</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5538398146138817</v>
+        <v>0.2574170854664446</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6978036884940182</v>
+        <v>0.4051681800685882</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1929689977073865</v>
+        <v>0.1200638197234249</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>103.14</v>
+        <v>209.05</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.02494288189146521</v>
+        <v>-0.02676908714295734</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.05828032381010684</v>
+        <v>-0.01637413893345419</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.1630581758537579</v>
+        <v>0.03525979613839958</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.3610451445114873</v>
+        <v>0.1214527061041539</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1637435987183533</v>
+        <v>0.2143072205995868</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>-0.1249492365973937</v>
+        <v>0.1930896546246796</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.4222635707587059</v>
+        <v>0.2049612529914484</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.8658471463941766</v>
+        <v>0.5162932645962155</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>3.198937543877196</v>
+        <v>0.6378481658446225</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.6132925871587993</v>
+        <v>0.1787577095976636</v>
       </c>
     </row>
     <row r="13">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>185.47</v>
+        <v>429.18</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.00547541185121303</v>
+        <v>0.03429324027022851</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.0105627941305636</v>
+        <v>0.05008441596405899</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.03516215391048516</v>
+        <v>0.006047788409172083</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.09693635682607438</v>
+        <v>0.1153036443925328</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1409098998436606</v>
+        <v>0.02613267824454568</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.217330839307921</v>
+        <v>0.08113961094296984</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4314566256098578</v>
+        <v>0.5076458241517798</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4442875190354245</v>
+        <v>0.6999386790725202</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3639163496434898</v>
+        <v>0.3263816528602612</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1089941242360377</v>
+        <v>0.09872625369393195</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>500.26</v>
+        <v>152.52</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.01946163411555712</v>
+        <v>-0.002446855470853215</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.00708624149545356</v>
+        <v>0.01908255997735764</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.06507439301059192</v>
+        <v>-0.02007260179707437</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.01503500775153288</v>
+        <v>0.05234187101211063</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>-0.1946778897260528</v>
+        <v>-0.03662681045437166</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.4263976656966508</v>
+        <v>0.2696698964108162</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.5863167680808199</v>
+        <v>0.4467971463798959</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7361231583136925</v>
+        <v>0.555410419135101</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.482264719107691</v>
+        <v>1.27676271016182</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3539917917103961</v>
+        <v>0.3155456510738266</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>103.69</v>
+        <v>485.14</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.01239996382704511</v>
+        <v>-0.03022427302208563</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.03845772684994486</v>
+        <v>0.007350515988492345</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.1746913604255935</v>
+        <v>-0.1168675302517548</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.369206362670955</v>
+        <v>-0.004779753762141237</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.2136001811623969</v>
+        <v>-0.2083553731659464</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>-0.1048860003503831</v>
+        <v>0.3832858332105695</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2807243524244734</v>
+        <v>0.5120887156736547</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.6988138925974754</v>
+        <v>0.6987110495995432</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>2.781843660666441</v>
+        <v>1.293840968831629</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.5580014485750293</v>
+        <v>0.3188268135972747</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>152.89</v>
+        <v>31.2</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.006119983118534567</v>
+        <v>0.008403368597089678</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.01453219964004648</v>
+        <v>0.002248686285256207</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.01741649490723229</v>
+        <v>0.02699149522136324</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.04934799308170468</v>
+        <v>0.06303238015075907</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.01365679608037851</v>
+        <v>0.1002339860657626</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.2727842154315607</v>
+        <v>0.1286330810561378</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.4592480425549732</v>
+        <v>0.2901853062550197</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.5429579189053095</v>
+        <v>0.3280326616848959</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>1.351580548471401</v>
+        <v>0.2740522369808664</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.32980089138236</v>
+        <v>0.08408269414169212</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>414.95</v>
+        <v>108.01</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.02487158467391692</v>
+        <v>-0.01567484888438619</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.002667849247886878</v>
+        <v>0.003250961008877118</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.01066810727690037</v>
+        <v>-0.002677755377243574</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.07589198321691426</v>
+        <v>0.02398557734906026</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.02486308040000951</v>
+        <v>-0.02570808640113764</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.04529312273229369</v>
+        <v>0.06855955856390472</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.4768315772644252</v>
+        <v>0.3568496477598939</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.6652294244766919</v>
+        <v>0.5433234962554168</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.3195428976470995</v>
+        <v>0.7357731113146404</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.09683467374751586</v>
+        <v>0.2017966400508191</v>
       </c>
     </row>
     <row r="18">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>109.73</v>
+        <v>97.95</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.01040520164539216</v>
+        <v>-0.05031997742989269</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.04704198627495271</v>
+        <v>-0.02411084718658385</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.01133643646943394</v>
+        <v>0.0796957190283758</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.05408266056999134</v>
+        <v>0.328135551840572</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.005798671502418307</v>
+        <v>0.04646410767644094</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.08557579510471847</v>
+        <v>-0.1689817712618231</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.3772645215508754</v>
+        <v>0.2766035598922716</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.5698875424821077</v>
+        <v>0.7063862443904645</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.8159850787144027</v>
+        <v>2.853722750828505</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.220030698572333</v>
+        <v>0.5678102121891515</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>30.94</v>
+        <v>56.71</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.01111111595912861</v>
+        <v>-0.009605296073746383</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.02150538542465985</v>
+        <v>-0.009778267309496824</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.04881357742568193</v>
+        <v>0.008177761501736214</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.1061852446769662</v>
+        <v>0.00585310411680795</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.0876331567687727</v>
+        <v>0.1295921399728448</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1192277973310563</v>
+        <v>0.2341191744405544</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.3065200715476364</v>
+        <v>0.1563118701947661</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.333026239170555</v>
+        <v>0.2139146223520154</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.298693778243728</v>
+        <v>0.1805961530962943</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.09102722181241973</v>
+        <v>0.05689973235370505</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>57.26</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.002612811814624472</v>
+        <v>-0.01144003384036463</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01524816972318144</v>
+        <v>-0.04858024661792859</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.005973298726727361</v>
+        <v>0.07204269007022956</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.009520400021306274</v>
+        <v>0.3294197593085566</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.1362512251684804</v>
+        <v>0.1007934348841093</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.2460882207347193</v>
+        <v>-0.1496028552272287</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1677623735262805</v>
+        <v>0.1921837328483802</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.2358929665320748</v>
+        <v>0.5707686660196767</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.179860437144562</v>
+        <v>2.487313996537913</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05668014284990086</v>
+        <v>0.5164578757331455</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>123</v>
+        <v>55.59</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.02235892690543984</v>
+        <v>0.00506235350469697</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.07236271379765724</v>
+        <v>0.01219959952623295</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.06705997728853541</v>
+        <v>0.01645641887874127</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.1929007785075274</v>
+        <v>0.0239349592719027</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.001416854141543578</v>
+        <v>0.09775354493795252</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.03192644568444858</v>
+        <v>0.1096094319411538</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2933886966188599</v>
+        <v>0.2359599877833838</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.5235049658937658</v>
+        <v>0.235594774420586</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1.484326390887332</v>
+        <v>0.7176262490656098</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3543665454810989</v>
+        <v>0.1975938473477061</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>110.32</v>
+        <v>76.37</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.07744897306814025</v>
+        <v>-0.009853423232194625</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.08252375361106701</v>
+        <v>-0.008568038987068372</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.03801280543780283</v>
+        <v>0.001705205750986538</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.213507812680958</v>
+        <v>0.1032938659316347</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1858213621099751</v>
+        <v>-0.1199278321003493</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.3527115622104939</v>
+        <v>0.01721868989143682</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.07158087244109468</v>
+        <v>0.2118903641402832</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.02690261788790416</v>
+        <v>0.6204500785702178</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.5951641357813047</v>
+        <v>0.323995279895916</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1684275600745069</v>
+        <v>0.09806692997583011</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>77.13</v>
+        <v>109.98</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.01593781761927904</v>
+        <v>0.00438359230076335</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.03419141002623949</v>
+        <v>0.07349933267929298</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.03308322354881077</v>
+        <v>0.0783410693256068</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.1238525475764416</v>
+        <v>0.1628251345711269</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.094334708998008</v>
+        <v>0.08204427739932241</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0273415206988894</v>
+        <v>0.3485426265809966</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.2366166656198008</v>
+        <v>0.05678385446639722</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.6603653939958316</v>
+        <v>0.01758209860677784</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.3853278412159706</v>
+        <v>0.5276591713126926</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1147672142923335</v>
+        <v>0.1517073998352301</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>55.31</v>
+        <v>73.56</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.003064134288896181</v>
+        <v>-0.01062543284116302</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.007284675414140684</v>
+        <v>-0.01605142513840518</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.01766334730675356</v>
+        <v>-0.04948962218969832</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.03925456459093635</v>
+        <v>-0.03286878885414235</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.06962949050167255</v>
+        <v>0.06292481440320019</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1040204899446253</v>
+        <v>0.1145710569023737</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.2367409651420747</v>
+        <v>0.1888463198548427</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2421240624434589</v>
+        <v>0.1501555932605541</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7249112721198103</v>
+        <v>0.7955806877121991</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1992845902699236</v>
+        <v>0.2154440591988103</v>
       </c>
     </row>
     <row r="25">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>74.34999999999999</v>
+        <v>67.81</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.00308398164771595</v>
+        <v>-0.008915530936515426</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.004818640272562735</v>
+        <v>-0.01424630533348903</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.04372992316242963</v>
+        <v>-0.04573599931973193</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.01549256118846409</v>
+        <v>-0.02641785968377175</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.07480331894998149</v>
+        <v>0.07377789848259275</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.126541043098632</v>
+        <v>0.1232176423175408</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.198190174209165</v>
+        <v>0.1702825132734951</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1582644817186409</v>
+        <v>0.1372944562027678</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8535497924999462</v>
+        <v>0.8831678479734686</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2283857009074384</v>
+        <v>0.2348939897036377</v>
       </c>
     </row>
     <row r="26">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>195.35</v>
+        <v>132.69</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.002000407141044214</v>
+        <v>-0.008157372887716119</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.03441884982750332</v>
+        <v>-0.02685222218765482</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.01739498824141039</v>
+        <v>0.008119665452022806</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.03551557075961354</v>
+        <v>-0.01733906062450408</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.1025320730022015</v>
+        <v>0.1553989227386021</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1523063754411451</v>
+        <v>0.06252281457104747</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1301589907852347</v>
+        <v>0.08317634379885952</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1323071529322364</v>
+        <v>0.1147183251831743</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.180986623493694</v>
+        <v>0.692591361657422</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2968338381395514</v>
+        <v>0.1917469250263137</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>68.42</v>
+        <v>118.13</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.004075673824379122</v>
+        <v>-0.03959351826489454</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.002914668750092386</v>
+        <v>0.002205773316175552</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.04187096120750622</v>
+        <v>0.0002540116823408489</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.01155739725006732</v>
+        <v>0.1736710925239742</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.08156350063015205</v>
+        <v>-0.05589957016043301</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1333218079574128</v>
+        <v>-0.008931152890786387</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1772172951694551</v>
+        <v>0.2197892404961077</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1434055713817428</v>
+        <v>0.4400803396251158</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.9439034805359205</v>
+        <v>1.308966916538867</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2480296382860141</v>
+        <v>0.3217193154110005</v>
       </c>
     </row>
     <row r="28">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>133.78</v>
+        <v>143.94</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.01320357341754086</v>
+        <v>-0.007857729358012877</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.0008229266990229522</v>
+        <v>-0.01653455970793538</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.002322601002161973</v>
+        <v>0.0003475088746258681</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.01820046842446221</v>
+        <v>-0.02188095365977627</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.1387338883824909</v>
+        <v>0.1245583487494526</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.07126149403816884</v>
+        <v>0.07330366969481239</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.08963670743614971</v>
+        <v>0.09330246407775045</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1216701120997679</v>
+        <v>0.1134289781006304</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.7252648386173806</v>
+        <v>0.6778246525316725</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1993665264426143</v>
+        <v>0.1882710699005079</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>86.40000000000001</v>
+        <v>194.47</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.009401509783854234</v>
+        <v>-0.004504759945316739</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.00150695360926445</v>
+        <v>-0.001488977686958326</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.01974129652619316</v>
+        <v>0.01816754565813161</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.008946992160661527</v>
+        <v>0.04407820764520576</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.02297696711730346</v>
+        <v>0.06664219499818858</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.06220449560621866</v>
+        <v>0.1471155118363248</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.2015232535686169</v>
+        <v>0.1167468220155197</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2223582362394017</v>
+        <v>0.1297303209994909</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4538853224177233</v>
+        <v>1.140614444762822</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1328612384498735</v>
+        <v>0.2887820655709239</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>293.83</v>
+        <v>85.14</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.01935814942676717</v>
+        <v>-0.01458335780067166</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.03453981387951366</v>
+        <v>-0.01946334683597606</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.004809528967770982</v>
+        <v>-0.02496564719187688</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.1128237277051727</v>
+        <v>0.002944987652226061</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.07069195938580974</v>
+        <v>0.01780226172605381</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.206892214200902</v>
+        <v>0.04671398738931121</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.101229212602586</v>
+        <v>0.1752403433254921</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.07229398712808988</v>
+        <v>0.206221067154251</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.8120875586331813</v>
+        <v>0.4110025111600617</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2191572515920148</v>
+        <v>0.1216118668438508</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>144.62</v>
+        <v>292.49</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.01094245718888065</v>
+        <v>-0.004560447875053941</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.003330066113303554</v>
+        <v>0.02090747027705064</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.005843171075705311</v>
+        <v>0.01934198001584697</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.02985182792238505</v>
+        <v>0.0644127557009031</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.105415123044259</v>
+        <v>0.03214759402424949</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.07837410613987705</v>
+        <v>0.2013882451672302</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.09618904411916929</v>
+        <v>0.08265467230372803</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1194475363644438</v>
+        <v>0.0577152262884002</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.7021953412139073</v>
+        <v>0.7252993118648809</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1939967165941587</v>
+        <v>0.1993745147395998</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>66.86</v>
+        <v>105.63</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.01849680101919393</v>
+        <v>-0.01289603640093073</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01080035163620552</v>
+        <v>-0.01501306082080311</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03143558173719874</v>
+        <v>-0.04519569849167215</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.003150773888446423</v>
+        <v>-0.03065067385399456</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.07087356402039879</v>
+        <v>-0.0525388597277785</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.08811896223178595</v>
+        <v>0.03571370863132728</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.145653019256009</v>
+        <v>0.2238039344669769</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1272357546581819</v>
+        <v>0.2361417539434949</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.6952676097207109</v>
+        <v>0.3479426040050007</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1923747061836572</v>
+        <v>0.1046477188292656</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>107.01</v>
+        <v>93.77</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.007604559778353503</v>
+        <v>-0.01190732207211131</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.003469643179854875</v>
+        <v>-0.03090125493129248</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.04719077141461248</v>
+        <v>-0.008668989603245691</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.05275736053882962</v>
+        <v>-0.02434714340260991</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.03227196371513608</v>
+        <v>0.05053043978247507</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.04924480786706842</v>
+        <v>0.0526416716441227</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.2471182760515491</v>
+        <v>0.08870234743015004</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2483778937130097</v>
+        <v>0.1308846853102006</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3936192061307255</v>
+        <v>0.4243006793652089</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1169868002755157</v>
+        <v>0.1251244449965172</v>
       </c>
     </row>
     <row r="34">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2398,37 +2398,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>19.94</v>
+        <v>65.37</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.004592241164112942</v>
+        <v>-0.02228534026574391</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.005386523977323421</v>
+        <v>-0.04999265999221203</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.02053050895854269</v>
+        <v>-0.04191705217116815</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.07911255029238795</v>
+        <v>-0.02243158274846446</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.1934171470993917</v>
+        <v>0.04167710439685512</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.165517166805937</v>
+        <v>0.06386986090884239</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.01447991925322045</v>
+        <v>0.1095242100290603</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.0943688001426094</v>
+        <v>0.1047080568208931</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.1463158666827324</v>
+        <v>0.616152171692627</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.04656956560216963</v>
+        <v>0.1735296947723128</v>
       </c>
     </row>
     <row r="35">
@@ -2454,37 +2454,37 @@
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>239.51</v>
+        <v>236.38</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.00424065304800858</v>
+        <v>-0.01306830485495292</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.02092919128550164</v>
+        <v>-0.01240861142664285</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.02411595975286329</v>
+        <v>0.008275048716957389</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.0533004756133495</v>
+        <v>0.06061834280797318</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.0354973132794707</v>
+        <v>0.01994372710642311</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>-0.0118506579760792</v>
+        <v>-0.02476409481986896</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.201509107846672</v>
+        <v>0.1771643162235665</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1679440625960094</v>
+        <v>0.1514640445291633</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.4150646678888199</v>
+        <v>0.3605252189070798</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1226871774513179</v>
+        <v>0.1080742571739794</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>94.90000000000001</v>
+        <v>64.23</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.01361602298159847</v>
+        <v>-0.001006334806403331</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.008980791469992866</v>
+        <v>0.02302174097974174</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.002732262780838823</v>
+        <v>0.01142210472287153</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.03947369843537185</v>
+        <v>0.06421384049318624</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.03967447518882583</v>
+        <v>0.01168179948035886</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.06532686169843749</v>
+        <v>0.211461258920312</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.1068792791381836</v>
+        <v>0.06080392942103341</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.1521247659623972</v>
+        <v>0.02141235894613769</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.4578938695178663</v>
+        <v>0.8783208249748731</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1339014306516646</v>
+        <v>0.2338335952420236</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>24.18</v>
+        <v>178.39</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.01086957475136097</v>
+        <v>-0.01827091080045284</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.01044713735109859</v>
+        <v>0.001066231451515964</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.008203398788982241</v>
+        <v>-0.05713529457165345</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0.01129236551596602</v>
+        <v>-0.005352699644253667</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.0699026218591392</v>
+        <v>-0.07230708618617632</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-0.008326910457219339</v>
+        <v>0.007682056666696191</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.2288695777599072</v>
+        <v>0.1763587152568953</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.3110616082767637</v>
+        <v>0.2587633204958708</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.5704425961087913</v>
+        <v>0.8240334046660189</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1623600870306985</v>
+        <v>0.2218304076185909</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>181.71</v>
+        <v>19.73</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.004866476104085082</v>
+        <v>-0.0108514769135919</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.003036007069108004</v>
+        <v>-0.0259444064981903</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.0345358895283493</v>
+        <v>-0.01818726402600468</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.02975178397512446</v>
+        <v>0.01993790761686953</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.06054030020464729</v>
+        <v>0.1389571575076343</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.02643597684195131</v>
+        <v>0.1528695841779473</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.2072660329993872</v>
+        <v>-0.03068309979482176</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.2698392065852875</v>
+        <v>-0.1154439478115183</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.8955458628444235</v>
+        <v>0.1048158473778946</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.2375937255885336</v>
+        <v>0.03378437794766409</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>64.29000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.01180358812076632</v>
+        <v>-0.0004016438387508536</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.02486850605252533</v>
+        <v>-0.02059556113979122</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.0003112536720988324</v>
+        <v>0.01385122597657595</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.05307128122779647</v>
+        <v>-0.0008029651714878128</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.03653690241905228</v>
+        <v>0.05588242973991364</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.2126816226462667</v>
+        <v>-0.02844328112493577</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.07339530527866356</v>
+        <v>0.09790205867378488</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.02211628757177997</v>
+        <v>0.09049851861996694</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.9501667853320555</v>
+        <v>0.2348171787576088</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.2493685953203773</v>
+        <v>0.0728381804768039</v>
       </c>
     </row>
     <row r="40">
@@ -2734,37 +2734,37 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>56.06</v>
+        <v>54.7</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.002668523636803921</v>
+        <v>-0.02425973201990528</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.0003568960998736603</v>
+        <v>-0.02181683558572389</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.03858686240797482</v>
+        <v>-0.06861908412579942</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.0247042132959987</v>
+        <v>-0.02945351010353292</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.00990292923562841</v>
+        <v>-0.02688828311025171</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.01939202841685472</v>
+        <v>-0.005338149015765792</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1705380751625702</v>
+        <v>0.13649393914632</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.2065085551166912</v>
+        <v>0.1860980806989365</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.818736742316422</v>
+        <v>0.7311704443157068</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2206466030226337</v>
+        <v>0.200733450764135</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>234.26</v>
+        <v>23.63</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.008968653575532226</v>
+        <v>-0.02274611817483929</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.01389124046839529</v>
+        <v>-0.005471425373018701</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.06179665899194831</v>
+        <v>-0.02917013095194254</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.03956381046446</v>
+        <v>-0.00421409116724758</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.01711405769960672</v>
+        <v>-0.09591007939751295</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>-0.03751605632718502</v>
+        <v>-0.03088362374276743</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1515788162993894</v>
+        <v>0.1966867928406613</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1817485548610145</v>
+        <v>0.2888416885228728</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.099350919197255</v>
+        <v>0.5541236334223028</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.2804472149867825</v>
+        <v>0.1583199106142226</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>29.35</v>
+        <v>13.51</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.01377687648719195</v>
+        <v>0.008961903098002821</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.00307587668776077</v>
+        <v>0.005208381747325852</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.07878217767724449</v>
+        <v>0.02503792989871667</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.052308652496037</v>
+        <v>0.08951618100800607</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.00928474754030395</v>
+        <v>0.09025767424155728</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.03163443214042583</v>
+        <v>0.1284516871339132</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.1268238933470183</v>
+        <v>0.005204958039536134</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.1324300054723355</v>
+        <v>-0.06073994766337687</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.5648015338211572</v>
+        <v>0.1934462596016899</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1609666768189806</v>
+        <v>0.06072048430556842</v>
       </c>
     </row>
     <row r="43">
@@ -2902,37 +2902,37 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>97.65000000000001</v>
+        <v>96.44</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.009735311616780207</v>
+        <v>-0.01239118346712964</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.009634857636346972</v>
+        <v>-0.02684153454764659</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.009433965184638571</v>
+        <v>-0.01571750217151191</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.02874477186524582</v>
+        <v>-0.02536629190750594</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.01641237789962102</v>
+        <v>0.01661468954834078</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.04048231066887786</v>
+        <v>0.02758950346307687</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1036049579521161</v>
+        <v>0.08635028691987245</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1027595566691841</v>
+        <v>0.08602520252489199</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.3586535688327857</v>
+        <v>0.3183635067141131</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1075659047166808</v>
+        <v>0.09650779730587677</v>
       </c>
     </row>
     <row r="44">
@@ -2958,37 +2958,37 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>59.85</v>
+        <v>58.74</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.005483579750435896</v>
+        <v>-0.01854631284801544</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.006474156598257785</v>
+        <v>-0.01624514186700265</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.0250855339768421</v>
+        <v>-0.05425855576828165</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.03296172137090936</v>
+        <v>-0.03021294412378539</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.02994454553492321</v>
+        <v>-0.03293245315669513</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.0006064779694855416</v>
+        <v>-0.01914154288734349</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1375388476614838</v>
+        <v>0.1089543463384499</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.1645529124886174</v>
+        <v>0.1491067082310065</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.6494895717028224</v>
+        <v>0.5956282324024154</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.18154388827699</v>
+        <v>0.168540863086265</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>74.69</v>
+        <v>228.35</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.01425358650532527</v>
+        <v>-0.02522832981261702</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.003867710089939913</v>
+        <v>-0.0216366235005494</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.003493243788316835</v>
+        <v>-0.09096334045511401</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.009022161077294366</v>
+        <v>-0.04719184422002864</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.03448509793657073</v>
+        <v>-0.0294329609003765</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.02805290456246157</v>
+        <v>-0.06179791869751117</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.1013579311350352</v>
+        <v>0.1148639905275106</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.09529676924548602</v>
+        <v>0.1566955050625127</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.2351877107139491</v>
+        <v>1.009219225563303</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.0729454787019761</v>
+        <v>0.26185399893989</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>13.39</v>
+        <v>28.5</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.001495920563565178</v>
+        <v>-0.02896083033805952</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.007524483202164145</v>
+        <v>-0.03943377395636627</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.01107825841601739</v>
+        <v>-0.07617505194201779</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.07463886856569291</v>
+        <v>-0.08887470030754774</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.08573156099566237</v>
+        <v>-0.02796724772711956</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.1184284398340698</v>
+        <v>0.001757442380306617</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.002438978766084121</v>
+        <v>0.09211075348672804</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-0.06209206605126483</v>
+        <v>0.09211075348672804</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.2042272045919782</v>
+        <v>0.4926459093010964</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.06390490551087069</v>
+        <v>0.142840436430097</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>48.37</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.006659723203021439</v>
+        <v>-0.005658827630127927</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0.1033302637666498</v>
+        <v>-0.03095104161201512</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.06895025263833743</v>
+        <v>-0.01644965074647187</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0.1996527603668088</v>
+        <v>-0.04098908838506676</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-0.03568582378334462</v>
+        <v>0.02733391382002881</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.1098638425458085</v>
+        <v>-0.005300282501337739</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.1314808437876374</v>
+        <v>0.02774594647611783</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.27719331644162</v>
+        <v>0.03090363503342508</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>1.349103040712502</v>
+        <v>0.3890203954732305</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.3293337233590132</v>
+        <v>0.115756796295218</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>266.05</v>
+        <v>71.7</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.002250163574909148</v>
+        <v>-0.01014770524165931</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.02108326960064955</v>
+        <v>-0.009737618802974302</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.08918184788162986</v>
+        <v>0.007940726231711714</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.02570776483304904</v>
+        <v>-0.003406453227408957</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.04586581025154646</v>
+        <v>0.06871777132806356</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.05908252104130807</v>
+        <v>-0.07663207907251601</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.1615841488119443</v>
+        <v>0.04368494046218396</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>0.2157839606918286</v>
+        <v>-0.03349294548434179</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>1.272701760368182</v>
+        <v>0.01480840986727761</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.3147630275308808</v>
+        <v>0.004911969671939964</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>27.86</v>
+        <v>47.7</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.008433466028960002</v>
+        <v>-0.002538664294353565</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0.03916300043979071</v>
+        <v>-0.02636049939127583</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.02770193411197619</v>
+        <v>-0.001703600090696811</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.08577553494588286</v>
+        <v>-0.0002389083137375181</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.117709168731817</v>
+        <v>0.001265925870347129</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.1428827612355619</v>
+        <v>-0.05834673640859633</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>-0.06469611018604993</v>
+        <v>0.0546054417190136</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.1654237218411977</v>
+        <v>0.01901200860951291</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.3481278780710768</v>
+        <v>0.1207439919754676</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.1046983276107851</v>
+        <v>0.03872872030189467</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>72.44</v>
+        <v>256.52</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.0004142905369381999</v>
+        <v>-0.03582033157886411</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0.01357214501379</v>
+        <v>-0.03422309716955507</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0.0006907452987900964</v>
+        <v>-0.1300573362449934</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0.03411847659567613</v>
+        <v>-0.03148832137410451</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.08207087916771694</v>
+        <v>-0.1091113144646929</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.0671659541357007</v>
+        <v>-0.09278649712595732</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.06192865945662662</v>
+        <v>0.1151612176119026</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.01633652057566171</v>
+        <v>0.1837711482463826</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.04854419109303687</v>
+        <v>1.13493544031813</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.01592640022844583</v>
+        <v>0.287641352439743</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>86.59</v>
+        <v>54.97</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.0185878607802874</v>
+        <v>0.006407951220483099</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.001614285871370025</v>
+        <v>-0.0162848931642442</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.03023859950669117</v>
+        <v>-0.001997106149142169</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.03294622009686787</v>
+        <v>0.0468482760960427</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>0.03354970184710826</v>
+        <v>0.1244512176565467</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.0003605856206634339</v>
+        <v>-0.08478817152057316</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.03273779625803841</v>
+        <v>-0.1430827422054431</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.01388916681436414</v>
+        <v>-0.1117135736789118</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.4480708622462588</v>
+        <v>0.06243518783464097</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1313490198877358</v>
+        <v>0.02039302675113652</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>47.82</v>
+        <v>19.35</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.01503603612168725</v>
+        <v>-0.01015095915385356</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.01198350852829144</v>
+        <v>-0.02531116571965486</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.004372248382466637</v>
+        <v>-0.006082741988302942</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.008500929946164804</v>
+        <v>0.01190439373566798</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.01352839709025433</v>
+        <v>0.03735120507107248</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.05595011066244671</v>
+        <v>0.05534577819654629</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.05868168784371908</v>
+        <v>-0.04627030316433367</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.01881310068191921</v>
+        <v>-0.197671511211941</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.1291837505681623</v>
+        <v>0.1630752817707217</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.04132958355072414</v>
+        <v>0.05164527603247682</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>19.55</v>
+        <v>111.46</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.001481522912788691</v>
+        <v>0.0004487516445552675</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>0.002873403198657476</v>
+        <v>-0.007656700611540224</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.01558842421294981</v>
+        <v>0.005775125351117794</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.003336783140917676</v>
+        <v>0.02974871844284221</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.04855154057290867</v>
+        <v>-0.03405688063519186</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.06616841017940644</v>
+        <v>-0.05034669892222399</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.02135404514820882</v>
+        <v>-0.02530976117652806</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>-0.190727699206089</v>
+        <v>0.01321263422170049</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.2108326605965962</v>
+        <v>0.7022115385063521</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.06584661184754892</v>
+        <v>0.1940005037530486</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>45.53</v>
+        <v>27.01</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.002847154370338889</v>
+        <v>-0.03056960723720403</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.003501857128938024</v>
+        <v>-0.01497811244411418</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.002628756682822919</v>
+        <v>0.02560475302459797</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.005678142193316749</v>
+        <v>0.05628864115319931</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-0.007844859776415025</v>
+        <v>0.03070568135061058</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.1021494852829112</v>
+        <v>0.1079452841064195</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.002418601323448066</v>
+        <v>-0.1129734192423287</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>0.008337524384908201</v>
+        <v>-0.1994578725057421</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.3107720733022772</v>
+        <v>0.2629708987800405</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.09439909853506201</v>
+        <v>0.08093052484410945</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>54.62</v>
+        <v>45.51</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.01390143466778182</v>
+        <v>-0.05912757232802612</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.01496847285184222</v>
+        <v>-0.003939599706412777</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.02655501091176093</v>
+        <v>0.005745819260402296</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.06326649927147976</v>
+        <v>0.1648323183263838</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>0.1125198395015694</v>
+        <v>-0.1034278994011091</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.09061540551572755</v>
+        <v>-0.1624954325774725</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.1481418131020827</v>
+        <v>0.05305883115165888</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-0.1165165132553329</v>
+        <v>0.1724244846247063</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.0711769903096382</v>
+        <v>1.165100197950444</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.02318401126855751</v>
+        <v>0.293677425721405</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>111.41</v>
+        <v>35.89</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.01065622006694034</v>
+        <v>-0.006917543005593108</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.006595621204560587</v>
+        <v>0.01815601105385634</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.0101288259328095</v>
+        <v>-0.0510312089039997</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.03483187695004508</v>
+        <v>0.01902322957761493</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.03922384863474582</v>
+        <v>-0.1056551247402403</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.05077266624930143</v>
+        <v>-0.07975530691001131</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.01783103545430709</v>
+        <v>0.02539077954063584</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.01457977124394838</v>
+        <v>0.07490305037016398</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.7626048840368653</v>
+        <v>0.3545476520962678</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.2079575049460129</v>
+        <v>0.1064490730259693</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>43.18</v>
+        <v>44.74</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.007584418043843133</v>
+        <v>-0.01735113380212305</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.01347955554986158</v>
+        <v>-0.02314405188321533</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.01952771554208454</v>
+        <v>-0.01148909991936542</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.05472854604418065</v>
+        <v>-0.02802513871476109</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.03731223899373526</v>
+        <v>-0.02760262311229067</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.08318578049921332</v>
+        <v>-0.1177282096980724</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.02017163692871327</v>
+        <v>-0.01993280440576872</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.04090407670597185</v>
+        <v>-0.004950844075900296</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.4853426222212511</v>
+        <v>0.2607721672859273</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.1409734739741302</v>
+        <v>0.08030288923594497</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>17.83</v>
+        <v>42.23</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.008484141173140225</v>
+        <v>-0.02200094386811713</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>0.01134434330459477</v>
+        <v>-0.02290610019678962</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.02886713883586078</v>
+        <v>-0.04413763579605512</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.001122990362909304</v>
+        <v>-0.04780155591486246</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.2277383548660169</v>
+        <v>-0.04323138602203247</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.01877840099188033</v>
+        <v>-0.1033565586799418</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.07243764284457255</v>
+        <v>-0.04849574131158119</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.2564121432298727</v>
+        <v>0.02959333989884261</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1629882052191838</v>
+        <v>0.4681225962636701</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.0516190306893749</v>
+        <v>0.1365471074674436</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>36.14</v>
+        <v>102.81</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.01431373298468941</v>
+        <v>-0.01636049693258479</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>0.009215247241055824</v>
+        <v>-0.03274064659853826</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.04442094972850286</v>
+        <v>-0.04972737555603823</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>0.0524169839563875</v>
+        <v>-0.008486882651100092</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.0976273614468619</v>
+        <v>0.003199395854959874</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.07334513200934378</v>
+        <v>-0.1046464128880304</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.04141666058415017</v>
+        <v>-0.04989614825259092</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.07438463962708841</v>
+        <v>-0.09129718989191327</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.4142460990012753</v>
+        <v>0.2658415102648566</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.1224706563563254</v>
+        <v>0.08174885556402889</v>
       </c>
     </row>
     <row r="60">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>104.52</v>
+        <v>94.69</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.0139622958201282</v>
+        <v>-0.009829497427682132</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.0104147517033768</v>
+        <v>-0.03189852975222129</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.0457409129194426</v>
+        <v>-0.03219535991810407</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.04320762827722979</v>
+        <v>0.003710050001083598</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>0.01317224611168433</v>
+        <v>0.01918710125414336</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.08975434158564388</v>
+        <v>-0.1161925606892656</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.03674762415027688</v>
+        <v>-0.08396533696129438</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.08325970781190706</v>
+        <v>-0.1391235202134378</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.3475664630608197</v>
+        <v>0.1287408752319787</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.1045449592881247</v>
+        <v>0.04119342635012568</v>
       </c>
     </row>
     <row r="61">
@@ -3896,51 +3896,51 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>95.63</v>
+        <v>17.3</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.01726441627094066</v>
+        <v>-0.02972522091493901</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.01147406072837298</v>
+        <v>-0.007458466198456137</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.03918418138964286</v>
+        <v>-0.04472674467100923</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.0239845481016645</v>
+        <v>-0.01424501486427832</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>0.02369446729182312</v>
+        <v>-0.2640461121439773</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.1074189374307434</v>
+        <v>-0.04794542978890637</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.07469354390900318</v>
+        <v>0.02892246413704291</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.1312053444004524</v>
+        <v>0.2148291906747992</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1961177939485734</v>
+        <v>0.125611224414576</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.06151137018321462</v>
+        <v>0.04023023268622161</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>49.74</v>
+        <v>47.57</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.01968025672803764</v>
+        <v>-0.04362689807833287</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>0.000201128822090002</v>
+        <v>-0.01552152327683765</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.05202972134026085</v>
+        <v>-0.06578944608376214</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.03529867428915567</v>
+        <v>-0.03567812833776329</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2945681439299139</v>
+        <v>-0.3565535033347771</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.0956363331187855</v>
+        <v>-0.1350909146395597</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.03841336313097599</v>
+        <v>-0.02739726347921445</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.2143555368711547</v>
+        <v>0.1448856935812921</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1092702940060968</v>
+        <v>-0.1782666368817573</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.03783701469231271</v>
+        <v>-0.06335078525284621</v>
       </c>
     </row>
   </sheetData>
@@ -4091,17 +4091,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4158,17 +4158,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.369206362670955</v>
+        <v>0.3294197593085566</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4624,21 +4624,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.05472854604418065</v>
+        <v>-0.08887470030754774</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.3610451445114873</v>
+        <v>0.328135551840572</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4669,21 +4669,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.05275736053882962</v>
+        <v>-0.04780155591486246</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.2593050980278939</v>
+        <v>0.2143518743578259</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.052308652496037</v>
+        <v>-0.04719184422002864</v>
       </c>
     </row>
     <row r="20">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.2381257388833407</v>
+        <v>0.1775297982709156</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.04320762827722979</v>
+        <v>-0.04098908838506676</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.213507812680958</v>
+        <v>0.1736710925239742</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.03956381046446</v>
+        <v>-0.03567812833776329</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.2130872437580336</v>
+        <v>0.1648323183263838</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.03947369843537185</v>
+        <v>-0.03286878885414235</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1996527603668088</v>
+        <v>0.1628251345711269</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.03529867428915567</v>
+        <v>-0.03148832137410451</v>
       </c>
     </row>
     <row r="24">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.1970920482898146</v>
+        <v>0.152757092330881</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.03296172137090936</v>
+        <v>-0.03065067385399456</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.1929007785075274</v>
+        <v>0.1454689932276994</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.03294622009686787</v>
+        <v>-0.03021294412378539</v>
       </c>
     </row>
     <row r="26">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.1405511653127289</v>
+        <v>0.1214527061041539</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.02985182792238505</v>
+        <v>-0.02945351010353292</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3675183606502821</v>
+        <v>0.3194625597125427</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2945681439299139</v>
+        <v>-0.3565535033347771</v>
       </c>
     </row>
     <row r="32">
@@ -5158,21 +5158,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2991913647319246</v>
+        <v>0.2143072205995868</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.2277383548660169</v>
+        <v>-0.2640461121439773</v>
       </c>
     </row>
     <row r="33">
@@ -5203,21 +5203,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2918618656533372</v>
+        <v>0.2135335737595909</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1946778897260528</v>
+        <v>-0.2083553731659464</v>
       </c>
     </row>
     <row r="34">
@@ -5248,21 +5248,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.264599691098145</v>
+        <v>0.195517833747145</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.0976273614468619</v>
+        <v>-0.1199278321003493</v>
       </c>
     </row>
     <row r="35">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2524740777631889</v>
+        <v>0.1899883913110376</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.094334708998008</v>
+        <v>-0.1091113144646929</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.243225832058245</v>
+        <v>0.1874742130713498</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.0699026218591392</v>
+        <v>-0.1056551247402403</v>
       </c>
     </row>
     <row r="37">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.22960351112463</v>
+        <v>0.1773528235249215</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.06054030020464729</v>
+        <v>-0.1034278994011091</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.2136001811623969</v>
+        <v>0.1579130290056037</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.04586581025154646</v>
+        <v>-0.09591007939751295</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1934171470993917</v>
+        <v>0.1553989227386021</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.03922384863474582</v>
+        <v>-0.07230708618617632</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1858213621099751</v>
+        <v>0.1389571575076343</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.03778337531486142</v>
+        <v>-0.07062593009241236</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.6208309991169259</v>
+        <v>0.5988244309135209</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1249492365973937</v>
+        <v>-0.1689817712618231</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.6062960081727999</v>
+        <v>0.5960963983369636</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1098638425458085</v>
+        <v>-0.1624954325774725</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5415778104186986</v>
+        <v>0.5362472997444092</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5736,21 +5736,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1074189374307434</v>
+        <v>-0.1496028552272287</v>
       </c>
     </row>
     <row r="48">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4263976656966508</v>
+        <v>0.3832858332105695</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1048860003503831</v>
+        <v>-0.1350909146395597</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4100450497944867</v>
+        <v>0.3697615758326191</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.1021494852829112</v>
+        <v>-0.1177282096980724</v>
       </c>
     </row>
     <row r="50">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3527115622104939</v>
+        <v>0.3485426265809966</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.0956363331187855</v>
+        <v>-0.1161925606892656</v>
       </c>
     </row>
     <row r="51">
@@ -5894,21 +5894,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3220941573732861</v>
+        <v>0.2816901953744504</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.09061540551572755</v>
+        <v>-0.1046464128880304</v>
       </c>
     </row>
     <row r="52">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3097074275398546</v>
+        <v>0.2770629853733622</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.08975434158564388</v>
+        <v>-0.1033565586799418</v>
       </c>
     </row>
     <row r="53">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2727842154315607</v>
+        <v>0.2696698964108162</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.08318578049921332</v>
+        <v>-0.09278649712595732</v>
       </c>
     </row>
     <row r="54">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2655044537686493</v>
+        <v>0.266480624123407</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.07334513200934378</v>
+        <v>-0.08478817152057316</v>
       </c>
     </row>
     <row r="55"/>
@@ -6135,21 +6135,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>1.043047874174863</v>
+        <v>0.923462653161536</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6157,21 +6157,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.190727699206089</v>
+        <v>-0.1994578725057421</v>
       </c>
     </row>
     <row r="60">
@@ -6180,21 +6180,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.9310050622889963</v>
+        <v>0.9144810780686863</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6202,21 +6202,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1654237218411977</v>
+        <v>-0.197671511211941</v>
       </c>
     </row>
     <row r="61">
@@ -6225,21 +6225,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.8717462955109481</v>
+        <v>0.8482676796351563</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1312053444004524</v>
+        <v>-0.1391235202134378</v>
       </c>
     </row>
     <row r="62">
@@ -6270,21 +6270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.8658471463941766</v>
+        <v>0.8168475521495351</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6292,21 +6292,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1165165132553329</v>
+        <v>-0.1154439478115183</v>
       </c>
     </row>
     <row r="63">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.8321598701053672</v>
+        <v>0.7897597987467058</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6337,21 +6337,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.0943688001426094</v>
+        <v>-0.1117135736789118</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.7855420908745894</v>
+        <v>0.7063862443904645</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.08325970781190706</v>
+        <v>-0.09129718989191327</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.7361231583136925</v>
+        <v>0.6999386790725202</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06209206605126483</v>
+        <v>-0.06073994766337687</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.6988138925974754</v>
+        <v>0.6987110495995432</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.01633652057566171</v>
+        <v>-0.03349294548434179</v>
       </c>
     </row>
     <row r="67">
@@ -6495,21 +6495,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.6652294244766919</v>
+        <v>0.6204500785702178</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.008337524384908201</v>
+        <v>-0.004950844075900296</v>
       </c>
     </row>
     <row r="68">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.6603653939958316</v>
+        <v>0.5707686660196767</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.01388916681436414</v>
+        <v>0.01321263422170049</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.198937543877196</v>
+        <v>2.853722750828505</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1092702940060968</v>
+        <v>-0.1782666368817573</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.895703557390161</v>
+        <v>2.6116842591124</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.04854419109303687</v>
+        <v>0.01480840986727761</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.781843660666441</v>
+        <v>2.487313996537913</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.0711769903096382</v>
+        <v>0.06243518783464097</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.999999903474261</v>
+        <v>2.16359932298873</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6803,21 +6803,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1291837505681623</v>
+        <v>0.1048158473778946</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.809194912919116</v>
+        <v>1.602476911986245</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6848,21 +6848,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1463158666827324</v>
+        <v>0.1207439919754676</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.484326390887332</v>
+        <v>1.308966916538867</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1629882052191838</v>
+        <v>0.125611224414576</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.482264719107691</v>
+        <v>1.293840968831629</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6938,21 +6938,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.179860437144562</v>
+        <v>0.1287408752319787</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.351580548471401</v>
+        <v>1.27676271016182</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1961177939485734</v>
+        <v>0.1630752817707217</v>
       </c>
     </row>
     <row r="81">
@@ -7006,21 +7006,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.349103040712502</v>
+        <v>1.222486343295206</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,21 +7028,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.2042272045919782</v>
+        <v>0.1805961530962943</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.331180190758338</v>
+        <v>1.165100197950444</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,21 +7073,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2108326605965962</v>
+        <v>0.1934462596016899</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -689,10 +689,10 @@
         <v>0.7897597987467058</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.8056374078355901</v>
+        <v>0.8056372494408137</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2177089961532312</v>
+        <v>0.2177089605464608</v>
       </c>
     </row>
     <row r="4">
@@ -904,13 +904,13 @@
         <v>0.125742584616398</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.5960963983369636</v>
+        <v>0.5960963013022056</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>0.3670992475406898</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3766502254135238</v>
+        <v>0.3766500810404216</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>1.151349983541433</v>
@@ -966,13 +966,13 @@
         <v>0.4830527866977201</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.9144810780686863</v>
+        <v>0.9144809275003962</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.602476911986245</v>
+        <v>1.602477190217051</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.3755053854805361</v>
+        <v>0.3755054344989612</v>
       </c>
     </row>
     <row r="9">
@@ -1019,16 +1019,16 @@
         <v>0.2342206535407039</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2940286933299185</v>
+        <v>0.2940287837823385</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>0.4971559260941103</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.6736711062572551</v>
+        <v>0.6736712575689949</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1872897164139793</v>
+        <v>0.1872897521937822</v>
       </c>
     </row>
     <row r="10">
@@ -1081,10 +1081,10 @@
         <v>0.4536533424611577</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3641599439164334</v>
+        <v>0.3641600941893819</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1090601421010695</v>
+        <v>0.1090601828249675</v>
       </c>
     </row>
     <row r="11">
@@ -1193,10 +1193,10 @@
         <v>0.5162932645962155</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6378481658446225</v>
+        <v>0.6378479700426256</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1787577095976636</v>
+        <v>0.1787576626248271</v>
       </c>
     </row>
     <row r="13">
@@ -1305,10 +1305,10 @@
         <v>0.555410419135101</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.27676271016182</v>
+        <v>1.276763228771462</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3155456510738266</v>
+        <v>0.3155457509604775</v>
       </c>
     </row>
     <row r="15">
@@ -1358,7 +1358,7 @@
         <v>0.5120887156736547</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.6987110495995432</v>
+        <v>0.6987112311185213</v>
       </c>
       <c r="O15" s="6" t="n">
         <v>1.293840968831629</v>
@@ -1523,16 +1523,16 @@
         <v>-0.1689817712618231</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2766035598922716</v>
+        <v>0.2766036868320665</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>0.7063862443904645</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.853722750828505</v>
+        <v>2.853722461636317</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.5678102121891515</v>
+        <v>0.5678101729717933</v>
       </c>
     </row>
     <row r="19">
@@ -1585,10 +1585,10 @@
         <v>0.2139146223520154</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1805961530962943</v>
+        <v>0.1805960593394176</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05689973235370505</v>
+        <v>0.05689970437585679</v>
       </c>
     </row>
     <row r="20">
@@ -1641,10 +1641,10 @@
         <v>0.5707686660196767</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>2.487313996537913</v>
+        <v>2.487313761069948</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.5164578757331455</v>
+        <v>0.5164578416020771</v>
       </c>
     </row>
     <row r="21">
@@ -1694,7 +1694,7 @@
         <v>0.2359599877833838</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.235594774420586</v>
+        <v>0.2355946696557609</v>
       </c>
       <c r="O21" s="6" t="n">
         <v>0.7176262490656098</v>
@@ -1859,10 +1859,10 @@
         <v>0.1145710569023737</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1888463198548427</v>
+        <v>0.1888463931490807</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1501555932605541</v>
+        <v>0.1501555246593815</v>
       </c>
       <c r="O24" s="6" t="n">
         <v>0.7955806877121991</v>
@@ -1921,10 +1921,10 @@
         <v>0.1372944562027678</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8831678479734686</v>
+        <v>0.8831680474741836</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2348939897036377</v>
+        <v>0.2348940333114031</v>
       </c>
     </row>
     <row r="26">
@@ -1971,7 +1971,7 @@
         <v>0.06252281457104747</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.08317634379885952</v>
+        <v>0.08317641126012387</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>0.1147183251831743</v>
@@ -2030,13 +2030,13 @@
         <v>0.2197892404961077</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.4400803396251158</v>
+        <v>0.4400802056872786</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.308966916538867</v>
+        <v>1.308966744377671</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3217193154110005</v>
+        <v>0.3217192825609869</v>
       </c>
     </row>
     <row r="28">
@@ -2086,13 +2086,13 @@
         <v>0.09330246407775045</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1134289781006304</v>
+        <v>0.113428846679998</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6778246525316725</v>
+        <v>0.6778245033203869</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1882710699005079</v>
+        <v>0.1882710346756391</v>
       </c>
     </row>
     <row r="29">
@@ -2136,7 +2136,7 @@
         <v>0.06664219499818858</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.1471155118363248</v>
+        <v>0.147115408588308</v>
       </c>
       <c r="M29" s="6" t="n">
         <v>0.1167468220155197</v>
@@ -2145,10 +2145,10 @@
         <v>0.1297303209994909</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.140614444762822</v>
+        <v>1.140614085225248</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2887820655709239</v>
+        <v>0.2887819934163138</v>
       </c>
     </row>
     <row r="30">
@@ -2198,7 +2198,7 @@
         <v>0.1752403433254921</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.206221067154251</v>
+        <v>0.2062209367744834</v>
       </c>
       <c r="O30" s="6" t="n">
         <v>0.4110025111600617</v>
@@ -2313,10 +2313,10 @@
         <v>0.2361417539434949</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3479426040050007</v>
+        <v>0.3479422103038055</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1046477188292656</v>
+        <v>0.1046476112823598</v>
       </c>
     </row>
     <row r="33">
@@ -2478,13 +2478,13 @@
         <v>0.1771643162235665</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1514640445291633</v>
+        <v>0.1514639589417182</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3605252189070798</v>
+        <v>0.360524979932094</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1080742571739794</v>
+        <v>0.1080741922965724</v>
       </c>
     </row>
     <row r="36">
@@ -2534,13 +2534,13 @@
         <v>0.06080392942103341</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.02141235894613769</v>
+        <v>0.02141242091252193</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.8783208249748731</v>
+        <v>0.8783210345276919</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.2338335952420236</v>
+        <v>0.2338336411257893</v>
       </c>
     </row>
     <row r="37">
@@ -2587,7 +2587,7 @@
         <v>0.007682056666696191</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1763587152568953</v>
+        <v>0.1763585968903234</v>
       </c>
       <c r="N37" s="6" t="n">
         <v>0.2587633204958708</v>
@@ -2696,19 +2696,19 @@
         <v>0.05588242973991364</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>-0.02844328112493577</v>
+        <v>-0.02844337758295579</v>
       </c>
       <c r="M39" s="6" t="n">
         <v>0.09790205867378488</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.09049851861996694</v>
+        <v>0.09049864014122999</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.2348171787576088</v>
+        <v>0.2348174903863443</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.0728381804768039</v>
+        <v>0.07283827072691906</v>
       </c>
     </row>
     <row r="40">
@@ -2811,16 +2811,16 @@
         <v>-0.03088362374276743</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1966867928406613</v>
+        <v>0.1966866772487805</v>
       </c>
       <c r="N41" s="6" t="n">
         <v>0.2888416885228728</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.5541236334223028</v>
+        <v>0.554123535944107</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1583199106142226</v>
+        <v>0.158319886396729</v>
       </c>
     </row>
     <row r="42">
@@ -2870,7 +2870,7 @@
         <v>0.005204958039536134</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.06073994766337687</v>
+        <v>-0.06073988538798591</v>
       </c>
       <c r="O42" s="6" t="n">
         <v>0.1934462596016899</v>
@@ -2979,16 +2979,16 @@
         <v>-0.01914154288734349</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1089543463384499</v>
+        <v>0.108954426202897</v>
       </c>
       <c r="N44" s="6" t="n">
         <v>0.1491067082310065</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5956282324024154</v>
+        <v>0.5956283977468539</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.168540863086265</v>
+        <v>0.1685409034489933</v>
       </c>
     </row>
     <row r="45">
@@ -3038,13 +3038,13 @@
         <v>0.1148639905275106</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.1566955050625127</v>
+        <v>0.156695415658481</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>1.009219225563303</v>
+        <v>1.009218820926981</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.26185399893989</v>
+        <v>0.2618539142316962</v>
       </c>
     </row>
     <row r="46">
@@ -3203,7 +3203,7 @@
         <v>-0.07663207907251601</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.04368494046218396</v>
+        <v>0.04368482456309852</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>-0.03349294548434179</v>
@@ -3321,10 +3321,10 @@
         <v>0.1837711482463826</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>1.13493544031813</v>
+        <v>1.13493557588026</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.287641352439743</v>
+        <v>0.2876413796935569</v>
       </c>
     </row>
     <row r="51">
@@ -3368,19 +3368,19 @@
         <v>0.1244512176565467</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.08478817152057316</v>
+        <v>-0.08478811339361347</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>-0.1430827422054431</v>
+        <v>-0.143082844121369</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>-0.1117135736789118</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.06243518783464097</v>
+        <v>0.06243510950264519</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.02039302675113652</v>
+        <v>0.02039300167370905</v>
       </c>
     </row>
     <row r="52">
@@ -3486,7 +3486,7 @@
         <v>-0.02530976117652806</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.01321263422170049</v>
+        <v>0.01321256395133674</v>
       </c>
       <c r="O53" s="6" t="n">
         <v>0.7022115385063521</v>
@@ -3545,10 +3545,10 @@
         <v>-0.1994578725057421</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.2629708987800405</v>
+        <v>0.2629711240656807</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.08093052484410945</v>
+        <v>0.08093058911534778</v>
       </c>
     </row>
     <row r="55">
@@ -3651,10 +3651,10 @@
         <v>-0.07975530691001131</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.02539077954063584</v>
+        <v>0.02539089129525696</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.07490305037016398</v>
+        <v>0.07490292756258543</v>
       </c>
       <c r="O56" s="6" t="n">
         <v>0.3545476520962678</v>
@@ -3763,7 +3763,7 @@
         <v>-0.1033565586799418</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.04849574131158119</v>
+        <v>-0.04849565952905677</v>
       </c>
       <c r="N58" s="6" t="n">
         <v>0.02959333989884261</v>
@@ -3819,16 +3819,16 @@
         <v>-0.1046464128880304</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.04989614825259092</v>
+        <v>-0.04989621524056631</v>
       </c>
       <c r="N59" s="6" t="n">
         <v>-0.09129718989191327</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.2658415102648566</v>
+        <v>0.2658416291735022</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.08174885556402889</v>
+        <v>0.08174888943590664</v>
       </c>
     </row>
     <row r="60">
@@ -3875,16 +3875,16 @@
         <v>-0.1161925606892656</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.08396533696129438</v>
+        <v>-0.08396526935147219</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1391235202134378</v>
+        <v>-0.1391234605006069</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.1287408752319787</v>
+        <v>0.12874066992469</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.04119342635012568</v>
+        <v>0.04119336322237643</v>
       </c>
     </row>
     <row r="61">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5960963983369636</v>
+        <v>0.5960963013022056</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.08478817152057316</v>
+        <v>-0.08478811339361347</v>
       </c>
     </row>
     <row r="55"/>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.9144810780686863</v>
+        <v>0.9144809275003962</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1391235202134378</v>
+        <v>-0.1391234605006069</v>
       </c>
     </row>
     <row r="62">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06073994766337687</v>
+        <v>-0.06073988538798591</v>
       </c>
     </row>
     <row r="66">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.6987110495995432</v>
+        <v>0.6987112311185213</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.01321263422170049</v>
+        <v>0.01321256395133674</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.853722750828505</v>
+        <v>2.853722461636317</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.487313996537913</v>
+        <v>2.487313761069948</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.06243518783464097</v>
+        <v>0.06243510950264519</v>
       </c>
     </row>
     <row r="76">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.602476911986245</v>
+        <v>1.602477190217051</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.308966916538867</v>
+        <v>1.308966744377671</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1287408752319787</v>
+        <v>0.12874066992469</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.27676271016182</v>
+        <v>1.276763228771462</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1805961530962943</v>
+        <v>0.1805960593394176</v>
       </c>
     </row>
     <row r="82">

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -745,10 +745,10 @@
         <v>0.8168475521495351</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.064730871609922</v>
+        <v>1.064731271917388</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2733696185660617</v>
+        <v>0.2733697008591651</v>
       </c>
     </row>
     <row r="5">
@@ -904,13 +904,13 @@
         <v>0.125742584616398</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.5960963013022056</v>
+        <v>0.5960963983369636</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>0.3670992475406898</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3766500810404216</v>
+        <v>0.3766502254135238</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>1.151349983541433</v>
@@ -966,13 +966,13 @@
         <v>0.4830527866977201</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.9144809275003962</v>
+        <v>0.9144810780686863</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.602477190217051</v>
+        <v>1.602476911986245</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.3755054344989612</v>
+        <v>0.3755053854805361</v>
       </c>
     </row>
     <row r="9">
@@ -1016,7 +1016,7 @@
         <v>0.2135335737595909</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2342206535407039</v>
+        <v>0.2342207358251966</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>0.2940287837823385</v>
@@ -1025,10 +1025,10 @@
         <v>0.4971559260941103</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.6736712575689949</v>
+        <v>0.6736714088807618</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1872897521937822</v>
+        <v>0.1872897879735895</v>
       </c>
     </row>
     <row r="10">
@@ -1190,7 +1190,7 @@
         <v>0.2049612529914484</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.5162932645962155</v>
+        <v>0.5162930967790991</v>
       </c>
       <c r="O12" s="6" t="n">
         <v>0.6378479700426256</v>
@@ -1281,34 +1281,34 @@
         <v>152.52</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.002446855470853215</v>
+        <v>-0.002420008624923531</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.01908255997735764</v>
+        <v>0.0191099862379307</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.02007260179707437</v>
+        <v>-0.0200462293075222</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.05234187101211063</v>
+        <v>0.05237019237045759</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>-0.03662681045437166</v>
+        <v>-0.03660088348322788</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.2696698964108162</v>
+        <v>0.2697040666525496</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4467971463798959</v>
+        <v>0.4468360835937109</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.555410419135101</v>
+        <v>0.5554522794250605</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.276763228771462</v>
+        <v>1.276824243299484</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3155457509604775</v>
+        <v>0.3155575025390724</v>
       </c>
     </row>
     <row r="15">
@@ -1352,19 +1352,19 @@
         <v>-0.2083553731659464</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.3832858332105695</v>
+        <v>0.383285712843749</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>0.5120887156736547</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.6987112311185213</v>
+        <v>0.6987110495995432</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.293840968831629</v>
+        <v>1.293841134324624</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.3188268135972747</v>
+        <v>0.3188268453135963</v>
       </c>
     </row>
     <row r="16">
@@ -1411,16 +1411,16 @@
         <v>0.1286330810561378</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2901853062550197</v>
+        <v>0.2901852044944273</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.3280326616848959</v>
+        <v>0.3280327695033314</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2740522369808664</v>
+        <v>0.2740521377492848</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.08408269414169212</v>
+        <v>0.08408266599652414</v>
       </c>
     </row>
     <row r="17">
@@ -1523,16 +1523,16 @@
         <v>-0.1689817712618231</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2766036868320665</v>
+        <v>0.2766035598922716</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>0.7063862443904645</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.853722461636317</v>
+        <v>2.853722750828505</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.5678101729717933</v>
+        <v>0.5678102121891515</v>
       </c>
     </row>
     <row r="19">
@@ -1585,10 +1585,10 @@
         <v>0.2139146223520154</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1805960593394176</v>
+        <v>0.180595965582556</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05689970437585679</v>
+        <v>0.05689967639801141</v>
       </c>
     </row>
     <row r="20">
@@ -1641,10 +1641,10 @@
         <v>0.5707686660196767</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>2.487313761069948</v>
+        <v>2.487313996537913</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.5164578416020771</v>
+        <v>0.5164578757331455</v>
       </c>
     </row>
     <row r="21">
@@ -1694,13 +1694,13 @@
         <v>0.2359599877833838</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2355946696557609</v>
+        <v>0.235594774420586</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.7176262490656098</v>
+        <v>0.7176260466142543</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1975938473477061</v>
+        <v>0.1975938002954623</v>
       </c>
     </row>
     <row r="22">
@@ -1753,10 +1753,10 @@
         <v>0.6204500785702178</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.323995279895916</v>
+        <v>0.3239953674568072</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.09806692997583011</v>
+        <v>0.09806695418229028</v>
       </c>
     </row>
     <row r="23">
@@ -1859,16 +1859,16 @@
         <v>0.1145710569023737</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1888463931490807</v>
+        <v>0.1888463198548427</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1501555246593815</v>
+        <v>0.1501554560582175</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7955806877121991</v>
+        <v>0.7955810221060633</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2154440591988103</v>
+        <v>0.2154441346501694</v>
       </c>
     </row>
     <row r="25">
@@ -1953,34 +1953,34 @@
         <v>132.69</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.008157372887716119</v>
+        <v>-0.008147677887849647</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.02685222218765482</v>
+        <v>-0.02684270992500537</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.008119665452022806</v>
+        <v>0.008129519555642561</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.01733906062450408</v>
+        <v>-0.01732945537321151</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.1553989227386021</v>
+        <v>0.1554102164580851</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.06252281457104747</v>
+        <v>0.06253313553731465</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.08317641126012387</v>
+        <v>0.08318693156169754</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1147183251831743</v>
+        <v>0.1147292212605544</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.692591361657422</v>
+        <v>0.6926079062911943</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1917469250263137</v>
+        <v>0.1917508080175323</v>
       </c>
     </row>
     <row r="27">
@@ -2033,10 +2033,10 @@
         <v>0.4400802056872786</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.308966744377671</v>
+        <v>1.3089665722165</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3217192825609869</v>
+        <v>0.3217192497109764</v>
       </c>
     </row>
     <row r="28">
@@ -2145,10 +2145,10 @@
         <v>0.1297303209994909</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.140614085225248</v>
+        <v>1.140614624531654</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2887819934163138</v>
+        <v>0.288782101648235</v>
       </c>
     </row>
     <row r="30">
@@ -2198,13 +2198,13 @@
         <v>0.1752403433254921</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2062209367744834</v>
+        <v>0.206221067154251</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4110025111600617</v>
+        <v>0.4110026003635907</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1216118668438508</v>
+        <v>0.1216118904799379</v>
       </c>
     </row>
     <row r="31">
@@ -2313,10 +2313,10 @@
         <v>0.2361417539434949</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3479422103038055</v>
+        <v>0.3479423415375116</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1046476112823598</v>
+        <v>0.1046476471313236</v>
       </c>
     </row>
     <row r="33">
@@ -2425,10 +2425,10 @@
         <v>0.1047080568208931</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.616152171692627</v>
+        <v>0.6161520192711962</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1735296947723128</v>
+        <v>0.173529657879937</v>
       </c>
     </row>
     <row r="35">
@@ -2478,13 +2478,13 @@
         <v>0.1771643162235665</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1514639589417182</v>
+        <v>0.1514640445291633</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.360524979932094</v>
+        <v>0.3605252189070798</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1080741922965724</v>
+        <v>0.1080742571739794</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>64.23</v>
+        <v>178.39</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.001006334806403331</v>
+        <v>-0.01827091080045284</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.02302174097974174</v>
+        <v>0.001066231451515964</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.01142210472287153</v>
+        <v>-0.05713529457165345</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.06421384049318624</v>
+        <v>-0.005352699644253667</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.01168179948035886</v>
+        <v>-0.07230708618617632</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.211461258920312</v>
+        <v>0.007682056666696191</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.06080392942103341</v>
+        <v>0.1763587152568953</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.02141242091252193</v>
+        <v>0.2587633204958708</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.8783210345276919</v>
+        <v>0.8240334046660189</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.2338336411257893</v>
+        <v>0.2218304076185909</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>178.39</v>
+        <v>19.73</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.01827091080045284</v>
+        <v>-0.01083139150469459</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.001066231451515964</v>
+        <v>-0.02592462756264369</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.05713529457165345</v>
+        <v>-0.01816732757581307</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.005352699644253667</v>
+        <v>0.01995861822750711</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.07230708618617632</v>
+        <v>0.1389802848941604</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.007682056666696191</v>
+        <v>0.1528929940668193</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1763585968903234</v>
+        <v>-0.03066341708202658</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.2587633204958708</v>
+        <v>-0.1154259862318505</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.8240334046660189</v>
+        <v>0.1048382814992959</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2218304076185909</v>
+        <v>0.03379137515819997</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>19.73</v>
+        <v>74.66</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.0108514769135919</v>
+        <v>-0.0004016438387508536</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.0259444064981903</v>
+        <v>-0.02059556113979122</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.01818726402600468</v>
+        <v>0.01385122597657595</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.01993790761686953</v>
+        <v>-0.0008029651714878128</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.1389571575076343</v>
+        <v>0.05588242973991364</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.1528695841779473</v>
+        <v>-0.02844328112493577</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>-0.03068309979482176</v>
+        <v>0.09790205867378488</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>-0.1154439478115183</v>
+        <v>0.09049864014122999</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.1048158473778946</v>
+        <v>0.2348174124791458</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.03378437794766409</v>
+        <v>0.07283824816438744</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>74.66</v>
+        <v>54.7</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.0004016438387508536</v>
+        <v>-0.02425973201990528</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.02059556113979122</v>
+        <v>-0.02181683558572389</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.01385122597657595</v>
+        <v>-0.06861908412579942</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.0008029651714878128</v>
+        <v>-0.02945351010353292</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.05588242973991364</v>
+        <v>-0.02688828311025171</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>-0.02844337758295579</v>
+        <v>-0.005338149015765792</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.09790205867378488</v>
+        <v>0.13649393914632</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.09049864014122999</v>
+        <v>0.1860980806989365</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.2348174903863443</v>
+        <v>0.7311704443157068</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.07283827072691906</v>
+        <v>0.200733450764135</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>54.7</v>
+        <v>23.63</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.02425973201990528</v>
+        <v>-0.02274611817483929</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.02181683558572389</v>
+        <v>-0.005471425373018701</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.06861908412579942</v>
+        <v>-0.02917013095194254</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.02945351010353292</v>
+        <v>-0.00421409116724758</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.02688828311025171</v>
+        <v>-0.09591007939751295</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>-0.005338149015765792</v>
+        <v>-0.03088362374276743</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.13649393914632</v>
+        <v>0.1966867928406613</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.1860980806989365</v>
+        <v>0.2888416885228728</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.7311704443157068</v>
+        <v>0.554123535944107</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.200733450764135</v>
+        <v>0.158319886396729</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>23.63</v>
+        <v>13.51</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.02274611817483929</v>
+        <v>0.008961903098002821</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.005471425373018701</v>
+        <v>0.005208381747325852</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.02917013095194254</v>
+        <v>0.02503792989871667</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.00421409116724758</v>
+        <v>0.08951618100800607</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.09591007939751295</v>
+        <v>0.09025767424155728</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>-0.03088362374276743</v>
+        <v>0.1284516871339132</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1966866772487805</v>
+        <v>0.005204886712538492</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.2888416885228728</v>
+        <v>-0.06073994766337687</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.554123535944107</v>
+        <v>0.1934463601443803</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.158319886396729</v>
+        <v>0.06072051409260681</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>13.51</v>
+        <v>96.44</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.008961903098002821</v>
+        <v>-0.01239118346712964</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.005208381747325852</v>
+        <v>-0.02684153454764659</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.02503792989871667</v>
+        <v>-0.01571750217151191</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0.08951618100800607</v>
+        <v>-0.02536629190750594</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.09025767424155728</v>
+        <v>0.01661468954834078</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.1284516871339132</v>
+        <v>0.02758950346307687</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.005204958039536134</v>
+        <v>0.08635028691987245</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.06073988538798591</v>
+        <v>0.08602520252489199</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.1934462596016899</v>
+        <v>0.3183636442142885</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.06072048430556842</v>
+        <v>0.09650783542637198</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>96.44</v>
+        <v>58.74</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.01239118346712964</v>
+        <v>-0.01854631284801544</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.02684153454764659</v>
+        <v>-0.01624514186700265</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.01571750217151191</v>
+        <v>-0.05425855576828165</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.02536629190750594</v>
+        <v>-0.03021294412378539</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.01661468954834078</v>
+        <v>-0.03293245315669513</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.02758950346307687</v>
+        <v>-0.01914154288734349</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.08635028691987245</v>
+        <v>0.1089543463384499</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.08602520252489199</v>
+        <v>0.1491067082310065</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.3183635067141131</v>
+        <v>0.5956282324024154</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.09650779730587677</v>
+        <v>0.168540863086265</v>
       </c>
     </row>
     <row r="44">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2958,37 +2958,37 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>58.74</v>
+        <v>228.35</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.01854631284801544</v>
+        <v>-0.02522832981261702</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.01624514186700265</v>
+        <v>-0.0216366235005494</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.05425855576828165</v>
+        <v>-0.09096334045511401</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.03021294412378539</v>
+        <v>-0.04719184422002864</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.03293245315669513</v>
+        <v>-0.0294329609003765</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.01914154288734349</v>
+        <v>-0.06179791869751117</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.108954426202897</v>
+        <v>0.1148639905275106</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.1491067082310065</v>
+        <v>0.1566955050625127</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5956283977468539</v>
+        <v>1.009218955805737</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1685409034489933</v>
+        <v>0.2618539424677584</v>
       </c>
     </row>
     <row r="45">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -3014,37 +3014,37 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>228.35</v>
+        <v>28.5</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.02522832981261702</v>
+        <v>-0.02896083033805952</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.0216366235005494</v>
+        <v>-0.03943377395636627</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.09096334045511401</v>
+        <v>-0.07617505194201779</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.04719184422002864</v>
+        <v>-0.08887470030754774</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.0294329609003765</v>
+        <v>-0.02796724772711956</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.06179791869751117</v>
+        <v>0.001757442380306617</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.1148639905275106</v>
+        <v>0.09211075348672804</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.156695415658481</v>
+        <v>0.09211075348672804</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>1.009218820926981</v>
+        <v>0.4926459093010964</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.2618539142316962</v>
+        <v>0.142840436430097</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>28.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.02896083033805952</v>
+        <v>-0.005658827630127927</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.03943377395636627</v>
+        <v>-0.03095104161201512</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.07617505194201779</v>
+        <v>-0.01644965074647187</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.08887470030754774</v>
+        <v>-0.04098908838506676</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.02796724772711956</v>
+        <v>0.02733391382002881</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.001757442380306617</v>
+        <v>-0.005300282501337739</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.09211075348672804</v>
+        <v>0.02774585287987064</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.09211075348672804</v>
+        <v>0.03090363503342508</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.4926459093010964</v>
+        <v>0.3890204809551383</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.142840436430097</v>
+        <v>0.115756819183535</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>86.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.005658827630127927</v>
+        <v>-0.01021542612125981</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.03095104161201512</v>
+        <v>-0.009805367738694337</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.01644965074647187</v>
+        <v>0.007871767829607856</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.04098908838506676</v>
+        <v>-0.003474635310684482</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.02733391382002881</v>
+        <v>0.06864465485613902</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.005300282501337739</v>
+        <v>-0.0766952514146233</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.02774594647611783</v>
+        <v>0.04361353661479361</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.03090363503342508</v>
+        <v>-0.03355906919615059</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.3890203954732305</v>
+        <v>0.01473898161166187</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.115756796295218</v>
+        <v>0.004889052086191725</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>71.7</v>
+        <v>61.15</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.01014770524165931</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.009737618802974302</v>
+        <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.007940726231711714</v>
+        <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.003406453227408957</v>
+        <v>0</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.06871777132806356</v>
+        <v>-0.03676991128905338</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.07663207907251601</v>
+        <v>0.1534804029332366</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.04368482456309852</v>
+        <v>0.01001314637388417</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.03349294548434179</v>
+        <v>-0.02752018177199667</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.01480840986727761</v>
+        <v>0.7883069496014827</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.004911969671939964</v>
+        <v>0.2138006193598696</v>
       </c>
     </row>
     <row r="49">
@@ -3241,34 +3241,34 @@
         <v>47.7</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.002538664294353565</v>
+        <v>-0.002509387968435139</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.02636049939127583</v>
+        <v>-0.02633192225617653</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.001703600090696811</v>
+        <v>-0.001674299254944445</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.0002389083137375181</v>
+        <v>-0.0002095644880542036</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.001265925870347129</v>
+        <v>0.001295313864174474</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.05834673640859633</v>
+        <v>-0.05831909809635283</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.0546054417190136</v>
+        <v>0.05463639527232123</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.01901200860951291</v>
+        <v>0.01904191746573702</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.1207439919754676</v>
+        <v>0.1207766858367583</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.03872872030189467</v>
+        <v>0.03873882065271106</v>
       </c>
     </row>
     <row r="50">
@@ -3409,34 +3409,34 @@
         <v>19.35</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.01015095915385356</v>
+        <v>-0.01013046576877663</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.02531116571965486</v>
+        <v>-0.0252909862046109</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.006082741988302942</v>
+        <v>-0.006062164376705148</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.01190439373566798</v>
+        <v>0.01192534374475618</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.03735120507107248</v>
+        <v>0.03737268191938803</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0.05534577819654629</v>
+        <v>0.05536762759633307</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.04627030316433367</v>
+        <v>-0.04625055757775431</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.197671511211941</v>
+        <v>-0.1976549001672258</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.1630752817707217</v>
+        <v>0.163099361553233</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.05164527603247682</v>
+        <v>0.05165253357781463</v>
       </c>
     </row>
     <row r="53">
@@ -3489,10 +3489,10 @@
         <v>0.01321256395133674</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.7022115385063521</v>
+        <v>0.702211736840799</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.1940005037530486</v>
+        <v>0.1940005501263331</v>
       </c>
     </row>
     <row r="54">
@@ -3521,34 +3521,34 @@
         <v>27.01</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.03056960723720403</v>
+        <v>-0.0305803553702465</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.01497811244411418</v>
+        <v>-0.01498903344099678</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>0.02560475302459797</v>
+        <v>0.02559338208304651</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.05628864115319931</v>
+        <v>0.05627693001753542</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.03070568135061058</v>
+        <v>0.0306942538547601</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0.1079452841064195</v>
+        <v>0.1079330002504497</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1129734192423287</v>
+        <v>-0.1129831981964121</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.1994578725057421</v>
+        <v>-0.1994667481644347</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.2629711240656807</v>
+        <v>0.2629571214289039</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.08093058911534778</v>
+        <v>0.08092659431977678</v>
       </c>
     </row>
     <row r="55">
@@ -3601,10 +3601,10 @@
         <v>0.1724244846247063</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1.165100197950444</v>
+        <v>1.165100394412779</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.293677425721405</v>
+        <v>0.2936774648510614</v>
       </c>
     </row>
     <row r="56">
@@ -3763,7 +3763,7 @@
         <v>-0.1033565586799418</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.04849565952905677</v>
+        <v>-0.04849574131158119</v>
       </c>
       <c r="N58" s="6" t="n">
         <v>0.02959333989884261</v>
@@ -3816,19 +3816,19 @@
         <v>0.003199395854959874</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.1046464128880304</v>
+        <v>-0.1046464723780145</v>
       </c>
       <c r="M59" s="6" t="n">
         <v>-0.04989621524056631</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.09129718989191327</v>
+        <v>-0.0912972511690463</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.2658416291735022</v>
+        <v>0.2658415102648566</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.08174888943590664</v>
+        <v>0.08174885556402889</v>
       </c>
     </row>
     <row r="60">
@@ -3872,19 +3872,19 @@
         <v>0.01918710125414336</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.1161925606892656</v>
+        <v>-0.1161924977529548</v>
       </c>
       <c r="M60" s="6" t="n">
         <v>-0.08396526935147219</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1391234605006069</v>
+        <v>-0.1391235799262603</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.12874066992469</v>
+        <v>0.1287405672710737</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.04119336322237643</v>
+        <v>0.0411933316585078</v>
       </c>
     </row>
     <row r="61">
@@ -3937,10 +3937,10 @@
         <v>0.2148291906747992</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.125611224414576</v>
+        <v>0.125611084726037</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.04023023268622161</v>
+        <v>0.04023018965530523</v>
       </c>
     </row>
     <row r="62">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1553989227386021</v>
+        <v>0.1554102164580851</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1389571575076343</v>
+        <v>0.1389802848941604</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5960963013022056</v>
+        <v>0.5960963983369636</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3832858332105695</v>
+        <v>0.383285712843749</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.1161925606892656</v>
+        <v>-0.1161924977529548</v>
       </c>
     </row>
     <row r="51">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.1046464128880304</v>
+        <v>-0.1046464723780145</v>
       </c>
     </row>
     <row r="52">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2696698964108162</v>
+        <v>0.2697040666525496</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1994578725057421</v>
+        <v>-0.1994667481644347</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.9144809275003962</v>
+        <v>0.9144810780686863</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.197671511211941</v>
+        <v>-0.1976549001672258</v>
       </c>
     </row>
     <row r="61">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1391234605006069</v>
+        <v>-0.1391235799262603</v>
       </c>
     </row>
     <row r="62">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1154439478115183</v>
+        <v>-0.1154259862318505</v>
       </c>
     </row>
     <row r="63">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.09129718989191327</v>
+        <v>-0.0912972511690463</v>
       </c>
     </row>
     <row r="65">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06073988538798591</v>
+        <v>-0.06073994766337687</v>
       </c>
     </row>
     <row r="66">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.6987112311185213</v>
+        <v>0.6987110495995432</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.03349294548434179</v>
+        <v>-0.03355906919615059</v>
       </c>
     </row>
     <row r="67">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>PBS</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Media &amp; Entertainment</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.004950844075900296</v>
+        <v>-0.02752018177199667</v>
       </c>
     </row>
     <row r="68">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.01321256395133674</v>
+        <v>-0.004950844075900296</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.853722461636317</v>
+        <v>2.853722750828505</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.01480840986727761</v>
+        <v>0.01473898161166187</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.487313761069948</v>
+        <v>2.487313996537913</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1048158473778946</v>
+        <v>0.1048382814992959</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.602477190217051</v>
+        <v>1.602476911986245</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1207439919754676</v>
+        <v>0.1207766858367583</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.308966744377671</v>
+        <v>1.3089665722165</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.125611224414576</v>
+        <v>0.125611084726037</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.293840968831629</v>
+        <v>1.293841134324624</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.12874066992469</v>
+        <v>0.1287405672710737</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.276763228771462</v>
+        <v>1.276824243299484</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1630752817707217</v>
+        <v>0.163099361553233</v>
       </c>
     </row>
     <row r="81">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1805960593394176</v>
+        <v>0.180595965582556</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.165100197950444</v>
+        <v>1.165100394412779</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1934462596016899</v>
+        <v>0.1934463601443803</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>178.39</v>
+        <v>64.23</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.01827091080045284</v>
+        <v>-0.0009332331270702765</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.001066231451515964</v>
+        <v>0.02309660092116617</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.05713529457165345</v>
+        <v>0.01149611585722199</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.005352699644253667</v>
+        <v>0.06429171467960026</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.07230708618617632</v>
+        <v>0.01175582961795585</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.007682056666696191</v>
+        <v>0.2115499079834238</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.1763587152568953</v>
+        <v>0.06088155408611962</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.2587633204958708</v>
+        <v>0.02148710112051977</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.8240334046660189</v>
+        <v>0.8784584812670804</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.2218304076185909</v>
+        <v>0.2338637357815057</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>19.73</v>
+        <v>178.39</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.01083139150469459</v>
+        <v>-0.01827091080045284</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.02592462756264369</v>
+        <v>0.001066231451515964</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.01816732757581307</v>
+        <v>-0.05713529457165345</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0.01995861822750711</v>
+        <v>-0.005352699644253667</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.1389802848941604</v>
+        <v>-0.07230708618617632</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.1528929940668193</v>
+        <v>0.007682056666696191</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-0.03066341708202658</v>
+        <v>0.1763587152568953</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>-0.1154259862318505</v>
+        <v>0.2587633204958708</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.1048382814992959</v>
+        <v>0.8240334046660189</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.03379137515819997</v>
+        <v>0.2218304076185909</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>74.66</v>
+        <v>19.73</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.0004016438387508536</v>
+        <v>-0.01083139150469459</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.02059556113979122</v>
+        <v>-0.02592462756264369</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0.01385122597657595</v>
+        <v>-0.01816732757581307</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.0008029651714878128</v>
+        <v>0.01995861822750711</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.05588242973991364</v>
+        <v>0.1389802848941604</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>-0.02844328112493577</v>
+        <v>0.1528929940668193</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.09790205867378488</v>
+        <v>-0.03066341708202658</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.09049864014122999</v>
+        <v>-0.1154259862318505</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.2348174124791458</v>
+        <v>0.1048382814992959</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.07283824816438744</v>
+        <v>0.03379137515819997</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>54.7</v>
+        <v>74.66</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.02425973201990528</v>
+        <v>-0.0004016438387508536</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.02181683558572389</v>
+        <v>-0.02059556113979122</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.06861908412579942</v>
+        <v>0.01385122597657595</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.02945351010353292</v>
+        <v>-0.0008029651714878128</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.02688828311025171</v>
+        <v>0.05588242973991364</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>-0.005338149015765792</v>
+        <v>-0.02844328112493577</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.13649393914632</v>
+        <v>0.09790205867378488</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1860980806989365</v>
+        <v>0.09049864014122999</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.7311704443157068</v>
+        <v>0.2348174124791458</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.200733450764135</v>
+        <v>0.07283824816438744</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>23.63</v>
+        <v>54.7</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.02274611817483929</v>
+        <v>-0.02425973201990528</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.005471425373018701</v>
+        <v>-0.02181683558572389</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.02917013095194254</v>
+        <v>-0.06861908412579942</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.00421409116724758</v>
+        <v>-0.02945351010353292</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.09591007939751295</v>
+        <v>-0.02688828311025171</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>-0.03088362374276743</v>
+        <v>-0.005338149015765792</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1966867928406613</v>
+        <v>0.13649393914632</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.2888416885228728</v>
+        <v>0.1860980806989365</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.554123535944107</v>
+        <v>0.7311704443157068</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.158319886396729</v>
+        <v>0.200733450764135</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>13.51</v>
+        <v>23.63</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.008961903098002821</v>
+        <v>-0.02274611817483929</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.005208381747325852</v>
+        <v>-0.005471425373018701</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.02503792989871667</v>
+        <v>-0.02917013095194254</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.08951618100800607</v>
+        <v>-0.00421409116724758</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.09025767424155728</v>
+        <v>-0.09591007939751295</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.1284516871339132</v>
+        <v>-0.03088362374276743</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.005204886712538492</v>
+        <v>0.1966867928406613</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>-0.06073994766337687</v>
+        <v>0.2888416885228728</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.1934463601443803</v>
+        <v>0.554123535944107</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.06072051409260681</v>
+        <v>0.158319886396729</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>96.44</v>
+        <v>13.51</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.01239118346712964</v>
+        <v>0.008961903098002821</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.02684153454764659</v>
+        <v>0.005208381747325852</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.01571750217151191</v>
+        <v>0.02503792989871667</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.02536629190750594</v>
+        <v>0.08951618100800607</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.01661468954834078</v>
+        <v>0.09025767424155728</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.02758950346307687</v>
+        <v>0.1284516871339132</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.08635028691987245</v>
+        <v>0.005204886712538492</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.08602520252489199</v>
+        <v>-0.06073994766337687</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.3183636442142885</v>
+        <v>0.1934463601443803</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.09650783542637198</v>
+        <v>0.06072051409260681</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>58.74</v>
+        <v>96.44</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.01854631284801544</v>
+        <v>-0.01239118346712964</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.01624514186700265</v>
+        <v>-0.02684153454764659</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.05425855576828165</v>
+        <v>-0.01571750217151191</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.03021294412378539</v>
+        <v>-0.02536629190750594</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.03293245315669513</v>
+        <v>0.01661468954834078</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>-0.01914154288734349</v>
+        <v>0.02758950346307687</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1089543463384499</v>
+        <v>0.08635028691987245</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1491067082310065</v>
+        <v>0.08602520252489199</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.5956282324024154</v>
+        <v>0.3183636442142885</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.168540863086265</v>
+        <v>0.09650783542637198</v>
       </c>
     </row>
     <row r="44">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2958,37 +2958,37 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>228.35</v>
+        <v>58.74</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.02522832981261702</v>
+        <v>-0.01854631284801544</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.0216366235005494</v>
+        <v>-0.01624514186700265</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.09096334045511401</v>
+        <v>-0.05425855576828165</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.04719184422002864</v>
+        <v>-0.03021294412378539</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.0294329609003765</v>
+        <v>-0.03293245315669513</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.06179791869751117</v>
+        <v>-0.01914154288734349</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1148639905275106</v>
+        <v>0.1089543463384499</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.1566955050625127</v>
+        <v>0.1491067082310065</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>1.009218955805737</v>
+        <v>0.5956282324024154</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.2618539424677584</v>
+        <v>0.168540863086265</v>
       </c>
     </row>
     <row r="45">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -3014,37 +3014,37 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>28.5</v>
+        <v>228.35</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.02896083033805952</v>
+        <v>-0.02522832981261702</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.03943377395636627</v>
+        <v>-0.0216366235005494</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.07617505194201779</v>
+        <v>-0.09096334045511401</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.08887470030754774</v>
+        <v>-0.04719184422002864</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.02796724772711956</v>
+        <v>-0.0294329609003765</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.001757442380306617</v>
+        <v>-0.06179791869751117</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.09211075348672804</v>
+        <v>0.1148639905275106</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.09211075348672804</v>
+        <v>0.1566955050625127</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.4926459093010964</v>
+        <v>1.009218955805737</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.142840436430097</v>
+        <v>0.2618539424677584</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>86.09999999999999</v>
+        <v>28.5</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.005658827630127927</v>
+        <v>-0.02896083033805952</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.03095104161201512</v>
+        <v>-0.03943377395636627</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.01644965074647187</v>
+        <v>-0.07617505194201779</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.04098908838506676</v>
+        <v>-0.08887470030754774</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.02733391382002881</v>
+        <v>-0.02796724772711956</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.005300282501337739</v>
+        <v>0.001757442380306617</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.02774585287987064</v>
+        <v>0.09211075348672804</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.03090363503342508</v>
+        <v>0.09211075348672804</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.3890204809551383</v>
+        <v>0.4926459093010964</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.115756819183535</v>
+        <v>0.142840436430097</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>71.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.01021542612125981</v>
+        <v>-0.005658827630127927</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.009805367738694337</v>
+        <v>-0.03095104161201512</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.007871767829607856</v>
+        <v>-0.01644965074647187</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.003474635310684482</v>
+        <v>-0.04098908838506676</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.06864465485613902</v>
+        <v>0.02733391382002881</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.0766952514146233</v>
+        <v>-0.005300282501337739</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.04361353661479361</v>
+        <v>0.02774585287987064</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.03355906919615059</v>
+        <v>0.03090363503342508</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.01473898161166187</v>
+        <v>0.3890204809551383</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.004889052086191725</v>
+        <v>0.115756819183535</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>61.15</v>
+        <v>71.7</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0</v>
+        <v>-0.01021542612125981</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>-0.009805367738694337</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0</v>
+        <v>0.007871767829607856</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0</v>
+        <v>-0.003474635310684482</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.03676991128905338</v>
+        <v>0.06864465485613902</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.1534804029332366</v>
+        <v>-0.0766952514146233</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.01001314637388417</v>
+        <v>0.04361353661479361</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.02752018177199667</v>
+        <v>-0.03355906919615059</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.7883069496014827</v>
+        <v>0.01473898161166187</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.2138006193598696</v>
+        <v>0.004889052086191725</v>
       </c>
     </row>
     <row r="49">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>PBS</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.02752018177199667</v>
+        <v>-0.004950844075900296</v>
       </c>
     </row>
     <row r="68">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.004950844075900296</v>
+        <v>0.01321256395133674</v>
       </c>
     </row>
     <row r="69"/>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -491,13 +491,13 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>15.47</v>
+        <v>15.8</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.04385968863626877</v>
+        <v>0.02100839066937898</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.05309739339183528</v>
+        <v>0.04845672195445694</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.1050000190734863</v>
+        <v>0.1429088585442873</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.152757092330881</v>
+        <v>0.1769746636734653</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.195517833747145</v>
+        <v>0.2117376494967731</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.2816901953744504</v>
+        <v>0.3086164437159893</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7639680113510074</v>
+        <v>0.6911134709047653</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8482676796351563</v>
+        <v>0.887096809110518</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.16359932298873</v>
+        <v>2.249999926414021</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4680037263200747</v>
+        <v>0.4812480230242917</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>39.26</v>
+        <v>39.67</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.03300493110712854</v>
+        <v>0.01044319574479546</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.01033526257465445</v>
+        <v>-0.04363552057053455</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.094813096857566</v>
+        <v>0.1025569392344587</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.2143518743578259</v>
+        <v>0.2270335886848038</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3194625597125427</v>
+        <v>0.3587062983637059</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.266480624123407</v>
+        <v>0.2797067291881183</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4394737385007925</v>
+        <v>0.4974458072821419</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7897597987467058</v>
+        <v>0.8084506106611833</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.8056372494408137</v>
+        <v>0.8034913247561903</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2177089605464608</v>
+        <v>0.2172263705183965</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>162.5</v>
+        <v>163.4</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.03406048786221938</v>
+        <v>0.005538423978365348</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.01017237124670456</v>
+        <v>-0.03370793614012024</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.01861719578404819</v>
+        <v>0.02054833098239395</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.1053670231410271</v>
+        <v>0.1114890143668859</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1899883913110376</v>
+        <v>0.224071285817685</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2770629853733622</v>
+        <v>0.2841359016334368</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.3250863827018096</v>
+        <v>0.3692240279363803</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.8168475521495351</v>
+        <v>0.8269100241973946</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.064731271917388</v>
+        <v>1.026776678496459</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2733697008591651</v>
+        <v>0.2655188919386098</v>
       </c>
     </row>
     <row r="5">
@@ -760,12 +760,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>116.97</v>
+        <v>545.22</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.0135773366966665</v>
+        <v>-0.02049841740401626</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.06753674862178949</v>
+        <v>-0.01907098787631545</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.01220148573812874</v>
+        <v>-0.04308764586863023</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.0953272798754663</v>
+        <v>0.008676560324226035</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1773528235249215</v>
+        <v>-0.1029763036259287</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.5988244309135209</v>
+        <v>0.3416836313072191</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3976866662272542</v>
+        <v>0.5495140164495547</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3870868717720912</v>
+        <v>0.8840347128359942</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.222486343295206</v>
+        <v>2.537876723613505</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3050075782935981</v>
+        <v>0.5237518011583417</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>556.63</v>
+        <v>192.72</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.02856892690608637</v>
+        <v>0.01989836141638968</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.01797735425986446</v>
+        <v>0.05467085714848774</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.06302287942466867</v>
+        <v>0.0397625836228539</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.02978553403754547</v>
+        <v>0.08635855609531884</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.07062593009241236</v>
+        <v>0.1536581228730449</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.3697615758326191</v>
+        <v>0.2649162818199591</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.5849948869035908</v>
+        <v>0.4499736010417688</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.923462653161536</v>
+        <v>0.4825786620435926</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.6116842591124</v>
+        <v>0.3577888961036169</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5342751774802219</v>
+        <v>0.1073308962520023</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>100.15</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.006349830179928517</v>
+        <v>-0.007363413370670036</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.07422501254721525</v>
+        <v>-0.0471659811757108</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.02413335298350372</v>
+        <v>-0.03243614317609866</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.09060219458702656</v>
+        <v>0.02997356727453715</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.125742584616398</v>
+        <v>0.2226489567263978</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.5960963983369636</v>
+        <v>0.2251325766780652</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3670992475406898</v>
+        <v>0.3088623578319443</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3766502254135238</v>
+        <v>0.4861318683167188</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.151349983541433</v>
+        <v>0.6459086889977386</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2909329596035206</v>
+        <v>0.1806882628921627</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>92.86</v>
+        <v>210.82</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.03722132142541301</v>
+        <v>0.008466894267505465</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.01766633016513974</v>
+        <v>-0.02578552093182973</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.06320133391242422</v>
+        <v>0.03566520855127853</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.1775297982709156</v>
+        <v>0.1309479275927459</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.05713141721587411</v>
+        <v>0.2449056253897566</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>-0.02637862179896378</v>
+        <v>0.2031914185820416</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.4830527866977201</v>
+        <v>0.2417370243949832</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.9144810780686863</v>
+        <v>0.5291313901080761</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.602476911986245</v>
+        <v>0.6351995815040408</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.3755053854805361</v>
+        <v>0.1781219722756464</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>70.62</v>
+        <v>111.85</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.02472035388756666</v>
+        <v>-0.0437719303509404</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.02834338951491511</v>
+        <v>0.034785847567953</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.002840167322312181</v>
+        <v>-0.02975364626558075</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.03761394769055548</v>
+        <v>0.04738269046927246</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2135335737595909</v>
+        <v>0.06523808070591519</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2342207358251966</v>
+        <v>0.5288407992801922</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2940287837823385</v>
+        <v>0.3559354906913332</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4971559260941103</v>
+        <v>0.3263714018301793</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.6736714088807618</v>
+        <v>1.110026661742447</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1872897879735895</v>
+        <v>0.2826140146650482</v>
       </c>
     </row>
     <row r="10">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>188.96</v>
+        <v>426.88</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.01881708885638633</v>
+        <v>-0.005359028454772985</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.01460481712025596</v>
+        <v>0.05223200550638829</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.03059722074502824</v>
+        <v>0.01519659158800857</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.06516354687209436</v>
+        <v>0.1093267004265213</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1579130290056037</v>
+        <v>0.01495520245295756</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2402374618787975</v>
+        <v>0.07534575300434443</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.4329287921225777</v>
+        <v>0.4821655419921176</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4536533424611577</v>
+        <v>0.6908286593200013</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3641600941893819</v>
+        <v>0.2855068790405277</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1090601828249675</v>
+        <v>0.08732189913170463</v>
       </c>
     </row>
     <row r="11">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>28.82</v>
+        <v>96.2</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.003457827842528238</v>
+        <v>-0.03944088384877387</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.04043317332262464</v>
+        <v>0.04044990158774087</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.03371594556503466</v>
+        <v>-0.0127258360231437</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.1454689932276994</v>
+        <v>0.04758788010510173</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1874742130713498</v>
+        <v>0.02265238779525358</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.5362472997444092</v>
+        <v>0.5331448524710878</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2712836170195403</v>
+        <v>0.3286946277395031</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.2574170854664446</v>
+        <v>0.3223537850937013</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.4051681800685882</v>
+        <v>1.06343615881672</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1200638197234249</v>
+        <v>0.2731034026507091</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>209.05</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.02676908714295734</v>
+        <v>-0.03898344521633024</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.01637413893345419</v>
+        <v>-0.07350500263171345</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03525979613839958</v>
+        <v>0.04288884167388041</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.1214527061041539</v>
+        <v>0.1316256298894252</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.2143072205995868</v>
+        <v>-0.005737750763619598</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1930896546246796</v>
+        <v>-0.06433373745751181</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2049612529914484</v>
+        <v>0.4129328515752897</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.5162930967790991</v>
+        <v>0.8398480098440948</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6378479700426256</v>
+        <v>1.472291291144035</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1787576626248271</v>
+        <v>0.3521759679475669</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>429.18</v>
+        <v>151.77</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.03429324027022851</v>
+        <v>-0.004917387745808077</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.05008441596405899</v>
+        <v>-0.001250345044824908</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.006047788409172083</v>
+        <v>0.002179092879917022</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.1153036443925328</v>
+        <v>0.04719528008244156</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.02613267824454568</v>
+        <v>-0.06504887569728424</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.08113961094296984</v>
+        <v>0.2634604394343898</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.5076458241517798</v>
+        <v>0.4424291063149859</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6999386790725202</v>
+        <v>0.5478035174470266</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3263816528602612</v>
+        <v>1.258913932041123</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09872625369393195</v>
+        <v>0.312098869558711</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>152.52</v>
+        <v>472.93</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.002420008624923531</v>
+        <v>-0.02516803727580452</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.0191099862379307</v>
+        <v>-0.03666510555179614</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.0200462293075222</v>
+        <v>-0.08654923012284366</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.05237019237045759</v>
+        <v>-0.02982749401709106</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>-0.03660088348322788</v>
+        <v>-0.2130161300266236</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.2697040666525496</v>
+        <v>0.3484711264598097</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4468360835937109</v>
+        <v>0.4921420951075131</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.5554522794250605</v>
+        <v>0.6559578265824006</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.276824243299484</v>
+        <v>1.224316359055333</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3155575025390724</v>
+        <v>0.305365665120976</v>
       </c>
     </row>
     <row r="15">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>485.14</v>
+        <v>27.92</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.03022427302208563</v>
+        <v>-0.03122830076545435</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.007350515988492345</v>
+        <v>0.01601166453374003</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.1168675302517548</v>
+        <v>0.006126128875457493</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.004779753762141237</v>
+        <v>0.1096979429896825</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.2083553731659464</v>
+        <v>0.05837759531917253</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.383285712843749</v>
+        <v>0.4882729070178737</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.5120887156736547</v>
+        <v>0.2392365390757987</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.6987110495995432</v>
+        <v>0.2181500865338775</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.293841134324624</v>
+        <v>0.3520581400514864</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.3188268453135963</v>
+        <v>0.1057708127675674</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>31.2</v>
+        <v>31.86</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.008403368597089678</v>
+        <v>0.02115384074592974</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.002248686285256207</v>
+        <v>0.0432219926409072</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.02699149522136324</v>
+        <v>0.03643464045454214</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.06303238015075907</v>
+        <v>0.08551959782823504</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1002339860657626</v>
+        <v>0.09285310424339688</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1286330810561378</v>
+        <v>0.1525080055133874</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2901852044944273</v>
+        <v>0.3100222511738098</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.3280327695033314</v>
+        <v>0.356125763214781</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2740521377492848</v>
+        <v>0.273158842187083</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.08408266599652414</v>
+        <v>0.08382924029929906</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>108.01</v>
+        <v>57.43</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.01567484888438619</v>
+        <v>0.01269619524469823</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.003250961008877118</v>
+        <v>0.007543865003083905</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.002677755377243574</v>
+        <v>0.01682012695890744</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.02398557734906026</v>
+        <v>0.0186236115141607</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.02570808640113764</v>
+        <v>0.1371447510800847</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.06855955856390472</v>
+        <v>0.2497877924344776</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.3568496477598939</v>
+        <v>0.1899960193637875</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5433234962554168</v>
+        <v>0.2293267194077908</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.7357731113146404</v>
+        <v>0.1965024612062771</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2017966400508191</v>
+        <v>0.06162515075603148</v>
       </c>
     </row>
     <row r="18">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>97.95</v>
+        <v>108.34</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.05031997742989269</v>
+        <v>0.003055218916151237</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.02411084718658385</v>
+        <v>-0.005233746258857752</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.0796957190283758</v>
+        <v>0.01546530938913926</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.328135551840572</v>
+        <v>0.02711407745484329</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.04646410767644094</v>
+        <v>-0.02947237298643401</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>-0.1689817712618231</v>
+        <v>0.07182424194026349</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2766035598922716</v>
+        <v>0.3571349998743247</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.7063862443904645</v>
+        <v>0.5480386873949172</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.853722750828505</v>
+        <v>0.7128509172066892</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.5678102121891515</v>
+        <v>0.1964829700257331</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>56.71</v>
+        <v>55.86</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.009605296073746383</v>
+        <v>0.004856996888335186</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.009778267309496824</v>
+        <v>0.02288958040705569</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.008177761501736214</v>
+        <v>0.009943938228252236</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.00585310411680795</v>
+        <v>0.02890820818294393</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1295921399728448</v>
+        <v>0.09061510414098706</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2341191744405544</v>
+        <v>0.1149988014993593</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1563118701947661</v>
+        <v>0.2406616121320353</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2139146223520154</v>
+        <v>0.2415959491215225</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.180595965582556</v>
+        <v>0.7027846575741334</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05689967639801141</v>
+        <v>0.1941344917357091</v>
       </c>
     </row>
     <row r="20">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>98.51000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.01144003384036463</v>
+        <v>-0.03736596372380518</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.04858024661792859</v>
+        <v>-0.08278211949026737</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.07204269007022956</v>
+        <v>0.0772306892551835</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3294197593085566</v>
+        <v>0.2785084869902013</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.1007934348841093</v>
+        <v>0.03202577112717875</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.1496028552272287</v>
+        <v>-0.2000335682506748</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1921837328483802</v>
+        <v>0.2224483271674043</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.5707686660196767</v>
+        <v>0.6426254778837703</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>2.487313996537913</v>
+        <v>2.765135603970966</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.5164578757331455</v>
+        <v>0.5557036622576663</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>55.59</v>
+        <v>94.67</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.00506235350469697</v>
+        <v>-0.03898085355814707</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.01219959952623295</v>
+        <v>-0.1028240979842188</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01645641887874127</v>
+        <v>0.06430580569925648</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.0239349592719027</v>
+        <v>0.2775978423536425</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.09775354493795252</v>
+        <v>0.09217810147253114</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1096094319411538</v>
+        <v>-0.1827520617938825</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2359599877833838</v>
+        <v>0.1513832277144378</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.235594774420586</v>
+        <v>0.5095387626758376</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.7176260466142543</v>
+        <v>2.370960592145052</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1975938002954623</v>
+        <v>0.4994013303015234</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>76.37</v>
+        <v>132.67</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.009853423232194625</v>
+        <v>-0.000150759455067262</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.008568038987068372</v>
+        <v>-0.01885817947594715</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.001705205750986538</v>
+        <v>0.001585319677144037</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.1032938659316347</v>
+        <v>-0.01747760224903006</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>-0.1199278321003493</v>
+        <v>0.1490582211977725</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.01721868989143682</v>
+        <v>0.06237294862081022</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2118903641402832</v>
+        <v>0.0916962683374769</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.6204500785702178</v>
+        <v>0.1145611652906096</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.3239953674568072</v>
+        <v>0.6729561624141074</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.09806695418229028</v>
+        <v>0.1871206337378382</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>109.98</v>
+        <v>143.82</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.00438359230076335</v>
+        <v>-0.0008336467635975398</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.07349933267929298</v>
+        <v>-0.01039010863421919</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.0783410693256068</v>
+        <v>-0.008069509101442662</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.1628251345711269</v>
+        <v>-0.02269635943717097</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.08204427739932241</v>
+        <v>0.1257254583887788</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.3485426265809966</v>
+        <v>0.07240891356421386</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.05678385446639722</v>
+        <v>0.1011366065827151</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.01758209860677784</v>
+        <v>0.1125006403254671</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.5276591713126926</v>
+        <v>0.6591223859116471</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1517073998352301</v>
+        <v>0.1838394486444668</v>
       </c>
     </row>
     <row r="24">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>73.56</v>
+        <v>72.62</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.01062543284116302</v>
+        <v>-0.01277861396424018</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.01605142513840518</v>
+        <v>-0.0230055030586348</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.04948962218969832</v>
+        <v>-0.05504223567373911</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.03286878885414235</v>
+        <v>-0.04522738525414327</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.06292481440320019</v>
+        <v>0.06931203497849237</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1145710569023737</v>
+        <v>0.1003283836305031</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1888463198548427</v>
+        <v>0.160937456072793</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1501554560582175</v>
+        <v>0.1354581989354657</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7955810221060633</v>
+        <v>0.7314479546439516</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2154441346501694</v>
+        <v>0.2007976073836559</v>
       </c>
     </row>
     <row r="25">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>67.81</v>
+        <v>66.95</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.008915530936515426</v>
+        <v>-0.01268250466472065</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.01424630533348903</v>
+        <v>-0.02177097369977021</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.04573599931973193</v>
+        <v>-0.05169973944428397</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.02641785968377175</v>
+        <v>-0.038765319719821</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.07377789848259275</v>
+        <v>0.07643601346000417</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1232176423175408</v>
+        <v>0.1089724293293519</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1702825132734951</v>
+        <v>0.1457275567200924</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1372944562027678</v>
+        <v>0.122870713956815</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8831680474741836</v>
+        <v>0.8228831161762968</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2348940333114031</v>
+        <v>0.2215735130180485</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>132.69</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.008147677887849647</v>
+        <v>-0.02173633105157469</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.02684270992500537</v>
+        <v>-0.02454625072867245</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.008129519555642561</v>
+        <v>0.009321838323413267</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.01732945537321151</v>
+        <v>0.07931230521457322</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.1554102164580851</v>
+        <v>-0.1284567417271874</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.06253313553731465</v>
+        <v>-0.004891912303892632</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.08318693156169754</v>
+        <v>0.1938256599778958</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1147292212605544</v>
+        <v>0.5852274392098655</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6926079062911943</v>
+        <v>0.2921638298890086</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1917508080175323</v>
+        <v>0.08919555432629078</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>118.13</v>
+        <v>94.33</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.03959351826489454</v>
+        <v>0.005972114834555509</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.002205773316175552</v>
+        <v>-0.0249120951615962</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.0002540116823408489</v>
+        <v>-0.0007415221789486282</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.1736710925239742</v>
+        <v>-0.01852043250434809</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.05589957016043301</v>
+        <v>0.07892377980779064</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.008931152890786387</v>
+        <v>0.05892816858681993</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.2197892404961077</v>
+        <v>0.1073465019323001</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.4400802056872786</v>
+        <v>0.137638353839127</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.3089665722165</v>
+        <v>0.4380734502500632</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3217192497109764</v>
+        <v>0.1287394119258278</v>
       </c>
     </row>
     <row r="28">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>143.94</v>
+        <v>191.39</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.007857729358012877</v>
+        <v>-0.01583792776120363</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.01653455970793538</v>
+        <v>-0.02739099208804097</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.0003475088746258681</v>
+        <v>0.005199608849264514</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.02188095365977627</v>
+        <v>0.02754217241547385</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.1245583487494526</v>
+        <v>0.04352606981735585</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.07330366969481239</v>
+        <v>0.1289475792261048</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.09330246407775045</v>
+        <v>0.1116455825441227</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.113428846679998</v>
+        <v>0.1118377337858594</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6778245033203869</v>
+        <v>1.08706168960691</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1882710346756391</v>
+        <v>0.2779438198350019</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>194.47</v>
+        <v>115.77</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.004504759945316739</v>
+        <v>-0.019977995980892</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.001488977686958326</v>
+        <v>-0.04274851739683605</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.01816754565813161</v>
+        <v>0.01883304973488475</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.04407820764520576</v>
+        <v>0.1502234961546411</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.06664219499818858</v>
+        <v>-0.09109365879575426</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.147115408588308</v>
+        <v>-0.02873072233512153</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1167468220155197</v>
+        <v>0.211390831761769</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1297303209994909</v>
+        <v>0.4113104203879236</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.140614624531654</v>
+        <v>1.215598278649114</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.288782101648235</v>
+        <v>0.3036579968504807</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>85.14</v>
+        <v>75.08</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01458335780067166</v>
+        <v>0.005625477475813101</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01946334683597606</v>
+        <v>-0.01210523906506988</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.02496564719187688</v>
+        <v>0.008597519729425018</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.002944987652226061</v>
+        <v>0.004817995241839235</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.01780226172605381</v>
+        <v>0.07543344316556366</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.04671398738931121</v>
+        <v>-0.02297790768707175</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1752403433254921</v>
+        <v>0.1093525898401695</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.206221067154251</v>
+        <v>0.09663309347387106</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4110026003635907</v>
+        <v>0.2495867306852904</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1216118904799379</v>
+        <v>0.0770986170308201</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>292.49</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.004560447875053941</v>
+        <v>-0.02595723632036284</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.02090747027705064</v>
+        <v>-0.0500573034801749</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.01934198001584697</v>
+        <v>-0.03771176593747139</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.0644127557009031</v>
+        <v>-0.02308869240858613</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.03214759402424949</v>
+        <v>-0.02065438963442345</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.2013882451672302</v>
+        <v>0.01954418505881761</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.08265467230372803</v>
+        <v>0.1469346160384069</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.0577152262884002</v>
+        <v>0.1749107748640586</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.7252993118648809</v>
+        <v>0.3708645590657016</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1993745147395998</v>
+        <v>0.1108741211442541</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>105.63</v>
+        <v>233.2</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.01289603640093073</v>
+        <v>-0.01345294808732589</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01501306082080311</v>
+        <v>-0.0309578106677485</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.04519569849167215</v>
+        <v>0.006908423154408094</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.03065067385399456</v>
+        <v>0.04634989930171196</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.0525388597277785</v>
+        <v>0.01100429215552889</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.03571370863132728</v>
+        <v>-0.03788389282515359</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.2238039344669769</v>
+        <v>0.1635628163482648</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.2361417539434949</v>
+        <v>0.1359733740776485</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3479423415375116</v>
+        <v>0.3272392164709372</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1046476471313236</v>
+        <v>0.09896299416762955</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>93.77</v>
+        <v>106.18</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.01190732207211131</v>
+        <v>-0.03455176337306631</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.03090125493129248</v>
+        <v>0.04251351886033539</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.008668989603245691</v>
+        <v>0.04138879225770586</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.02434714340260991</v>
+        <v>0.1226474756771712</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.05053043978247507</v>
+        <v>-0.01392841676746626</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.0526416716441227</v>
+        <v>0.3019481008488767</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.08870234743015004</v>
+        <v>0.02046611164336154</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1308846853102006</v>
+        <v>-0.01757715727695175</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4243006793652089</v>
+        <v>0.4680254727889628</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1251244449965172</v>
+        <v>0.1365220442021109</v>
       </c>
     </row>
     <row r="34">
@@ -2398,37 +2398,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>65.37</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.02228534026574391</v>
+        <v>-0.0110142449204772</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.04999265999221203</v>
+        <v>-0.06004648628550313</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.04191705217116815</v>
+        <v>-0.04617877411904014</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.02243158274846446</v>
+        <v>-0.0331987607225962</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.04167710439685512</v>
+        <v>0.01597621596981358</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.06386986090884239</v>
+        <v>0.05215213769727844</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.1095242100290603</v>
+        <v>0.09730363863460112</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1047080568208931</v>
+        <v>0.09254053171744325</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.6161520192711962</v>
+        <v>0.6062057378158512</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.173529657879937</v>
+        <v>0.171117285118642</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>236.38</v>
+        <v>96.3</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.01306830485495292</v>
+        <v>-0.00145167343534125</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.01240861142664285</v>
+        <v>-0.02972289116616811</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.008275048716957389</v>
+        <v>-0.01352181579272116</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.06061834280797318</v>
+        <v>-0.02678114177073199</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.01994372710642311</v>
+        <v>0.03250920361576015</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>-0.02476409481986896</v>
+        <v>0.026097779078464</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1771643162235665</v>
+        <v>0.09738822618680398</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1514640445291633</v>
+        <v>0.08444864858827539</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3605252189070798</v>
+        <v>0.3142161567501167</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1080742571739794</v>
+        <v>0.09535677975887369</v>
       </c>
     </row>
     <row r="36">
@@ -2510,37 +2510,37 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>64.23</v>
+        <v>63.89</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.0009332331270702765</v>
+        <v>-0.005293538058774749</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.02309660092116617</v>
+        <v>0.004717710903297423</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.01149611585722199</v>
+        <v>0.01541642162955248</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.06429171467960026</v>
+        <v>0.05865784598230506</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.01175582961795585</v>
+        <v>-0.001931494055822824</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.2115499079834238</v>
+        <v>0.2051365224354085</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.06088155408611962</v>
+        <v>0.05144545358094188</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.02148710112051977</v>
+        <v>0.01607982027419097</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.8784584812670804</v>
+        <v>0.8544537103512664</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.2338637357815057</v>
+        <v>0.2285853501284278</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>178.39</v>
+        <v>287.14</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.01827091080045284</v>
+        <v>-0.01829114077254579</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.001066231451515964</v>
+        <v>-0.001425745650966315</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.05713529457165345</v>
+        <v>0.0119114912830891</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.005352699644253667</v>
+        <v>0.04494343214628449</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.07230708618617632</v>
+        <v>-0.009041948608804584</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.007682056666696191</v>
+        <v>0.1794134836523946</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1763587152568953</v>
+        <v>0.06585011564168641</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.2587633204958708</v>
+        <v>0.03836840818709386</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.8240334046660189</v>
+        <v>0.6800655812758387</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2218304076185909</v>
+        <v>0.188799859001554</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>19.73</v>
+        <v>102.71</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.01083139150469459</v>
+        <v>-0.02764364522267204</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.02592462756264369</v>
+        <v>-0.0471286927164587</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.01816732757581307</v>
+        <v>-0.05170343089604079</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.01995861822750711</v>
+        <v>-0.05744702272281099</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.1389802848941604</v>
+        <v>-0.08552949319805758</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.1528929940668193</v>
+        <v>0.007082806317664891</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>-0.03066341708202658</v>
+        <v>0.1888780982690961</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>-0.1154259862318505</v>
+        <v>0.2019702898525493</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.1048382814992959</v>
+        <v>0.3029057252864018</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.03379137515819997</v>
+        <v>0.09220542871102833</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>74.66</v>
+        <v>175.47</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.0004016438387508536</v>
+        <v>-0.01636862032028663</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.02059556113979122</v>
+        <v>-0.0219608849059868</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.01385122597657595</v>
+        <v>-0.04511315593136034</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.0008029651714878128</v>
+        <v>-0.02163370365637496</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.05588242973991364</v>
+        <v>-0.08890777335931177</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>-0.02844328112493577</v>
+        <v>-0.008812308322446394</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.09790205867378488</v>
+        <v>0.1705195566488473</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.09049864014122999</v>
+        <v>0.2381591016295708</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.2348174124791458</v>
+        <v>0.7929329336461668</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.07283824816438744</v>
+        <v>0.2148463361122466</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>54.7</v>
+        <v>23.39</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.02425973201990528</v>
+        <v>-0.01015657129250525</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.02181683558572389</v>
+        <v>-0.02582260863486352</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.06861908412579942</v>
+        <v>-0.0282509478104398</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.02945351010353292</v>
+        <v>-0.01432786174237943</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.02688828311025171</v>
+        <v>-0.1040678784364861</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>-0.005338149015765792</v>
+        <v>-0.04072652330895832</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.13649393914632</v>
+        <v>0.1947544620022732</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.1860980806989365</v>
+        <v>0.2757514760286375</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.7311704443157068</v>
+        <v>0.5432165197751146</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.200733450764135</v>
+        <v>0.1556037821328513</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>23.63</v>
+        <v>53.92</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.02274611817483929</v>
+        <v>-0.01425964502952271</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.005471425373018701</v>
+        <v>-0.03073886151963467</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.02917013095194254</v>
+        <v>-0.05915203495223775</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.00421409116724758</v>
+        <v>-0.04329315853410576</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.09591007939751295</v>
+        <v>-0.03510979353589005</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>-0.03088362374276743</v>
+        <v>-0.01952167393520898</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1966867928406613</v>
+        <v>0.1338361533904657</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.2888416885228728</v>
+        <v>0.1691847430979714</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.554123535944107</v>
+        <v>0.6886924315602654</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.158319886396729</v>
+        <v>0.1908311477077549</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>13.51</v>
+        <v>58.39</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.008961903098002821</v>
+        <v>-0.005958499809622375</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.005208381747325852</v>
+        <v>-0.01964408926570727</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.02503792989871667</v>
+        <v>-0.0448225360803397</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0.08951618100800607</v>
+        <v>-0.03599142011159795</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.09025767424155728</v>
+        <v>-0.02395472282934874</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.1284516871339132</v>
+        <v>-0.02498598781731565</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.005204886712538492</v>
+        <v>0.1164900174411128</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.06073994766337687</v>
+        <v>0.1422597561287762</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.1934463601443803</v>
+        <v>0.5727986365903002</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.06072051409260681</v>
+        <v>0.1629410695434417</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>96.44</v>
+        <v>13.35</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.01239118346712964</v>
+        <v>-0.01184306770551047</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.02684153454764659</v>
+        <v>-0.002987301032667533</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.01571750217151191</v>
+        <v>0.009833593934573726</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.02536629190750594</v>
+        <v>0.07661296711007903</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.01661468954834078</v>
+        <v>0.06303715746007565</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.02758950346307687</v>
+        <v>0.1150873574007887</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.08635028691987245</v>
+        <v>-0.001242089430010918</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.08602520252489199</v>
+        <v>-0.0718636065184215</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.3183636442142885</v>
+        <v>0.1770733840633811</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.09650783542637198</v>
+        <v>0.05584746086376025</v>
       </c>
     </row>
     <row r="44">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2958,37 +2958,37 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>58.74</v>
+        <v>225.46</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.01854631284801544</v>
+        <v>-0.01265600749902474</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.01624514186700265</v>
+        <v>-0.03772939062206426</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.05425855576828165</v>
+        <v>-0.1058851386440325</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.03021294412378539</v>
+        <v>-0.05925059138471189</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.03293245315669513</v>
+        <v>-0.0186669661545884</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.01914154288734349</v>
+        <v>-0.07367181127407607</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1089543463384499</v>
+        <v>0.1331294186937346</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.1491067082310065</v>
+        <v>0.1420563580763534</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5956282324024154</v>
+        <v>0.9791904174253179</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.168540863086265</v>
+        <v>0.2555360677509591</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>228.35</v>
+        <v>85.92</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.02522832981261702</v>
+        <v>-0.002090595915978821</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.0216366235005494</v>
+        <v>-0.02241439565802461</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.09096334045511401</v>
+        <v>-0.01388728477694501</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.04719184422002864</v>
+        <v>-0.04299399268026804</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.0294329609003765</v>
+        <v>0.03342997406905823</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.06179791869751117</v>
+        <v>-0.007379797668365717</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.1148639905275106</v>
+        <v>0.0220832746435411</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.1566955050625127</v>
+        <v>0.02874843210425659</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>1.009218955805737</v>
+        <v>0.3788223543277842</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.2618539424677584</v>
+        <v>0.1130194967903728</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>28.5</v>
+        <v>71.25</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.02896083033805952</v>
+        <v>-0.006276108331873753</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.03943377395636627</v>
+        <v>-0.01886536346415257</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.07617505194201779</v>
+        <v>0.005503801669336505</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.08887470030754774</v>
+        <v>-0.009728936454934667</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.02796724772711956</v>
+        <v>0.07159036196559199</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.001757442380306617</v>
+        <v>-0.08249001204007855</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.09211075348672804</v>
+        <v>0.04808351107437514</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.09211075348672804</v>
+        <v>-0.03962455717423252</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.4926459093010964</v>
+        <v>0.004868061355520759</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.142840436430097</v>
+        <v>0.001620061103192461</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>86.09999999999999</v>
+        <v>48.11</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.005658827630127927</v>
+        <v>0.008595384504284098</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.03095104161201512</v>
+        <v>-0.01231776812560759</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.01644965074647187</v>
+        <v>0.0008321388762491111</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.04098908838506676</v>
+        <v>0.008384018728876619</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.02733391382002881</v>
+        <v>0.007792568939519295</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.005300282501337739</v>
+        <v>-0.05022498866415004</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.02774585287987064</v>
+        <v>0.06814923186492061</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.03090363503342508</v>
+        <v>0.02780105833352087</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.3890204809551383</v>
+        <v>0.1396383012869169</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.115756819183535</v>
+        <v>0.04453343374279095</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>71.7</v>
+        <v>27.89</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.01021542612125981</v>
+        <v>-0.02140353018777408</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.009805367738694337</v>
+        <v>-0.07311401634374015</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.007871767829607856</v>
+        <v>-0.08014512960534748</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.003474635310684482</v>
+        <v>-0.1083759981643599</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.06864465485613902</v>
+        <v>-0.03594887329957197</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.0766952514146233</v>
+        <v>-0.01968370327850766</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.04361353661479361</v>
+        <v>0.07322277472981154</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.03355906919615059</v>
+        <v>0.06873572800608208</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.01473898161166187</v>
+        <v>0.463739679545502</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.004889052086191725</v>
+        <v>0.1354149684351527</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>47.7</v>
+        <v>19.1</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.002509387968435139</v>
+        <v>-0.03173473872098576</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.02633192225617653</v>
+        <v>-0.0565571948776975</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.001674299254944445</v>
+        <v>-0.04833080857518113</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.0002095644880542036</v>
+        <v>-0.01240950202816049</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.001295313864174474</v>
+        <v>0.07532942893472283</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.05831909809635283</v>
+        <v>0.1163062361268539</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.05463639527232123</v>
+        <v>-0.07393937544389206</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.01904191746573702</v>
+        <v>-0.1434977114381563</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.1207766858367583</v>
+        <v>0.05907281879766013</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.03873882065271106</v>
+        <v>0.01931545084562281</v>
       </c>
     </row>
     <row r="50">
@@ -3294,37 +3294,37 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>256.52</v>
+        <v>252.04</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.03582033157886411</v>
+        <v>-0.01746450927572851</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.03422309716955507</v>
+        <v>-0.04836704746903453</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.1300573362449934</v>
+        <v>-0.1321833156278207</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.03148832137410451</v>
+        <v>-0.04840290256911794</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.1091113144646929</v>
+        <v>-0.09966081033777352</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.09278649712595732</v>
+        <v>-0.1086305357619672</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.1151612176119026</v>
+        <v>0.1251466573300055</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.1837711482463826</v>
+        <v>0.1630971660474938</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>1.13493557588026</v>
+        <v>1.091995296912629</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.2876413796935569</v>
+        <v>0.2789500049866638</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>54.97</v>
+        <v>42.56</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.006407951220483099</v>
+        <v>0.007814393431963884</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.0162848931642442</v>
+        <v>-0.0173170163061348</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.001997106149142169</v>
+        <v>-0.03316672124693631</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>0.0468482760960427</v>
+        <v>-0.04036070264747738</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>0.1244512176565467</v>
+        <v>-0.006223457291792633</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.08478811339361347</v>
+        <v>-0.09634983406127684</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>-0.143082844121369</v>
+        <v>-0.01809175250155892</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>-0.1117135736789118</v>
+        <v>0.03763898733174176</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.06243510950264519</v>
+        <v>0.4871537475462031</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.02039300167370905</v>
+        <v>0.1414370273202417</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>19.35</v>
+        <v>54.29</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.01013046576877663</v>
+        <v>-0.01237038912270705</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.0252909862046109</v>
+        <v>-0.02548910774154167</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.006062164376705148</v>
+        <v>-0.02074310497236576</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.01192534374475618</v>
+        <v>0.03389835556829945</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.03737268191938803</v>
+        <v>0.1132698534181711</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0.05536762759633307</v>
+        <v>-0.09610969796856794</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.04625055757775431</v>
+        <v>-0.1438392185196125</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.1976549001672258</v>
+        <v>-0.1227020224249226</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.163099361553233</v>
+        <v>0.04749668512496052</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.05165253357781463</v>
+        <v>0.0155879806839514</v>
       </c>
     </row>
     <row r="53">
@@ -3462,37 +3462,37 @@
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>111.46</v>
+        <v>110.88</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.0004487516445552675</v>
+        <v>-0.005203676976662464</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.007656700611540224</v>
+        <v>-0.02032163850111446</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.005775125351117794</v>
+        <v>0.003620509452666232</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.02974871844284221</v>
+        <v>0.02439023874493351</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.03405688063519186</v>
+        <v>-0.0384183714146864</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.05034669892222399</v>
+        <v>-0.05528838794085389</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.02530976117652806</v>
+        <v>-0.02582277038576264</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.01321256395133674</v>
+        <v>0.007940133059838095</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.702211736840799</v>
+        <v>0.7092525069386775</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.1940005501263331</v>
+        <v>0.1956445131031088</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>27.01</v>
+        <v>44.44</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.0305803553702465</v>
+        <v>-0.00670547698933599</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.01498903344099678</v>
+        <v>-0.0313862774167849</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>0.02559338208304651</v>
+        <v>-0.01354052432146868</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.05627693001753542</v>
+        <v>-0.03454269378132224</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.0306942538547601</v>
+        <v>-0.01855124061911329</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0.1079330002504497</v>
+        <v>-0.1236442628862823</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1129831981964121</v>
+        <v>-0.01663394738990154</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.1994667481644347</v>
+        <v>-0.01162312329420756</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.2629571214289039</v>
+        <v>0.2547880098416866</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.08092659431977678</v>
+        <v>0.0785909865700638</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>45.51</v>
+        <v>19.04</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.05912757232802612</v>
+        <v>-0.01586805213242104</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.003939599706412777</v>
+        <v>-0.04283125248043052</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.005745819260402296</v>
+        <v>-0.006729600181172746</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.1648323183263838</v>
+        <v>-0.00413194036390363</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.1034278994011091</v>
+        <v>-0.004184096244488567</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.1624954325774725</v>
+        <v>0.03862099906276484</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.05305883115165888</v>
+        <v>-0.06293111160320741</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.1724244846247063</v>
+        <v>-0.2103865540395649</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1.165100394412779</v>
+        <v>0.1458845153142456</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.2936774648510614</v>
+        <v>0.04643827664308775</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>35.89</v>
+        <v>43.94</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.006917543005593108</v>
+        <v>-0.03449790711333356</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.01815601105385634</v>
+        <v>-0.08724555081408203</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.0510312089039997</v>
+        <v>0.007336077548372177</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.01902322957761493</v>
+        <v>0.1246480412061512</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.1056551247402403</v>
+        <v>-0.1305896748963186</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.07975530691001131</v>
+        <v>-0.1913875873514074</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.02539089129525696</v>
+        <v>0.04157357758052793</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.07490292756258543</v>
+        <v>0.1319782936567251</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.3545476520962678</v>
+        <v>1.064611884443392</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.1064490730259693</v>
+        <v>0.2733451573387657</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>44.74</v>
+        <v>17.24</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.01735113380212305</v>
+        <v>-0.003468177375051562</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.02314405188321533</v>
+        <v>-0.02322945361322626</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.01148909991936542</v>
+        <v>-0.028184893261049</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.02802513871476109</v>
+        <v>-0.01766378800107027</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.02760262311229067</v>
+        <v>-0.2497278011989613</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.1177282096980724</v>
+        <v>-0.0512473239091269</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.01993280440576872</v>
+        <v>0.0526141411873462</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.004950844075900296</v>
+        <v>0.2106159475611487</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.2607721672859273</v>
+        <v>0.122405321100701</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.08030288923594497</v>
+        <v>0.03924171830756773</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>42.23</v>
+        <v>26.25</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.02200094386811713</v>
+        <v>-0.02810177186602592</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.02290610019678962</v>
+        <v>-0.05897115722419133</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.04413763579605512</v>
+        <v>0.009615384615384581</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.04780155591486246</v>
+        <v>0.02659367670283652</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.04323138602203247</v>
+        <v>-0.01145074438781213</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.1033565586799418</v>
+        <v>0.07679811983457019</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.04849574131158119</v>
+        <v>-0.1240320078740984</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.02959333989884261</v>
+        <v>-0.2219631509786856</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.4681225962636701</v>
+        <v>0.2168164224807103</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.1365471074674436</v>
+        <v>0.06759948138761196</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>102.81</v>
+        <v>35.15</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.01636049693258479</v>
+        <v>-0.02061849753006584</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.03274064659853826</v>
+        <v>-0.01952571765790989</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.04972737555603823</v>
+        <v>-0.03830363174842666</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.008486882651100092</v>
+        <v>-0.001987498364510842</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>0.003199395854959874</v>
+        <v>-0.13380340873604</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.1046464723780145</v>
+        <v>-0.09872936984154346</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.04989621524056631</v>
+        <v>0.001969716345187722</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.0912972511690463</v>
+        <v>0.05274016448104657</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.2658415102648566</v>
+        <v>0.3266189146771643</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.08174885556402889</v>
+        <v>0.09879176280399227</v>
       </c>
     </row>
     <row r="60">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>94.69</v>
+        <v>100.56</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.009829497427682132</v>
+        <v>-0.02188503115874185</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.03189852975222129</v>
+        <v>-0.05470953041068272</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.03219535991810407</v>
+        <v>-0.05087304903162493</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.003710050001083598</v>
+        <v>-0.03018617811858204</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>0.01918710125414336</v>
+        <v>-0.02445891390065003</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.1161924977529548</v>
+        <v>-0.1242412540400673</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.08396526935147219</v>
+        <v>-0.06812165987550589</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1391235799262603</v>
+        <v>-0.1111842391412462</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.1287405672710737</v>
+        <v>0.2206524247647434</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.0411933316585078</v>
+        <v>0.06872017031955724</v>
       </c>
     </row>
     <row r="61">
@@ -3896,51 +3896,51 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>17.3</v>
+        <v>92.36</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.02972522091493901</v>
+        <v>-0.02460662974949734</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.007458466198456137</v>
+        <v>-0.05908723344920441</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.04472674467100923</v>
+        <v>-0.04071456396599193</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.01424501486427832</v>
+        <v>-0.02098787157514248</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.2640461121439773</v>
+        <v>-0.005464118141478513</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.04794542978890637</v>
+        <v>-0.1379400831182362</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.02892246413704291</v>
+        <v>-0.1041780471485316</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.2148291906747992</v>
+        <v>-0.1603067890115963</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.125611084726037</v>
+        <v>0.08523621694307493</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.04023018965530523</v>
+        <v>0.02764100754018251</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>47.57</v>
+        <v>46.86</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.04362689807833287</v>
+        <v>-0.01492535398418149</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.01552152327683765</v>
+        <v>-0.04073690738851832</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.06578944608376214</v>
+        <v>-0.06035689564871316</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.03567812833776329</v>
+        <v>-0.05007097362701063</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.3565535033347771</v>
+        <v>-0.3412062080727857</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1350909146395597</v>
+        <v>-0.1479999889026988</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.02739726347921445</v>
+        <v>-0.0163727705560458</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.1448856935812921</v>
+        <v>0.1277978693331661</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1782666368817573</v>
+        <v>-0.1930257949151184</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.06335078525284621</v>
+        <v>-0.06899241854661819</v>
       </c>
     </row>
   </sheetData>
@@ -4016,7 +4016,7 @@
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -4158,17 +4158,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3294197593085566</v>
+        <v>0.2785084869902013</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.08887470030754774</v>
+        <v>-0.1083759981643599</v>
       </c>
     </row>
     <row r="18">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.328135551840572</v>
+        <v>0.2775978423536425</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4669,21 +4669,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.04780155591486246</v>
+        <v>-0.05925059138471189</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.2143518743578259</v>
+        <v>0.2270335886848038</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.04719184422002864</v>
+        <v>-0.05744702272281099</v>
       </c>
     </row>
     <row r="20">
@@ -4737,21 +4737,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1775297982709156</v>
+        <v>0.1769746636734653</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.04098908838506676</v>
+        <v>-0.05007097362701063</v>
       </c>
     </row>
     <row r="21">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1736710925239742</v>
+        <v>0.1502234961546411</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.03567812833776329</v>
+        <v>-0.04840290256911794</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1648323183263838</v>
+        <v>0.1316256298894252</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.03286878885414235</v>
+        <v>-0.04522738525414327</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1628251345711269</v>
+        <v>0.1309479275927459</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.03148832137410451</v>
+        <v>-0.04329315853410576</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.152757092330881</v>
+        <v>0.1246480412061512</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.03065067385399456</v>
+        <v>-0.04299399268026804</v>
       </c>
     </row>
     <row r="25">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.1454689932276994</v>
+        <v>0.1226474756771712</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.03021294412378539</v>
+        <v>-0.04036070264747738</v>
       </c>
     </row>
     <row r="26">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.1214527061041539</v>
+        <v>0.1114890143668859</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.02945351010353292</v>
+        <v>-0.038765319719821</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3194625597125427</v>
+        <v>0.3587062983637059</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.3565535033347771</v>
+        <v>-0.3412062080727857</v>
       </c>
     </row>
     <row r="32">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2143072205995868</v>
+        <v>0.2449056253897566</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.2640461121439773</v>
+        <v>-0.2497278011989613</v>
       </c>
     </row>
     <row r="33">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2135335737595909</v>
+        <v>0.224071285817685</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.2083553731659464</v>
+        <v>-0.2130161300266236</v>
       </c>
     </row>
     <row r="34">
@@ -5248,21 +5248,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.195517833747145</v>
+        <v>0.2226489567263978</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1199278321003493</v>
+        <v>-0.13380340873604</v>
       </c>
     </row>
     <row r="35">
@@ -5293,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1899883913110376</v>
+        <v>0.2117376494967731</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1091113144646929</v>
+        <v>-0.1305896748963186</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1874742130713498</v>
+        <v>0.1536581228730449</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.1056551247402403</v>
+        <v>-0.1284567417271874</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1773528235249215</v>
+        <v>0.1490582211977725</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.1034278994011091</v>
+        <v>-0.1040678784364861</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1579130290056037</v>
+        <v>0.1371447510800847</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.09591007939751295</v>
+        <v>-0.1029763036259287</v>
       </c>
     </row>
     <row r="39">
@@ -5473,12 +5473,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1554102164580851</v>
+        <v>0.1257254583887788</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.07230708618617632</v>
+        <v>-0.09966081033777352</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1389802848941604</v>
+        <v>0.1132698534181711</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.07062593009241236</v>
+        <v>-0.09109365879575426</v>
       </c>
     </row>
     <row r="41"/>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5988244309135209</v>
+        <v>0.5331448524710878</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1689817712618231</v>
+        <v>-0.2000335682506748</v>
       </c>
     </row>
     <row r="46">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5960963983369636</v>
+        <v>0.5288407992801922</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1624954325774725</v>
+        <v>-0.1913875873514074</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5362472997444092</v>
+        <v>0.4882729070178737</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1496028552272287</v>
+        <v>-0.1827520617938825</v>
       </c>
     </row>
     <row r="48">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.383285712843749</v>
+        <v>0.3484711264598097</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1350909146395597</v>
+        <v>-0.1479999889026988</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.3697615758326191</v>
+        <v>0.3416836313072191</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.1177282096980724</v>
+        <v>-0.1379400831182362</v>
       </c>
     </row>
     <row r="50">
@@ -5849,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3485426265809966</v>
+        <v>0.3086164437159893</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.1161924977529548</v>
+        <v>-0.1242412540400673</v>
       </c>
     </row>
     <row r="51">
@@ -5894,21 +5894,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.2816901953744504</v>
+        <v>0.3019481008488767</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.1046464723780145</v>
+        <v>-0.1236442628862823</v>
       </c>
     </row>
     <row r="52">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2770629853733622</v>
+        <v>0.2841359016334368</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.1033565586799418</v>
+        <v>-0.1086305357619672</v>
       </c>
     </row>
     <row r="53">
@@ -5984,21 +5984,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2697040666525496</v>
+        <v>0.2797067291881183</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.09278649712595732</v>
+        <v>-0.09872936984154346</v>
       </c>
     </row>
     <row r="54">
@@ -6029,21 +6029,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.266480624123407</v>
+        <v>0.2649162818199591</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.08478811339361347</v>
+        <v>-0.09634983406127684</v>
       </c>
     </row>
     <row r="55"/>
@@ -6135,21 +6135,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.923462653161536</v>
+        <v>0.887096809110518</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1994667481644347</v>
+        <v>-0.2219631509786856</v>
       </c>
     </row>
     <row r="60">
@@ -6180,21 +6180,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.9144810780686863</v>
+        <v>0.8840347128359942</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1976549001672258</v>
+        <v>-0.2103865540395649</v>
       </c>
     </row>
     <row r="61">
@@ -6225,21 +6225,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.8482676796351563</v>
+        <v>0.8398480098440948</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1391235799262603</v>
+        <v>-0.1603067890115963</v>
       </c>
     </row>
     <row r="62">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.8168475521495351</v>
+        <v>0.8269100241973946</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1154259862318505</v>
+        <v>-0.1434977114381563</v>
       </c>
     </row>
     <row r="63">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.7897597987467058</v>
+        <v>0.8084506106611833</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1117135736789118</v>
+        <v>-0.1227020224249226</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.7063862443904645</v>
+        <v>0.6908286593200013</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.0912972511690463</v>
+        <v>-0.1111842391412462</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.6999386790725202</v>
+        <v>0.6559578265824006</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06073994766337687</v>
+        <v>-0.0718636065184215</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.6987110495995432</v>
+        <v>0.6426254778837703</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.03355906919615059</v>
+        <v>-0.03962455717423252</v>
       </c>
     </row>
     <row r="67">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.6204500785702178</v>
+        <v>0.5852274392098655</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.004950844075900296</v>
+        <v>-0.01757715727695175</v>
       </c>
     </row>
     <row r="68">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.5707686660196767</v>
+        <v>0.5480386873949172</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.01321256395133674</v>
+        <v>-0.01162312329420756</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.853722750828505</v>
+        <v>2.765135603970966</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1782666368817573</v>
+        <v>-0.1930257949151184</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.6116842591124</v>
+        <v>2.537876723613505</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.01473898161166187</v>
+        <v>0.004868061355520759</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.487313996537913</v>
+        <v>2.370960592145052</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.06243510950264519</v>
+        <v>0.04749668512496052</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>2.16359932298873</v>
+        <v>2.249999926414021</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.1048382814992959</v>
+        <v>0.05907281879766013</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.602476911986245</v>
+        <v>1.472291291144035</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6848,21 +6848,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1207766858367583</v>
+        <v>0.08523621694307493</v>
       </c>
     </row>
     <row r="78">
@@ -6871,21 +6871,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.3089665722165</v>
+        <v>1.258913932041123</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.125611084726037</v>
+        <v>0.122405321100701</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.293841134324624</v>
+        <v>1.224316359055333</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6938,21 +6938,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1287405672710737</v>
+        <v>0.1396383012869169</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.276824243299484</v>
+        <v>1.215598278649114</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.163099361553233</v>
+        <v>0.1458845153142456</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.222486343295206</v>
+        <v>1.110026661742447</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,21 +7028,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.180595965582556</v>
+        <v>0.1770733840633811</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.165100394412779</v>
+        <v>1.091995296912629</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,21 +7073,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1934463601443803</v>
+        <v>0.1965024612062771</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -491,9 +491,9 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>15.8</v>
+        <v>16.58</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.02100839066937898</v>
+        <v>0.04969926202091535</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.04845672195445694</v>
+        <v>0.1009295791326441</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.1429088585442873</v>
+        <v>0.1838628909834843</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.1769746636734653</v>
+        <v>0.2354694358753515</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.2117376494967731</v>
+        <v>0.2812983354992451</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.3086164437159893</v>
+        <v>0.3567921081344905</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.6911134709047653</v>
+        <v>0.7924324241844383</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.887096809110518</v>
+        <v>1.067331543311319</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.249999926414021</v>
+        <v>2.411522524324826</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4812480230242917</v>
+        <v>0.5053913434059478</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>39.67</v>
+        <v>40.2</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.01044319574479546</v>
+        <v>0.01336028783608678</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.04363552057053455</v>
+        <v>-0.01058332005590878</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.1025569392344587</v>
+        <v>-0.01349691379289686</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.2270335886848038</v>
+        <v>0.2434271106141792</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3587062983637059</v>
+        <v>0.4075838531202307</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2797067291881183</v>
+        <v>0.3060338163493836</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4974458072821419</v>
+        <v>0.5558245005926878</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.8084506106611833</v>
+        <v>0.8171940409589018</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.8034913247561903</v>
+        <v>0.8275864879648183</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2172263705183965</v>
+        <v>0.2226232383910636</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>163.4</v>
+        <v>165.37</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.005538423978365348</v>
+        <v>0.01205631147055697</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.03370793614012024</v>
+        <v>-0.01793458212130972</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.02054833098239395</v>
+        <v>-0.02465354089845873</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.1114890143668859</v>
+        <v>0.1248894721201954</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.224071285817685</v>
+        <v>0.2956506285933507</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2841359016334368</v>
+        <v>0.30803894418497</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.3692240279363803</v>
+        <v>0.4019919518325965</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.8269100241973946</v>
+        <v>0.7886184282512805</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.026776678496459</v>
+        <v>1.051212129413673</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2655188919386098</v>
+        <v>0.2705844189401536</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>545.22</v>
+        <v>71.47</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.02049841740401626</v>
+        <v>0.01954354887878917</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.01907098787631545</v>
+        <v>-0.01840401569595251</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.04308764586863023</v>
+        <v>-0.03497159631745206</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.008676560324226035</v>
+        <v>0.05010290603042789</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.1029763036259287</v>
+        <v>0.2843653732659497</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.3416836313072191</v>
+        <v>0.244301945768415</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5495140164495547</v>
+        <v>0.3630825515705862</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8840347128359942</v>
+        <v>0.5100862732252522</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.537876723613505</v>
+        <v>0.6780755859111898</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5237518011583417</v>
+        <v>0.1883303057312902</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>192.72</v>
+        <v>213.8</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.01989836141638968</v>
+        <v>0.01413526052561109</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.05467085714848774</v>
+        <v>-0.006644021298924718</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.0397625836228539</v>
+        <v>-0.01456491318363973</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.08635855609531884</v>
+        <v>0.146934171190169</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1536581228730449</v>
+        <v>0.3016988438868702</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.2649162818199591</v>
+        <v>0.2303717916070285</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.4499736010417688</v>
+        <v>0.2659125181587148</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4825786620435926</v>
+        <v>0.5265590454438931</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.3577888961036169</v>
+        <v>0.6583139461325982</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1073308962520023</v>
+        <v>0.18364713444235</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>70.09999999999999</v>
+        <v>550.48</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.007363413370670036</v>
+        <v>0.009647500180232971</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.0471659811757108</v>
+        <v>-0.009518395877060382</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.03243614317609866</v>
+        <v>-0.01861228474557386</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.02997356727453715</v>
+        <v>0.01840776762175067</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2226489567263978</v>
+        <v>-0.1292767255553585</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2251325766780652</v>
+        <v>0.3545607928998029</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3088623578319443</v>
+        <v>0.5363015306353625</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4861318683167188</v>
+        <v>0.9275091582215409</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.6459086889977386</v>
+        <v>2.572008036267961</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1806882628921627</v>
+        <v>0.5286362085435738</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>210.82</v>
+        <v>193.16</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.008466894267505465</v>
+        <v>0.002283117676521673</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.02578552093182973</v>
+        <v>0.047164678692317</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.03566520855127853</v>
+        <v>0.03665540580656157</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.1309479275927459</v>
+        <v>0.08883884051778046</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2449056253897566</v>
+        <v>0.1495808761924273</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2031914185820416</v>
+        <v>0.2214016465031587</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.2417370243949832</v>
+        <v>0.4754574973597461</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5291313901080761</v>
+        <v>0.4687375056880663</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6351995815040408</v>
+        <v>0.3608887416320063</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1781219722756464</v>
+        <v>0.1081729382561345</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>111.85</v>
+        <v>436.58</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.0437719303509404</v>
+        <v>0.02272297033944226</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.034785847567953</v>
+        <v>0.07829475722968415</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.02975364626558075</v>
+        <v>0.04272847220268416</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.04738269046927246</v>
+        <v>0.1345338981370645</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.06523808070591519</v>
+        <v>0.0142408507176115</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.5288407992801922</v>
+        <v>0.104063916897229</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.3559354906913332</v>
+        <v>0.5203590022576066</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.3263714018301793</v>
+        <v>0.7436411626157104</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.110026661742447</v>
+        <v>0.3147174137241147</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2826140146650482</v>
+        <v>0.09549602256443945</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>426.88</v>
+        <v>109.38</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.005359028454772985</v>
+        <v>-0.0220831582869857</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.05223200550638829</v>
+        <v>-0.00209837930529011</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01519659158800857</v>
+        <v>-0.02591507381230218</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.1093267004265213</v>
+        <v>0.02425317272859062</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.01495520245295756</v>
+        <v>0.03805631965750345</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.07534575300434443</v>
+        <v>0.4644529880585526</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.4821655419921176</v>
+        <v>0.314684815139606</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.6908286593200013</v>
+        <v>0.3153167212457799</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2855068790405277</v>
+        <v>1.063430757473046</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.08732189913170463</v>
+        <v>0.2731022918054198</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>96.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.03944088384877387</v>
+        <v>0.007395827856438553</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.04044990158774087</v>
+        <v>-0.05903285886123344</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.0127258360231437</v>
+        <v>0.01835073367674256</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.04758788010510173</v>
+        <v>0.1399949382460211</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.02265238779525358</v>
+        <v>-0.03688342628807351</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.5331448524710878</v>
+        <v>-0.03626594030534103</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.3286946277395031</v>
+        <v>0.4280062758543757</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.3223537850937013</v>
+        <v>0.840889273070164</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.06343615881672</v>
+        <v>1.490575931944308</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2731034026507091</v>
+        <v>0.355501270479667</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>89.23999999999999</v>
+        <v>152.22</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.03898344521633024</v>
+        <v>0.002983391275576119</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.07350500263171345</v>
+        <v>0.00172931596225312</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.04288884167388041</v>
+        <v>0.004903603594619499</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.1316256298894252</v>
+        <v>0.05031947334486397</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.005737750763619598</v>
+        <v>-0.08822400936482877</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>-0.06433373745751181</v>
+        <v>0.2774861111537961</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.4129328515752897</v>
+        <v>0.4359307666498595</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.8398480098440948</v>
+        <v>0.5680083680989021</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.472291291144035</v>
+        <v>1.265652898883488</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3521759679475669</v>
+        <v>0.3134023591534538</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>151.77</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.004917387745808077</v>
+        <v>-0.02765068728792142</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.001250345044824908</v>
+        <v>-0.00128125925571132</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.002179092879917022</v>
+        <v>-0.02093364015945864</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.04719528008244156</v>
+        <v>0.01862135522569908</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-0.06504887569728424</v>
+        <v>-0.007416883087548953</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2634604394343898</v>
+        <v>0.4792307935928624</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4424291063149859</v>
+        <v>0.2836666758802304</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.5478035174470266</v>
+        <v>0.3001889548879484</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.258913932041123</v>
+        <v>1.006380730850689</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.312098869558711</v>
+        <v>0.2612594970426476</v>
       </c>
     </row>
     <row r="14">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>472.93</v>
+        <v>27.44</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.02516803727580452</v>
+        <v>-0.0171919606348383</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.03666510555179614</v>
+        <v>-0.001455568007460606</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.08654923012284366</v>
+        <v>-0.01472171783828435</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.02982749401709106</v>
+        <v>0.09062005963724284</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>-0.2130161300266236</v>
+        <v>0.07020285441722307</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.3484711264598097</v>
+        <v>0.4503171471145455</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4921420951075131</v>
+        <v>0.2098765504776277</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6559578265824006</v>
+        <v>0.2233615764920773</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.224316359055333</v>
+        <v>0.3288136097317085</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.305365665120976</v>
+        <v>0.09939735853094511</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>27.92</v>
+        <v>110.26</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.03122830076545435</v>
+        <v>0.01769436506449851</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.01601166453374003</v>
+        <v>0.01525787599760831</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.006126128875457493</v>
+        <v>0.03333652237743667</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.1096979429896825</v>
+        <v>0.04528820890421481</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.05837759531917253</v>
+        <v>-0.02917140018972386</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.4882729070178737</v>
+        <v>0.09664812791096411</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2392365390757987</v>
+        <v>0.3777504398062899</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.2181500865338775</v>
+        <v>0.6022508846047454</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.3520581400514864</v>
+        <v>0.7431585163763001</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1057708127675674</v>
+        <v>0.2034987051327517</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>31.86</v>
+        <v>57.65</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.02115384074592974</v>
+        <v>0.003830771713983383</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.0432219926409072</v>
+        <v>0.004180485614086127</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.03643464045454214</v>
+        <v>0.02035400930759135</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.08551959782823504</v>
+        <v>0.02252572603234482</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.09285310424339688</v>
+        <v>0.1554439948511699</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1525080055133874</v>
+        <v>0.2583937732973016</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.3100222511738098</v>
+        <v>0.1999777037905699</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.356125763214781</v>
+        <v>0.2309085839992004</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.273158842187083</v>
+        <v>0.2010857980758913</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.08382924029929906</v>
+        <v>0.06297898162607107</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>57.43</v>
+        <v>477.1</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.01269619524469823</v>
+        <v>0.008817401079049603</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.007543865003083905</v>
+        <v>-0.02773529291956234</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.01682012695890744</v>
+        <v>-0.05205639245958105</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.0186236115141607</v>
+        <v>-0.02127309391597298</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1371447510800847</v>
+        <v>-0.2543047390550509</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.2497877924344776</v>
+        <v>0.3415209554982268</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1899960193637875</v>
+        <v>0.4688370804763946</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2293267194077908</v>
+        <v>0.6907646427422343</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1965024612062771</v>
+        <v>1.243928887481634</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.06162515075603148</v>
+        <v>0.3091910565157479</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>108.34</v>
+        <v>31.95</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.003055218916151237</v>
+        <v>0.002824863492270291</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.005233746258857752</v>
+        <v>0.04411765897516906</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.01546530938913926</v>
+        <v>0.02865425989375714</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.02711407745484329</v>
+        <v>0.08858604251028401</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.02947237298643401</v>
+        <v>0.09073215721022643</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.07182424194026349</v>
+        <v>0.1267182939586222</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.3571349998743247</v>
+        <v>0.3380610793536984</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.5480386873949172</v>
+        <v>0.3426643054288006</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7128509172066892</v>
+        <v>0.2767553421202382</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1964829700257331</v>
+        <v>0.08484883737787086</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>55.86</v>
+        <v>98.69</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.004856996888335186</v>
+        <v>0.04666456128068952</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.02288958040705569</v>
+        <v>-0.01927849413655658</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.009943938228252236</v>
+        <v>0.02941482855986211</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.02890820818294393</v>
+        <v>0.3381695246292373</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.09061510414098706</v>
+        <v>0.07349672652070116</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1149988014993593</v>
+        <v>-0.1552601666271142</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2406616121320353</v>
+        <v>0.2954226516119658</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2415959491215225</v>
+        <v>0.6706813574220807</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.7027846575741334</v>
+        <v>2.940834305239044</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1941344917357091</v>
+        <v>0.5795355021424335</v>
       </c>
     </row>
     <row r="20">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>94.29000000000001</v>
+        <v>97.63</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.03736596372380518</v>
+        <v>0.03126649563455497</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.08278211949026737</v>
+        <v>-0.04676821910918283</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.0772306892551835</v>
+        <v>0.003082250248839236</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.2785084869902013</v>
+        <v>0.3175438497143095</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.03202577112717875</v>
+        <v>0.1088017475255374</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.2000335682506748</v>
+        <v>-0.1535460347388159</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2224483271674043</v>
+        <v>0.2049878630743098</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.6426254778837703</v>
+        <v>0.5175779820865787</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>2.765135603970966</v>
+        <v>2.476358716783612</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.5557036622576663</v>
+        <v>0.5148682428207703</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>94.67</v>
+        <v>55.79</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.03898085355814707</v>
+        <v>-0.001253127355162365</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.1028240979842188</v>
+        <v>0.005587623933828834</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.06430580569925648</v>
+        <v>0.01621128169238584</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.2775978423536425</v>
+        <v>0.02761885516131879</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.09217810147253114</v>
+        <v>0.07809363741073483</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>-0.1827520617938825</v>
+        <v>0.1000725031706504</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1513832277144378</v>
+        <v>0.2527608037774149</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.5095387626758376</v>
+        <v>0.2474686220359641</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>2.370960592145052</v>
+        <v>0.7006504560238958</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.4994013303015234</v>
+        <v>0.1936353898375283</v>
       </c>
     </row>
     <row r="22">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>132.67</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.000150759455067262</v>
+        <v>0.0223078360770752</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.01885817947594715</v>
+        <v>-0.004558916049041684</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.001585319677144037</v>
+        <v>-0.01013336181640623</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.01747760224903006</v>
+        <v>-0.0239284742735123</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1490582211977725</v>
+        <v>0.0738304248449968</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.06237294862081022</v>
+        <v>0.1084394647796998</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0916962683374769</v>
+        <v>0.19339467026087</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1145611652906096</v>
+        <v>0.1684574363974549</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6729561624141074</v>
+        <v>0.7700729727841857</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1871206337378382</v>
+        <v>0.2096611242323083</v>
       </c>
     </row>
     <row r="23">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>143.82</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.0008336467635975398</v>
+        <v>0.02091115145175015</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.01039010863421919</v>
+        <v>-0.005094592280473931</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.008069509101442662</v>
+        <v>-0.01114010766585238</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.02269635943717097</v>
+        <v>-0.0186647957398075</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.1257254583887788</v>
+        <v>0.08181771032422103</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.07240891356421386</v>
+        <v>0.116796055972372</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1011366065827151</v>
+        <v>0.1766095494963524</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1125006403254671</v>
+        <v>0.1554341810646078</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.6591223859116471</v>
+        <v>0.8610015078049706</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1838394486444668</v>
+        <v>0.2300296350418083</v>
       </c>
     </row>
     <row r="24">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>72.62</v>
+        <v>133.36</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.01277861396424018</v>
+        <v>0.005200892823768566</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.0230055030586348</v>
+        <v>-0.01630159028155764</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.05504223567373911</v>
+        <v>0.003461299736593482</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.04522738525414327</v>
+        <v>-0.0123676085613752</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.06931203497849237</v>
+        <v>0.1535420326941228</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1003283836305031</v>
+        <v>0.05777560679355354</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.160937456072793</v>
+        <v>0.1009361170600751</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1354581989354657</v>
+        <v>0.1183323722666942</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7314479546439516</v>
+        <v>0.681657189899106</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2007976073836559</v>
+        <v>0.1891751433451923</v>
       </c>
     </row>
     <row r="25">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>66.95</v>
+        <v>144.79</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01268250466472065</v>
+        <v>0.006744443836158354</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.02177097369977021</v>
+        <v>-0.009779838070250513</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.05169973944428397</v>
+        <v>0.003395635648041129</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.038765319719821</v>
+        <v>-0.01610498992252196</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.07643601346000417</v>
+        <v>0.1247155010417504</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1089724293293519</v>
+        <v>0.07187164050195305</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1457275567200924</v>
+        <v>0.1124754208526837</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.122870713956815</v>
+        <v>0.1245767411256224</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8228831161762968</v>
+        <v>0.6703123906707464</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2215735130180485</v>
+        <v>0.1864949686716206</v>
       </c>
     </row>
     <row r="26">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>74.70999999999999</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.02173633105157469</v>
+        <v>-0.006023249280640353</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.02454625072867245</v>
+        <v>-0.02186506945140909</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.009321838323413267</v>
+        <v>-0.004157135039056015</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.07931230521457322</v>
+        <v>0.0728113381486033</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.1284567417271874</v>
+        <v>-0.1368146164084919</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>-0.004891912303892632</v>
+        <v>-0.00851876268967533</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1938256599778958</v>
+        <v>0.1906023531791992</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.5852274392098655</v>
+        <v>0.5975590030289653</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.2921638298890086</v>
+        <v>0.2843807202893318</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.08919555432629078</v>
+        <v>0.08700429294416545</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>94.33</v>
+        <v>119.46</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.005972114834555509</v>
+        <v>0.03187356438113231</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.0249120951615962</v>
+        <v>-0.007065069332306551</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.0007415221789486282</v>
+        <v>0.02041513108293014</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.01852043250434809</v>
+        <v>0.1868852188120174</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.07892377980779064</v>
+        <v>-0.1000397622952742</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.05892816858681993</v>
+        <v>-0.02002452276153754</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1073465019323001</v>
+        <v>0.2397795076357809</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.137638353839127</v>
+        <v>0.4704032469736874</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.4380734502500632</v>
+        <v>1.286217293026362</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1287394119258278</v>
+        <v>0.3173641333946438</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2048,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>191.39</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.01583792776120363</v>
+        <v>-0.003922429125409188</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.02739099208804097</v>
+        <v>-0.02338634259859507</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.005199608849264514</v>
+        <v>-0.01406090161988127</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.02754217241547385</v>
+        <v>-0.02237021654588711</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.04352606981735585</v>
+        <v>0.07493632048442778</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1289475792261048</v>
+        <v>0.04845360324478087</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.1116455825441227</v>
+        <v>0.1030030137612008</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1118377337858594</v>
+        <v>0.1526221996522346</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.08706168960691</v>
+        <v>0.4324328756722202</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2779438198350019</v>
+        <v>0.1272617217258167</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>115.77</v>
+        <v>190.82</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.019977995980892</v>
+        <v>-0.002978170579692851</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.04274851739683605</v>
+        <v>-0.02123512129195038</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.01883304973488475</v>
+        <v>0.003365310090891693</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.1502234961546411</v>
+        <v>0.02448197654819251</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.09109365879575426</v>
+        <v>0.05029993680015621</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>-0.02873072233512153</v>
+        <v>0.1170774143854139</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.211390831761769</v>
+        <v>0.1083348141464999</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.4113104203879236</v>
+        <v>0.1229028147322326</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.215598278649114</v>
+        <v>1.080846237004466</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.3036579968504807</v>
+        <v>0.2766739488429166</v>
       </c>
     </row>
     <row r="30">
@@ -2174,37 +2174,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>75.08</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.005625477475813101</v>
+        <v>0.006126785738601148</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01210523906506988</v>
+        <v>-0.003035445924889135</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.008597519729425018</v>
+        <v>0.006260839517967076</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.004817995241839235</v>
+        <v>0.01097429980497666</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.07543344316556366</v>
+        <v>0.08186822294364893</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.02297790768707175</v>
+        <v>-0.005851823291624259</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1093525898401695</v>
+        <v>0.1313807417591584</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.09663309347387106</v>
+        <v>0.1022549227633958</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2495867306852904</v>
+        <v>0.2572426010242386</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.0770986170308201</v>
+        <v>0.07929383450117622</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>82.93000000000001</v>
+        <v>65.23</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.02595723632036284</v>
+        <v>0.008971412488250508</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.0500573034801749</v>
+        <v>-0.04242512144927135</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.03771176593747139</v>
+        <v>-0.04172170340271897</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.02308869240858613</v>
+        <v>-0.02452518801088677</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.02065438963442345</v>
+        <v>0.03878494450619563</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.01954418505881761</v>
+        <v>0.07501614442876381</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1469346160384069</v>
+        <v>0.1037912705256077</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1749107748640586</v>
+        <v>0.1105546390949121</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3708645590657016</v>
+        <v>0.6206159792177859</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1108741211442541</v>
+        <v>0.1746091300994219</v>
       </c>
     </row>
     <row r="32">
@@ -2286,37 +2286,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>233.2</v>
+        <v>237.1</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.01345294808732589</v>
+        <v>0.01672388167371652</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.0309578106677485</v>
+        <v>-0.01426014506792772</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.006908423154408094</v>
+        <v>0.007564162518677975</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.04634989930171196</v>
+        <v>0.06384893120693902</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.01100429215552889</v>
+        <v>0.01432767031533633</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.03788389282515359</v>
+        <v>-0.01966532214842542</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1635628163482648</v>
+        <v>0.1921991469859821</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1359733740776485</v>
+        <v>0.1640779307972855</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3272392164709372</v>
+        <v>0.3494356908892731</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.09896299416762955</v>
+        <v>0.1050554331272677</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>106.18</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.03455176337306631</v>
+        <v>0.004702753987860575</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.04251351886033539</v>
+        <v>-0.04471453188827945</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.04138879225770586</v>
+        <v>-0.0377641388308444</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.1226474756771712</v>
+        <v>-0.0184945188610246</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.01392841676746626</v>
+        <v>-0.006089736355634146</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.3019481008488767</v>
+        <v>0.02221387089270976</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.02046611164336154</v>
+        <v>0.1433808791084306</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.01757715727695175</v>
+        <v>0.1929815113257618</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.4680254727889628</v>
+        <v>0.3773114846887253</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1365220442021109</v>
+        <v>0.1126128110997744</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>64.65000000000001</v>
+        <v>287.39</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.0110142449204772</v>
+        <v>0.0008706553849908705</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.06004648628550313</v>
+        <v>-0.002983470430398927</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.04617877411904014</v>
+        <v>0.003842279055096709</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.0331987607225962</v>
+        <v>0.04585321777249329</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.01597621596981358</v>
+        <v>0.005422678178020224</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.05215213769727844</v>
+        <v>0.1852112327293227</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.09730363863460112</v>
+        <v>0.0579811483973891</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.09254053171744325</v>
+        <v>0.04948151654891042</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.6062057378158512</v>
+        <v>0.6815283394213141</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.171117285118642</v>
+        <v>0.1891447705875082</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>96.3</v>
+        <v>64.13</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.00145167343534125</v>
+        <v>0.003736122538418707</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.02972289116616811</v>
+        <v>0.009265019394679497</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.01352181579272116</v>
+        <v>0.01421320133825099</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.02678114177073199</v>
+        <v>0.06261312142115338</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.03250920361576015</v>
+        <v>-0.0003886430139099506</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.026097779078464</v>
+        <v>0.208955051070598</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.09738822618680398</v>
+        <v>0.05208442332523422</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.08444864858827539</v>
+        <v>0.02361961068371721</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3142161567501167</v>
+        <v>0.8613821766549639</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.09535677975887369</v>
+        <v>0.2301134970631369</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>63.89</v>
+        <v>103.38</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.005293538058774749</v>
+        <v>0.006523202949250129</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.004717710903297423</v>
+        <v>-0.0412687053887737</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.01541642162955248</v>
+        <v>-0.04011141891582692</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.05865784598230506</v>
+        <v>-0.0512985583616119</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.001931494055822824</v>
+        <v>-0.07355053555076785</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.2051365224354085</v>
+        <v>0.0143459848018288</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.05144545358094188</v>
+        <v>0.1797985076621647</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.01607982027419097</v>
+        <v>0.2177284140071871</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.8544537103512664</v>
+        <v>0.3114049706753383</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.2285853501284278</v>
+        <v>0.09457521124484924</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>287.14</v>
+        <v>95.78</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.01829114077254579</v>
+        <v>-0.005399836510715961</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.001425745650966315</v>
+        <v>-0.02869893330836881</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.0119114912830891</v>
+        <v>-0.02869893330836881</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0.04494343214628449</v>
+        <v>-0.03203636449431568</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.009041948608804584</v>
+        <v>0.02226203542587979</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.1794134836523946</v>
+        <v>0.01800381639649262</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.06585011564168641</v>
+        <v>0.0953445694612558</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.03836840818709386</v>
+        <v>0.0967853480708567</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.6800655812758387</v>
+        <v>0.3071197404601087</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.188799859001554</v>
+        <v>0.09338167577020884</v>
       </c>
     </row>
     <row r="38">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>102.71</v>
+        <v>54.28</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.02764364522267204</v>
+        <v>0.006676569409805655</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.0471286927164587</v>
+        <v>-0.03433553347466467</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.05170343089604079</v>
+        <v>-0.0440295888296417</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.05744702272281099</v>
+        <v>-0.03690563890222276</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.08552949319805758</v>
+        <v>-0.04420489296019836</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.007082806317664891</v>
+        <v>-0.01796666055649665</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1888780982690961</v>
+        <v>0.1418824110794847</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.2019702898525493</v>
+        <v>0.1869436974060901</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.3029057252864018</v>
+        <v>0.699967103791391</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.09220542871102833</v>
+        <v>0.1934754936282588</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>175.47</v>
+        <v>23.34</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.01636862032028663</v>
+        <v>-0.002146195381655613</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.0219608849059868</v>
+        <v>-0.02425586093068244</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.04511315593136034</v>
+        <v>-0.02831809174934363</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.02163370365637496</v>
+        <v>-0.01644330673333461</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.08890777335931177</v>
+        <v>-0.1053077195795974</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>-0.008812308322446394</v>
+        <v>-0.04512668240281625</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1705195566488473</v>
+        <v>0.1778408456506591</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.2381591016295708</v>
+        <v>0.2982217210445501</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.7929329336461668</v>
+        <v>0.5399043787149045</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.2148463361122466</v>
+        <v>0.1547764486077652</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>23.39</v>
+        <v>175.53</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.01015657129250525</v>
+        <v>0.0003419248770522021</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.02582260863486352</v>
+        <v>-0.02930931260349978</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.0282509478104398</v>
+        <v>-0.03966517150902393</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.01432786174237943</v>
+        <v>-0.02129917588078556</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.1040678784364861</v>
+        <v>-0.1075646194307903</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>-0.04072652330895832</v>
+        <v>-0.001285601695105054</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1947544620022732</v>
+        <v>0.1648228291841252</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.2757514760286375</v>
+        <v>0.2604558577687122</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.5432165197751146</v>
+        <v>0.7935459820190667</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.1556037821328513</v>
+        <v>0.2149847823954065</v>
       </c>
     </row>
     <row r="41">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2790,37 +2790,37 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>53.92</v>
+        <v>58.63</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.01425964502952271</v>
+        <v>0.004110321647123438</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.03073886151963467</v>
+        <v>-0.0257560523296847</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.05915203495223775</v>
+        <v>-0.03616637673379652</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.04329315853410576</v>
+        <v>-0.03202903477766994</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.03510979353589005</v>
+        <v>-0.03727205567040037</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>-0.01952167393520898</v>
+        <v>-0.02421219252325557</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1338361533904657</v>
+        <v>0.1283174026453402</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1691847430979714</v>
+        <v>0.1580859543064936</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.6886924315602654</v>
+        <v>0.5792633448728437</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1908311477077549</v>
+        <v>0.1645322453999587</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>58.39</v>
+        <v>103.42</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.005958499809622375</v>
+        <v>-0.02599361582499382</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.01964408926570727</v>
+        <v>0.01005956426835386</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.0448225360803397</v>
+        <v>0.005933281050842343</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.03599142011159795</v>
+        <v>0.09346580848751973</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.02395472282934874</v>
+        <v>-0.01232327533382038</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>-0.02498598781731565</v>
+        <v>0.2497208622454836</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.1164900174411128</v>
+        <v>-0.01692277891110405</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.1422597561287762</v>
+        <v>-0.03570994383977133</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.5727986365903002</v>
+        <v>0.4298661826279815</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1629410695434417</v>
+        <v>0.1265880276387767</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>13.35</v>
+        <v>28.33</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.01184306770551047</v>
+        <v>0.01577628338783432</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.002987301032667533</v>
+        <v>-0.04805108515382261</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.009833593934573726</v>
+        <v>-0.05282513981165271</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0.07661296711007903</v>
+        <v>-0.09430948523600602</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.06303715746007565</v>
+        <v>-0.005964914957682255</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.1150873574007887</v>
+        <v>0.02274365138680778</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>-0.001242089430010918</v>
+        <v>0.07174637447801069</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-0.0718636065184215</v>
+        <v>0.08724937691931101</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.1770733840633811</v>
+        <v>0.4868320515360296</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.05584746086376025</v>
+        <v>0.1413547174675709</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>225.46</v>
+        <v>13.34</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.01265600749902474</v>
+        <v>-0.000749080793714163</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.03772939062206426</v>
+        <v>-0.002243809515929285</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.1058851386440325</v>
+        <v>0.006033176645940497</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.05925059138471189</v>
+        <v>0.07580649701415321</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.0186669661545884</v>
+        <v>0.0697626042364361</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.07367181127407607</v>
+        <v>0.09524940014989602</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1331294186937346</v>
+        <v>-0.000617505035313104</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.1420563580763534</v>
+        <v>-0.06850898684132811</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.9791904174253179</v>
+        <v>0.176191364295825</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.2555360677509591</v>
+        <v>0.05558366789667546</v>
       </c>
     </row>
     <row r="45">
@@ -3014,37 +3014,37 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>85.92</v>
+        <v>86.38</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.002090595915978821</v>
+        <v>0.005353806963172447</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.02241439565802461</v>
+        <v>-0.02096799312169861</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.01388728477694501</v>
+        <v>-0.02758082322565258</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.04299399268026804</v>
+        <v>-0.0378703672544819</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.03342997406905823</v>
+        <v>0.03424585456649454</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.007379797668365717</v>
+        <v>0.007432058836457589</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.0220832746435411</v>
+        <v>0.03206700469097368</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.02874843210425659</v>
+        <v>0.03241690898800065</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.3788223543277842</v>
+        <v>0.3862040484703759</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1130194967903728</v>
+        <v>0.1150021914655597</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>71.25</v>
+        <v>48.48</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.006276108331873753</v>
+        <v>0.007690686493259991</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.01886536346415257</v>
+        <v>-0.001441806301219928</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.005503801669336505</v>
+        <v>0.0008257827551896302</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.009728936454934667</v>
+        <v>0.0161391840817342</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.07159036196559199</v>
+        <v>0.01980307104278012</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.08249001204007855</v>
+        <v>-0.03477764952441187</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.04808351107437514</v>
+        <v>0.08016741108708336</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-0.03962455717423252</v>
+        <v>0.0346148360392291</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.004868061355520759</v>
+        <v>0.1484027984044385</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.001620061103192461</v>
+        <v>0.04720429325185727</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>48.11</v>
+        <v>19.2</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.008595384504284098</v>
+        <v>0.005497358122473983</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.01231776812560759</v>
+        <v>-0.04137967737875425</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.0008321388762491111</v>
+        <v>-0.04689824876994941</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0.008384018728876619</v>
+        <v>-0.006980363382456889</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.007792568939519295</v>
+        <v>0.08441563616703673</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.05022498866415004</v>
+        <v>0.1333726922150458</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.06814923186492061</v>
+        <v>-0.07889690300560637</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.02780105833352087</v>
+        <v>-0.1151808343141028</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.1396383012869169</v>
+        <v>0.0648949213603689</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.04453343374279095</v>
+        <v>0.02117988587656261</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>27.89</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.02140353018777408</v>
+        <v>-0.0001291375411184292</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.07311401634374015</v>
+        <v>-0.01614700528631352</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.08014512960534748</v>
+        <v>-0.008478768780283308</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.1083759981643599</v>
+        <v>-0.009856817625121583</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.03594887329957197</v>
+        <v>0.0652613426685944</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.01968370327850766</v>
+        <v>-0.06080007982170466</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.07322277472981154</v>
+        <v>0.05005913957817598</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>0.06873572800608208</v>
+        <v>-0.02473456824615816</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.463739679545502</v>
+        <v>0.004738295164928852</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.1354149684351527</v>
+        <v>0.001576943663170516</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>19.1</v>
+        <v>223.37</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.03173473872098576</v>
+        <v>-0.009269988177247446</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.0565571948776975</v>
+        <v>-0.05503853751113519</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.04833080857518113</v>
+        <v>-0.09254519335424705</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.01240950202816049</v>
+        <v>-0.06797132728032818</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.07532942893472283</v>
+        <v>-0.02103623953394218</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.1163062361268539</v>
+        <v>-0.1073833798571413</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>-0.07393937544389206</v>
+        <v>0.1110817968787832</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.1434977114381563</v>
+        <v>0.1310135315759953</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.05907281879766013</v>
+        <v>0.9608434769813692</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01931545084562281</v>
+        <v>0.2516444441168573</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>252.04</v>
+        <v>112.42</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.01746450927572851</v>
+        <v>0.0138888974898479</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.04836704746903453</v>
+        <v>-0.001687260814993596</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.1321833156278207</v>
+        <v>0.009881409244849593</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.04840290256911794</v>
+        <v>0.03861788976046276</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.09966081033777352</v>
+        <v>-0.007550772797766503</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.1086305357619672</v>
+        <v>-0.04070466614306756</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.1251466573300055</v>
+        <v>-0.01554984940400972</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.1630971660474938</v>
+        <v>0.02368547401203314</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>1.091995296912629</v>
+        <v>0.7329921397918144</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.2789500049866638</v>
+        <v>0.2011544768778719</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>42.56</v>
+        <v>54.42</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.007814393431963884</v>
+        <v>0.002394497167539811</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.0173170163061348</v>
+        <v>-0.0175122085465198</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.03316672124693631</v>
+        <v>-0.03919493722856315</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.04036070264747738</v>
+        <v>0.03637402225223196</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.006223457291792633</v>
+        <v>0.1309876828615109</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.09634983406127684</v>
+        <v>-0.0852844090674969</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>-0.01809175250155892</v>
+        <v>-0.1356756287126859</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.03763898733174176</v>
+        <v>-0.1139004366000687</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.4871537475462031</v>
+        <v>0.0500049902535491</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1414370273202417</v>
+        <v>0.01639796699500962</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>54.29</v>
+        <v>250.21</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.01237038912270705</v>
+        <v>-0.007260699178753383</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.02548910774154167</v>
+        <v>-0.06165380670887743</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.02074310497236576</v>
+        <v>-0.119288978041416</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.03389835556829945</v>
+        <v>-0.05531216283293838</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.1132698534181711</v>
+        <v>-0.1038936106658203</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.09610969796856794</v>
+        <v>-0.1362579380296409</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.1438392185196125</v>
+        <v>0.1090646002605711</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.1227020224249226</v>
+        <v>0.1532203112333286</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.04749668512496052</v>
+        <v>1.076805948378379</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.0155879806839514</v>
+        <v>0.2758471260518707</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>110.88</v>
+        <v>42.67</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.005203676976662464</v>
+        <v>0.002584511092692976</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.02032163850111446</v>
+        <v>-0.01930591093983502</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.003620509452666232</v>
+        <v>-0.03066792991321432</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.02439023874493351</v>
+        <v>-0.03788050423848577</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.0384183714146864</v>
+        <v>-0.0218116968426082</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.05528838794085389</v>
+        <v>-0.08712907858395402</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.02582277038576264</v>
+        <v>-0.00849662444104482</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.007940133059838095</v>
+        <v>0.04378681549711683</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.7092525069386775</v>
+        <v>0.4909972135319352</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.1956445131031088</v>
+        <v>0.1424195082127104</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>44.44</v>
+        <v>26.8</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.00670547698933599</v>
+        <v>0.02110479445684521</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.0313862774167849</v>
+        <v>-0.02982479358515611</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.01354052432146868</v>
+        <v>0.005401388143445818</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.03454269378132224</v>
+        <v>0.04825972524034672</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-0.01855124061911329</v>
+        <v>0.03829733911581479</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.1236442628862823</v>
+        <v>0.08363747066517369</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.01663394738990154</v>
+        <v>-0.1022739025449896</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.01162312329420756</v>
+        <v>-0.190539605856079</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.2547880098416866</v>
+        <v>0.2424970829688795</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.0785909865700638</v>
+        <v>0.07505774572625268</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>19.04</v>
+        <v>44.69</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.01586805213242104</v>
+        <v>0.005738098019696602</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.04283125248043052</v>
+        <v>-0.02113447559817683</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.006729600181172746</v>
+        <v>-0.01769231439946772</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.00413194036390363</v>
+        <v>-0.02900280512440734</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.004184096244488567</v>
+        <v>-0.01444319297321806</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.03862099906276484</v>
+        <v>-0.1008851233556936</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.06293111160320741</v>
+        <v>-0.01203474182893027</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-0.2103865540395649</v>
+        <v>0.006225591042967604</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.1458845153142456</v>
+        <v>0.261988106436098</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.04643827664308775</v>
+        <v>0.08065007343166108</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>43.94</v>
+        <v>19.17</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.03449790711333356</v>
+        <v>0.006827686686747159</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.08724555081408203</v>
+        <v>-0.02063959031857321</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.007336077548372177</v>
+        <v>-0.01393960746154865</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.1246480412061512</v>
+        <v>0.002667534728630461</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.1305896748963186</v>
+        <v>0.007356772706092585</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.1913875873514074</v>
+        <v>0.05098685947619219</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.04157357758052793</v>
+        <v>-0.05949943283253034</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.1319782936567251</v>
+        <v>-0.1875935575575753</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>1.064611884443392</v>
+        <v>0.1537082557640066</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.2733451573387657</v>
+        <v>0.04881446110279142</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>17.24</v>
+        <v>35.19</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.003468177375051562</v>
+        <v>0.001137897556011014</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.02322945361322626</v>
+        <v>-0.01234921213067275</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.028184893261049</v>
+        <v>-0.0327103465219305</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.01766378800107027</v>
+        <v>-0.000851862378031476</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.2497278011989613</v>
+        <v>-0.133671330769584</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.0512473239091269</v>
+        <v>-0.07809379614292034</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.0526141411873462</v>
+        <v>0.00596358187861501</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.2106159475611487</v>
+        <v>0.06185044753853797</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.122405321100701</v>
+        <v>0.3281284710979335</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.03924171830756773</v>
+        <v>0.0992083756435036</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>26.25</v>
+        <v>17.37</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.02810177186602592</v>
+        <v>0.007540665304011318</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.05897115722419133</v>
+        <v>-0.01753390614205086</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>0.009615384615384581</v>
+        <v>-0.02579916356931999</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.02659367670283652</v>
+        <v>-0.01025631941037597</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.01145074438781213</v>
+        <v>-0.2666685080043432</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.07679811983457019</v>
+        <v>-0.04982965158025365</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.1240320078740984</v>
+        <v>0.04976844740744668</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.2219631509786856</v>
+        <v>0.2395570367577551</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.2168164224807103</v>
+        <v>0.1308690741767504</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.06759948138761196</v>
+        <v>0.04184739267431459</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>35.15</v>
+        <v>101.17</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.02061849753006584</v>
+        <v>0.006066036447506251</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.01952571765790989</v>
+        <v>-0.04556605500994992</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.03830363174842666</v>
+        <v>-0.06523149744997203</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.001987498364510842</v>
+        <v>-0.02430325212775408</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.13380340873604</v>
+        <v>-0.02879609144110673</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.09872936984154346</v>
+        <v>-0.1018759307657902</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.001969716345187722</v>
+        <v>-0.05961074191697935</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.05274016448104657</v>
+        <v>-0.09787933626557921</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.3266189146771643</v>
+        <v>0.2280568331330339</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.09879176280399227</v>
+        <v>0.07087674759830631</v>
       </c>
     </row>
     <row r="60">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>100.56</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.02188503115874185</v>
+        <v>0.004980501098232892</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.05470953041068272</v>
+        <v>-0.04614117743725099</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.05087304903162493</v>
+        <v>-0.06488013603473031</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.03018617811858204</v>
+        <v>-0.01611190059433909</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.02445891390065003</v>
+        <v>-0.0029761312080826</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.1242412540400673</v>
+        <v>-0.1125160511339908</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.06812165987550589</v>
+        <v>-0.09815010403135205</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1111842391412462</v>
+        <v>-0.1521419176692589</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2206524247647434</v>
+        <v>0.09064133488492465</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.06872017031955724</v>
+        <v>0.02934426949475788</v>
       </c>
     </row>
     <row r="61">
@@ -3896,51 +3896,51 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>92.36</v>
+        <v>44.32</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.02460662974949734</v>
+        <v>0.008648181155933132</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.05908723344920441</v>
+        <v>-0.07762746308972701</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.04071456396599193</v>
+        <v>-0.01532989674382823</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.02098787157514248</v>
+        <v>0.1343742012031675</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.005464118141478513</v>
+        <v>-0.1703481614758123</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.1379400831182362</v>
+        <v>-0.2148804411722669</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.1041780471485316</v>
+        <v>0.02597654445904651</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.1603067890115963</v>
+        <v>0.1431732714705201</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.08523621694307493</v>
+        <v>1.082467022036751</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.02764100754018251</v>
+        <v>0.2770053327740341</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>46.86</v>
+        <v>47.27</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.01492535398418149</v>
+        <v>0.008749463125733214</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.04073690738851832</v>
+        <v>-0.03095527591882752</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.06035689564871316</v>
+        <v>-0.06340401596080791</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.05007097362701063</v>
+        <v>-0.04175960463869643</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.3412062080727857</v>
+        <v>-0.3459249667434603</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1479999889026988</v>
+        <v>-0.1612845999671324</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.0163727705560458</v>
+        <v>-0.00755827424477129</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.1277978693331661</v>
+        <v>0.1534895311319979</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1930257949151184</v>
+        <v>-0.1859652038643103</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.06899241854661819</v>
+        <v>-0.06628502716665963</v>
       </c>
     </row>
   </sheetData>
@@ -4015,7 +4015,7 @@
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -4158,17 +4158,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.2785084869902013</v>
+        <v>0.3381695246292373</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1083759981643599</v>
+        <v>-0.09430948523600602</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.2775978423536425</v>
+        <v>0.3175438497143095</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.05925059138471189</v>
+        <v>-0.06797132728032818</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.2270335886848038</v>
+        <v>0.2434271106141792</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.05744702272281099</v>
+        <v>-0.05531216283293838</v>
       </c>
     </row>
     <row r="20">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1769746636734653</v>
+        <v>0.2354694358753515</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.05007097362701063</v>
+        <v>-0.0512985583616119</v>
       </c>
     </row>
     <row r="21">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1502234961546411</v>
+        <v>0.1868852188120174</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.04840290256911794</v>
+        <v>-0.04175960463869643</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1316256298894252</v>
+        <v>0.146934171190169</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.04522738525414327</v>
+        <v>-0.03788050423848577</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1309479275927459</v>
+        <v>0.1399949382460211</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.04329315853410576</v>
+        <v>-0.0378703672544819</v>
       </c>
     </row>
     <row r="24">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.1246480412061512</v>
+        <v>0.1345338981370645</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.04299399268026804</v>
+        <v>-0.03690563890222276</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.1226474756771712</v>
+        <v>0.1343742012031675</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.04036070264747738</v>
+        <v>-0.03203636449431568</v>
       </c>
     </row>
     <row r="26">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.1114890143668859</v>
+        <v>0.1248894721201954</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.038765319719821</v>
+        <v>-0.03202903477766994</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3587062983637059</v>
+        <v>0.4075838531202307</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.3412062080727857</v>
+        <v>-0.3459249667434603</v>
       </c>
     </row>
     <row r="32">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2449056253897566</v>
+        <v>0.3016988438868702</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.2497278011989613</v>
+        <v>-0.2666685080043432</v>
       </c>
     </row>
     <row r="33">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.224071285817685</v>
+        <v>0.2956506285933507</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.2130161300266236</v>
+        <v>-0.2543047390550509</v>
       </c>
     </row>
     <row r="34">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2226489567263978</v>
+        <v>0.2843653732659497</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.13380340873604</v>
+        <v>-0.1703481614758123</v>
       </c>
     </row>
     <row r="35">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2117376494967731</v>
+        <v>0.2812983354992451</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1305896748963186</v>
+        <v>-0.1368146164084919</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1536581228730449</v>
+        <v>0.1554439948511699</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.1284567417271874</v>
+        <v>-0.133671330769584</v>
       </c>
     </row>
     <row r="37">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1490582211977725</v>
+        <v>0.1535420326941228</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.1040678784364861</v>
+        <v>-0.1292767255553585</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1371447510800847</v>
+        <v>0.1495808761924273</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.1029763036259287</v>
+        <v>-0.1075646194307903</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1257254583887788</v>
+        <v>0.1309876828615109</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.09966081033777352</v>
+        <v>-0.1053077195795974</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1132698534181711</v>
+        <v>0.1247155010417504</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.09109365879575426</v>
+        <v>-0.1038936106658203</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5331448524710878</v>
+        <v>0.4792307935928624</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5646,21 +5646,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.2000335682506748</v>
+        <v>-0.2148804411722669</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5288407992801922</v>
+        <v>0.4644529880585526</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1913875873514074</v>
+        <v>-0.1612845999671324</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4882729070178737</v>
+        <v>0.4503171471145455</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5736,12 +5736,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1827520617938825</v>
+        <v>-0.1552601666271142</v>
       </c>
     </row>
     <row r="48">
@@ -5759,21 +5759,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3484711264598097</v>
+        <v>0.3567921081344905</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1479999889026988</v>
+        <v>-0.1535460347388159</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.3416836313072191</v>
+        <v>0.3545607928998029</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.1379400831182362</v>
+        <v>-0.1362579380296409</v>
       </c>
     </row>
     <row r="50">
@@ -5849,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3086164437159893</v>
+        <v>0.3415209554982268</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.1242412540400673</v>
+        <v>-0.1125160511339908</v>
       </c>
     </row>
     <row r="51">
@@ -5894,21 +5894,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3019481008488767</v>
+        <v>0.30803894418497</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.1236442628862823</v>
+        <v>-0.1073833798571413</v>
       </c>
     </row>
     <row r="52">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2841359016334368</v>
+        <v>0.3060338163493836</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.1086305357619672</v>
+        <v>-0.1018759307657902</v>
       </c>
     </row>
     <row r="53">
@@ -5984,21 +5984,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2797067291881183</v>
+        <v>0.2774861111537961</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.09872936984154346</v>
+        <v>-0.1008851233556936</v>
       </c>
     </row>
     <row r="54">
@@ -6029,21 +6029,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2649162818199591</v>
+        <v>0.2583937732973016</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.09634983406127684</v>
+        <v>-0.08712907858395402</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.887096809110518</v>
+        <v>1.067331543311319</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2219631509786856</v>
+        <v>-0.190539605856079</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8840347128359942</v>
+        <v>0.9275091582215409</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2103865540395649</v>
+        <v>-0.1875935575575753</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.8398480098440948</v>
+        <v>0.840889273070164</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1603067890115963</v>
+        <v>-0.1521419176692589</v>
       </c>
     </row>
     <row r="62">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.8269100241973946</v>
+        <v>0.8171940409589018</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1434977114381563</v>
+        <v>-0.1151808343141028</v>
       </c>
     </row>
     <row r="63">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.8084506106611833</v>
+        <v>0.7886184282512805</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1227020224249226</v>
+        <v>-0.1139004366000687</v>
       </c>
     </row>
     <row r="64">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.6908286593200013</v>
+        <v>0.7436411626157104</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1111842391412462</v>
+        <v>-0.09787933626557921</v>
       </c>
     </row>
     <row r="65">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.6559578265824006</v>
+        <v>0.6907646427422343</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.0718636065184215</v>
+        <v>-0.06850898684132811</v>
       </c>
     </row>
     <row r="66">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.6426254778837703</v>
+        <v>0.6706813574220807</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6472,21 +6472,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.03962455717423252</v>
+        <v>-0.03570994383977133</v>
       </c>
     </row>
     <row r="67">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5852274392098655</v>
+        <v>0.6022508846047454</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.01757715727695175</v>
+        <v>-0.02473456824615816</v>
       </c>
     </row>
     <row r="68">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.5480386873949172</v>
+        <v>0.5975590030289653</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.01162312329420756</v>
+        <v>0.006225591042967604</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.765135603970966</v>
+        <v>2.940834305239044</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1930257949151184</v>
+        <v>-0.1859652038643103</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.537876723613505</v>
+        <v>2.572008036267961</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.004868061355520759</v>
+        <v>0.004738295164928852</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.370960592145052</v>
+        <v>2.476358716783612</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.04749668512496052</v>
+        <v>0.0500049902535491</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>2.249999926414021</v>
+        <v>2.411522524324826</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.05907281879766013</v>
+        <v>0.0648949213603689</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.472291291144035</v>
+        <v>1.490575931944308</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.08523621694307493</v>
+        <v>0.09064133488492465</v>
       </c>
     </row>
     <row r="78">
@@ -6871,21 +6871,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.258913932041123</v>
+        <v>1.286217293026362</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.122405321100701</v>
+        <v>0.1308690741767504</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.224316359055333</v>
+        <v>1.265652898883488</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1396383012869169</v>
+        <v>0.1484027984044385</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.215598278649114</v>
+        <v>1.243928887481634</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1458845153142456</v>
+        <v>0.1537082557640066</v>
       </c>
     </row>
     <row r="81">
@@ -7006,21 +7006,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.110026661742447</v>
+        <v>1.082467022036751</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1770733840633811</v>
+        <v>0.176191364295825</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.091995296912629</v>
+        <v>1.080846237004466</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1965024612062771</v>
+        <v>0.2010857980758913</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -491,12 +491,12 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>16.58</v>
+        <v>16.14</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.04969926202091535</v>
+        <v>-0.02653802992052523</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.1009295791326441</v>
+        <v>0.08906880715289223</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.1838628909834843</v>
+        <v>0.1374207094382778</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.2354694358753515</v>
+        <v>0.1569892193782523</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.2812983354992451</v>
+        <v>0.2789223087170745</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.3567921081344905</v>
+        <v>0.291199951171875</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7924324241844383</v>
+        <v>0.7354837697452878</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1.067331543311319</v>
+        <v>0.9828008241901471</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.411522524324826</v>
+        <v>2.320987437499749</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5053913434059478</v>
+        <v>0.4919550687466925</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>40.2</v>
+        <v>40.29</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.01336028783608678</v>
+        <v>0.002238809723378532</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.01058332005590878</v>
+        <v>-0.007635408134099908</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.01349691379289686</v>
+        <v>0.02545176830486673</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.2434271106141792</v>
+        <v>0.2427514864612361</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.4075838531202307</v>
+        <v>0.4004807108043775</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3060338163493836</v>
+        <v>0.3563488472305776</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5558245005926878</v>
+        <v>0.5197135535505404</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.8171940409589018</v>
+        <v>0.7986445514990987</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.8275864879648183</v>
+        <v>0.831678106364389</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2226232383910636</v>
+        <v>0.2235349652662386</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>165.37</v>
+        <v>164.38</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.01205631147055697</v>
+        <v>-0.005986516681417697</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.01793458212130972</v>
+        <v>-0.02288528171255444</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.02465354089845873</v>
+        <v>0.00612070002517906</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.1248894721201954</v>
+        <v>0.1158781318791959</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2956506285933507</v>
+        <v>0.2673601017388425</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.30803894418497</v>
+        <v>0.3323187923557203</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4019919518325965</v>
+        <v>0.355049820320311</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.7886184282512805</v>
+        <v>0.7632926119456243</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.051212129413673</v>
+        <v>1.038932127882104</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2705844189401536</v>
+        <v>0.2680438042519697</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>71.47</v>
+        <v>71.03</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.01954354887878917</v>
+        <v>-0.006156463325745598</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.01840401569595251</v>
+        <v>-0.01905820760971222</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.03497159631745206</v>
+        <v>-0.01742982598247322</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.05010290603042789</v>
+        <v>0.04103759760519998</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.2843653732659497</v>
+        <v>0.2624063208426435</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.244301945768415</v>
+        <v>0.2777075263067894</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3630825515705862</v>
+        <v>0.3186257916320487</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5100862732252522</v>
+        <v>0.5052136977032666</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6780755859111898</v>
+        <v>0.6677445751086986</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1883303057312902</v>
+        <v>0.1858866467684095</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>213.8</v>
+        <v>552.6</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.01413526052561109</v>
+        <v>0.003851175687410668</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.006644021298924718</v>
+        <v>-0.03560213684827662</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.01456491318363973</v>
+        <v>-0.01786198949976237</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.146934171190169</v>
+        <v>0.01308978353254853</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.3016988438868702</v>
+        <v>-0.1337200902390255</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.2303717916070285</v>
+        <v>0.4130823378403456</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.2659125181587148</v>
+        <v>0.5213092221557571</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5265590454438931</v>
+        <v>0.9352702427713244</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6583139461325982</v>
+        <v>2.58576482180878</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.18364713444235</v>
+        <v>0.5305960941860213</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>550.48</v>
+        <v>213.81</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.009647500180232971</v>
+        <v>4.674699108164759e-05</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.009518395877060382</v>
+        <v>-0.004608964055393905</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.01861228474557386</v>
+        <v>0.01413459043617071</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.01840776762175067</v>
+        <v>0.1500725799951705</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.1292767255553585</v>
+        <v>0.2766570481781769</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3545607928998029</v>
+        <v>0.2580614548197333</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5363015306353625</v>
+        <v>0.2438467443616017</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.9275091582215409</v>
+        <v>0.5271739876768911</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.572008036267961</v>
+        <v>0.6583910747688715</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5286362085435738</v>
+        <v>0.1836654847421033</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>193.16</v>
+        <v>192.33</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.002283117676521673</v>
+        <v>-0.004296965289494414</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.047164678692317</v>
+        <v>0.03698711686634648</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.03665540580656157</v>
+        <v>0.0260336354348405</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.08883884051778046</v>
+        <v>0.1035689877104935</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1495808761924273</v>
+        <v>0.1293909085410792</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2214016465031587</v>
+        <v>0.2205134516540377</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.4754574973597461</v>
+        <v>0.4321958029276494</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.4687375056880663</v>
+        <v>0.5041175605435426</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3608887416320063</v>
+        <v>0.3550411956189878</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1081729382561345</v>
+        <v>0.1065834387832723</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>436.58</v>
+        <v>111.53</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.02272297033944226</v>
+        <v>0.01965625872980836</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.07829475722968415</v>
+        <v>-0.05945355829731069</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.04272847220268416</v>
+        <v>0.01603354459373252</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.1345338981370645</v>
+        <v>0.01714543754907538</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.0142408507176115</v>
+        <v>0.09118481340677431</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.104063916897229</v>
+        <v>0.4821262296252076</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.5203590022576066</v>
+        <v>0.3236746217146977</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.7436411626157104</v>
+        <v>0.3422999601675059</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.3147174137241147</v>
+        <v>1.103989934902573</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.09549602256443945</v>
+        <v>0.281389672130232</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>109.38</v>
+        <v>91.25</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.0220831582869857</v>
+        <v>0.0150166679778363</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.00209837930529011</v>
+        <v>-0.05391391511430166</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.02591507381230218</v>
+        <v>0.01467807951011713</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.02425317272859062</v>
+        <v>0.149823579866474</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.03805631965750345</v>
+        <v>0.01451627063278749</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.4644529880585526</v>
+        <v>0.05217301343437675</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.314684815139606</v>
+        <v>0.3888683093117413</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3153167212457799</v>
+        <v>0.8363110664567146</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.063430757473046</v>
+        <v>1.527976083787906</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2731022918054198</v>
+        <v>0.3622526256348353</v>
       </c>
     </row>
     <row r="11">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>89.90000000000001</v>
+        <v>101.36</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.007395827856438553</v>
+        <v>0.02705439358490769</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.05903285886123344</v>
+        <v>-0.01725808405885565</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.01835073367674256</v>
+        <v>0.04001643302395896</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.1399949382460211</v>
+        <v>0.3373795934284731</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-0.03688342628807351</v>
+        <v>0.16013016761884</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>-0.03626594030534103</v>
+        <v>-0.04748692911769004</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4280062758543757</v>
+        <v>0.3417800449392447</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.840889273070164</v>
+        <v>0.6835003079552564</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.490575931944308</v>
+        <v>3.047451187585888</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.355501270479667</v>
+        <v>0.5936533987441197</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>152.22</v>
+        <v>429.81</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.002983391275576119</v>
+        <v>-0.01550686981055938</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.00172931596225312</v>
+        <v>0.0358115072042664</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.004903603594619499</v>
+        <v>0.03304811825381893</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.05031947334486397</v>
+        <v>0.124774270710313</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.08822400936482877</v>
+        <v>-0.003269801164412445</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2774861111537961</v>
+        <v>0.1176669447869587</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.4359307666498595</v>
+        <v>0.4340019192636544</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.5680083680989021</v>
+        <v>0.7502709785625572</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.265652898883488</v>
+        <v>0.2943302619518193</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3134023591534538</v>
+        <v>0.08980392678651405</v>
       </c>
     </row>
     <row r="13">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>93.54000000000001</v>
+        <v>28.45</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.02765068728792142</v>
+        <v>0.03680758779972537</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.00128125925571132</v>
+        <v>-0.01625170512152785</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.02093364015945864</v>
+        <v>0.02818939951192001</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.01862135522569908</v>
+        <v>0.1018590665840493</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-0.007416883087548953</v>
+        <v>0.1522883818368193</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.4792307935928624</v>
+        <v>0.4840897574184868</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2836666758802304</v>
+        <v>0.2326690146007209</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3001889548879484</v>
+        <v>0.2594068424421965</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.006380730850689</v>
+        <v>0.3777240333413783</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2612594970426476</v>
+        <v>0.1127238876668903</v>
       </c>
     </row>
     <row r="14">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>27.44</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.0171919606348383</v>
+        <v>0.01902927904506146</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.001455568007460606</v>
+        <v>-0.0542712686875314</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.01472171783828435</v>
+        <v>0.02001073095398542</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.09062005963724284</v>
+        <v>0.01501433263476426</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.07020285441722307</v>
+        <v>0.04071096437281452</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.4503171471145455</v>
+        <v>0.495350705866505</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2098765504776277</v>
+        <v>0.2908266134760549</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.2233615764920773</v>
+        <v>0.3273164645556579</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.3288136097317085</v>
+        <v>1.044560375064047</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.09939735853094511</v>
+        <v>0.2692094973257417</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>110.26</v>
+        <v>153.04</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.01769436506449851</v>
+        <v>0.005386887786453132</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.01525787599760831</v>
+        <v>0.000981057604049651</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.03333652237743667</v>
+        <v>0.01552751416905673</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.04528820890421481</v>
+        <v>0.04222280783755594</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.02917140018972386</v>
+        <v>-0.07571782197150689</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.09664812791096411</v>
+        <v>0.3290334925516047</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.3777504398062899</v>
+        <v>0.4361338191167652</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.6022508846047454</v>
+        <v>0.5793093375985185</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.7431585163763001</v>
+        <v>1.277816190694107</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2034987051327517</v>
+        <v>0.3157485250967675</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>57.65</v>
+        <v>101.49</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.003830771713983383</v>
+        <v>0.03953703491696481</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.004180485614086127</v>
+        <v>-0.02121713304886752</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.02035400930759135</v>
+        <v>0.01642463109374503</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.02252572603234482</v>
+        <v>0.3345166836442843</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1554439948511699</v>
+        <v>0.1939999748678769</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.2583937732973016</v>
+        <v>-0.0356328399479281</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.1999777037905699</v>
+        <v>0.2611287467453818</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2309085839992004</v>
+        <v>0.5679002625445309</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2010857980758913</v>
+        <v>2.613803632752981</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.06297898162607107</v>
+        <v>0.5345752283058569</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>477.1</v>
+        <v>110.85</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.008817401079049603</v>
+        <v>0.005350955255394085</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.02773529291956234</v>
+        <v>0.01020682660096472</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.05205639245958105</v>
+        <v>0.05772896227279078</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.02127309391597298</v>
+        <v>0.04981534537986287</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.2543047390550509</v>
+        <v>-0.01256016065631549</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.3415209554982268</v>
+        <v>0.1590338684811714</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.4688370804763946</v>
+        <v>0.348337816399531</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.6907646427422343</v>
+        <v>0.6150270682329779</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.243928887481634</v>
+        <v>0.7525337370739409</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3091910565157479</v>
+        <v>0.205652438944552</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>31.95</v>
+        <v>58</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.002824863492270291</v>
+        <v>0.006071092191801242</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.04411765897516906</v>
+        <v>0.0129235365029432</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.02865425989375714</v>
+        <v>0.02836876650414522</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.08858604251028401</v>
+        <v>0.02022869932709681</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.09073215721022643</v>
+        <v>0.1608317085704944</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1267182939586222</v>
+        <v>0.2802273032885436</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.3380610793536984</v>
+        <v>0.2023008614708504</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.3426643054288006</v>
+        <v>0.239166569748654</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.2767553421202382</v>
+        <v>0.2083776046495234</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.08484883737787086</v>
+        <v>0.06512576255878311</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>98.69</v>
+        <v>478.52</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.04666456128068952</v>
+        <v>0.002976279379565128</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.01927849413655658</v>
+        <v>-0.04345744278487995</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.02941482855986211</v>
+        <v>-0.03667915122377496</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.3381695246292373</v>
+        <v>-0.03360532863189902</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.07349672652070116</v>
+        <v>-0.2632396691450031</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>-0.1552601666271142</v>
+        <v>0.4152482948354108</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2954226516119658</v>
+        <v>0.4207579910339028</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.6706813574220807</v>
+        <v>0.7002465551887624</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>2.940834305239044</v>
+        <v>1.250607285241203</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.5795355021424335</v>
+        <v>0.3104885781713693</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>97.63</v>
+        <v>31.75</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.03126649563455497</v>
+        <v>-0.006259804637358424</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.04676821910918283</v>
+        <v>0.02617968493732792</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.003082250248839236</v>
+        <v>0.004111295297794637</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3175438497143095</v>
+        <v>0.09144035178616083</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.1088017475255374</v>
+        <v>0.07297791725353031</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.1535460347388159</v>
+        <v>0.1228005043722469</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2049878630743098</v>
+        <v>0.2888288861791835</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.5175779820865787</v>
+        <v>0.3783578655063586</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>2.476358716783612</v>
+        <v>0.2687630064042024</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.5148682428207703</v>
+        <v>0.08258042278730571</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>55.79</v>
+        <v>55.42</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.001253127355162365</v>
+        <v>-0.006632062027427832</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.005587623933828834</v>
+        <v>0.001988732470135313</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01621128169238584</v>
+        <v>0.009287895154806547</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.02761885516131879</v>
+        <v>0.02413596401317508</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.07809363741073483</v>
+        <v>0.0737945992226825</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1000725031706504</v>
+        <v>0.09610590203325553</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2527608037774149</v>
+        <v>0.2337334950794669</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2474686220359641</v>
+        <v>0.2451110091041762</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.7006504560238958</v>
+        <v>0.6893720296053669</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1936353898375283</v>
+        <v>0.190990872467965</v>
       </c>
     </row>
     <row r="22">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>74.23999999999999</v>
+        <v>69.11</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.0223078360770752</v>
+        <v>0.01111927071246721</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.004558916049041684</v>
+        <v>0.01008480648746102</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.01013336181640623</v>
+        <v>0.007140743867048771</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.0239284742735123</v>
+        <v>-0.01999427254444541</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.0738304248449968</v>
+        <v>0.1193997564192053</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1084394647796998</v>
+        <v>0.1361901985131193</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.19339467026087</v>
+        <v>0.1671897085004139</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1684574363974549</v>
+        <v>0.1669334172919332</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7700729727841857</v>
+        <v>0.8816946828083627</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2096611242323083</v>
+        <v>0.2345718946069837</v>
       </c>
     </row>
     <row r="23">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>68.34999999999999</v>
+        <v>147.87</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.02091115145175015</v>
+        <v>0.0212722009384172</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.005094592280473931</v>
+        <v>0.02247268780064937</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.01114010766585238</v>
+        <v>0.02587758945007268</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.0186647957398075</v>
+        <v>0.004483312093064074</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.08181771032422103</v>
+        <v>0.1588731669446615</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.116796055972372</v>
+        <v>0.1034968710671986</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1766095494963524</v>
+        <v>0.1378489450060874</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1554341810646078</v>
+        <v>0.1422805775332263</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8610015078049706</v>
+        <v>0.7058434613377909</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2300296350418083</v>
+        <v>0.1948490933750473</v>
       </c>
     </row>
     <row r="24">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>133.36</v>
+        <v>74.87</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.005200892823768566</v>
+        <v>0.008486057394136326</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.01630159028155764</v>
+        <v>0.006994005153099447</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.003461299736593482</v>
+        <v>0.002141663285639472</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.0123676085613752</v>
+        <v>-0.02841934702043725</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.1535420326941228</v>
+        <v>0.1094263629937107</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.05777560679355354</v>
+        <v>0.1254862390771467</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1009361170600751</v>
+        <v>0.178948854327444</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1183323722666942</v>
+        <v>0.1767456606926607</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.681657189899106</v>
+        <v>0.7850939136230417</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1891751433451923</v>
+        <v>0.2130732417908634</v>
       </c>
     </row>
     <row r="25">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>144.79</v>
+        <v>135.15</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.006744443836158354</v>
+        <v>0.01342226513152744</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.009779838070250513</v>
+        <v>0.01024065727080514</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.003395635648041129</v>
+        <v>0.0110720112801117</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.01610498992252196</v>
+        <v>-0.0005177290606919183</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.1247155010417504</v>
+        <v>0.1787729857964029</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.07187164050195305</v>
+        <v>0.08026684958158703</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1124754208526837</v>
+        <v>0.1211721611721612</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1245767411256224</v>
+        <v>0.1277823025759601</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.6703123906707464</v>
+        <v>0.7042290025192495</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1864949686716206</v>
+        <v>0.194472027994786</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>74.26000000000001</v>
+        <v>198.06</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.006023249280640353</v>
+        <v>0.03794146293094758</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.02186506945140909</v>
+        <v>0.01387249229796339</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.004157135039056015</v>
+        <v>0.04876881735460348</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.0728113381486033</v>
+        <v>0.05733498726479302</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.1368146164084919</v>
+        <v>0.109086150560056</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>-0.00851876268967533</v>
+        <v>0.1650156221769481</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1906023531791992</v>
+        <v>0.1283114549422031</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.5975590030289653</v>
+        <v>0.1655074949058668</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.2843807202893318</v>
+        <v>1.159796767058759</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.08700429294416545</v>
+        <v>0.292620270886548</v>
       </c>
     </row>
     <row r="27">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>119.46</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.03187356438113231</v>
+        <v>0.002693198794625484</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.007065069332306551</v>
+        <v>-0.03461685808405746</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.02041513108293014</v>
+        <v>-0.001609047246390105</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.1868852188120174</v>
+        <v>0.07275601722983405</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.1000397622952742</v>
+        <v>-0.1187830029032533</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.02002452276153754</v>
+        <v>0.06297199123406139</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.2397795076357809</v>
+        <v>0.1886990523410852</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.4704032469736874</v>
+        <v>0.598446727687884</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.286217293026362</v>
+        <v>0.2878398128970554</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3173641333946438</v>
+        <v>0.08797925775977444</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2048,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>93.95999999999999</v>
+        <v>118.38</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.003922429125409188</v>
+        <v>-0.009040698470883068</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.02338634259859507</v>
+        <v>-0.03756099793969137</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.01406090161988127</v>
+        <v>0.03208370011410167</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.02237021654588711</v>
+        <v>0.1480942348237499</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.07493632048442778</v>
+        <v>-0.07833976807831888</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.04845360324478087</v>
+        <v>0.01069573474015062</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.1030030137612008</v>
+        <v>0.1907290248805784</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1526221996522346</v>
+        <v>0.4571096377524888</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.4324328756722202</v>
+        <v>1.265548457238499</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1272617217258167</v>
+        <v>0.313382177184296</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>190.82</v>
+        <v>94.27</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.002978170579692851</v>
+        <v>0.003299250336465498</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.02123512129195038</v>
+        <v>-0.006638618257984952</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.003365310090891693</v>
+        <v>-0.01555978968175398</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.02448197654819251</v>
+        <v>-0.01822537035181582</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.05029993680015621</v>
+        <v>0.07335361409623053</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.1170774143854139</v>
+        <v>0.06014823354058407</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1083348141464999</v>
+        <v>0.1125523865863327</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1229028147322326</v>
+        <v>0.152414378173273</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.080846237004466</v>
+        <v>0.4371591646345165</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2766739488429166</v>
+        <v>0.1285001545619042</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>75.54000000000001</v>
+        <v>293.42</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.006126785738601148</v>
+        <v>0.020981935599514</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.003035445924889135</v>
+        <v>-0.001395273332425617</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.006260839517967076</v>
+        <v>0.03309634806587503</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.01097429980497666</v>
+        <v>0.03736965563419647</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.08186822294364893</v>
+        <v>0.04635903065937974</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.005851823291624259</v>
+        <v>0.2114281214415874</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1313807417591584</v>
+        <v>0.0804979233527352</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.1022549227633958</v>
+        <v>0.05683618335519225</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2572426010242386</v>
+        <v>0.7168100587478097</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.07929383450117622</v>
+        <v>0.1974041243953104</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>65.23</v>
+        <v>106.95</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.008971412488250508</v>
+        <v>0.03413265172883029</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.04242512144927135</v>
+        <v>-0.03054752316809639</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.04172170340271897</v>
+        <v>0.04945533416761827</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.02452518801088677</v>
+        <v>0.09782384477948769</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.03878494450619563</v>
+        <v>0.06756539815239604</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.07501614442876381</v>
+        <v>0.2716363184445163</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1037912705256077</v>
+        <v>0.002718856892706345</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1105546390949121</v>
+        <v>-0.003260805417516055</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.6206159792177859</v>
+        <v>0.4786713070584545</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1746091300994219</v>
+        <v>0.1392627086160061</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>237.1</v>
+        <v>75.13</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.01672388167371652</v>
+        <v>-0.005427636446124207</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01426014506792772</v>
+        <v>0.005890946547456588</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.007564162518677975</v>
+        <v>0.002000451984115692</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.06384893120693902</v>
+        <v>0.01253369735074927</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.01432767031533633</v>
+        <v>0.07339763549119849</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.01966532214842542</v>
+        <v>0.005917148278979711</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1921991469859821</v>
+        <v>0.1332216618316726</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1640779307972855</v>
+        <v>0.1020636444438079</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3494356908892731</v>
+        <v>0.2504188246498156</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1050554331272677</v>
+        <v>0.07733764229529827</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>83.31999999999999</v>
+        <v>236.13</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.004702753987860575</v>
+        <v>-0.004091105844508669</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.04471453188827945</v>
+        <v>-0.01411210263263973</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.0377641388308444</v>
+        <v>0.006521733757422821</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.0184945188610246</v>
+        <v>0.04403770082019109</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.006089736355634146</v>
+        <v>0.01255209975934335</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.02221387089270976</v>
+        <v>0.005591930111985555</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1433808791084306</v>
+        <v>0.1769046746985605</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1929815113257618</v>
+        <v>0.1663112969436042</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3773114846887253</v>
+        <v>0.3439147732251464</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1126128110997744</v>
+        <v>0.1035463432528485</v>
       </c>
     </row>
     <row r="34">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2398,37 +2398,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>287.39</v>
+        <v>64.86</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.0008706553849908705</v>
+        <v>0.01138318085448975</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.002983470430398927</v>
+        <v>0.00886607072183998</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.003842279055096709</v>
+        <v>0.03395506270777338</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.04585321777249329</v>
+        <v>0.05738507416053795</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.005422678178020224</v>
+        <v>0.01417196926036568</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.1852112327293227</v>
+        <v>0.2313295373278899</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0579811483973891</v>
+        <v>0.0716411778872319</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.04948151654891042</v>
+        <v>0.03199860544173916</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.6815283394213141</v>
+        <v>0.8826084929784705</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1891447705875082</v>
+        <v>0.2347717112560468</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>64.13</v>
+        <v>64.91</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.003736122538418707</v>
+        <v>-0.004905713296888936</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.009265019394679497</v>
+        <v>-0.02916537437094013</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.01421320133825099</v>
+        <v>-0.03965072970833794</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.06261312142115338</v>
+        <v>-0.02843876614152008</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.0003886430139099506</v>
+        <v>0.04482178318559438</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.208955051070598</v>
+        <v>0.0789566595411606</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.05208442332523422</v>
+        <v>0.09358724063983948</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.02361961068371721</v>
+        <v>0.09878109574817051</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.8613821766549639</v>
+        <v>0.612665396179364</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.2301134970631369</v>
+        <v>0.1726851412999242</v>
       </c>
     </row>
     <row r="36">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2510,37 +2510,37 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>103.38</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.006523202949250129</v>
+        <v>0.003360523047556629</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.0412687053887737</v>
+        <v>-0.03240744215634239</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.04011141891582692</v>
+        <v>-0.0309493250590025</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.0512985583616119</v>
+        <v>-0.02654865920138505</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.07355053555076785</v>
+        <v>0.002262898912537059</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.0143459848018288</v>
+        <v>0.02992207172108619</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.1797985076621647</v>
+        <v>0.1188743760996529</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.2177284140071871</v>
+        <v>0.196990553189881</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.3114049706753383</v>
+        <v>0.3819397973908454</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.09457521124484924</v>
+        <v>0.1138576911105125</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>95.78</v>
+        <v>23.61</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.005399836510715961</v>
+        <v>0.01156814293052766</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.02869893330836881</v>
+        <v>-0.02357318807403852</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.02869893330836881</v>
+        <v>-0.01337232305655289</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.03203636449431568</v>
+        <v>-0.007983135831917343</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.02226203542587979</v>
+        <v>-0.0841048638237093</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.01800381639649262</v>
+        <v>0.009552977545299379</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.0953445694612558</v>
+        <v>0.1855310210585654</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.0967853480708567</v>
+        <v>0.312529000155233</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.3071197404601087</v>
+        <v>0.5577316769798648</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.09338167577020884</v>
+        <v>0.1592156005448311</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>54.28</v>
+        <v>96.66</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.006676569409805655</v>
+        <v>0.009187772959156959</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.03433553347466467</v>
+        <v>-0.01013822681310628</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.0440295888296417</v>
+        <v>-0.01967540407742396</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.03690563890222276</v>
+        <v>-0.02432619400563851</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.04420489296019836</v>
+        <v>0.03285627917320766</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>-0.01796666055649665</v>
+        <v>0.03284802743082982</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1418824110794847</v>
+        <v>0.1025896552165277</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1869436974060901</v>
+        <v>0.1062526129538244</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.699967103791391</v>
+        <v>0.3191292598658884</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1934754936282588</v>
+        <v>0.09672005332952827</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>23.34</v>
+        <v>177.54</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.002146195381655613</v>
+        <v>0.01145100279618427</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.02425586093068244</v>
+        <v>-0.02294872749798949</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.02831809174934363</v>
+        <v>-0.01998239292779236</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.01644330673333461</v>
+        <v>-0.02461273970536837</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.1053077195795974</v>
+        <v>-0.09578854407269466</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>-0.04512668240281625</v>
+        <v>0.05377720615558723</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1778408456506591</v>
+        <v>0.1718280328817541</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.2982217210445501</v>
+        <v>0.2702761716056028</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.5399043787149045</v>
+        <v>0.8140837406549888</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.1547764486077652</v>
+        <v>0.2196047587941405</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>175.53</v>
+        <v>104.28</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.0003419248770522021</v>
+        <v>0.008705760783420224</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.02930931260349978</v>
+        <v>-0.02551166528768145</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.03966517150902393</v>
+        <v>-0.02213053848329871</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.02129917588078556</v>
+        <v>-0.0587598346640873</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.1075646194307903</v>
+        <v>-0.05840599448471029</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>-0.001285601695105054</v>
+        <v>0.03053176004230651</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1648228291841252</v>
+        <v>0.1575008589252989</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.2604558577687122</v>
+        <v>0.2313515374700759</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.7935459820190667</v>
+        <v>0.3228214925920887</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2149847823954065</v>
+        <v>0.0977423371521835</v>
       </c>
     </row>
     <row r="41">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2790,37 +2790,37 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>58.63</v>
+        <v>54.69</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.004110321647123438</v>
+        <v>0.007553424035235734</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.0257560523296847</v>
+        <v>-0.0244381504284934</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.03616637673379652</v>
+        <v>-0.02408997620919573</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.03202903477766994</v>
+        <v>-0.04953080019936662</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.03727205567040037</v>
+        <v>-0.04370915305157308</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>-0.02421219252325557</v>
+        <v>0.009692279066308318</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1283174026453402</v>
+        <v>0.1367545364630502</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1580859543064936</v>
+        <v>0.2013794953933861</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.5792633448728437</v>
+        <v>0.7128075738572706</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1645322453999587</v>
+        <v>0.1964728776866276</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>103.42</v>
+        <v>28.42</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.02599361582499382</v>
+        <v>0.00317684972927168</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.01005956426835386</v>
+        <v>-0.03168655172362256</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.005933281050842343</v>
+        <v>-0.02870813896162405</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0.09346580848751973</v>
+        <v>-0.1300887153612158</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.01232327533382038</v>
+        <v>0.02120014927076297</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.2497208622454836</v>
+        <v>0.03609186146933285</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>-0.01692277891110405</v>
+        <v>0.05651832916795985</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.03570994383977133</v>
+        <v>0.08369055090284006</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.4298661826279815</v>
+        <v>0.4915554935364241</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1265880276387767</v>
+        <v>0.142562077310209</v>
       </c>
     </row>
     <row r="43">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2902,37 +2902,37 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>28.33</v>
+        <v>58.92</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.01577628338783432</v>
+        <v>0.004946223700271979</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.04805108515382261</v>
+        <v>-0.01553885261296895</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.05282513981165271</v>
+        <v>-0.02191240824605301</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.09430948523600602</v>
+        <v>-0.03536351665613691</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.005964914957682255</v>
+        <v>-0.03440719614491161</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.02274365138680778</v>
+        <v>-0.01072651202072217</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.07174637447801069</v>
+        <v>0.1228109201125143</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.08724937691931101</v>
+        <v>0.1699454579251287</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.4868320515360296</v>
+        <v>0.5870747346582244</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1413547174675709</v>
+        <v>0.1664491007972912</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>13.34</v>
+        <v>225.98</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.000749080793714163</v>
+        <v>0.01168465177689715</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.002243809515929285</v>
+        <v>-0.03534533839944765</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.006033176645940497</v>
+        <v>-0.04874558827269937</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>0.07580649701415321</v>
+        <v>-0.08168077842146315</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.0697626042364361</v>
+        <v>0.005552193867865318</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.09524940014989602</v>
+        <v>-0.07631073274122968</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>-0.000617505035313104</v>
+        <v>0.1223360780748943</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>-0.06850898684132811</v>
+        <v>0.1532927129651023</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.176191364295825</v>
+        <v>0.9837551173382917</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.05558366789667546</v>
+        <v>0.2565005605998525</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>86.38</v>
+        <v>13.35</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.005353806963172447</v>
+        <v>0.0007496423363906324</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.02096799312169861</v>
+        <v>-0.002987301032667533</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.02758082322565258</v>
+        <v>0.004514704273056447</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.0378703672544819</v>
+        <v>0.0478807395063261</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.03424585456649454</v>
+        <v>0.09556167484056877</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.007432058836457589</v>
+        <v>0.09099608243395685</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.03206700469097368</v>
+        <v>-0.01610860183931628</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.03241690898800065</v>
+        <v>-0.06372205811809772</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.3862040484703759</v>
+        <v>0.177073087138198</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1150021914655597</v>
+        <v>0.0558473720820607</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>48.48</v>
+        <v>27.92</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.007690686493259991</v>
+        <v>0.04144903841282188</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.001441806301219928</v>
+        <v>0.001938223838838793</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.0008257827551896302</v>
+        <v>0.04117713093968245</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.0161391840817342</v>
+        <v>0.06302363565196267</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.01980307104278012</v>
+        <v>0.1348738503058318</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.03477764952441187</v>
+        <v>0.1321170678125398</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.08016741108708336</v>
+        <v>-0.07899539356105423</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.0346148360392291</v>
+        <v>-0.1536902643414675</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.1484027984044385</v>
+        <v>0.2939975066974352</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.04720429325185727</v>
+        <v>0.08971052737255469</v>
       </c>
     </row>
     <row r="47">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -3126,37 +3126,37 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>19.2</v>
+        <v>86.73</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.005497358122473983</v>
+        <v>0.00405193464511</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.04137967737875425</v>
+        <v>0.001616896003744372</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.04689824876994941</v>
+        <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.006980363382456889</v>
+        <v>-0.05171655122334329</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.08441563616703673</v>
+        <v>0.04254689082282681</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.1333726922150458</v>
+        <v>0.0175371338452881</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>-0.07889690300560637</v>
+        <v>0.0216998565488149</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.1151808343141028</v>
+        <v>0.03134186963797037</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.0648949213603689</v>
+        <v>0.3918210270865699</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.02117988587656261</v>
+        <v>0.116506179567921</v>
       </c>
     </row>
     <row r="48">
@@ -3182,37 +3182,37 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>71.23999999999999</v>
+        <v>71.22</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.0001291375411184292</v>
+        <v>-0.0002806940435995386</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.01614700528631352</v>
+        <v>-0.01684154030350749</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.008478768780283308</v>
+        <v>-0.003497971116972365</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.009856817625121583</v>
+        <v>-0.0204923378150299</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.0652613426685944</v>
+        <v>0.07289768349353531</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.06080007982170466</v>
+        <v>-0.03936722813143589</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.05005913957817598</v>
+        <v>0.03824973365159079</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.02473456824615816</v>
+        <v>-0.02214449150025655</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.004738295164928852</v>
+        <v>0.004444976229975861</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.001576943663170516</v>
+        <v>0.001479468835854814</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>223.37</v>
+        <v>18.99</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.009269988177247446</v>
+        <v>-0.01119500929143458</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.05503853751113519</v>
+        <v>-0.04773842599832367</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.09254519335424705</v>
+        <v>-0.05286780579936745</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.06797132728032818</v>
+        <v>-0.04764296577208449</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.02103623953394218</v>
+        <v>0.09642032942950896</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.1073833798571413</v>
+        <v>0.1453558418879299</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.1110817968787832</v>
+        <v>-0.09312324322857091</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1310135315759953</v>
+        <v>-0.1274982630989679</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.9608434769813692</v>
+        <v>0.05297341282133794</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.2516444441168573</v>
+        <v>0.01735487036831773</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>112.42</v>
+        <v>48.12</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.0138888974898479</v>
+        <v>-0.007425755234133691</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.001687260814993596</v>
+        <v>0.006273509807090516</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0.009881409244849593</v>
+        <v>-0.00578517737947648</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0.03861788976046276</v>
+        <v>0.01412008763271944</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.007550772797766503</v>
+        <v>0.01585227585243842</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.04070466614306756</v>
+        <v>-0.02221136855708539</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.01554984940400972</v>
+        <v>0.07475726012906092</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.02368547401203314</v>
+        <v>0.02866527530995855</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.7329921397918144</v>
+        <v>0.1398749373105197</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.2011544768778719</v>
+        <v>0.04460572484664738</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>54.42</v>
+        <v>253.93</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.002394497167539811</v>
+        <v>0.0148674547863632</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.0175122085465198</v>
+        <v>-0.0455553304765377</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.03919493722856315</v>
+        <v>-0.06567814476300371</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>0.03637402225223196</v>
+        <v>-0.07199507311147468</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>0.1309876828615109</v>
+        <v>-0.07121558809941042</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.0852844090674969</v>
+        <v>-0.1063680253149141</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>-0.1356756287126859</v>
+        <v>0.115429451125969</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>-0.1139004366000687</v>
+        <v>0.1846219412614858</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.0500049902535491</v>
+        <v>1.107682766915945</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.01639796699500962</v>
+        <v>0.2821389138413939</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>250.21</v>
+        <v>113.38</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.007260699178753383</v>
+        <v>0.008539397794954384</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.06165380670887743</v>
+        <v>0.01768237614714829</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.119288978041416</v>
+        <v>0.02439462360677203</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.05531216283293838</v>
+        <v>0.01832226497777523</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.1038936106658203</v>
+        <v>0.01423053962854359</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.1362579380296409</v>
+        <v>-0.0332509979130996</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.1090646002605711</v>
+        <v>-0.006280762970138576</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.1532203112333286</v>
+        <v>0.01544221513067323</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>1.076805948378379</v>
+        <v>0.7477910546061839</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.2758471260518707</v>
+        <v>0.20456388311119</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>42.67</v>
+        <v>45.19</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.002584511092692976</v>
+        <v>0.0109619207026006</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.01930591093983502</v>
+        <v>-0.007467607329313064</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.03066792991321432</v>
+        <v>-0.01094331396428883</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.03788050423848577</v>
+        <v>-0.01546847223457315</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.0218116968426082</v>
+        <v>0.01186741560921845</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.08712907858395402</v>
+        <v>-0.06516345709424398</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.00849662444104482</v>
+        <v>-0.004663583433486274</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.04378681549711683</v>
+        <v>0.01824484490579614</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.4909972135319352</v>
+        <v>0.2759646758287027</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.1424195082127104</v>
+        <v>0.08462485018619192</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>26.8</v>
+        <v>43.03</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.02110479445684521</v>
+        <v>0.008436855537846455</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.02982479358515611</v>
+        <v>-0.003473865790152075</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>0.005401388143445818</v>
+        <v>-0.01690659517312254</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.04825972524034672</v>
+        <v>-0.02998200659952932</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.03829733911581479</v>
+        <v>-0.009270912206644</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0.08363747066517369</v>
+        <v>-0.07356011177014676</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1022739025449896</v>
+        <v>0.003064578275240759</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.190539605856079</v>
+        <v>0.05522987760049025</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.2424970829688795</v>
+        <v>0.5035767420492943</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.07505774572625268</v>
+        <v>0.1456233753429523</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>44.69</v>
+        <v>19.48</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.005738098019696602</v>
+        <v>0.01632758080835162</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.02113447559817683</v>
+        <v>-0.003172180834800975</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.01769231439946772</v>
+        <v>-0.0003078925907008534</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.02900280512440734</v>
+        <v>0.02434276197312513</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.01444319297321806</v>
+        <v>0.03621953803857969</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.1008851233556936</v>
+        <v>0.07611158764101256</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.01203474182893027</v>
+        <v>-0.05610267461984508</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.006225591042967604</v>
+        <v>-0.17593231266981</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.261988106436098</v>
+        <v>0.1725455205392559</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.08065007343166108</v>
+        <v>0.0544918737949911</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>19.17</v>
+        <v>53.91</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0.006827686686747159</v>
+        <v>-0.009371524048015001</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.02063959031857321</v>
+        <v>-0.01299888499371959</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.01393960746154865</v>
+        <v>-0.02777278438842901</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.002667534728630461</v>
+        <v>-0.005534020330697165</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>0.007356772706092585</v>
+        <v>0.1125392221678678</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>0.05098685947619219</v>
+        <v>-0.08418084822211425</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.05949943283253034</v>
+        <v>-0.1444528882786297</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.1875935575575753</v>
+        <v>-0.1164747197631892</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.1537082557640066</v>
+        <v>0.0401647666780629</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.04881446110279142</v>
+        <v>0.01321290577347423</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>35.19</v>
+        <v>45.7</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.001137897556011014</v>
+        <v>0.03113720842999901</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.01234921213067275</v>
+        <v>-0.05519946718843716</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.0327103465219305</v>
+        <v>0.04242702107385288</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.000851862378031476</v>
+        <v>0.119823553665666</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.133671330769584</v>
+        <v>-0.09307399649765513</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.07809379614292034</v>
+        <v>-0.1211538314819336</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.00596358187861501</v>
+        <v>0.02706077971868948</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.06185044753853797</v>
+        <v>0.1582383263797029</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.3281284710979335</v>
+        <v>1.147309231750509</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.0992083756435036</v>
+        <v>0.2901242257129268</v>
       </c>
     </row>
     <row r="58">
@@ -3742,37 +3742,37 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>17.37</v>
+        <v>17.63</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.007540665304011318</v>
+        <v>0.01496823885845466</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.01753390614205086</v>
+        <v>-0.01121709275351934</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.02579916356931999</v>
+        <v>0</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.01025631941037597</v>
+        <v>-0.02001115146924692</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.2666685080043432</v>
+        <v>-0.2344167200553614</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.04982965158025365</v>
+        <v>-0.002408608955747127</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.04976844740744668</v>
+        <v>0.07060416207464137</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.2395570367577551</v>
+        <v>0.2545671180799656</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1308690741767504</v>
+        <v>0.1477961925966675</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.04184739267431459</v>
+        <v>0.04701987709632438</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>101.17</v>
+        <v>35.81</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.006066036447506251</v>
+        <v>0.01761872039720558</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.04556605500994992</v>
+        <v>-0.009131101879651493</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.06523149744997203</v>
+        <v>0</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.02430325212775408</v>
+        <v>-0.0033397976862104</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.02879609144110673</v>
+        <v>-0.1103076579844193</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.1018759307657902</v>
+        <v>-0.0290539815824512</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.05961074191697935</v>
+        <v>0.0133092561063004</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.09787933626557921</v>
+        <v>0.08479379403150489</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.2280568331330339</v>
+        <v>0.3515284925735507</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.07087674759830631</v>
+        <v>0.1056264044769886</v>
       </c>
     </row>
     <row r="60">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>92.81999999999999</v>
+        <v>102.27</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0.004980501098232892</v>
+        <v>0.01087277349045901</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.04614117743725099</v>
+        <v>-0.02152698117359975</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.06488013603473031</v>
+        <v>-0.03171753471313021</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.01611190059433909</v>
+        <v>-0.03845434320998953</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.0029761312080826</v>
+        <v>-0.01417295258838625</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.1125160511339908</v>
+        <v>-0.07826234585770897</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.09815010403135205</v>
+        <v>-0.06100960325061766</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1521419176692589</v>
+        <v>-0.09304697900482028</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.09064133488492465</v>
+        <v>0.2414092169130997</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.02934426949475788</v>
+        <v>0.07474389916272184</v>
       </c>
     </row>
     <row r="61">
@@ -3896,51 +3896,51 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>44.32</v>
+        <v>93.62</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.008648181155933132</v>
+        <v>0.008618865054816682</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.07762746308972701</v>
+        <v>-0.02101845199795926</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.01532989674382823</v>
+        <v>-0.03225134573169119</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.1343742012031675</v>
+        <v>-0.03494484398513753</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.1703481614758123</v>
+        <v>0.01420930681949861</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.2148804411722669</v>
+        <v>-0.09390332565340553</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.02597654445904651</v>
+        <v>-0.1087263600373448</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.1431732714705201</v>
+        <v>-0.1500031967628672</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>1.082467022036751</v>
+        <v>0.1000414253735029</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.2770053327740341</v>
+        <v>0.03229307365410916</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>47.27</v>
+        <v>47.72</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.008749463125733214</v>
+        <v>0.009519796035152073</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.03095527591882752</v>
+        <v>-0.04061118595896951</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.06340401596080791</v>
+        <v>-0.0404182252168751</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.04175960463869643</v>
+        <v>-0.06869633767484684</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.3459249667434603</v>
+        <v>-0.3210982984898271</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1612845999671324</v>
+        <v>-0.1239214218602668</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.00755827424477129</v>
+        <v>0.007176026697405469</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.1534895311319979</v>
+        <v>0.1479432660819728</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1859652038643103</v>
+        <v>-0.1782157586395819</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.06628502716665963</v>
+        <v>-0.06333145453714173</v>
       </c>
     </row>
   </sheetData>
@@ -4158,17 +4158,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3381695246292373</v>
+        <v>0.3373795934284731</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.09430948523600602</v>
+        <v>-0.1300887153612158</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.3175438497143095</v>
+        <v>0.3345166836442843</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.06797132728032818</v>
+        <v>-0.08168077842146315</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.2434271106141792</v>
+        <v>0.2427514864612361</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.05531216283293838</v>
+        <v>-0.07199507311147468</v>
       </c>
     </row>
     <row r="20">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.2354694358753515</v>
+        <v>0.1569892193782523</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.0512985583616119</v>
+        <v>-0.06869633767484684</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1868852188120174</v>
+        <v>0.1500725799951705</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.04175960463869643</v>
+        <v>-0.0587598346640873</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.146934171190169</v>
+        <v>0.149823579866474</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.03788050423848577</v>
+        <v>-0.05171655122334329</v>
       </c>
     </row>
     <row r="23">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1399949382460211</v>
+        <v>0.1480942348237499</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.0378703672544819</v>
+        <v>-0.04953080019936662</v>
       </c>
     </row>
     <row r="24">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.1345338981370645</v>
+        <v>0.124774270710313</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.03690563890222276</v>
+        <v>-0.04764296577208449</v>
       </c>
     </row>
     <row r="25">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.1343742012031675</v>
+        <v>0.119823553665666</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.03203636449431568</v>
+        <v>-0.03845434320998953</v>
       </c>
     </row>
     <row r="26">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.1248894721201954</v>
+        <v>0.1158781318791959</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.03202903477766994</v>
+        <v>-0.03536351665613691</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.4075838531202307</v>
+        <v>0.4004807108043775</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.3459249667434603</v>
+        <v>-0.3210982984898271</v>
       </c>
     </row>
     <row r="32">
@@ -5158,21 +5158,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.3016988438868702</v>
+        <v>0.2789223087170745</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5180,21 +5180,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.2666685080043432</v>
+        <v>-0.2632396691450031</v>
       </c>
     </row>
     <row r="33">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2956506285933507</v>
+        <v>0.2766570481781769</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5225,21 +5225,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.2543047390550509</v>
+        <v>-0.2344167200553614</v>
       </c>
     </row>
     <row r="34">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2843653732659497</v>
+        <v>0.2673601017388425</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1703481614758123</v>
+        <v>-0.1337200902390255</v>
       </c>
     </row>
     <row r="35">
@@ -5293,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2812983354992451</v>
+        <v>0.2624063208426435</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1368146164084919</v>
+        <v>-0.1187830029032533</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1554439948511699</v>
+        <v>0.1939999748678769</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.133671330769584</v>
+        <v>-0.1103076579844193</v>
       </c>
     </row>
     <row r="37">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1535420326941228</v>
+        <v>0.1787729857964029</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.1292767255553585</v>
+        <v>-0.09578854407269466</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1495808761924273</v>
+        <v>0.1608317085704944</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.1075646194307903</v>
+        <v>-0.09307399649765513</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1309876828615109</v>
+        <v>0.16013016761884</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.1053077195795974</v>
+        <v>-0.0841048638237093</v>
       </c>
     </row>
     <row r="40">
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1247155010417504</v>
+        <v>0.1588731669446615</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.1038936106658203</v>
+        <v>-0.07833976807831888</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4792307935928624</v>
+        <v>0.495350705866505</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.2148804411722669</v>
+        <v>-0.1239214218602668</v>
       </c>
     </row>
     <row r="46">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4644529880585526</v>
+        <v>0.4840897574184868</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1612845999671324</v>
+        <v>-0.1211538314819336</v>
       </c>
     </row>
     <row r="47">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4503171471145455</v>
+        <v>0.4821262296252076</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5736,21 +5736,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1552601666271142</v>
+        <v>-0.1063680253149141</v>
       </c>
     </row>
     <row r="48">
@@ -5759,21 +5759,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.3567921081344905</v>
+        <v>0.4152482948354108</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1535460347388159</v>
+        <v>-0.09390332565340553</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.3545607928998029</v>
+        <v>0.4130823378403456</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.1362579380296409</v>
+        <v>-0.08418084822211425</v>
       </c>
     </row>
     <row r="50">
@@ -5849,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3415209554982268</v>
+        <v>0.3563488472305776</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.1125160511339908</v>
+        <v>-0.07826234585770897</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.30803894418497</v>
+        <v>0.3323187923557203</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.1073833798571413</v>
+        <v>-0.07631073274122968</v>
       </c>
     </row>
     <row r="52">
@@ -5939,21 +5939,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3060338163493836</v>
+        <v>0.3290334925516047</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.1018759307657902</v>
+        <v>-0.07356011177014676</v>
       </c>
     </row>
     <row r="53">
@@ -5984,21 +5984,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2774861111537961</v>
+        <v>0.291199951171875</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.1008851233556936</v>
+        <v>-0.06516345709424398</v>
       </c>
     </row>
     <row r="54">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2583937732973016</v>
+        <v>0.2802273032885436</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.08712907858395402</v>
+        <v>-0.04748692911769004</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>1.067331543311319</v>
+        <v>0.9828008241901471</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6157,21 +6157,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.190539605856079</v>
+        <v>-0.17593231266981</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.9275091582215409</v>
+        <v>0.9352702427713244</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6202,21 +6202,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1875935575575753</v>
+        <v>-0.1536902643414675</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.840889273070164</v>
+        <v>0.8363110664567146</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1521419176692589</v>
+        <v>-0.1500031967628672</v>
       </c>
     </row>
     <row r="62">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.8171940409589018</v>
+        <v>0.7986445514990987</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1151808343141028</v>
+        <v>-0.1274982630989679</v>
       </c>
     </row>
     <row r="63">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.7886184282512805</v>
+        <v>0.7632926119456243</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1139004366000687</v>
+        <v>-0.1164747197631892</v>
       </c>
     </row>
     <row r="64">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.7436411626157104</v>
+        <v>0.7502709785625572</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.09787933626557921</v>
+        <v>-0.09304697900482028</v>
       </c>
     </row>
     <row r="65">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.6907646427422343</v>
+        <v>0.7002465551887624</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06850898684132811</v>
+        <v>-0.06372205811809772</v>
       </c>
     </row>
     <row r="66">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.6706813574220807</v>
+        <v>0.6835003079552564</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6472,21 +6472,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.03570994383977133</v>
+        <v>-0.02214449150025655</v>
       </c>
     </row>
     <row r="67">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.6022508846047454</v>
+        <v>0.6150270682329779</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.02473456824615816</v>
+        <v>-0.003260805417516055</v>
       </c>
     </row>
     <row r="68">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.5975590030289653</v>
+        <v>0.598446727687884</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.006225591042967604</v>
+        <v>0.01544221513067323</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.940834305239044</v>
+        <v>3.047451187585888</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1859652038643103</v>
+        <v>-0.1782157586395819</v>
       </c>
     </row>
     <row r="74">
@@ -6691,21 +6691,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.572008036267961</v>
+        <v>2.613803632752981</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.004738295164928852</v>
+        <v>0.004444976229975861</v>
       </c>
     </row>
     <row r="75">
@@ -6736,21 +6736,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.476358716783612</v>
+        <v>2.58576482180878</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.0500049902535491</v>
+        <v>0.0401647666780629</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>2.411522524324826</v>
+        <v>2.320987437499749</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.0648949213603689</v>
+        <v>0.05297341282133794</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.490575931944308</v>
+        <v>1.527976083787906</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.09064133488492465</v>
+        <v>0.1000414253735029</v>
       </c>
     </row>
     <row r="78">
@@ -6871,21 +6871,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.286217293026362</v>
+        <v>1.277816190694107</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6893,21 +6893,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1308690741767504</v>
+        <v>0.1398749373105197</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.265652898883488</v>
+        <v>1.265548457238499</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6938,21 +6938,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1484027984044385</v>
+        <v>0.1477961925966675</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.243928887481634</v>
+        <v>1.250607285241203</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1537082557640066</v>
+        <v>0.1725455205392559</v>
       </c>
     </row>
     <row r="81">
@@ -7006,21 +7006,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.082467022036751</v>
+        <v>1.159796767058759</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.176191364295825</v>
+        <v>0.177073087138198</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.080846237004466</v>
+        <v>1.147309231750509</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2010857980758913</v>
+        <v>0.2083776046495234</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -493,11 +493,11 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>16.14</v>
+        <v>16.56</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.02653802992052523</v>
+        <v>0.02602231054378579</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.08906880715289223</v>
+        <v>0.06701024339586703</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.1374207094382778</v>
+        <v>0.1227118281994837</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.1569892193782523</v>
+        <v>0.1905103988209815</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.2789223087170745</v>
+        <v>0.3080568456189587</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.291199951171875</v>
+        <v>0.3904281845596043</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7354837697452878</v>
+        <v>0.7864076211639559</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9828008241901471</v>
+        <v>1.05382612303641</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.320987437499749</v>
+        <v>2.407407203910378</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4919550687466925</v>
+        <v>0.5047857818684167</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>40.29</v>
+        <v>39.77</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.002238809723378532</v>
+        <v>-0.01290643946258307</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.007635408134099908</v>
+        <v>0.01221683713544097</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.02545176830486673</v>
+        <v>-0.007734564848518088</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.2427514864612361</v>
+        <v>0.2085942562754242</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.4004807108043775</v>
+        <v>0.3330338350387942</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3563488472305776</v>
+        <v>0.3107218277520876</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5197135535505404</v>
+        <v>0.4873256286897041</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7986445514990987</v>
+        <v>0.7799142811192761</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.831678106364389</v>
+        <v>0.8080379773288264</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2235349652662386</v>
+        <v>0.2182483994985938</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>164.38</v>
+        <v>163.81</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.005986516681417697</v>
+        <v>-0.003467619584420323</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.02288528171255444</v>
+        <v>0.00880645789371215</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.00612070002517906</v>
+        <v>-0.01158509755893433</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.1158781318791959</v>
+        <v>0.07854880360970617</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2673601017388425</v>
+        <v>0.2289821983098801</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.3323187923557203</v>
+        <v>0.2970321384628321</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.355049820320311</v>
+        <v>0.3347931928537671</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.7632926119456243</v>
+        <v>0.7605620048012858</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.038932127882104</v>
+        <v>1.031862271467704</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2680438042519697</v>
+        <v>0.2665764888835123</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>71.03</v>
+        <v>567.01</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.006156463325745598</v>
+        <v>0.02607679119856665</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.01905820760971222</v>
+        <v>0.02513066981646972</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.01742982598247322</v>
+        <v>0.01175908614330279</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.04103759760519998</v>
+        <v>-0.01511179565229881</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.2624063208426435</v>
+        <v>-0.09644163100698233</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2777075263067894</v>
+        <v>0.4207216263949596</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3186257916320487</v>
+        <v>0.5729378401263647</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5052136977032666</v>
+        <v>0.962238198420496</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6677445751086986</v>
+        <v>2.679269698059737</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1858866467684095</v>
+        <v>0.5437863900589888</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>552.6</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.003851175687410668</v>
+        <v>-0.001407834377581851</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.03560213684827662</v>
+        <v>0.001977671815762472</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.01786198949976237</v>
+        <v>-0.02568684983780201</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.01308978353254853</v>
+        <v>0.01618907169072847</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.1337200902390255</v>
+        <v>0.2264403169559062</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.4130823378403456</v>
+        <v>0.255623993101787</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.5213092221557571</v>
+        <v>0.3119185439397616</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.9352702427713244</v>
+        <v>0.5097710717165607</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.58576482180878</v>
+        <v>0.6653965177983405</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5305960941860213</v>
+        <v>0.1853298393538045</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>213.81</v>
+        <v>211.92</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>4.674699108164759e-05</v>
+        <v>-0.008839621211494064</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.004608964055393905</v>
+        <v>0.01421393282642081</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.01413459043617071</v>
+        <v>-0.007679337930309171</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.1500725799951705</v>
+        <v>0.1144885878056472</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2766570481781769</v>
+        <v>0.2363636153222182</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2580614548197333</v>
+        <v>0.2262509055575741</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2438467443616017</v>
+        <v>0.2337111912183685</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5271739876768911</v>
+        <v>0.513782248173986</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.6583910747688715</v>
+        <v>0.6437319149283676</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1836654847421033</v>
+        <v>0.1801675322144818</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>192.33</v>
+        <v>190.71</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.004296965289494414</v>
+        <v>-0.008422997461470016</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.03698711686634648</v>
+        <v>0.02565345923324958</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.0260336354348405</v>
+        <v>0.006172910568631895</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.1035689877104935</v>
+        <v>0.1091015417189676</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1293909085410792</v>
+        <v>0.1205983771082659</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2205134516540377</v>
+        <v>0.1968337610097921</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.4321958029276494</v>
+        <v>0.4201325826783964</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5041175605435426</v>
+        <v>0.4755471156377615</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3550411956189878</v>
+        <v>0.3436275426224642</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1065834387832723</v>
+        <v>0.1034677185086605</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>111.53</v>
+        <v>110.75</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.01965625872980836</v>
+        <v>-0.006993623131301141</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.05945355829731069</v>
+        <v>-0.04145751149014942</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.01603354459373252</v>
+        <v>-0.00779432651114742</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.01714543754907538</v>
+        <v>-0.02910493296840833</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.09118481340677431</v>
+        <v>0.09501681499253722</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.4821262296252076</v>
+        <v>0.4591567559091367</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.3236746217146977</v>
+        <v>0.3147291225215165</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.3422999601675059</v>
+        <v>0.329395029278567</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.103989934902573</v>
+        <v>1.089275422225814</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.281389672130232</v>
+        <v>0.2783954957132815</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>91.25</v>
+        <v>90.66</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.0150166679778363</v>
+        <v>-0.006465713291952002</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.05391391511430166</v>
+        <v>-0.03982201418928433</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.01467807951011713</v>
+        <v>-0.04154765649575343</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.149823579866474</v>
+        <v>0.07941428703401665</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.01451627063278749</v>
+        <v>0.00829179347400455</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.05217301343437675</v>
+        <v>0.03185216130393309</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.3888683093117413</v>
+        <v>0.3854325519966197</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.8363110664567146</v>
+        <v>0.8568221916336818</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.527976083787906</v>
+        <v>1.511630649787596</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3622526256348353</v>
+        <v>0.3593102488878379</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>101.36</v>
+        <v>154.67</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.02705439358490769</v>
+        <v>0.01066789210248964</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.01725808405885565</v>
+        <v>0.0181857922004296</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.04001643302395896</v>
+        <v>0.02398281560362414</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.3373795934284731</v>
+        <v>0.02107612743849274</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.16013016761884</v>
+        <v>-0.04891910342687056</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>-0.04748692911769004</v>
+        <v>0.3253599586674232</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.3417800449392447</v>
+        <v>0.4501081076596072</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.6835003079552564</v>
+        <v>0.578673275007314</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>3.047451187585888</v>
+        <v>1.302115426630493</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.5936533987441197</v>
+        <v>0.3204106899760575</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>429.81</v>
+        <v>427.53</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.01550686981055938</v>
+        <v>-0.005304666695162386</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.0358115072042664</v>
+        <v>0.02204107306665959</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03304811825381893</v>
+        <v>0.02937426287882183</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.124774270710313</v>
+        <v>0.09022059271573446</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.003269801164412445</v>
+        <v>-0.02606101193610832</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1176669447869587</v>
+        <v>0.1155963429872124</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.4340019192636544</v>
+        <v>0.4152100524714475</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.7502709785625572</v>
+        <v>0.686901318166441</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.2943302619518193</v>
+        <v>0.2874642713187028</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.08980392678651405</v>
+        <v>0.08787349378588938</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>28.45</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.03680758779972537</v>
+        <v>-0.02042225416692445</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.01625170512152785</v>
+        <v>0.001513027302828096</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.02818939951192001</v>
+        <v>-0.00261177426680026</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.1018590665840493</v>
+        <v>0.2633923596158334</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1522883818368193</v>
+        <v>0.1232143680144002</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.4840897574184868</v>
+        <v>-0.07484011411747349</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2326690146007209</v>
+        <v>0.3188627175254046</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2594068424421965</v>
+        <v>0.667452058862966</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3777240333413783</v>
+        <v>2.96479280873354</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1127238876668903</v>
+        <v>0.5827299927667153</v>
       </c>
     </row>
     <row r="14">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>95.31999999999999</v>
+        <v>491.45</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.01902927904506146</v>
+        <v>0.02702086326636177</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.0542712686875314</v>
+        <v>0.01994441296318117</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.02001073095398542</v>
+        <v>-0.01360817018203053</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.01501433263476426</v>
+        <v>-0.06488436186468072</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.04071096437281452</v>
+        <v>-0.2369785136923589</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.495350705866505</v>
+        <v>0.4512169702577657</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2908266134760549</v>
+        <v>0.4527741153832447</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.3273164645556579</v>
+        <v>0.7176842127044878</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.044560375064047</v>
+        <v>1.311421134607436</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2692094973257417</v>
+        <v>0.3221874380157463</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>153.04</v>
+        <v>94.59</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.005386887786453132</v>
+        <v>-0.007658449006197721</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.000981057604049651</v>
+        <v>-0.04028004585068057</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.01552751416905673</v>
+        <v>-0.002741192835141737</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.04222280783755594</v>
+        <v>-0.03420467653673798</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.07571782197150689</v>
+        <v>0.0437854267918143</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.3290334925516047</v>
+        <v>0.4666866198161983</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.4361338191167652</v>
+        <v>0.2728825433955198</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.5793093375985185</v>
+        <v>0.3144203085311212</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.277816190694107</v>
+        <v>1.028902545713761</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.3157485250967675</v>
+        <v>0.2659612009972099</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>101.49</v>
+        <v>27.79</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.03953703491696481</v>
+        <v>-0.023198588039121</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.02121713304886752</v>
+        <v>-0.0364077403434524</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.01642463109374503</v>
+        <v>-0.009269102624062997</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.3345166836442843</v>
+        <v>0.04004497117026773</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1939999748678769</v>
+        <v>0.1205645875181562</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>-0.0356328399479281</v>
+        <v>0.4280576681887558</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2611287467453818</v>
+        <v>0.2082609093707541</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.5679002625445309</v>
+        <v>0.2351111518012152</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>2.613803632752981</v>
+        <v>0.3457627810602957</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.5345752283058569</v>
+        <v>0.10405193787137</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>110.85</v>
+        <v>110.99</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.005350955255394085</v>
+        <v>0.001262962486022312</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.01020682660096472</v>
+        <v>0.02116105778544974</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.05772896227279078</v>
+        <v>0.03535448715877498</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.04981534537986287</v>
+        <v>0.02266653563200749</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.01256016065631549</v>
+        <v>-0.0068898018767245</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1590338684811714</v>
+        <v>0.1585594397508008</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.348337816399531</v>
+        <v>0.3531193395948253</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.6150270682329779</v>
+        <v>0.5989490097960306</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.7525337370739409</v>
+        <v>0.7547473330976813</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.205652438944552</v>
+        <v>0.2061598385123551</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>58</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.006071092191801242</v>
+        <v>-0.0219725665038677</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.0129235365029432</v>
+        <v>-0.003913691757918891</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.02836876650414522</v>
+        <v>-0.03471749130851498</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.02022869932709681</v>
+        <v>0.2738706939008904</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1608317085704944</v>
+        <v>0.1488425970281919</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.2802273032885436</v>
+        <v>-0.06252356714123164</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2023008614708504</v>
+        <v>0.2284175382375464</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.239166569748654</v>
+        <v>0.5484111186288985</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.2083776046495234</v>
+        <v>2.534399092100397</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.06512576255878311</v>
+        <v>0.5232523693507594</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>478.52</v>
+        <v>57.42</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.002976279379565128</v>
+        <v>-0.01000003156990836</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.04345744278487995</v>
+        <v>0.01002638012529933</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.03667915122377496</v>
+        <v>0.008075826753270565</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.03360532863189902</v>
+        <v>0.01700317215797953</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-0.2632396691450031</v>
+        <v>0.1142430316265477</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.4152482948354108</v>
+        <v>0.2569254322450725</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.4207579910339028</v>
+        <v>0.191992558672281</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.7002465551887624</v>
+        <v>0.225738815810046</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>1.250607285241203</v>
+        <v>0.1962939806074318</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.3104885781713693</v>
+        <v>0.06156348739121942</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>31.75</v>
+        <v>31.43</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.006259804637358424</v>
+        <v>-0.01007873054564468</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02617968493732792</v>
+        <v>0.02111759597238372</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.004111295297794637</v>
+        <v>-0.002222212534102153</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.09144035178616083</v>
+        <v>0.09895104496360929</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.07297791725353031</v>
+        <v>0.06038211504326374</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1228005043722469</v>
+        <v>0.1126523979656706</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2888288861791835</v>
+        <v>0.2727916910005277</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3783578655063586</v>
+        <v>0.3507295192821345</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2687630064042024</v>
+        <v>0.2559757731264143</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.08258042278730571</v>
+        <v>0.07893120519632069</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>55.42</v>
+        <v>55.72</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.006632062027427832</v>
+        <v>0.005413263472930252</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.001988732470135313</v>
+        <v>0.008689346988623337</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.009287895154806547</v>
+        <v>0.01771691727311642</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.02413596401317508</v>
+        <v>0.03230086972659829</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.0737945992226825</v>
+        <v>0.0662262387473207</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.09610590203325553</v>
+        <v>0.09994511820069629</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2337334950794669</v>
+        <v>0.2280284456503152</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2451110091041762</v>
+        <v>0.2531516326049295</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6893720296053669</v>
+        <v>0.6985170455054195</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.190990872467965</v>
+        <v>0.1931360554271127</v>
       </c>
     </row>
     <row r="22">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>69.11</v>
+        <v>75.27</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01111927071246721</v>
+        <v>0.005342512111803588</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01008480648746102</v>
+        <v>0.01305509490535139</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.007140743867048771</v>
+        <v>0.005476837154315461</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.01999427254444541</v>
+        <v>-0.03301644162042705</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1193997564192053</v>
+        <v>0.0818832979789208</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1361901985131193</v>
+        <v>0.1281466370425597</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1671897085004139</v>
+        <v>0.1812278219463916</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1669334172919332</v>
+        <v>0.1658585681447444</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.8816946828083627</v>
+        <v>0.7946304730260325</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2345718946069837</v>
+        <v>0.2152296185275528</v>
       </c>
     </row>
     <row r="23">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>147.87</v>
+        <v>69.34</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.0212722009384172</v>
+        <v>0.003327965931237742</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.02247268780064937</v>
+        <v>0.01285418149556428</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.02587758945007268</v>
+        <v>0.008728520406855234</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.004483312093064074</v>
+        <v>-0.0274895740529546</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.1588731669446615</v>
+        <v>0.09027802561583509</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.1034968710671986</v>
+        <v>0.1340714556710767</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1378489450060874</v>
+        <v>0.1673939545428915</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1422805775332263</v>
+        <v>0.1521993796768515</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.7058434613377909</v>
+        <v>0.8879568986057398</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1948490933750473</v>
+        <v>0.235939915886342</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>74.87</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.008486057394136326</v>
+        <v>-0.003760391925055284</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.006994005153099447</v>
+        <v>-0.02484552908151294</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.002141663285639472</v>
+        <v>-0.03171910045445736</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.02841934702043725</v>
+        <v>0.03473284668674204</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.1094263629937107</v>
+        <v>-0.1054409651563527</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1254862390771467</v>
+        <v>0.04721499187198175</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.178948854327444</v>
+        <v>0.2004044839169432</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1767456606926607</v>
+        <v>0.588710634750039</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7850939136230417</v>
+        <v>0.2829970304638725</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2130732417908634</v>
+        <v>0.08661380197202639</v>
       </c>
     </row>
     <row r="25">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>135.15</v>
+        <v>145.56</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.01342226513152744</v>
+        <v>-0.01562181399115536</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.01024065727080514</v>
+        <v>0.003308489946795223</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.0110720112801117</v>
+        <v>0.01076316305035507</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.0005177290606919183</v>
+        <v>-0.01248301502090166</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.1787729857964029</v>
+        <v>0.1275527650539514</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.08026684958158703</v>
+        <v>0.08897152942565123</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1211721611721612</v>
+        <v>0.1217609095235412</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1277823025759601</v>
+        <v>0.1120592556117526</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.7042290025192495</v>
+        <v>0.6791949442949536</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.194472027994786</v>
+        <v>0.1885944717893018</v>
       </c>
     </row>
     <row r="26">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>198.06</v>
+        <v>133.01</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.03794146293094758</v>
+        <v>-0.01586756070491879</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.01387249229796339</v>
+        <v>-0.01462811250536822</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.04876881735460348</v>
+        <v>-0.007643853052042404</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.05733498726479302</v>
+        <v>-0.01448216843934003</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.109086150560056</v>
+        <v>0.1455417151332605</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1650156221769481</v>
+        <v>0.06733866289525925</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1283114549422031</v>
+        <v>0.1056358693566866</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1655074949058668</v>
+        <v>0.09901300435663973</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.159796767058759</v>
+        <v>0.6771868840113111</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.292620270886548</v>
+        <v>0.1881204904137768</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>74.45999999999999</v>
+        <v>196.46</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.002693198794625484</v>
+        <v>-0.008078313967732065</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.03461685808405746</v>
+        <v>0.006764411849684349</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.001609047246390105</v>
+        <v>0.009921389742874487</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.07275601722983405</v>
+        <v>0.03947093499400633</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.1187830029032533</v>
+        <v>0.07029646204223305</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.06297199123406139</v>
+        <v>0.1414666715604893</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1886990523410852</v>
+        <v>0.1130401293267402</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.598446727687884</v>
+        <v>0.1431284326051845</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.2878398128970554</v>
+        <v>1.142349250667966</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.08797925775977444</v>
+        <v>0.2891301249854279</v>
       </c>
     </row>
     <row r="28">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>118.38</v>
+        <v>118.62</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.009040698470883068</v>
+        <v>0.002027415937933208</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.03756099793969137</v>
+        <v>-0.001010570316206105</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.03208370011410167</v>
+        <v>-0.006033128987787628</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.1480942348237499</v>
+        <v>0.09975896602394241</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.07833976807831888</v>
+        <v>-0.07733261946376224</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.01069573474015062</v>
+        <v>0.009559797760272604</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.1907290248805784</v>
+        <v>0.1797676152908976</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.4571096377524888</v>
+        <v>0.4595270714141015</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.265548457238499</v>
+        <v>1.270141500556228</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.313382177184296</v>
+        <v>0.3142691366904795</v>
       </c>
     </row>
     <row r="29">
@@ -2118,37 +2118,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>94.27</v>
+        <v>93.25</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.003299250336465498</v>
+        <v>-0.01081994992455992</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.006638618257984952</v>
+        <v>-0.01468722948661039</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.01555978968175398</v>
+        <v>-0.0295555879501137</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.01822537035181582</v>
+        <v>-0.02580444201006649</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.07335361409623053</v>
+        <v>0.04797425486860396</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.06014823354058407</v>
+        <v>0.04668740551097428</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1125523865863327</v>
+        <v>0.1043611483474245</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.152414378173273</v>
+        <v>0.1314212219792492</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4371591646345165</v>
+        <v>0.4216088437415528</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1285001545619042</v>
+        <v>0.1244151939945586</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>293.42</v>
+        <v>84.17</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.020981935599514</v>
+        <v>0.006818178292200106</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.001395273332425617</v>
+        <v>-0.02569743299441596</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.03309634806587503</v>
+        <v>-0.03286223888850515</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.03736965563419647</v>
+        <v>-0.04188958872048065</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.04635903065937974</v>
+        <v>-0.0008282407921043067</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.2114281214415874</v>
+        <v>0.03707137247853587</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0804979233527352</v>
+        <v>0.1247097831940027</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.05683618335519225</v>
+        <v>0.2060063265339362</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.7168100587478097</v>
+        <v>0.3913619338444343</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1974041243953104</v>
+        <v>0.1163834059256812</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>106.95</v>
+        <v>74.47</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.03413265172883029</v>
+        <v>-0.008784720575573002</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.03054752316809639</v>
+        <v>-0.009180447149899518</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.04945533416761827</v>
+        <v>-0.01128516300537774</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.09782384477948769</v>
+        <v>-0.001876415875930348</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.06756539815239604</v>
+        <v>0.06608844172302319</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.2716363184445163</v>
+        <v>0.005609342619908197</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.002718856892706345</v>
+        <v>0.1291064288258332</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-0.003260805417516055</v>
+        <v>0.09410059227111911</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4786713070584545</v>
+        <v>0.2394344807462208</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1392627086160061</v>
+        <v>0.07417372403092681</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>75.13</v>
+        <v>235.46</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.005427636446124207</v>
+        <v>-0.002837412252110094</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.005890946547456588</v>
+        <v>-0.01282910239720736</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.002000451984115692</v>
+        <v>-0.01756578415004817</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.01253369735074927</v>
+        <v>0.01869000318260028</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.07339763549119849</v>
+        <v>0.01028346336990027</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.005917148278979711</v>
+        <v>0.002526666725571003</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1332216618316726</v>
+        <v>0.1787946615967617</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1020636444438079</v>
+        <v>0.1583233335340049</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2504188246498156</v>
+        <v>0.3401016493618083</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07733764229529827</v>
+        <v>0.102501647798418</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>236.13</v>
+        <v>290.87</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.004091105844508669</v>
+        <v>-0.008690676142903642</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01411210263263973</v>
+        <v>-0.01202407697051189</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.006521733757422821</v>
+        <v>0.01454476014163908</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.04403770082019109</v>
+        <v>0.009684839888112196</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.01255209975934335</v>
+        <v>0.03556675470204085</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.005591930111985555</v>
+        <v>0.1782791638905572</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1769046746985605</v>
+        <v>0.07122600237482568</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1663112969436042</v>
+        <v>0.03767256840843269</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3439147732251464</v>
+        <v>0.7018898185283531</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1035463432528485</v>
+        <v>0.1939252765147901</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>64.86</v>
+        <v>23.67</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.01138318085448975</v>
+        <v>0.002541273375320285</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.00886607072183998</v>
+        <v>-0.006714219384152953</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.03395506270777338</v>
+        <v>-0.007963140368705046</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.05738507416053795</v>
+        <v>-0.01045150498338687</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.01417196926036568</v>
+        <v>-0.07209292187952021</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.2313295373278899</v>
+        <v>-0.005258706222803666</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0716411778872319</v>
+        <v>0.1915167337000405</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.03199860544173916</v>
+        <v>0.3029708506937354</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.8826084929784705</v>
+        <v>0.5616902990164667</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.2347717112560468</v>
+        <v>0.1601967311538599</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>64.91</v>
+        <v>105.52</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.004905713296888936</v>
+        <v>0.01189104217764636</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.02916537437094013</v>
+        <v>-0.009852707654730453</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.03965072970833794</v>
+        <v>-0.02422787831856443</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.02843876614152008</v>
+        <v>-0.07527827465900394</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.04482178318559438</v>
+        <v>-0.05866941959258631</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.0789566595411606</v>
+        <v>0.04577228207439621</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.09358724063983948</v>
+        <v>0.1688142550425002</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.09878109574817051</v>
+        <v>0.2470162422883753</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.612665396179364</v>
+        <v>0.3385513483003941</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1726851412999242</v>
+        <v>0.1020763395140063</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>83.59999999999999</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.003360523047556629</v>
+        <v>-0.001848755812843716</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.03240744215634239</v>
+        <v>-0.03153961976421404</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.0309493250590025</v>
+        <v>-0.04664505902957827</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.02654865920138505</v>
+        <v>-0.03629335593591942</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.002262898912537059</v>
+        <v>0.033750762030341</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.02992207172108619</v>
+        <v>0.07322856697281521</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.1188743760996529</v>
+        <v>0.09339906483382743</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.196990553189881</v>
+        <v>0.09325281447598921</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.3819397973908454</v>
+        <v>0.6096842767689001</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1138576911105125</v>
+        <v>0.1719621000532308</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>23.61</v>
+        <v>178.99</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.01156814293052766</v>
+        <v>0.008167242660048535</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.02357318807403852</v>
+        <v>-0.001116116666763145</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.01337232305655289</v>
+        <v>-0.01072230841292054</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.007983135831917343</v>
+        <v>-0.04160414029883408</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.0841048638237093</v>
+        <v>-0.08775580703392161</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.009552977545299379</v>
+        <v>0.05212708305715297</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1855310210585654</v>
+        <v>0.1713391261765778</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.312529000155233</v>
+        <v>0.2654763786259509</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.5577316769798648</v>
+        <v>0.8289000879191262</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1592156005448311</v>
+        <v>0.2229160933316909</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>96.66</v>
+        <v>28.8</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.009187772959156959</v>
+        <v>0.01337083602204392</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.01013822681310628</v>
+        <v>-0.01302265469982988</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.01967540407742396</v>
+        <v>-0.02603992105885777</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.02432619400563851</v>
+        <v>-0.1377246131337508</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.03285627917320766</v>
+        <v>0.02857140132359093</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.03284802743082982</v>
+        <v>0.05417275105302122</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1025896552165277</v>
+        <v>0.07900002643995951</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1062526129538244</v>
+        <v>0.1180550994535934</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.3191292598658884</v>
+        <v>0.5114988374582785</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.09672005332952827</v>
+        <v>0.1476318848757938</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>177.54</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.01145100279618427</v>
+        <v>-0.009979967840326176</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.02294872749798949</v>
+        <v>0.0005094980493214329</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.01998239292779236</v>
+        <v>0.01506009474994285</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.02461273970536837</v>
+        <v>0.02200697149110398</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.09578854407269466</v>
+        <v>0.008148690452775886</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.05377720615558723</v>
+        <v>0.1947734242459387</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1718280328817541</v>
+        <v>0.05502014055549931</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.2702761716056028</v>
+        <v>0.01588134043435474</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.8140837406549888</v>
+        <v>0.8638201207626206</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.2196047587941405</v>
+        <v>0.2306503095550079</v>
       </c>
     </row>
     <row r="40">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2734,37 +2734,37 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>104.28</v>
+        <v>55.16</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.008705760783420224</v>
+        <v>0.008593915386817974</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.02551166528768145</v>
+        <v>-0.002712014502884164</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.02213053848329871</v>
+        <v>-0.02181237019949533</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.0587598346640873</v>
+        <v>-0.05838173227624499</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.05840599448471029</v>
+        <v>-0.04084830938626383</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.03053176004230651</v>
+        <v>0.0179943111460803</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1575008589252989</v>
+        <v>0.1413485120968303</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.2313515374700759</v>
+        <v>0.1929944163042134</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.3228214925920887</v>
+        <v>0.7275271940266179</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.0977423371521835</v>
+        <v>0.1998905441893197</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>54.69</v>
+        <v>104.57</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.007553424035235734</v>
+        <v>-0.02225336438831083</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.0244381504284934</v>
+        <v>-0.04502283383722172</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.02408997620919573</v>
+        <v>0.01160875414876461</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.04953080019936662</v>
+        <v>0.02519607543945312</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.04370915305157308</v>
+        <v>0.04526896066799857</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.009692279066308318</v>
+        <v>0.2211278421034955</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1367545364630502</v>
+        <v>-0.0311291712408025</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.2013794953933861</v>
+        <v>-0.02106319164620341</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.7128075738572706</v>
+        <v>0.4457658956519428</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1964728776866276</v>
+        <v>0.130748426228092</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>28.42</v>
+        <v>96.02</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.00317684972927168</v>
+        <v>-0.006621218650893268</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.03168655172362256</v>
+        <v>-0.0125462900812926</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.02870813896162405</v>
+        <v>-0.02517769905516343</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.1300887153612158</v>
+        <v>-0.02931663545854502</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.02120014927076297</v>
+        <v>0.007974151463466805</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.03609186146933285</v>
+        <v>0.02472073776768524</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.05651832916795985</v>
+        <v>0.09796714996985401</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.08369055090284006</v>
+        <v>0.0907556974513104</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.4915554935364241</v>
+        <v>0.3103948801703222</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.142562077310209</v>
+        <v>0.09429411221067929</v>
       </c>
     </row>
     <row r="43">
@@ -2902,37 +2902,37 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>58.92</v>
+        <v>59.26</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.004946223700271979</v>
+        <v>0.005770539089512194</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.01553885261296895</v>
+        <v>0.001013472260481985</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.02191240824605301</v>
+        <v>-0.007536438952257085</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.03536351665613691</v>
+        <v>-0.038611309079846</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.03440719614491161</v>
+        <v>-0.03639290640315862</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>-0.01072651202072217</v>
+        <v>-0.01078633131521167</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1228109201125143</v>
+        <v>0.1302466058922123</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1699454579251287</v>
+        <v>0.1626317541545088</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.5870747346582244</v>
+        <v>0.5962326834169862</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1664491007972912</v>
+        <v>0.1686883988186494</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>225.98</v>
+        <v>87.59</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.01168465177689715</v>
+        <v>0.009915749425464249</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.03534533839944765</v>
+        <v>0.008056127899174426</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.04874558827269937</v>
+        <v>-0.001368176352008144</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.08168077842146315</v>
+        <v>-0.05154306675559228</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.005552193867865318</v>
+        <v>0.05086778133418868</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.07631073274122968</v>
+        <v>0.02415917818882574</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.1223360780748943</v>
+        <v>0.03546527993676407</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.1532927129651023</v>
+        <v>0.01522071105444556</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.9837551173382917</v>
+        <v>0.4056219756362527</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.2565005605998525</v>
+        <v>0.1201843806873473</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>13.35</v>
+        <v>71.73</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.0007496423363906324</v>
+        <v>0.007160939728855453</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.002987301032667533</v>
+        <v>-0.005683338455554132</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.004514704273056447</v>
+        <v>-0.01048412924861986</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0.0478807395063261</v>
+        <v>-0.0220858234613196</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.09556167484056877</v>
+        <v>0.07432719106906349</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.09099608243395685</v>
+        <v>-0.03852714527555967</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>-0.01610860183931628</v>
+        <v>0.03859017754181493</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>-0.06372205811809772</v>
+        <v>-0.01921706737213924</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.177073087138198</v>
+        <v>0.01163785501843906</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.0558473720820607</v>
+        <v>0.003864332703456652</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>27.92</v>
+        <v>13.33</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.04144903841282188</v>
+        <v>-0.001498161587428326</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.001938223838838793</v>
+        <v>-0.00224548905255384</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.04117713093968245</v>
+        <v>0.003009778929107698</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.06302363565196267</v>
+        <v>0.0285493738016982</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.1348738503058318</v>
+        <v>0.06980238205707034</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.1321170678125398</v>
+        <v>0.08019332556919223</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>-0.07899539356105423</v>
+        <v>-0.02352861618097801</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-0.1536902643414675</v>
+        <v>-0.07036702348165735</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.2939975066974352</v>
+        <v>0.1753096414534518</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.08971052737255469</v>
+        <v>0.05531983188912237</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>86.73</v>
+        <v>225.61</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.00405193464511</v>
+        <v>-0.00163729146022995</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0.001616896003744372</v>
+        <v>-0.03096815774868833</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0</v>
+        <v>-0.04942275178448885</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.05171655122334329</v>
+        <v>-0.09990023497257317</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.04254689082282681</v>
+        <v>-0.02505346665852537</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.0175371338452881</v>
+        <v>-0.08525363284287069</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.0216998565488149</v>
+        <v>0.1038007786400301</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.03134186963797037</v>
+        <v>0.1422404266257944</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.3918210270865699</v>
+        <v>0.9805075299547608</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.116506179567921</v>
+        <v>0.2558145175615365</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>71.22</v>
+        <v>47.87</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.0002806940435995386</v>
+        <v>-0.005195345086226655</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.01684154030350749</v>
+        <v>-0.006640375678426791</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.003497971116972365</v>
+        <v>-0.01522323943993553</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.0204923378150299</v>
+        <v>0.0012549164791964</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.07289768349353531</v>
+        <v>0.01334722596038107</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.03936722813143589</v>
+        <v>-0.02334682770671714</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.03824973365159079</v>
+        <v>0.07440634813163904</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.02214449150025655</v>
+        <v>0.0220273484117155</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.004444976229975861</v>
+        <v>0.1339525862532467</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.001479468835854814</v>
+        <v>0.04279345962606884</v>
       </c>
     </row>
     <row r="49">
@@ -3238,37 +3238,37 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>18.99</v>
+        <v>18.98</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.01119500929143458</v>
+        <v>-0.0005266050027575853</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.04773842599832367</v>
+        <v>-0.04885995415672484</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.05286780579936745</v>
+        <v>-0.05374419144462206</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.04764296577208449</v>
+        <v>-0.04709306957695503</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.09642032942950896</v>
+        <v>0.08376628864578151</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.1453558418879299</v>
+        <v>0.1331343010290345</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>-0.09312324322857091</v>
+        <v>-0.09273425081178566</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.1274982630989679</v>
+        <v>-0.1340450690537156</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.05297341282133794</v>
+        <v>0.05241902305848978</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01735487036831773</v>
+        <v>0.01717629348270022</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>48.12</v>
+        <v>27.45</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.007425755234133691</v>
+        <v>-0.01665771582795261</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0.006273509807090516</v>
+        <v>0.01254150294847522</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.00578517737947648</v>
+        <v>-0.003738204021443869</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0.01412008763271944</v>
+        <v>0.02662876318453455</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.01585227585243842</v>
+        <v>0.1025455747810378</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.02221136855708539</v>
+        <v>0.08685723960865999</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.07475726012906092</v>
+        <v>-0.09920484676749575</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.02866527530995855</v>
+        <v>-0.1727666600219941</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.1398749373105197</v>
+        <v>0.2724423514458192</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.04460572484664738</v>
+        <v>0.08362588799993276</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>253.93</v>
+        <v>45.27</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.0148674547863632</v>
+        <v>0.001770343737240276</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.0455553304765377</v>
+        <v>0.0002209928546486051</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.06567814476300371</v>
+        <v>-0.009625872577592065</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.07199507311147468</v>
+        <v>-0.02140073280782429</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.07121558809941042</v>
+        <v>0.009139541726120637</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.1063680253149141</v>
+        <v>-0.06602023276972047</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.115429451125969</v>
+        <v>0.0006754221957898654</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.1846219412614858</v>
+        <v>0.01785805722952927</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>1.107682766915945</v>
+        <v>0.2782235719014956</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.2821389138413939</v>
+        <v>0.08526452578959365</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>113.38</v>
+        <v>43.08</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0.008539397794954384</v>
+        <v>0.001162050968541273</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0.01768237614714829</v>
+        <v>0.008191020186471221</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>0.02439462360677203</v>
+        <v>0.007248103109027237</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.01832226497777523</v>
+        <v>-0.02335068612660951</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.01423053962854359</v>
+        <v>-0.01331158159496793</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.0332509979130996</v>
+        <v>-0.07640784216740126</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.006280762970138576</v>
+        <v>0.006297891572330849</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.01544221513067323</v>
+        <v>0.05771788948399426</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.7477910546061839</v>
+        <v>0.505323874532484</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.20456388311119</v>
+        <v>0.1460669356876325</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>45.19</v>
+        <v>252.92</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.0109619207026006</v>
+        <v>-0.003977452589168928</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.007467607329313064</v>
+        <v>-0.03388215778469827</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.01094331396428883</v>
+        <v>-0.0726699155792947</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.01546847223457315</v>
+        <v>-0.1034067090206388</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.01186741560921845</v>
+        <v>-0.09787048785980845</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.06516345709424398</v>
+        <v>-0.1187246602366264</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.004663583433486274</v>
+        <v>0.08369958194634819</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.01824484490579614</v>
+        <v>0.17881408722577</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.2759646758287027</v>
+        <v>1.099300090397734</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.08462485018619192</v>
+        <v>0.2804368809799773</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>43.03</v>
+        <v>112.03</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.008436855537846455</v>
+        <v>-0.01190684871074466</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.003473865790152075</v>
+        <v>-0.008496319166499289</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.01690659517312254</v>
+        <v>0.005655271497205572</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.02998200659952932</v>
+        <v>-8.927290386229192e-05</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-0.009270912206644</v>
+        <v>-0.00697155659820714</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.07356011177014676</v>
+        <v>-0.05143633727196661</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.003064578275240759</v>
+        <v>-0.02370955630632343</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>0.05522987760049025</v>
+        <v>-0.005619632069683078</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.5035767420492943</v>
+        <v>0.7269803709409952</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.1456233753429523</v>
+        <v>0.1997639283163721</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>19.48</v>
+        <v>46.06</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.01632758080835162</v>
+        <v>0.007877474930886752</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.003172180834800975</v>
+        <v>0.01075272507676694</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.0003078925907008534</v>
+        <v>-0.0002170245626098577</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.02434276197312513</v>
+        <v>0.08401975885619772</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>0.03621953803857969</v>
+        <v>-0.08392994249123709</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.07611158764101256</v>
+        <v>-0.1271555623700106</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.05610267461984508</v>
+        <v>-0.01913093674887401</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-0.17593231266981</v>
+        <v>0.1945236933980603</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.1725455205392559</v>
+        <v>1.164224606392485</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.0544918737949911</v>
+        <v>0.2935030095034934</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>53.91</v>
+        <v>17.77</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.009371524048015001</v>
+        <v>0.007941083588286713</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.01299888499371959</v>
+        <v>0.01659044182619263</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.02777278438842901</v>
+        <v>0.01023310424186086</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.005534020330697165</v>
+        <v>-0.03633405948424429</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>0.1125392221678678</v>
+        <v>-0.2286712222590733</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.08418084822211425</v>
+        <v>-0.0150527826355944</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.1444528882786297</v>
+        <v>0.05812150966393848</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.1164747197631892</v>
+        <v>0.2530581176000797</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.0401647666780629</v>
+        <v>0.1569109381043947</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.01321290577347423</v>
+        <v>0.04978406386544476</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>45.7</v>
+        <v>35.95</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.03113720842999901</v>
+        <v>0.003909505285661696</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.05519946718843716</v>
+        <v>0.005594426935369379</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.04242702107385288</v>
+        <v>-0.002497229475627361</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.119823553665666</v>
+        <v>-0.03073603086973553</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.09307399649765513</v>
+        <v>-0.1025953484651687</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.1211538314819336</v>
+        <v>-0.03129605649027367</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.02706077971868948</v>
+        <v>-0.02051833114483048</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.1582383263797029</v>
+        <v>0.08641468215655701</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>1.147309231750509</v>
+        <v>0.3568122026868521</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.2901242257129268</v>
+        <v>0.1070653217762316</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>17.63</v>
+        <v>19.37</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.01496823885845466</v>
+        <v>-0.005871732149236308</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.01121709275351934</v>
+        <v>-0.01396929229819732</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>0</v>
+        <v>-0.01432054853212295</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.02001115146924692</v>
+        <v>0.005638661223493768</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.2344167200553614</v>
+        <v>0.01141520789353501</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.002408608955747127</v>
+        <v>0.04076304191862246</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.07060416207464137</v>
+        <v>-0.05507687769590708</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.2545671180799656</v>
+        <v>-0.1833480356113326</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1477961925966675</v>
+        <v>0.1656606473098625</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.04701987709632438</v>
+        <v>0.05242392306840715</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>35.81</v>
+        <v>53.63</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.01761872039720558</v>
+        <v>-0.005193818959179919</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.009131101879651493</v>
+        <v>-0.02826594668257154</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0</v>
+        <v>-0.04521981811696707</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.0033397976862104</v>
+        <v>-0.008870810142709629</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.1103076579844193</v>
+        <v>0.07702234386631335</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.0290539815824512</v>
+        <v>-0.08599407821122274</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.0133092561063004</v>
+        <v>-0.1501063305390812</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.08479379403150489</v>
+        <v>-0.1305694137774253</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.3515284925735507</v>
+        <v>0.03476233919221938</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.1056264044769886</v>
+        <v>0.0114557119376435</v>
       </c>
     </row>
     <row r="60">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>102.27</v>
+        <v>103.25</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0.01087277349045901</v>
+        <v>0.009582510893726859</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.02152698117359975</v>
+        <v>-0.01290629535195542</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.03171753471313021</v>
+        <v>-0.03051643192488263</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.03845434320998953</v>
+        <v>-0.05802390817385805</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.01417295258838625</v>
+        <v>-0.01261469178427499</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.07826234585770897</v>
+        <v>-0.06792440406997369</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.06100960325061766</v>
+        <v>-0.03510699735768508</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.09304697900482028</v>
+        <v>-0.1124011024099953</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2414092169130997</v>
+        <v>0.253305150326042</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.07474389916272184</v>
+        <v>0.07816594017575018</v>
       </c>
     </row>
     <row r="61">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>93.62</v>
+        <v>93.91</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.008618865054816682</v>
+        <v>0.003097638400122005</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.02101845199795926</v>
+        <v>-0.02593091904406331</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.03225134573169119</v>
+        <v>-0.03672165637610092</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.03494484398513753</v>
+        <v>-0.05608598172150703</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>0.01420930681949861</v>
+        <v>0.007327837714197871</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.09390332565340553</v>
+        <v>-0.0865154034454827</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.1087263600373448</v>
+        <v>-0.08649994652869564</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.1500031967628672</v>
+        <v>-0.1721642087216253</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1000414253735029</v>
+        <v>0.1034488570147916</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.03229307365410916</v>
+        <v>0.03335783430632522</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>47.72</v>
+        <v>48.04</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.009519796035152073</v>
+        <v>0.006705777171803318</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.04061118595896951</v>
+        <v>-0.01253855274859705</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.0404182252168751</v>
+        <v>-0.02595293566944612</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.06869633767484684</v>
+        <v>-0.09986880500335049</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.3210982984898271</v>
+        <v>-0.3180011463587297</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1239214218602668</v>
+        <v>-0.1244760005342106</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.007176026697405469</v>
+        <v>0</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.1479432660819728</v>
+        <v>0.143265121184724</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1782157586395819</v>
+        <v>-0.1727050566337196</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.06333145453714173</v>
+        <v>-0.0612424202847941</v>
       </c>
     </row>
   </sheetData>
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.3373795934284731</v>
+        <v>0.2738706939008904</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1300887153612158</v>
+        <v>-0.1377246131337508</v>
       </c>
     </row>
     <row r="18">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.3345166836442843</v>
+        <v>0.2633923596158334</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.08168077842146315</v>
+        <v>-0.1034067090206388</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.2427514864612361</v>
+        <v>0.2085942562754242</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.07199507311147468</v>
+        <v>-0.09990023497257317</v>
       </c>
     </row>
     <row r="20">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1569892193782523</v>
+        <v>0.1905103988209815</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.06869633767484684</v>
+        <v>-0.09986880500335049</v>
       </c>
     </row>
     <row r="21">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1500725799951705</v>
+        <v>0.1144885878056472</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.0587598346640873</v>
+        <v>-0.07527827465900394</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.149823579866474</v>
+        <v>0.1091015417189676</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.05171655122334329</v>
+        <v>-0.06488436186468072</v>
       </c>
     </row>
     <row r="23">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1480942348237499</v>
+        <v>0.09975896602394241</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.04953080019936662</v>
+        <v>-0.05838173227624499</v>
       </c>
     </row>
     <row r="24">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.124774270710313</v>
+        <v>0.09895104496360929</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.04764296577208449</v>
+        <v>-0.05802390817385805</v>
       </c>
     </row>
     <row r="25">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.119823553665666</v>
+        <v>0.09022059271573446</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.03845434320998953</v>
+        <v>-0.05608598172150703</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.1158781318791959</v>
+        <v>0.08401975885619772</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.03536351665613691</v>
+        <v>-0.05154306675559228</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.4004807108043775</v>
+        <v>0.3330338350387942</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.3210982984898271</v>
+        <v>-0.3180011463587297</v>
       </c>
     </row>
     <row r="32">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2789223087170745</v>
+        <v>0.3080568456189587</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.2632396691450031</v>
+        <v>-0.2369785136923589</v>
       </c>
     </row>
     <row r="33">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2766570481781769</v>
+        <v>0.2363636153222182</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.2344167200553614</v>
+        <v>-0.2286712222590733</v>
       </c>
     </row>
     <row r="34">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2673601017388425</v>
+        <v>0.2289821983098801</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1337200902390255</v>
+        <v>-0.1054409651563527</v>
       </c>
     </row>
     <row r="35">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2624063208426435</v>
+        <v>0.2264403169559062</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1187830029032533</v>
+        <v>-0.1025953484651687</v>
       </c>
     </row>
     <row r="36">
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1939999748678769</v>
+        <v>0.1488425970281919</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.1103076579844193</v>
+        <v>-0.09787048785980845</v>
       </c>
     </row>
     <row r="37">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1787729857964029</v>
+        <v>0.1455417151332605</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.09578854407269466</v>
+        <v>-0.09644163100698233</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1608317085704944</v>
+        <v>0.1275527650539514</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.09307399649765513</v>
+        <v>-0.08775580703392161</v>
       </c>
     </row>
     <row r="39">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.16013016761884</v>
+        <v>0.1232143680144002</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.0841048638237093</v>
+        <v>-0.08392994249123709</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1588731669446615</v>
+        <v>0.1205983771082659</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.07833976807831888</v>
+        <v>-0.07733261946376224</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.495350705866505</v>
+        <v>0.4666866198161983</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1239214218602668</v>
+        <v>-0.1271555623700106</v>
       </c>
     </row>
     <row r="46">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4840897574184868</v>
+        <v>0.4591567559091367</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1211538314819336</v>
+        <v>-0.1244760005342106</v>
       </c>
     </row>
     <row r="47">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4821262296252076</v>
+        <v>0.4512169702577657</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1063680253149141</v>
+        <v>-0.1187246602366264</v>
       </c>
     </row>
     <row r="48">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4152482948354108</v>
+        <v>0.4280576681887558</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.09390332565340553</v>
+        <v>-0.0865154034454827</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4130823378403456</v>
+        <v>0.4207216263949596</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.08418084822211425</v>
+        <v>-0.08599407821122274</v>
       </c>
     </row>
     <row r="50">
@@ -5849,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3563488472305776</v>
+        <v>0.3904281845